--- a/report.xlsx
+++ b/report.xlsx
@@ -720,7 +720,7 @@
         <v>37.93036529680365</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.77716048631313</v>
+        <v>34.76965869272961</v>
       </c>
       <c r="N2" s="6" t="n">
         <v>10.45400029158803</v>
@@ -744,10 +744,10 @@
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09066884030775024</v>
+        <v>0.09090415962969911</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1144356089853538</v>
+        <v>0.1146979601428062</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         <v>27.535</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.19478598519915</v>
+        <v>24.18264317759899</v>
       </c>
       <c r="N3" s="6" t="n">
         <v>11.09069562800033</v>
@@ -872,10 +872,10 @@
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1380551171993909</v>
+        <v>0.1386265677321155</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2236321448597434</v>
+        <v>0.2242597789543264</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>16.65590863952334</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.1895278702949</v>
+        <v>20.207596394201</v>
       </c>
       <c r="N4" s="6" t="n">
         <v>9.130520105868131</v>
@@ -998,10 +998,10 @@
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1750223805862554</v>
+        <v>-0.1757600303070632</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2894614358948004</v>
+        <v>0.2901656708796634</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         <v>20.37936507936508</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.76311457721979</v>
+        <v>22.77500684011763</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>3.561015029393565</v>
@@ -1124,10 +1124,10 @@
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1047198303979128</v>
+        <v>-0.1051873124592303</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1772913545578569</v>
+        <v>0.17771891846736</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         <v>27.45786163522012</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.39580978400739</v>
+        <v>16.37410678350809</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>17.45129729444267</v>
@@ -1250,10 +1250,10 @@
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6746877401568017</v>
+        <v>0.6769074489532174</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9278215828328569</v>
+        <v>0.9303402776833312</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
         <v>24.08138238573021</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>19.6096367335396</v>
+        <v>19.60576870666489</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>7.232693044219446</v>
@@ -1376,10 +1376,10 @@
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2280381688326893</v>
+        <v>0.2282804487815804</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2699368436425558</v>
+        <v>0.2705509847826661</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
         <v>309.6949152542373</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>174.1146800786864</v>
+        <v>173.9867834554464</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>13.92913075462029</v>
@@ -1502,10 +1502,10 @@
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7786835384258184</v>
+        <v>0.7799910378453681</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1211920138920415</v>
+        <v>0.1215655287458917</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
         <v>44.91191066997519</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.87640520950526</v>
+        <v>19.80286514742586</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>19.32793571781289</v>
@@ -1628,10 +1628,10 @@
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.259559019681158</v>
+        <v>1.26795013426697</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8532388312558883</v>
+        <v>0.8564104257536831</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>45.44299347061778</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.91850143588716</v>
+        <v>39.91873039403847</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>1.36670388957958</v>
@@ -1754,10 +1754,10 @@
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1383942742340534</v>
+        <v>0.1383877448518331</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.113636913092201</v>
+        <v>0.1136368918037924</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
         <v>23.96284829721363</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.65000478588037</v>
+        <v>20.64675644835125</v>
       </c>
       <c r="N11" s="6" t="n">
         <v>6.662887440086743</v>
@@ -1880,10 +1880,10 @@
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1604282200262945</v>
+        <v>0.1606107892616311</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1424463232227213</v>
+        <v>0.1427745098118778</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>12.8402369442784</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.00736252076394</v>
+        <v>23.00733563970968</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>2.863781900610106</v>
@@ -2006,10 +2006,10 @@
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4419074792823298</v>
+        <v>-0.4419068272244138</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06134979061163781</v>
+        <v>0.06139523027282179</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
         <v>15.31513327601032</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>14.22574077908948</v>
+        <v>14.22510989720509</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>3.207043060749312</v>
@@ -2132,10 +2132,10 @@
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07657896441654222</v>
+        <v>0.07662671056196224</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2895840775374785</v>
+        <v>-0.2895318430660836</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>31.47408666100255</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.80613921732385</v>
+        <v>24.7979651085753</v>
       </c>
       <c r="N14" s="6" t="n">
         <v>15.54683598532188</v>
@@ -2258,10 +2258,10 @@
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2688023067701726</v>
+        <v>0.2692205397981868</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1369119287200737</v>
+        <v>0.1372179948816117</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>31.25700164744646</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.70505128511245</v>
+        <v>25.69509642969269</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>14.2291172602115</v>
@@ -2384,10 +2384,10 @@
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2159867452024704</v>
+        <v>0.2164578456816593</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1557212564532875</v>
+        <v>0.1560881955092015</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
         <v>24.37721046878015</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.51984944825355</v>
+        <v>17.51388894681446</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>0.7648217780058605</v>
@@ -2510,10 +2510,10 @@
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3914052481318653</v>
+        <v>0.3918787850492815</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01022441291752063</v>
+        <v>0.01030287783379724</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         <v>21.36679536679537</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>15.0124804236027</v>
+        <v>15.01583088487154</v>
       </c>
       <c r="N17" s="6" t="n">
         <v>1.905675647260843</v>
@@ -2636,10 +2636,10 @@
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4232688245975917</v>
+        <v>0.4229512526224855</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08263869576574012</v>
+        <v>0.08247725756777813</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
         <v>30.7028901734104</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.37989743854772</v>
+        <v>21.37408831167713</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>6.535559653636819</v>
@@ -2762,10 +2762,10 @@
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4360634919629423</v>
+        <v>0.4364537904822234</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.08812494365126411</v>
+        <v>0.08833454717187483</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
         <v>38.68231046931408</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.58434948169261</v>
+        <v>34.57399762391755</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>1.158822939769515</v>
@@ -2888,10 +2888,10 @@
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1184917758765638</v>
+        <v>0.1188266653479055</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05057354649804369</v>
+        <v>0.05069788025443667</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         <v>21.52148148148148</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.57591250953377</v>
+        <v>20.57258134369886</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>3.967932970378711</v>
@@ -3014,10 +3014,10 @@
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04595514155251146</v>
+        <v>0.04612450532724499</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02511544798896215</v>
+        <v>0.02519525344873941</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
         <v>130.997461928934</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>38.36558989914167</v>
+        <v>38.30146529942742</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>20.37529543638785</v>
@@ -3266,10 +3266,10 @@
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.414451915722133</v>
+        <v>2.420168416660871</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.8858346653687155</v>
+        <v>0.8883604343143967</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
         <v>53.64296081277213</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>35.029973940036</v>
+        <v>35.00133660233855</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>16.1291333350506</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5313445823453273</v>
+        <v>0.5325974954107349</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2856372264178451</v>
+        <v>0.2864551702816613</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
         <v>78.82022471910109</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>84.60281007648415</v>
+        <v>84.14062311047331</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1.769598026490771</v>
@@ -3520,10 +3520,10 @@
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.06834980247293654</v>
+        <v>-0.06323221999897422</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1520990995166605</v>
+        <v>0.152523701668509</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
         <v>15.67915904936015</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>14.21483560557174</v>
+        <v>14.2131694053763</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>2.574385513112933</v>
@@ -3646,10 +3646,10 @@
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1030137445426695</v>
+        <v>0.1031430500947468</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3824139070636855</v>
+        <v>-0.3823711015222546</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
         <v>21.24803493449782</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.86679928185745</v>
+        <v>18.86344951193065</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>3.317246492032939</v>
@@ -3772,10 +3772,10 @@
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1262130166895976</v>
+        <v>0.1264130095112761</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04567790493352519</v>
+        <v>0.04578542708088928</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
         <v>37.36180904522614</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>25.61307332702475</v>
+        <v>25.59658996630991</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>13.18353233445217</v>
@@ -3898,10 +3898,10 @@
         <v>0.4470491333778837</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4587007411486659</v>
+        <v>0.4596400963722727</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2268454687601291</v>
+        <v>0.2273126002782788</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877209505000597</v>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
         <v>17.23311897106109</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.92738052268832</v>
+        <v>15.92478333473714</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>2.672409379667902</v>
@@ -4024,10 +4024,10 @@
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08198074043077996</v>
+        <v>0.0821572016914065</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3275865696303093</v>
+        <v>-0.3274869152039972</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>82.31677018633542</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>28.00741457457604</v>
+        <v>27.99208426195769</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>9.300687677165355</v>
@@ -4276,10 +4276,10 @@
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.939106355824045</v>
+        <v>1.940716004424403</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2439425326806988</v>
+        <v>0.2445053550059697</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
         <v>36.62790697674419</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.492394090000051</v>
+        <v>9.493088068672243</v>
       </c>
       <c r="N31" s="6" t="n">
         <v>2.480351620195931</v>
@@ -4402,10 +4402,10 @@
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.858658482724666</v>
+        <v>2.858376400996264</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.04999892076274981</v>
+        <v>-0.05010572930318846</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
         <v>7.917142991467138</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003951832075846838</v>
+        <v>0.003950478887045561</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.799454886225326</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2002.410782521819</v>
+        <v>2003.097026674181</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2585.694770015227</v>
+        <v>2585.930107902172</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
         <v>-98.18831168831169</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>138.2729550294376</v>
+        <v>137.6590676676727</v>
       </c>
       <c r="N34" s="6" t="n">
         <v>119.2881818090498</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.174644104217029</v>
+        <v>4.184692245707556</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
         <v>27.93555117653877</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6626937242120312</v>
+        <v>0.662234378283926</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.07436022855125</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>41.15454312586895</v>
+        <v>41.18378280047808</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>41.12456964192115</v>
+        <v>41.15666372328758</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
         <v>-22.07874015748031</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-79.96238534891215</v>
+        <v>-80.68007820889312</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>1.946562733600997</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02035935925193311</v>
+        <v>0.02043303423553744</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
         <v>19.69011522134627</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.72766832562197</v>
+        <v>16.72171575281377</v>
       </c>
       <c r="N38" s="6" t="n">
         <v>2.608047814399391</v>
@@ -5200,10 +5200,10 @@
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1770986151839637</v>
+        <v>0.1775176370901419</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.005192089385952725</v>
+        <v>0.005425181638038401</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>
@@ -5302,13 +5302,13 @@
         <v>23.1712962962963</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.79024564414526</v>
+        <v>16.77375562030881</v>
       </c>
       <c r="N39" s="6" t="n">
         <v>6.025642900929268</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.627550747068279</v>
+        <v>6.669635475948002</v>
       </c>
       <c r="P39" s="6" t="n">
         <v>0.5043164488017432</v>
@@ -5326,16 +5326,16 @@
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3800451040081179</v>
+        <v>0.3814018053441572</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.4179780294298492</v>
+        <v>0.4198565143825406</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
       </c>
       <c r="X39" s="4" t="n">
-        <v>0.4248105529048555</v>
+        <v>0.425824021246188</v>
       </c>
       <c r="Y39" s="4" t="n">
         <v>0.7443888710868384</v>
@@ -5353,7 +5353,7 @@
         <v>1.170812813065623</v>
       </c>
       <c r="AD39" s="6" t="n">
-        <v>2.320539913090065</v>
+        <v>2.335275265081172</v>
       </c>
       <c r="AE39" s="6" t="n">
         <v>0.5141842451501851</v>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:41 ET</t>
+          <t>2026-09-13 11:21 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -442,11 +442,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -470,7 +470,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>332.27</v>
+        <v>334.17001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2260432752552346</v>
+        <v>0.233054123310785</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.03569666540906058</v>
+        <v>-0.0301825173404533</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,40 +714,40 @@
         <v>235.03</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4880167778120</v>
+        <v>4908073951738</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>37.93036529680365</v>
+        <v>38.14726141552512</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.76965869272961</v>
+        <v>34.94378705930419</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.45400029158803</v>
+        <v>10.5137792091178</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.40440810128349</v>
+        <v>45.66404282435966</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.158983384068999</v>
+        <v>1.165610765474377</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.2305044817967</v>
+        <v>29.3961335169569</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.54988888319556</v>
+        <v>10.60966780072533</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02800784854422664</v>
+        <v>0.0278486023935314</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09090415962969911</v>
+        <v>0.0916750766247576</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1146979601428062</v>
+        <v>0.1170296262044463</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003190176663556746</v>
+        <v>0.003172038089234878</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3113031219292596</v>
+        <v>0.3090034763209347</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.3125421036337848</v>
+        <v>0.2978607153938829</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>14847202025.02401</v>
+        <v>13711498421.73662</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>495.63</v>
+        <v>508.12</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.0479764820938462</v>
+        <v>0.07438575163231675</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1049086180741169</v>
+        <v>-0.08235209130968724</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3680325346500</v>
+        <v>3773070466000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.535</v>
+        <v>28.23444444444445</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.18264317759899</v>
+        <v>24.77961551573403</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.09069562800033</v>
+        <v>11.37242165647799</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.323109110349083</v>
+        <v>8.534532841154917</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8746035962877013</v>
+        <v>0.8968202887342083</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.25470750389121</v>
+        <v>18.70520930644423</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.41577284918289</v>
+        <v>11.69749887766055</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01820137995780858</v>
+        <v>0.01775048193070232</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1386265677321155</v>
+        <v>0.1394222168829355</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2242597789543264</v>
+        <v>0.2251284786170114</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007344188204910922</v>
+        <v>0.007163662127056601</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5625067965786378</v>
+        <v>0.558727690336572</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4360525535827411</v>
+        <v>0.4353830518384593</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>13121876129.73938</v>
+        <v>12385142545.40151</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>338.5</v>
+        <v>347</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.07409172316590706</v>
+        <v>0.1010630072040466</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1715817038251634</v>
+        <v>-0.1507794718680404</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4096564670311</v>
+        <v>4199432616242</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.65590863952334</v>
+        <v>17.05486544190665</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.207596394201</v>
+        <v>20.73358038065668</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.130520105868131</v>
+        <v>9.349222133898973</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.364059689607794</v>
+        <v>6.516497179443543</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1481219642614271</v>
+        <v>0.1516699103088885</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.72985430859732</v>
+        <v>13.03057162050983</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.258013568029408</v>
+        <v>9.47671559606025</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01308601100055534</v>
+        <v>0.01277989599936413</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1757600303070632</v>
+        <v>-0.1774278668329795</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2901656708796634</v>
+        <v>0.2894117866894625</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002540620384047267</v>
+        <v>0.002478386167146974</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7789901606449278</v>
+        <v>0.7751385826763244</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3823461763573922</v>
+        <v>0.379213207556274</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8841449226.603495</v>
+        <v>8490362029.198562</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>256.78</v>
+        <v>254.78</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1336865342163354</v>
+        <v>0.1248565121412804</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1059192200557104</v>
+        <v>-0.112883008356546</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2762208138000</v>
+        <v>2740693938000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.37936507936508</v>
+        <v>20.22063492063492</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.77500684011763</v>
+        <v>22.60942955443562</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.561015029393565</v>
+        <v>3.533279107363862</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>5.006935354048076</v>
+        <v>4.967937493201841</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2306902747562646</v>
+        <v>0.228893481588913</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.44591132178727</v>
+        <v>11.36099673163069</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.747972279806106</v>
+        <v>3.720166933328177</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004208589439757852</v>
+        <v>-0.004241709831146357</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1051873124592303</v>
+        <v>-0.105654794520548</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.17771891846736</v>
+        <v>0.1781464823768628</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8296038041177198</v>
+        <v>0.831056140105345</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4652561170535028</v>
+        <v>0.4600153326456301</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>10365039248.01656</v>
+        <v>9344931571.26368</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>218.29</v>
+        <v>212.025</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1558908813608786</v>
+        <v>0.1227164053348313</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07715396973027822</v>
+        <v>-0.1036399763253572</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5287202090000</v>
+        <v>5135457525000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.45786163522012</v>
+        <v>26.66981132075471</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.37410678350809</v>
+        <v>15.88313975964608</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.45129729444267</v>
+        <v>16.95043890629074</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.06027975753764</v>
+        <v>22.39844159417252</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.220410045779318</v>
+        <v>0.2140841997176229</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.69733890536532</v>
+        <v>22.04793370480213</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.50548435648532</v>
+        <v>17.0046259683334</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02402140070269189</v>
+        <v>0.02473119471472992</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6769074489532174</v>
+        <v>0.6791271577496334</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9303402776833312</v>
+        <v>0.9328589725338055</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002382152182875991</v>
+        <v>0.002452540973941752</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.322780447691964</v>
+        <v>1.327160397548167</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4084395360415243</v>
+        <v>0.4148400572918929</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>27448909421.48951</v>
+        <v>27055168487.89567</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>648.03</v>
+        <v>663.325</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.003659189192663836</v>
+        <v>0.01985674788015412</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1805386949924127</v>
+        <v>-0.1611975214972179</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1650847721957</v>
+        <v>1689811529045</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.08138238573021</v>
+        <v>24.64781865477518</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>19.60576870666489</v>
+        <v>20.06455222816985</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.232693044219446</v>
+        <v>7.40281864570993</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.308605701685546</v>
+        <v>6.456995151232098</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-4.936683389074689</v>
+        <v>-5.052802824228906</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.32269614798453</v>
+        <v>16.68535705175956</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.657038493029512</v>
+        <v>7.827164094519996</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02482118699078128</v>
+        <v>0.02425076651060896</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2282804487815804</v>
+        <v>0.2284260508026987</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2705509847826661</v>
+        <v>0.2710650922747215</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003240590713392899</v>
+        <v>0.00316586891795123</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7840031621567214</v>
+        <v>0.7806994346944971</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4197310775348115</v>
+        <v>0.4169714993952099</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10201000387.61983</v>
+        <v>9992239438.008711</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>365.44</v>
+        <v>362.48</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.165795434770463</v>
+        <v>-0.1725523456534518</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.267405729406812</v>
+        <v>-0.2733396146983942</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1443322599663</v>
+        <v>1431631939377</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>309.6949152542373</v>
+        <v>307.1526271186441</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>173.9867834554464</v>
+        <v>172.4508465322345</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.92913075462029</v>
+        <v>13.8147864043853</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.61911717976467</v>
+        <v>13.5073177335421</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.243991406063495</v>
+        <v>-8.176316412031507</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>119.5082806503991</v>
+        <v>118.5232251775856</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.87241335723178</v>
+        <v>13.75806900699679</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.003992177494723192</v>
+        <v>0.004025220563815595</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7799910378453681</v>
+        <v>0.7811024607596293</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1215655287458917</v>
+        <v>0.1218155461162014</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.552710352419476</v>
+        <v>1.545780564140041</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5738652948790913</v>
+        <v>0.5740456608731275</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12812720116.62303</v>
+        <v>12684958207.25491</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>361.99</v>
+        <v>346.73999</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.04133825753598597</v>
+        <v>-0.002531514669893653</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2687070707070707</v>
+        <v>-0.2995151717171718</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1722196384200</v>
+        <v>1649643242739</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>44.91191066997519</v>
+        <v>43.01984987593052</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.80286514742586</v>
+        <v>18.94683586278015</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>19.32793571781289</v>
+        <v>18.51368336706545</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>17.30609228608687</v>
+        <v>16.57701667509279</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4468957447853964</v>
+        <v>0.4280688032208926</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>33.63068297265752</v>
+        <v>32.24245149989476</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.72571808448554</v>
+        <v>18.9114657337381</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02287950454518205</v>
+        <v>0.02388577055883724</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.26795013426697</v>
+        <v>1.270555895849621</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8564104257536831</v>
+        <v>0.8585251496160557</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.0070167684190171</v>
+        <v>0.007325373689951367</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.591136790691581</v>
+        <v>1.600700056177729</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3916057238939792</v>
+        <v>0.4025682119619466</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8616347746.350199</v>
+        <v>8505683809.747202</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>904.77</v>
+        <v>916</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.05882972498537153</v>
+        <v>0.07197191339964881</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1748563611491109</v>
+        <v>-0.1646146830825354</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>401246494830</v>
+        <v>406226764000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.44299347061778</v>
+        <v>46.00703164239076</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.91873039403847</v>
+        <v>40.41420144449886</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.36670388957958</v>
+        <v>1.383667410341739</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.98627869259005</v>
+        <v>12.13505231430362</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.584721851008112</v>
+        <v>3.62921539786181</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.98911505390463</v>
+        <v>27.33329398756047</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.330210448112485</v>
+        <v>1.347173968874644</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02194660916285617</v>
+        <v>0.0216775475679884</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006123103109077445</v>
+        <v>0.006048034934497817</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1861953189174849</v>
+        <v>-0.1891268944090583</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1839168874187742</v>
+        <v>0.1860969081064974</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1722789357.552694</v>
+        <v>1692630979.817741</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1493570522346479</v>
+        <v>-0.1131992318451388</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3801057184046132</v>
+        <v>-0.353756206951786</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>322288955923</v>
+        <v>335988318519</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>23.96284829721363</v>
+        <v>24.98142414860681</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.64675644835125</v>
+        <v>21.52099162675565</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.662887440086743</v>
+        <v>6.946103198183928</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.75389669001632</v>
+        <v>11.21100676895888</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7042739560522543</v>
+        <v>0.7342101487578345</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.70361875953483</v>
+        <v>11.15135368720985</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.770598660029434</v>
+        <v>7.05381441812662</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03411413204809534</v>
+        <v>0.03272318528353318</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1606107892616311</v>
+        <v>0.1607933584969679</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1427745098118778</v>
+        <v>0.1431026964010345</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09961480082447288</v>
+        <v>0.09790870291220452</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3634172639823042</v>
+        <v>0.3765823731261873</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2211242125.649261</v>
+        <v>2172210566.412371</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>510.37</v>
+        <v>512.91</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02721141940303728</v>
+        <v>0.03232362624372875</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05089820359281438</v>
+        <v>-0.04617473128277616</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1100793369280</v>
+        <v>1106271777411</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.8402369442784</v>
+        <v>12.9058746933681</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.00733563970968</v>
+        <v>23.1218111084785</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.863781900610106</v>
+        <v>2.878421209734147</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.466288622551745</v>
+        <v>1.473784113882457</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.353715828819828</v>
+        <v>0.3555239816539139</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.5582072300494</v>
+        <v>15.63180881811172</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.094517537634492</v>
+        <v>3.109156846758534</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02198047246656578</v>
+        <v>0.02186868238871257</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4419068272244138</v>
+        <v>-0.4418311509933723</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06139523027282179</v>
+        <v>0.0615833586816934</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.06432354147288388</v>
+        <v>0.05690917823923999</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1406752297569992</v>
+        <v>0.1400473515421361</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2108686234.881185</v>
+        <v>2075894072.081889</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>356.23</v>
+        <v>350.54</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.09447581410756301</v>
+        <v>0.07699394177151042</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.02802182810368348</v>
+        <v>-0.04354706684856746</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>954521847300</v>
+        <v>939275435400</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.31513327601032</v>
+        <v>15.07050730868444</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>14.22510989720509</v>
+        <v>13.99727393438135</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.207043060749312</v>
+        <v>3.155817518218746</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.651959169563105</v>
+        <v>2.609599885744184</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.8018888817171094</v>
+        <v>0.78908044970136</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.20804902640618</v>
+        <v>20.0443906762559</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.325178482560737</v>
+        <v>6.273952940030171</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1702779254972009</v>
+        <v>-0.1730418936494206</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07662671056196224</v>
+        <v>0.07667445670738182</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2895318430660836</v>
+        <v>-0.2894796085946888</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01684305083794178</v>
+        <v>0.01711644890740001</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7724829929363041</v>
+        <v>0.7707282381692373</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1682573598779749</v>
+        <v>0.171074244059474</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>1996875316.184591</v>
+        <v>1947689584.188324</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>370.45</v>
+        <v>376.08</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.0691814484346045</v>
+        <v>0.08543058206852772</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03921466919106775</v>
+        <v>-0.02461291075550487</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>691647639315</v>
+        <v>702159115113</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.47408666100255</v>
+        <v>31.95242141036533</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.7979651085753</v>
+        <v>25.16654507899095</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.54683598532188</v>
+        <v>15.78311263965564</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.15003476462562</v>
+        <v>20.45626960259253</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.122430186021555</v>
+        <v>2.154686312212137</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.16477556240979</v>
+        <v>24.52601948975875</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.8053101806105</v>
+        <v>16.04158683494425</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03038107672977968</v>
+        <v>0.02992626535456758</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2692205397981868</v>
+        <v>0.2696387728262006</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1372179948816117</v>
+        <v>0.1375240610011503</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007234444594412202</v>
+        <v>0.007126143373750267</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3161428791341334</v>
+        <v>0.3065458064898975</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1902203688985791</v>
+        <v>0.1931196194254112</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2295279806.026103</v>
+        <v>2225464739.478773</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>569.1900000000001</v>
+        <v>575.01</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01076127193479715</v>
+        <v>0.02109636320952157</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05390445796349852</v>
+        <v>-0.04423057744090952</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,40 +2354,40 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>499200120840</v>
+        <v>504304470360</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.25700164744646</v>
+        <v>31.57660626029654</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.69509642969269</v>
+        <v>25.94778138848124</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.2291172602115</v>
+        <v>14.37461079041131</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.47167706291215</v>
+        <v>90.38653003029764</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.381447840668392</v>
+        <v>1.395573223111319</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.17562492494122</v>
+        <v>23.40642387230964</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.60970044865034</v>
+        <v>14.75519397885015</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03294870997291243</v>
+        <v>0.0326152175257509</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2164578456816593</v>
+        <v>0.2169289461608479</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1560881955092015</v>
+        <v>0.1564551345566814</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005920694319998594</v>
+        <v>0.005860767638823673</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.3037572295055846</v>
+        <v>0.2947684382098303</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.2087301167230023</v>
+        <v>0.2091536729951674</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1597794977.672933</v>
+        <v>1526338069.898275</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>379.09</v>
+        <v>383.59</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1269025174734455</v>
+        <v>0.1402794499396951</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1787834149300291</v>
+        <v>-0.1690351371257746</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>344268462112</v>
+        <v>348355108605</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.37721046878015</v>
+        <v>24.66658092727156</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.51388894681446</v>
+        <v>17.71576097379578</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7648217780058605</v>
+        <v>0.7739006120578766</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.488723909616341</v>
+        <v>3.530136918646581</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7386358420109492</v>
+        <v>-0.7474038424568836</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.09961813888134</v>
+        <v>15.25901840263168</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8642221721151048</v>
+        <v>0.8733453990011751</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.0686005330116958</v>
+        <v>0.06779187319321366</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3918787850492815</v>
+        <v>0.3923523219666978</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01030287783379724</v>
+        <v>0.01038134275007363</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02360916932654515</v>
+        <v>0.02361896816913893</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.436475309780648</v>
+        <v>0.4262510099876727</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2272317203020928</v>
+        <v>0.2274706885088772</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1791619278.642578</v>
+        <v>1761291428.937432</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>166.02</v>
+        <v>165.245</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3536078103103009</v>
+        <v>0.3472890170746035</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.05889688793152303</v>
+        <v>-0.063290062921603</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>688063249200</v>
+        <v>684851272463</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.36679536679537</v>
+        <v>21.26705276705277</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>15.01583088487154</v>
+        <v>14.94907161018081</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.905675647260843</v>
+        <v>1.89677968332964</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.671534979643766</v>
+        <v>2.659063954410517</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.092165379665381</v>
+        <v>2.082398916773918</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>10.02218237660982</v>
+        <v>9.977462895412462</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.993694259125907</v>
+        <v>1.984798295194704</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04440434805306558</v>
+        <v>0.04461260601899614</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4229512526224855</v>
+        <v>0.4226336806473794</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08247725756777813</v>
+        <v>0.08231581936981591</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02481628719431394</v>
+        <v>0.02493267572392508</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.547064655600945</v>
+        <v>-0.5450501269668325</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2306851828723931</v>
+        <v>0.2307829930272591</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2252779834.290212</v>
+        <v>2205824710.227472</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>265.58</v>
+        <v>267.7</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2808294776100182</v>
+        <v>0.2910537358091794</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.05511082648450571</v>
+        <v>-0.04756822143949913</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>640020821321</v>
+        <v>645129805963</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.7028901734104</v>
+        <v>30.94797687861271</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.37408831167713</v>
+        <v>21.5388552700378</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.535559653636819</v>
+        <v>6.587729946828825</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.626622706570476</v>
+        <v>7.687502442009626</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.801502585944636</v>
+        <v>-3.831848189838765</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.8219738325922</v>
+        <v>19.97343193297166</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.827750935075412</v>
+        <v>6.879921228267418</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02923029904150114</v>
+        <v>0.02899881516414226</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4364537904822234</v>
+        <v>0.4368440890015042</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.08833454717187483</v>
+        <v>0.08854415069248511</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01988101513668198</v>
+        <v>0.01972357116174823</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.166496328835057</v>
+        <v>-0.1748754776236435</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2227528347813669</v>
+        <v>0.2116056571777831</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1697427104.77061</v>
+        <v>1652666672.513288</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>107.15</v>
+        <v>109.165</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04975170299706777</v>
+        <v>-0.03188189134554265</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2072358686001775</v>
+        <v>-0.1923276117194436</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>852708272000</v>
+        <v>868743803200</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.68231046931408</v>
+        <v>39.40974729241878</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.57399762391755</v>
+        <v>35.2136357103365</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.158822939769515</v>
+        <v>1.180615083713851</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.675574624890572</v>
+        <v>8.838722388485108</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.354085986215958</v>
+        <v>9.52999343616673</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.35750769158944</v>
+        <v>21.7318285487523</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.243387519025875</v>
+        <v>1.265179662970211</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01584246388077727</v>
+        <v>0.01555003897609384</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1188266653479055</v>
+        <v>0.1191615548192475</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05069788025443667</v>
+        <v>0.05082221401082943</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009122725151656555</v>
+        <v>0.008954335180689782</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.04357380101997047</v>
+        <v>-0.05815779045644878</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3087826617573923</v>
+        <v>0.3117912557655074</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2781691745.647964</v>
+        <v>2730355064.764832</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>145.27</v>
+        <v>146.19</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.02454338725332006</v>
+        <v>0.03103185642295614</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1314200298953662</v>
+        <v>-0.1259192825112108</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,40 +2984,40 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>345337142278</v>
+        <v>347524174500</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.52148148148148</v>
+        <v>21.65777777777778</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.57258134369886</v>
+        <v>20.69951704521253</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>3.967932970378711</v>
+        <v>3.993062028908907</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.479655594630922</v>
+        <v>6.520691480547218</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.53764232804254</v>
+        <v>20.66770793650816</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.42830254436812</v>
+        <v>17.53120233838336</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.256148799039434</v>
+        <v>4.28127785756963</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04607960758298587</v>
+        <v>0.04578962031316184</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04612450532724499</v>
+        <v>0.04629386910197875</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02519525344873941</v>
+        <v>0.02527505890851667</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02953534797274042</v>
+        <v>0.02934947670839319</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.0406028465259391</v>
+        <v>-0.04614514794490439</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1635680009252458</v>
+        <v>0.160865359695334</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1298280859.599813</v>
+        <v>1271783359.64692</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>308.74</v>
+        <v>310.20001</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1072234299314409</v>
+        <v>-0.1030015515869899</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2765319273579379</v>
+        <v>-0.2731106971294669</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>307849902580</v>
+        <v>309305705572</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.56005586592179</v>
+        <v>21.66201187150838</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.57412154818365</v>
+        <v>20.67141513891231</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.819701982432496</v>
+        <v>1.828307239632099</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.46828910152254</v>
+        <v>18.55562435698381</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.395600558659249</v>
+        <v>-7.430573839645349</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.40171033159105</v>
+        <v>15.46258438519757</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.177211321818698</v>
+        <v>2.1858165790183</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04905312580398088</v>
+        <v>0.04882224843564936</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.04792108938547468</v>
+        <v>0.0479210893854749</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03009004340221545</v>
+        <v>0.02994841940849711</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7194471644235487</v>
+        <v>0.7080513697226719</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.251315174403697</v>
+        <v>0.2497970071062758</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1239314204.777323</v>
+        <v>1199809742.470005</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>516.13</v>
+        <v>494.125</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.309616490717519</v>
+        <v>1.211146898021417</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1173191045439776</v>
+        <v>-0.1549518581225523</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,40 +3236,40 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>841601578000</v>
+        <v>805720225000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>130.997461928934</v>
+        <v>125.4124365482233</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>38.30146529942742</v>
+        <v>36.60731156027715</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>20.37529543638785</v>
+        <v>19.50660271153613</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.52243291086517</v>
+        <v>11.98854389801262</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.057594188050109</v>
+        <v>1.012504074884739</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>78.44668576226908</v>
+        <v>75.09892004105244</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>20.35568521970706</v>
+        <v>19.48699249485534</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009984534510936956</v>
+        <v>0.01042917844094084</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.420168416660871</v>
+        <v>2.42588491759961</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.8883604343143967</v>
+        <v>0.8908862032600786</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.533602493189448</v>
+        <v>2.54426273472138</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.672303867425101</v>
+        <v>0.6751876786133827</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>10307044310.83171</v>
+        <v>10128306494.24566</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1698.3</v>
+        <v>1596.773</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4592963938606747</v>
+        <v>0.3720573989955196</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1508330166603332</v>
+        <v>-0.2015975319506391</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,40 +3362,40 @@
         <v>833.92</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>654555374115</v>
+        <v>615425041743</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>53.64296081277213</v>
+        <v>50.35558962264151</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>35.00133660233855</v>
+        <v>32.88202121349596</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>16.1291333350506</v>
+        <v>15.14070077783596</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>26.10606724275385</v>
+        <v>24.50622390746561</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.651672374875111</v>
+        <v>3.427889004623443</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>40.93697402252889</v>
+        <v>38.40744733449237</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>15.9964463348383</v>
+        <v>15.00801377762366</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01755329173835631</v>
+        <v>0.01869922581994628</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5325974954107349</v>
+        <v>0.5314018957561457</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2864551702816613</v>
+        <v>0.2852182160662287</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004581051639875169</v>
+        <v>0.004872326874264533</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.687285180894966</v>
+        <v>1.694667569641459</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4028885051083511</v>
+        <v>0.424706163478566</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2050948937.47111</v>
+        <v>2020619636.414062</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>210.45</v>
+        <v>210.64999</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07604163826481103</v>
+        <v>-0.07516360342155404</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1725968154118341</v>
+        <v>-0.1718105366620798</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>166333366500</v>
+        <v>166491435676</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>78.82022471910109</v>
+        <v>78.89512734082395</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>84.14062311047331</v>
+        <v>83.76298271958655</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.769598026490771</v>
+        <v>1.771279702920368</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.291044772</v>
+        <v>27.31697936950037</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4218516503027515</v>
+        <v>0.4222525346531628</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.49415345323741</v>
+        <v>29.51689721956835</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.180800750039896</v>
+        <v>2.182482426469493</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001262524798354274</v>
+        <v>-0.001261326140575</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.06323221999897422</v>
+        <v>-0.05811463752501189</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.152523701668509</v>
+        <v>0.1529483038203574</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.223650238997503</v>
+        <v>1.242856591853039</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3374332140188102</v>
+        <v>0.3372040913177615</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1168522708.489583</v>
+        <v>1127510266.767813</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>1029.18</v>
+        <v>993.79</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1255987595112515</v>
+        <v>0.08689324628800277</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1081551833204794</v>
+        <v>-0.1388226934375515</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>303615304260</v>
+        <v>293175006530</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15.67915904936015</v>
+        <v>15.14000609384522</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>14.2131694053763</v>
+        <v>13.72281831984176</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.574385513112933</v>
+        <v>2.485861150699102</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.516309967248374</v>
+        <v>2.429782625344218</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3674977625374731</v>
+        <v>0.3548607643289953</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>27.33804683400759</v>
+        <v>27.00547913643169</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.27696400841127</v>
+        <v>7.188439645997439</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1367355315015635</v>
+        <v>-0.1416048403694735</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1031430500947468</v>
+        <v>0.1032723556468242</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3823711015222546</v>
+        <v>-0.3823282959808237</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01748965195592608</v>
+        <v>0.01811247849143179</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.561111812045423</v>
+        <v>1.56460922709919</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3182777581679786</v>
+        <v>0.3262811020805543</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1824376179.444377</v>
+        <v>1804383991.244456</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>243.29</v>
+        <v>249.94</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1653859348198972</v>
+        <v>-0.1425728987993139</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2682127173193768</v>
+        <v>-0.2482103110148589</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>229211780860</v>
+        <v>235476971960</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>21.24803493449782</v>
+        <v>21.82882096069869</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.86344951193065</v>
+        <v>19.37561604161878</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.317246492032939</v>
+        <v>3.407918896044691</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.637300330895159</v>
+        <v>6.81872187391153</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2590118987170374</v>
+        <v>0.2660916353542535</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>17.71233468096911</v>
+        <v>18.09857419148018</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.158093417369785</v>
+        <v>4.248765821381537</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.05946902008638755</v>
+        <v>0.05788676441072748</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1264130095112761</v>
+        <v>0.1266130023329546</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04578542708088928</v>
+        <v>0.04589294922825382</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02770356364832094</v>
+        <v>0.02696647195326879</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9033016742139656</v>
+        <v>0.9001586591133746</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3321552392656185</v>
+        <v>0.3284580294484706</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1234853481.073049</v>
+        <v>1200885175.557023</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1115.25</v>
+        <v>1145.4698</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.0322948046220759</v>
+        <v>0.06026677730687147</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1372374579352493</v>
+        <v>-0.1138592813213167</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,40 +3868,40 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1050276650250</v>
+        <v>1078735874922</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>37.36180904522614</v>
+        <v>38.37419765494138</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>25.59658996630991</v>
+        <v>26.27326956641244</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.18353233445217</v>
+        <v>13.5407649822383</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>29.37657841140529</v>
+        <v>30.1725921520706</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3960506466077799</v>
+        <v>0.4067823850792955</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>31.13765764172915</v>
+        <v>31.94597463423085</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>13.76117041754429</v>
+        <v>14.11840306533042</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01909392158268635</v>
+        <v>0.01859018548117725</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470491333778837</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4596400963722727</v>
+        <v>0.4605794515958792</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2273126002782788</v>
+        <v>0.227779731796429</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877209505000597</v>
@@ -3937,16 +3937,16 @@
         <v>33.16107129385138</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005998655010087425</v>
+        <v>0.005840398411202111</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3463582056680412</v>
+        <v>0.3418951356085352</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3219499093209016</v>
+        <v>0.328599026128182</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>3192849885.978597</v>
+        <v>3123879242.694877</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>214.38</v>
+        <v>208.45</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1785596877039992</v>
+        <v>0.1459593567585533</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.07694294940796553</v>
+        <v>-0.102475780409042</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,40 +3994,40 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>338137286400</v>
+        <v>328784011187</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>17.23311897106109</v>
+        <v>16.75361655948553</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.92478333473714</v>
+        <v>15.48176079312228</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.672409379667902</v>
+        <v>2.598051044503632</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>3.050173252307163</v>
+        <v>2.965303796426275</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4384380410586198</v>
+        <v>0.4262387346900449</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.94041252598221</v>
+        <v>23.61981806010836</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.552713499672012</v>
+        <v>5.478355164507741</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.0463835271376922</v>
+        <v>-0.04771106143087023</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.0821572016914065</v>
+        <v>0.08215188074267821</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3274869152039972</v>
+        <v>-0.3275002082938857</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.019358149081071</v>
+        <v>0.01990885104341569</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.369518247912609</v>
+        <v>1.373229260772864</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2705377143985447</v>
+        <v>0.2779897535596553</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>884303144.0093485</v>
+        <v>868968590.9007822</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>975.26</v>
+        <v>926.12</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.091940772564329</v>
+        <v>1.936148502232509</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2229003984063745</v>
+        <v>-0.2620557768924303</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1101448891400</v>
+        <v>1045950666800</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>21.76433831733988</v>
+        <v>20.66621066726177</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.267436501124496</v>
+        <v>5.951641913357892</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.20117521545517</v>
+        <v>11.58556045739637</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.92185854414042</v>
+        <v>10.37079217664112</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03102056379243497</v>
+        <v>0.02945540990055924</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.84335427676821</v>
+        <v>15.0316661487139</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.9949253539225</v>
+        <v>11.38040027693467</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02376142933580332</v>
+        <v>0.02502167228932509</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.472606114706539</v>
+        <v>2.472354514621996</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.765110056317434</v>
+        <v>1.764909716313137</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005434448249697517</v>
+        <v>0.0005722800501014988</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.884074907778928</v>
+        <v>2.883347275231924</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8406891342442575</v>
+        <v>0.8248513252611771</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>27580450013.27393</v>
+        <v>26663728391.69365</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>132.53</v>
+        <v>142.41</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1011868243949805</v>
+        <v>-0.03418105834218044</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.319402647823095</v>
+        <v>-0.2686646878177542</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,40 +4246,40 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>137017730860</v>
+        <v>147232287420</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>82.31677018633542</v>
+        <v>88.45341614906833</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>27.99208426195769</v>
+        <v>30.06241544274229</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.300687677165355</v>
+        <v>9.994046118653271</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>10.93827820389901</v>
+        <v>11.75371764141898</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>131.7068322981395</v>
+        <v>141.5254658385124</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>40.97670703926627</v>
+        <v>43.90138793063915</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>9.704570381482487</v>
+        <v>10.39722661485202</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03342633082049568</v>
+        <v>0.03110949307241409</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.940716004424403</v>
+        <v>1.94232565302476</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2445053550059697</v>
+        <v>0.2450681773312406</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7425686691485414</v>
+        <v>0.7207905166666362</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6075948118380816</v>
+        <v>0.6285644861216921</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2252923509.665476</v>
+        <v>2225653407.549097</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.72</v>
+        <v>27.7899</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.100873695950755</v>
+        <v>0.1036497086256092</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05100992810681282</v>
+        <v>-0.04861691201643281</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157988476800</v>
+        <v>158386867656</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.62790697674419</v>
+        <v>36.72026955602537</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.493088068672243</v>
+        <v>9.51772209731608</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.480351620195931</v>
+        <v>2.486606186510927</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.85439934264585</v>
+        <v>1.859075479516375</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6126260547437744</v>
+        <v>-0.6141708801848491</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.44347883396705</v>
+        <v>17.47282480988593</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.457147651343883</v>
+        <v>3.46296377166541</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06953671699681833</v>
+        <v>0.06937404337418766</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.858376400996264</v>
+        <v>2.858094319267862</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05010572930318846</v>
+        <v>-0.05021253784362711</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06204906204906205</v>
+        <v>0.06189298989920799</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3541261297162214</v>
+        <v>0.3493970084106297</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2146777093459052</v>
+        <v>0.2087004289670491</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>999586815.2629089</v>
+        <v>974752994.2939217</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>190.07</v>
+        <v>176.64</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1313017452200826</v>
+        <v>0.05136602449453043</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.04903187071596549</v>
+        <v>-0.1162255466052935</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,40 +4498,40 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1349221191324</v>
+        <v>1253887679462</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>7.917142991467138</v>
+        <v>7.414675307130095</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003950478887045561</v>
+        <v>0.00366847881386825</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6.799454886225326</v>
+        <v>6.3679221533799</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>4.927298446329551</v>
+        <v>4.614583589084575</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.01771757741788015</v>
+        <v>0.01659311748241866</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>7.998062425067403</v>
+        <v>7.488190590983496</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>6.769202581976064</v>
+        <v>6.337669849130638</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.07089086128968651</v>
+        <v>0.07569489726394341</v>
       </c>
       <c r="T32" s="4" t="n">
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2003.097026674181</v>
+        <v>2020.185260522643</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2585.930107902172</v>
+        <v>2609.025817305346</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.578365865207555</v>
+        <v>1.698369565217391</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9937298607955094</v>
+        <v>0.9828267271293428</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3435314431.302287</v>
+        <v>3297475706.806618</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>568.53</v>
+        <v>544.33</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5229842448194917</v>
+        <v>0.4581570259838426</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1537591354955867</v>
+        <v>-0.1897801527172053</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>71657946460</v>
+        <v>68607760359</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.820053339756524</v>
+        <v>1.825324155626536</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.3986133560350327</v>
+        <v>0.41033915708003</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3961573225.916544</v>
+        <v>3816249805.74646</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>151.21</v>
+        <v>152.04</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.06051567028842098</v>
+        <v>-0.0553587891716919</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.329861726644212</v>
+        <v>-0.3261833008331856</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1977201613485</v>
+        <v>1988054581802</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-98.18831168831169</v>
+        <v>-98.74025974025975</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>137.6590676676727</v>
+        <v>137.802885451069</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>119.2881818090498</v>
+        <v>119.9587390112217</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.969561089102686</v>
+        <v>7.008739231591524</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9818831168831168</v>
+        <v>-0.9874025974025975</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>461.4935477525798</v>
+        <v>464.1608109217663</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>116.0207308286576</v>
+        <v>116.6912880308296</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01437536759334413</v>
+        <v>-0.01429501074437222</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.184692245707556</v>
+        <v>4.195423725844542</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.457810540572236</v>
+        <v>3.441642708883008</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.783814195599935</v>
+        <v>0.7835565208528544</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14188247188.11424</v>
+        <v>14192963950.06558</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>764.29</v>
+        <v>762.13</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1187406050018327</v>
+        <v>0.1155788735820786</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.01934896134056996</v>
+        <v>-0.02212043060420599</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>814150923750</v>
+        <v>811850009181</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9952270977144121</v>
+        <v>0.9952897736453762</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1151986111457538</v>
+        <v>0.1151115487778224</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>30936755297.01904</v>
+        <v>29891923999.91215</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>433.24</v>
+        <v>420.435</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3555271107172935</v>
+        <v>0.3154626553282829</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.09553235908141966</v>
+        <v>-0.1222651356993737</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,40 +4914,40 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2246990595200</v>
+        <v>2180577718800</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>27.93555117653877</v>
+        <v>27.58780572620842</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.662234378283926</v>
+        <v>0.6422159848404414</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>14.07436022855125</v>
+        <v>13.89916072363153</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>9.714817505368815</v>
+        <v>9.59388616712771</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.5247819590387496</v>
+        <v>0.5182494035320432</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>18.51345021489235</v>
+        <v>18.27477474575392</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>13.58978081708063</v>
+        <v>13.41458131216091</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.01789632973916031</v>
+        <v>0.01812191372746905</v>
       </c>
       <c r="T36" s="4" t="n">
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>41.18378280047808</v>
+        <v>41.95720813156435</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>41.15666372328758</v>
+        <v>41.93251569219548</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.253900840180962</v>
+        <v>0.2616337840569886</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.161816965705875</v>
+        <v>2.179047823951394</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3552040270120096</v>
+        <v>0.3630682379655741</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4139233405.578207</v>
+        <v>4086501824.133639</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.04</v>
+        <v>28.1228</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01648545159974102</v>
+        <v>-0.01358120749818814</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06533333333333335</v>
+        <v>-0.06257333333333326</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,38 +5042,38 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70300113124</v>
+        <v>70507704043</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.07874015748031</v>
+        <v>-22.14393700787402</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-80.68007820889312</v>
+        <v>-81.65117073184392</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.946562733600997</v>
+        <v>1.952310786183026</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.14411474511237</v>
+        <v>2.150446153846154</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.164306903497528</v>
+        <v>0.164792089360923</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.35605175603306</v>
+        <v>16.3903643046281</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.739972674068946</v>
+        <v>2.745720726650976</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03100990742582123</v>
+        <v>0.03091860711661381</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02043303423553744</v>
+        <v>0.02050670921914222</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2915347672171608</v>
+        <v>0.2531405301144675</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1902322332709558</v>
+        <v>0.1891923299751187</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>532577590.4036903</v>
+        <v>503867970.4693958</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>324.69</v>
+        <v>327.07</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1288868874797695</v>
+        <v>-0.1225015685361674</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1620686985470593</v>
+        <v>-0.155926604557537</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,40 +5170,40 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>219266403900</v>
+        <v>220873641700</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.69011522134627</v>
+        <v>19.83444511825349</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.72171575281377</v>
+        <v>16.83829513817301</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.608047814399391</v>
+        <v>2.627164984001998</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.421815052508752</v>
+        <v>6.46888739789965</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.220959109795273</v>
+        <v>1.229908823926638</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.426969903737259</v>
+        <v>9.491977095130238</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.772262247094787</v>
+        <v>2.791379416697394</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.06864708743462911</v>
+        <v>0.06814756113110258</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1775176370901419</v>
+        <v>0.1779366589963201</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.005425181638038401</v>
+        <v>0.005658273890123855</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01090270719763467</v>
+        <v>0.01082337114379185</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9685305146415542</v>
+        <v>0.96112052940579</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.222332815308943</v>
+        <v>0.2216990654609904</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>780674338.0948893</v>
+        <v>765001632.2843527</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>150.15</v>
+        <v>143.56</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2327934451531496</v>
+        <v>-0.266465714193714</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.544309559939302</v>
+        <v>-0.564309559939302</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,40 +5296,40 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>432502570500</v>
+        <v>413520273200</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>23.1712962962963</v>
+        <v>22.15432098765432</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.77375562030881</v>
+        <v>16.02329270350585</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>6.025642900929268</v>
+        <v>5.761180784931106</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.669635475948002</v>
+        <v>6.376908883963337</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.5043164488017432</v>
+        <v>0.4821822803195354</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.71897433812355</v>
+        <v>14.21287421547978</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.69138540897502</v>
+        <v>7.426923292976859</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06640422961370585</v>
+        <v>-0.06945245943506501</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3814018053441572</v>
+        <v>0.3826322340605446</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.4198565143825406</v>
+        <v>0.4214263744375701</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01332001332001332</v>
+        <v>0.0139314572304263</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.030285433679443</v>
+        <v>2.074118099546188</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5780162656733132</v>
+        <v>0.5850709403993845</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4228908166.034698</v>
+        <v>4196707225.397536</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:21 ET</t>
+          <t>2026-09-14 13:18 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>334.17001</v>
+        <v>334.685</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.233054123310785</v>
+        <v>0.2349543852252631</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.0301825173404533</v>
+        <v>-0.02868792988362301</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,40 +714,40 @@
         <v>235.03</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4908073951738</v>
+        <v>4915637742860</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.14726141552512</v>
+        <v>38.2054794520548</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.94378705930419</v>
+        <v>34.9976389920305</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.5137792091178</v>
+        <v>10.52982459321841</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.66404282435966</v>
+        <v>45.73373251674108</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.165610765474377</v>
+        <v>1.167389649923895</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.3961335169569</v>
+        <v>29.44059035219543</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.60966780072533</v>
+        <v>10.62571318482594</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.0278486023935314</v>
+        <v>0.02780616659432947</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.0916750766247576</v>
+        <v>0.09165876763157565</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1170296262044463</v>
+        <v>0.1170129384289829</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003172038089234878</v>
+        <v>0.003167157177644651</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3090034763209347</v>
+        <v>0.3089494666609979</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2978607153938829</v>
+        <v>0.2980384634196376</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13711498421.73662</v>
+        <v>13752150765.22068</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>508.12</v>
+        <v>506.895</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.07438575163231675</v>
+        <v>0.07179557107309931</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.08235209130968724</v>
+        <v>-0.0845644007801778</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3773070466000</v>
+        <v>3763974167250</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>28.23444444444445</v>
+        <v>28.16083333333333</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.77961551573403</v>
+        <v>24.71987563340943</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.37242165647799</v>
+        <v>11.34277214929529</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.534532841154917</v>
+        <v>8.512282130804023</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8968202887342083</v>
+        <v>0.894482153905644</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.70520930644423</v>
+        <v>18.6577974414391</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.69749887766055</v>
+        <v>11.66784937047785</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01775048193070232</v>
+        <v>0.01779688090923892</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1394222168829355</v>
+        <v>0.13919801826484</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2251284786170114</v>
+        <v>0.2248874130489094</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007163662127056601</v>
+        <v>0.007180974363526963</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.558727690336572</v>
+        <v>0.5596168774681194</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4353830518384593</v>
+        <v>0.4347159227079213</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>12385142545.40151</v>
+        <v>12426165661.11973</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>347</v>
+        <v>347.6178</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1010630072040466</v>
+        <v>0.1030233435897834</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1507794718680404</v>
+        <v>-0.1492675167029687</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4199432616242</v>
+        <v>4206909300594</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.05486544190665</v>
+        <v>17.08625124131082</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.73358038065668</v>
+        <v>20.77049451886755</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.349222133898973</v>
+        <v>9.366427486430899</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.516497179443543</v>
+        <v>6.528489386241569</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1516699103088885</v>
+        <v>0.1519490260484302</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.03057162050983</v>
+        <v>13.05422913942035</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.47671559606025</v>
+        <v>9.493920948592177</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01277989599936413</v>
+        <v>0.01275642038752504</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1774278668329795</v>
+        <v>-0.1773786981436588</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2894117866894625</v>
+        <v>0.2894888778523226</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002478386167146974</v>
+        <v>0.002473981481960935</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7751385826763244</v>
+        <v>0.7754560373917703</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.379213207556274</v>
+        <v>0.3800493261617421</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8490362029.198562</v>
+        <v>8560941024.717615</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>254.78</v>
+        <v>254.9275</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1248565121412804</v>
+        <v>0.1255077262693156</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.112883008356546</v>
+        <v>-0.1123694289693593</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2740693938000</v>
+        <v>2742280610250</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.22063492063492</v>
+        <v>20.23234126984127</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.60942955443562</v>
+        <v>22.62251885053139</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.533279107363862</v>
+        <v>3.535324631613552</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.967937493201841</v>
+        <v>4.970813585439251</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.228893481588913</v>
+        <v>0.2290259950850053</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.36099673163069</v>
+        <v>11.36745556148301</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.720166933328177</v>
+        <v>3.722281882026094</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004241709831146357</v>
+        <v>-0.004239172299344014</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.105654794520548</v>
+        <v>-0.1056547945205478</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1781464823768628</v>
+        <v>0.178146482376863</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.831056140105345</v>
+        <v>0.8309482889059018</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4600153326456301</v>
+        <v>0.459928867433953</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>9344931571.26368</v>
+        <v>9381975738.114811</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>212.025</v>
+        <v>212.3</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1227164053348313</v>
+        <v>0.124172587442918</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1036399763253572</v>
+        <v>-0.1024773822609283</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,31 +1220,31 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5135457525000</v>
+        <v>5142118300000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>26.66981132075471</v>
+        <v>26.70440251572327</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>15.88313975964608</v>
+        <v>15.90374045972344</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>16.95043890629074</v>
+        <v>16.97242391135727</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.39844159417252</v>
+        <v>22.42749275058519</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2140841997176229</v>
+        <v>0.2143618705343773</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.04793370480213</v>
+        <v>22.07643912062893</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.0046259683334</v>
+        <v>17.02661097339992</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02473119471472992</v>
+        <v>0.0246991594884155</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002452540973941752</v>
+        <v>0.002449364107395195</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.327160397548167</v>
+        <v>1.326716800431758</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4148400572918929</v>
+        <v>0.414303605228308</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>27055168487.89567</v>
+        <v>27138865933.25239</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>663.325</v>
+        <v>665.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.01985674788015412</v>
+        <v>0.02358516549385681</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1611975214972179</v>
+        <v>-0.1581310065756196</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1689811529045</v>
+        <v>1695989183978</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.64781865477518</v>
+        <v>24.74144927536232</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.06455222816985</v>
+        <v>20.1379047162463</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.40281864570993</v>
+        <v>7.430940018786584</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.456995151232098</v>
+        <v>6.481523588072935</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.052802824228906</v>
+        <v>-5.071997101449271</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.68535705175956</v>
+        <v>16.74530407023311</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.827164094519996</v>
+        <v>7.85528546759665</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02425076651060896</v>
+        <v>0.02415899281162666</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2284260508026987</v>
+        <v>0.228600970358257</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2710650922747215</v>
+        <v>0.2712460833408099</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.00316586891795123</v>
+        <v>0.003154337213668795</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7806994346944971</v>
+        <v>0.7807945486452077</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4169714993952099</v>
+        <v>0.4183843080470762</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>9992239438.008711</v>
+        <v>10054200897.42441</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>362.48</v>
+        <v>360.89</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1725523456534518</v>
+        <v>-0.1761819025128951</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2733396146983942</v>
+        <v>-0.2765270733516428</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1431631939377</v>
+        <v>1425352159021</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>307.1526271186441</v>
+        <v>305.8389830508474</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>172.4508465322345</v>
+        <v>171.6943997048613</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.8147864043853</v>
+        <v>13.75570270916531</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.5073177335421</v>
+        <v>13.44954903405558</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.176316412031507</v>
+        <v>-8.141347576987343</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>118.5232251775856</v>
+        <v>118.0273621540572</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.75806900699679</v>
+        <v>13.70050967476042</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004025220563815595</v>
+        <v>0.004042061821617203</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7811024607596293</v>
+        <v>0.7812985372649175</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1218155461162014</v>
+        <v>0.1219390435997418</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.545780564140041</v>
+        <v>1.546418809196771</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5740456608731275</v>
+        <v>0.5744128004122112</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12684958207.25491</v>
+        <v>12725145634.4739</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>346.73999</v>
+        <v>346.187</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.002531514669893653</v>
+        <v>-0.004122303484597856</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2995151717171718</v>
+        <v>-0.3006323232323233</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,31 +1598,31 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1649643242739</v>
+        <v>1647012347460</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>43.01984987593052</v>
+        <v>42.95124069478908</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.94683586278015</v>
+        <v>18.91661895366691</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.51368336706545</v>
+        <v>18.48415724838391</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.57701667509279</v>
+        <v>16.55057921556826</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4280688032208926</v>
+        <v>0.427386107903594</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>32.24245149989476</v>
+        <v>32.19211196180854</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.9114657337381</v>
+        <v>18.88193961505656</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02388577055883724</v>
+        <v>0.02392392507607291</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
@@ -1631,7 +1631,7 @@
         <v>1.270555895849621</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8585251496160557</v>
+        <v>0.8585251496160555</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007325373689951367</v>
+        <v>0.007337075049034193</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.600700056177729</v>
+        <v>1.600406767478028</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.4025682119619466</v>
+        <v>0.4034940372471656</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8505683809.747202</v>
+        <v>8536323865.787517</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>916</v>
+        <v>919.0325</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07197191339964881</v>
+        <v>0.07552077238150967</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1646146830825354</v>
+        <v>-0.1618490652074783</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>406226764000</v>
+        <v>407571614068</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>46.00703164239076</v>
+        <v>46.15934203917629</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>40.41420144449886</v>
+        <v>40.54799627624607</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.383667410341739</v>
+        <v>1.388248165170801</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>12.13505231430362</v>
+        <v>12.17522649131577</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.62921539786181</v>
+        <v>3.641230240322527</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>27.33329398756047</v>
+        <v>27.42623455894955</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.347173968874644</v>
+        <v>1.351754723703706</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.0216775475679884</v>
+        <v>0.02160601890820294</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006048034934497817</v>
+        <v>0.006028078441186791</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1891268944090583</v>
+        <v>-0.1893238290308226</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1860969081064974</v>
+        <v>0.1875204007098069</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1692630979.817741</v>
+        <v>1699036251.032926</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>80.69</v>
+        <v>80.605</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1131992318451388</v>
+        <v>-0.1141334004570258</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.353756206951786</v>
+        <v>-0.3544369694057344</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,31 +1850,31 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>335988318519</v>
+        <v>335634383619</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>24.98142414860681</v>
+        <v>24.95510835913313</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>21.52099162675565</v>
+        <v>21.49832110639037</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.946103198183928</v>
+        <v>6.938786073732472</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>11.21100676895888</v>
+        <v>11.19919693409258</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7342101487578345</v>
+        <v>0.7334367212867178</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>11.15135368720985</v>
+        <v>11.14046651571306</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>7.05381441812662</v>
+        <v>7.046927712760543</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03272318528353318</v>
+        <v>0.03275566084268607</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09790870291220452</v>
+        <v>0.09879862549608635</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3765823731261873</v>
+        <v>0.3761471406826977</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2172210566.412371</v>
+        <v>2180220756.826574</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>512.91</v>
+        <v>515.005</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.03232362624372875</v>
+        <v>0.0365401905473699</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04617473128277616</v>
+        <v>-0.04227879644437837</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1106271777411</v>
+        <v>1110790385693</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.9058746933681</v>
+        <v>12.94225480595318</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.1218111084785</v>
+        <v>23.21625300719808</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.878421209734147</v>
+        <v>2.88653513383088</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.473784113882457</v>
+        <v>1.477938534505857</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3555239816539139</v>
+        <v>0.3565261611099031</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.63180881811172</v>
+        <v>15.67260293577646</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.109156846758534</v>
+        <v>3.117270770855267</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02186868238871257</v>
+        <v>0.02180721047835266</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4418311509933723</v>
+        <v>-0.4425347276349679</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.0615833586816934</v>
+        <v>0.06024522371398233</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.05690917823923999</v>
+        <v>0.0562478551022423</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1400473515421361</v>
+        <v>0.1410786097339412</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2075894072.081889</v>
+        <v>2082475540.992599</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>350.54</v>
+        <v>350.345</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07699394177151042</v>
+        <v>0.07639482663872821</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04354706684856746</v>
+        <v>-0.04407912687585258</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>939275435400</v>
+        <v>938752930950</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.07050730868444</v>
+        <v>15.06313413585555</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.99727393438135</v>
+        <v>13.98948746659678</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.155817518218746</v>
+        <v>3.154273549757587</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.609599885744184</v>
+        <v>2.608323151618535</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.78908044970136</v>
+        <v>0.7886943959068606</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.0443906762559</v>
+        <v>20.03945791579004</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.273952940030171</v>
+        <v>6.272408971569012</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1730418936494206</v>
+        <v>-0.173126594998888</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07667445670738182</v>
+        <v>0.0767466765185183</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2894796085946888</v>
+        <v>-0.2894319492040938</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01711644890740001</v>
+        <v>0.01712597582383079</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7707282381692373</v>
+        <v>0.7705390330702621</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.171074244059474</v>
+        <v>0.1713201326773638</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>1947689584.188324</v>
+        <v>1963832099.704082</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>376.08</v>
+        <v>375.11</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08543058206852772</v>
+        <v>0.08263099776570249</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.02461291075550487</v>
+        <v>-0.02712866664937619</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>702159115113</v>
+        <v>700348079318</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.95242141036533</v>
+        <v>31.87128292268479</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>25.16654507899095</v>
+        <v>25.10163455802036</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.78311263965564</v>
+        <v>15.74303374001978</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.45626960259253</v>
+        <v>20.40432390627665</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.154686312212137</v>
+        <v>2.1492148023521</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.52601948975875</v>
+        <v>24.46474276671936</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>16.04158683494425</v>
+        <v>16.0015079353084</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.02992626535456758</v>
+        <v>0.03000245218141613</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2696387728262006</v>
+        <v>0.2696895434843873</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1375240610011503</v>
+        <v>0.1375695486202875</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007126143373750267</v>
+        <v>0.007144570925861748</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3065458064898975</v>
+        <v>0.3075508365478325</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1931196194254112</v>
+        <v>0.1918794107986126</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2225464739.478773</v>
+        <v>2233883290.69644</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>575.01</v>
+        <v>573.13</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.02109636320952157</v>
+        <v>0.01775788011734258</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.04423057744090952</v>
+        <v>-0.04735547355473557</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>504304470360</v>
+        <v>502655642680</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.57660626029654</v>
+        <v>31.47336628226249</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.94778138848124</v>
+        <v>25.86294490040217</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.37461079041131</v>
+        <v>14.3276128803124</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>90.38653003029764</v>
+        <v>90.09101051505971</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.395573223111319</v>
+        <v>1.391010384796422</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.40642387230964</v>
+        <v>23.32235277807922</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.75519397885015</v>
+        <v>14.70219633554713</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.0326152175257509</v>
+        <v>0.03273591130842226</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005860767638823673</v>
+        <v>0.005879992322858688</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2947684382098303</v>
+        <v>0.2958611623346437</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.2091536729951674</v>
+        <v>0.2083591042955565</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1526338069.898275</v>
+        <v>1531829315.77463</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>383.59</v>
+        <v>384.95001</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1402794499396951</v>
+        <v>0.1443222859226783</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1690351371257746</v>
+        <v>-0.1660889692820935</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,31 +2480,31 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>348355108605</v>
+        <v>349590199406</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.66658092727156</v>
+        <v>24.75403575332777</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.71576097379578</v>
+        <v>17.77857181892202</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7739006120578766</v>
+        <v>0.7766444717092211</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.530136918646581</v>
+        <v>3.542652942293518</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7474038424568836</v>
+        <v>-0.7500537465205449</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.25901840263168</v>
+        <v>15.30618326305166</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8733453990011751</v>
+        <v>0.8760448658184653</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06779187319321366</v>
+        <v>0.06755624167991096</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02361896816913893</v>
+        <v>0.02353552348264649</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4262510099876727</v>
+        <v>0.4258615135957727</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2274706885088772</v>
+        <v>0.229015907648654</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1761291428.937432</v>
+        <v>1767154420.27863</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>165.245</v>
+        <v>165.00999</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3472890170746035</v>
+        <v>0.3453729143670921</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.063290062921603</v>
+        <v>-0.0646222436369821</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,37 +2606,37 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>684851272463</v>
+        <v>683877321834</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.26705276705277</v>
+        <v>21.23680694980695</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.94907161018081</v>
+        <v>14.92781117071753</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.89677968332964</v>
+        <v>1.894082207483521</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.659063954410517</v>
+        <v>2.655282256810432</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.082398916773918</v>
+        <v>2.079437347168598</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.977462895412462</v>
+        <v>9.963902844886878</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.984798295194704</v>
+        <v>1.982100819348585</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04461260601899614</v>
+        <v>0.04467614150161312</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4226336806473794</v>
+        <v>0.4226336806473792</v>
       </c>
       <c r="V17" s="4" t="n">
         <v>0.08231581936981591</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02493267572392508</v>
+        <v>0.02496818525957126</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5450501269668325</v>
+        <v>-0.5450069137685297</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2307829930272591</v>
+        <v>0.2311005986641769</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2205824710.227472</v>
+        <v>2211214617.743942</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>267.7</v>
+        <v>267.94</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2910537358091794</v>
+        <v>0.2922111990015372</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.04756822143949913</v>
+        <v>-0.04671434162308319</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>645129805963</v>
+        <v>645708181583</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.94797687861271</v>
+        <v>30.9757225433526</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.5388552700378</v>
+        <v>21.55816541297695</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.587729946828825</v>
+        <v>6.593636017757763</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.687502442009626</v>
+        <v>7.694394487531039</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.831848189838765</v>
+        <v>-3.835283541223006</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.97343193297166</v>
+        <v>19.99057813301909</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.879921228267418</v>
+        <v>6.885827299196356</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02899881516414226</v>
+        <v>0.02897284026065148</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01972357116174823</v>
+        <v>0.01970590430693439</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1748754776236435</v>
+        <v>-0.1749605068057416</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2116056571777831</v>
+        <v>0.2117999657919614</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1652666672.513288</v>
+        <v>1656033644.175008</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>109.165</v>
+        <v>109.595</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.03188189134554265</v>
+        <v>-0.02806848240750015</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1923276117194436</v>
+        <v>-0.1891461970997337</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,37 +2858,37 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>868743803200</v>
+        <v>872165777600</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>39.40974729241878</v>
+        <v>39.56498194945848</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>35.2136357103365</v>
+        <v>35.35234191979416</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.180615083713851</v>
+        <v>1.185265516416612</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.838722388485108</v>
+        <v>8.873538040269549</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.52999343616673</v>
+        <v>9.56753199868724</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.7318285487523</v>
+        <v>21.81031518009291</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.265179662970211</v>
+        <v>1.269748983474668</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01555003897609384</v>
+        <v>0.01549008787339144</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1191615548192475</v>
+        <v>0.1191615548192473</v>
       </c>
       <c r="V19" s="4" t="n">
         <v>0.05082221401082943</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.008954335180689782</v>
+        <v>0.008919202518363064</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05815779045644878</v>
+        <v>-0.05847599473739676</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3117912557655074</v>
+        <v>0.3133766429631844</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2730355064.764832</v>
+        <v>2737947162.130979</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.19</v>
+        <v>146.41</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03103185642295614</v>
+        <v>0.03258344687656467</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1259192825112108</v>
+        <v>-0.1246038863976084</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,37 +2984,37 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>347524174500</v>
+        <v>348047160466</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.65777777777778</v>
+        <v>21.69037037037037</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.69951704521253</v>
+        <v>20.73066755995326</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>3.993062028908907</v>
+        <v>3.999071151599412</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.520691480547218</v>
+        <v>6.530504409788072</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.66770793650816</v>
+        <v>20.6988105820108</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.53120233838336</v>
+        <v>17.55580881085913</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.28127785756963</v>
+        <v>4.287286980260134</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04578962031316184</v>
+        <v>0.04572081547424234</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04629386910197875</v>
+        <v>0.04629386910197852</v>
       </c>
       <c r="V20" s="4" t="n">
         <v>0.02527505890851667</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02934947670839319</v>
+        <v>0.02930537531589373</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04614514794490439</v>
+        <v>-0.04627493880228782</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.160865359695334</v>
+        <v>0.1612660247933156</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1271783359.64692</v>
+        <v>1275869520.073792</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>310.20001</v>
+        <v>312.215</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1030015515869899</v>
+        <v>-0.0971748499580386</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2731106971294669</v>
+        <v>-0.2683889865260692</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,31 +3110,31 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>309305705572</v>
+        <v>311314884155</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.66201187150838</v>
+        <v>21.80272346368715</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.67141513891231</v>
+        <v>20.80569203590775</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.828307239632099</v>
+        <v>1.840183502122051</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.55562435698381</v>
+        <v>18.6761575494975</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.430573839645349</v>
+        <v>-7.478841188125275</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.46258438519757</v>
+        <v>15.54659770666945</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.1858165790183</v>
+        <v>2.197692841508252</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04882224843564936</v>
+        <v>0.04850715712160229</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.02994841940849711</v>
+        <v>0.02975513668465641</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7080513697226719</v>
+        <v>0.7070527397636943</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2497970071062758</v>
+        <v>0.2514108575436683</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1199809742.470005</v>
+        <v>1204074926.913289</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>494.125</v>
+        <v>497.3313</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.211146898021417</v>
+        <v>1.225494685118055</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1549518581225523</v>
+        <v>-0.1494684726283926</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,37 +3236,37 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>805720225000</v>
+        <v>810948417780</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>125.4124365482233</v>
+        <v>126.2262182741117</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>36.60731156027715</v>
+        <v>36.84485069117665</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>19.50660271153613</v>
+        <v>19.63317801186297</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11.98854389801262</v>
+        <v>12.06633568814709</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.012504074884739</v>
+        <v>1.019074055790993</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>75.09892004105244</v>
+        <v>75.56587288486658</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>19.48699249485534</v>
+        <v>19.60815943784046</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.01042917844094084</v>
+        <v>0.01036479661397947</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.42588491759961</v>
+        <v>2.425884917599611</v>
       </c>
       <c r="V22" s="4" t="n">
         <v>0.8908862032600786</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.54426273472138</v>
+        <v>2.543095872510537</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6751876786133827</v>
+        <v>0.6729124485188845</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>10128306494.24566</v>
+        <v>10186009492.09697</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1596.773</v>
+        <v>1591</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3720573989955196</v>
+        <v>0.3670968395644665</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2015975319506391</v>
+        <v>-0.2044840896817937</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,40 +3362,40 @@
         <v>833.92</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>615425041743</v>
+        <v>613200023681</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>50.35558962264151</v>
+        <v>50.35558780841799</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>32.88202121349596</v>
+        <v>32.76313900014095</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.14070077783596</v>
+        <v>15.14070024513481</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>24.50622390746561</v>
+        <v>24.50622302454937</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.427889004623443</v>
+        <v>3.427888881122619</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>38.40744733449237</v>
+        <v>38.40744597124126</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>15.00801377762366</v>
+        <v>15.00801324492251</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01869922581994628</v>
+        <v>0.01869922647784843</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5314018957561457</v>
+        <v>0.5369585865445112</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2852182160662287</v>
+        <v>0.289881630621726</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004872326874264533</v>
+        <v>0.004890006285355123</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.694667569641459</v>
+        <v>1.694300974840055</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.424706163478566</v>
+        <v>0.4280493768934253</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2020619636.414062</v>
+        <v>2030300670.746045</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>210.64999</v>
+        <v>209.36</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07516360342155404</v>
+        <v>-0.08082716743701979</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1718105366620798</v>
+        <v>-0.1768822488696677</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,31 +3490,31 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>166491435676</v>
+        <v>165471863200</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>78.89512734082395</v>
+        <v>78.41198501872657</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>83.76298271958655</v>
+        <v>83.25003035686183</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.771279702920368</v>
+        <v>1.760432610245226</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.31697936950037</v>
+        <v>27.14969414809181</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4222525346531628</v>
+        <v>0.4196667213465624</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.51689721956835</v>
+        <v>29.37019614388489</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.182482426469493</v>
+        <v>2.171635333794351</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001261326140575</v>
+        <v>-0.001269097935678529</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
@@ -3523,7 +3523,7 @@
         <v>-0.05811463752501189</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1529483038203574</v>
+        <v>0.1529483038203576</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.242856591853039</v>
+        <v>1.244306259148119</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3372040913177615</v>
+        <v>0.3373287532882038</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1127510266.767813</v>
+        <v>1130451489.107964</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>993.79</v>
+        <v>987</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.08689324628800277</v>
+        <v>0.07946712493208685</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1388226934375515</v>
+        <v>-0.1447066265738871</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>293175006530</v>
+        <v>291171909000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15.14000609384522</v>
+        <v>15.03656307129799</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.72281831984176</v>
+        <v>13.62905813268781</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.485861150699102</v>
+        <v>2.468876679922331</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.429782625344218</v>
+        <v>2.413181307132033</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3548607643289953</v>
+        <v>0.3524362032146815</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>27.00547913643169</v>
+        <v>26.941671996942</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.188439645997439</v>
+        <v>7.171455175220668</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1416048403694735</v>
+        <v>-0.1425790013280436</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3649,7 +3649,7 @@
         <v>0.1032723556468242</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3823282959808237</v>
+        <v>-0.3823282959808239</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01811247849143179</v>
+        <v>0.0182370820668693</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.56460922709919</v>
+        <v>1.56529265689344</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3262811020805543</v>
+        <v>0.3307767954110263</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1804383991.244456</v>
+        <v>1820128846.091496</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>249.94</v>
+        <v>249.82001</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1425728987993139</v>
+        <v>-0.1429845283018868</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2482103110148589</v>
+        <v>-0.2485712266137279</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,37 +3742,37 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>235476971960</v>
+        <v>235363922780</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>21.82882096069869</v>
+        <v>21.81834148471616</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>19.37561604161878</v>
+        <v>19.3663142885227</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.407918896044691</v>
+        <v>3.406282802147706</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.81872187391153</v>
+        <v>6.815448374521074</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2660916353542535</v>
+        <v>0.2659638913543889</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>18.09857419148018</v>
+        <v>18.09160488132667</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.248765821381537</v>
+        <v>4.247129727484551</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.05788676441072748</v>
+        <v>0.0579145683798838</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1266130023329546</v>
+        <v>0.1266130023329548</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>0.04589294922825382</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02696647195326879</v>
+        <v>0.02697942410617949</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9001586591133746</v>
+        <v>0.9009800724990913</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3284580294484706</v>
+        <v>0.3283223522132666</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1200885175.557023</v>
+        <v>1205844276.762203</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1145.4698</v>
+        <v>1141.97</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06026677730687147</v>
+        <v>0.05702730153263569</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1138592813213167</v>
+        <v>-0.1165667427377868</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,40 +3868,40 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1078735874922</v>
+        <v>1075439969770</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.37419765494138</v>
+        <v>38.24051591289783</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.27326956641244</v>
+        <v>26.19299578806531</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.5407649822383</v>
+        <v>13.49359388388744</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.1725921520706</v>
+        <v>30.06748181941615</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4067823850792955</v>
+        <v>0.4053653032588752</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>31.94597463423085</v>
+        <v>31.83923970787889</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.11840306533042</v>
+        <v>14.07123196697956</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01859018548117725</v>
+        <v>0.01865517331727483</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470491333778837</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4605794515958792</v>
+        <v>0.4599519742725229</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.227779731796429</v>
+        <v>0.2272522672072184</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877209505000597</v>
@@ -3937,16 +3937,16 @@
         <v>33.16107129385138</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005840398411202111</v>
+        <v>0.005858297503437043</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3418951356085352</v>
+        <v>0.3432028134288552</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.328599026128182</v>
+        <v>0.3269722251953026</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>3123879242.694877</v>
+        <v>3130451230.05225</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>208.45</v>
+        <v>207.02</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1459593567585533</v>
+        <v>0.1380978941528219</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.102475780409042</v>
+        <v>-0.1086329386437028</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,40 +3994,40 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>328784011187</v>
+        <v>326528505600</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.75361655948553</v>
+        <v>16.64147909967846</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.48176079312228</v>
+        <v>15.37555346314308</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.598051044503632</v>
+        <v>2.580661394620996</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.965303796426275</v>
+        <v>2.945456043906283</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4262387346900449</v>
+        <v>0.4233857788037853</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.61981806010836</v>
+        <v>23.54484293454186</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.478355164507741</v>
+        <v>5.460965514625106</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04771106143087023</v>
+        <v>-0.04803255988686336</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08215188074267821</v>
+        <v>0.08233366295203259</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3275002082938857</v>
+        <v>-0.3273872607776852</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.01990885104341569</v>
+        <v>0.02004637233117573</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.373229260772864</v>
+        <v>1.374004116147848</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2779897535596553</v>
+        <v>0.2823070448686831</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>868968590.9007822</v>
+        <v>879160524.1304927</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>926.12</v>
+        <v>929.3766000000001</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.936148502232509</v>
+        <v>1.946473148296054</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2620557768924303</v>
+        <v>-0.2594608764940238</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1045950666800</v>
+        <v>1049628638274</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.66621066726177</v>
+        <v>20.74038384289221</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.951641913357892</v>
+        <v>5.972570213205689</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.58556045739637</v>
+        <v>11.62714223667944</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.37079217664112</v>
+        <v>10.40801402644851</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02945540990055924</v>
+        <v>0.02956112842472399</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.0316661487139</v>
+        <v>15.08389378506423</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.38040027693467</v>
+        <v>11.41994156273124</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02502167228932509</v>
+        <v>0.02493657227170147</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.472354514621996</v>
+        <v>2.472606114706539</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.764909716313137</v>
+        <v>1.765110056317433</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005722800501014988</v>
+        <v>0.000570274741154447</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.883347275231924</v>
+        <v>2.882371066500194</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8248513252611771</v>
+        <v>0.8234392765072377</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>26663728391.69365</v>
+        <v>26747478497.66545</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>142.41</v>
+        <v>142.485</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.03418105834218044</v>
+        <v>-0.03367241133267018</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2686646878177542</v>
+        <v>-0.2682795312387662</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>147232287420</v>
+        <v>147309827701</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>88.45341614906833</v>
+        <v>88.50000000000001</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>30.06241544274229</v>
+        <v>30.07824776602159</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.994046118653271</v>
+        <v>9.999309509978278</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.75371764141898</v>
+        <v>11.75990771812081</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>141.5254658385124</v>
+        <v>141.600000000003</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>43.90138793063915</v>
+        <v>43.92657715706506</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.39722661485202</v>
+        <v>10.40319221429541</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03110949307241409</v>
+        <v>0.03109093311341175</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7207905166666362</v>
+        <v>0.7225149791766128</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6285644861216921</v>
+        <v>0.6289425536683032</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2225653407.549097</v>
+        <v>2235225200.689582</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.7899</v>
+        <v>27.745</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1036497086256092</v>
+        <v>0.1018665474081419</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.04861691201643281</v>
+        <v>-0.05015405682985274</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>158386867656</v>
+        <v>158130962800</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.72026955602537</v>
+        <v>36.66094080338267</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.51772209731608</v>
+        <v>9.502344362161599</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.486606186510927</v>
+        <v>2.482588589550364</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.859075479516375</v>
+        <v>1.856071780725437</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6141708801848491</v>
+        <v>-0.6131785674194091</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.47282480988593</v>
+        <v>17.454765747782</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.46296377166541</v>
+        <v>3.459384620698317</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06937404337418766</v>
+        <v>0.06947406001628417</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06189298989920799</v>
+        <v>0.06199315191926473</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3493970084106297</v>
+        <v>0.3498045768491713</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2087004289670491</v>
+        <v>0.2087462236358475</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>974752994.2939217</v>
+        <v>977640917.3520991</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>176.64</v>
+        <v>176.71</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.05136602449453043</v>
+        <v>0.0517826663747083</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1162255466052935</v>
+        <v>-0.1158753189573223</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1253887679462</v>
+        <v>1254384577886</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.414675307130095</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.00366847881386825</v>
+        <v>0.003669932581514144</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.3679221533799</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2020.185260522643</v>
+        <v>2019.384609918622</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2609.025817305346</v>
+        <v>2607.991909731798</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.698369565217391</v>
+        <v>1.697696791353064</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9828267271293428</v>
+        <v>0.9825162353130277</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3297475706.806618</v>
+        <v>3307365433.320012</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>544.33</v>
+        <v>545.8599</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4581570259838426</v>
+        <v>0.4622553384671757</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1897801527172053</v>
+        <v>-0.1875029397317773</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>68607760359</v>
+        <v>68800590099</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.825324155626536</v>
+        <v>1.824524341866709</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.41033915708003</v>
+        <v>0.4087014210065971</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3816249805.74646</v>
+        <v>3834349727.93254</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>152.04</v>
+        <v>150.26</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.0553587891716919</v>
+        <v>-0.06641812457865315</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3261833008331856</v>
+        <v>-0.3340719730544229</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1988054581802</v>
+        <v>1964779541315</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-98.74025974025975</v>
+        <v>-97.57142857142857</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>137.802885451069</v>
+        <v>136.1895656924338</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>119.9587390112217</v>
+        <v>118.5387355242836</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.008739231591524</v>
+        <v>6.925773753379865</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9874025974025975</v>
+        <v>-0.9757142857142856</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>464.1608109217663</v>
+        <v>458.5124889164867</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>116.6912880308296</v>
+        <v>115.2712845438914</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01429501074437222</v>
+        <v>-0.01446625405157511</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.195423725844542</v>
+        <v>4.194740387198083</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.441642708883008</v>
+        <v>3.454987193948335</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7835565208528544</v>
+        <v>0.7838497221487578</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14192963950.06558</v>
+        <v>14229382840.13767</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>762.13</v>
+        <v>762.39</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1155788735820786</v>
+        <v>0.1159594523640861</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02212043060420599</v>
+        <v>-0.02178682782247199</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>811850009181</v>
+        <v>812126971120</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9952897736453762</v>
+        <v>0.9952948421645585</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1151115487778224</v>
+        <v>0.1150564439179</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29891923999.91215</v>
+        <v>30011516018.29659</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>420.435</v>
+        <v>422.765</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3154626553282829</v>
+        <v>0.3227527905142566</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1222651356993737</v>
+        <v>-0.117400835073069</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2180577718800</v>
+        <v>2192662217200</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>27.58780572620842</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6422159848404414</v>
+        <v>0.6457750682770683</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>13.89916072363153</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>41.95720813156435</v>
+        <v>41.72045652027547</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>41.93251569219548</v>
+        <v>41.69590016923872</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2616337840569886</v>
+        <v>0.2601918323418448</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.179047823951394</v>
+        <v>2.177614023658504</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3630682379655741</v>
+        <v>0.3604812217091501</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4086501824.133639</v>
+        <v>4103736969.691386</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.1228</v>
+        <v>28.11</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01358120749818814</v>
+        <v>-0.0140301727699258</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06257333333333326</v>
+        <v>-0.06300000000000006</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70507704043</v>
+        <v>70475612693</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.14393700787402</v>
+        <v>-22.13385826771653</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-81.65117073184392</v>
+        <v>-81.61400746981568</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.952310786183026</v>
+        <v>1.95142219833864</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.150446153846154</v>
+        <v>2.149467385346245</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.164792089360923</v>
+        <v>0.1647170847830068</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.3903643046281</v>
+        <v>16.3850599492562</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.745720726650976</v>
+        <v>2.74483213880659</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03091860711661381</v>
+        <v>0.03093268602709897</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2531405301144675</v>
+        <v>0.2531697245623366</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1891923299751187</v>
+        <v>0.1892040675167847</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>503867970.4693958</v>
+        <v>505844800.622419</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>327.07</v>
+        <v>326.14</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1225015685361674</v>
+        <v>-0.1249966721569867</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.155926604557537</v>
+        <v>-0.1583266664946192</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>220873641700</v>
+        <v>220245603400</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.83444511825349</v>
+        <v>19.77804730139479</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.83829513817301</v>
+        <v>16.79041665809687</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.627164984001998</v>
+        <v>2.619694829493417</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.46888739789965</v>
+        <v>6.450493582263711</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.229908823926638</v>
+        <v>1.226411666724046</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.491977095130238</v>
+        <v>9.466575125384242</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.791379416697394</v>
+        <v>2.783909262188812</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.06814756113110258</v>
+        <v>0.06834188636521041</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01082337114379185</v>
+        <v>0.01085423437787453</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.96112052940579</v>
+        <v>0.9619834805269214</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2216990654609904</v>
+        <v>0.2210563126348071</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>765001632.2843527</v>
+        <v>769196088.4264648</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>143.56</v>
+        <v>143.7</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.266465714193714</v>
+        <v>-0.2657503700866308</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.564309559939302</v>
+        <v>-0.5638846737481031</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>413520273200</v>
+        <v>413923539000</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.15432098765432</v>
+        <v>22.17592592592592</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.02329270350585</v>
+        <v>16.03891865069512</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.761180784931106</v>
+        <v>5.766799099990248</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.376908883963337</v>
+        <v>6.383127658299886</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4821822803195354</v>
+        <v>0.4826525054466233</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.21287421547978</v>
+        <v>14.22362596315354</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.426923292976859</v>
+        <v>7.432541608036001</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06945245943506501</v>
+        <v>-0.0693847952435486</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.0139314572304263</v>
+        <v>0.0139178844815588</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.074118099546188</v>
+        <v>2.073289074795495</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5850709403993845</v>
+        <v>0.5846173499538706</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4196707225.397536</v>
+        <v>4229605115.99961</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:18 ET</t>
+          <t>2026-09-14 14:50 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>334.685</v>
+        <v>333.08</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2349543852252631</v>
+        <v>0.2290320947482876</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.02868792988362301</v>
+        <v>-0.03334590939431759</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,40 +714,40 @@
         <v>235.03</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4915637742860</v>
+        <v>4892064536480</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.2054794520548</v>
+        <v>38.02283105022831</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.9976389920305</v>
+        <v>34.82980592337726</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.52982459321841</v>
+        <v>10.47948480790364</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.73373251674108</v>
+        <v>45.51509390066965</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.167389649923895</v>
+        <v>1.161808726534753</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.44059035219543</v>
+        <v>29.30111425566516</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.62571318482594</v>
+        <v>10.57537339951116</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02780616659432947</v>
+        <v>0.02793973770802866</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09165876763157565</v>
+        <v>0.0916750766247576</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1170129384289829</v>
+        <v>0.1170296262044463</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003167157177644651</v>
+        <v>0.003182418638165006</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3089494666609979</v>
+        <v>0.3089528812044592</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2980384634196376</v>
+        <v>0.2976224928133763</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13752150765.22068</v>
+        <v>13912657866.93765</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>506.895</v>
+        <v>505.41</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.07179557107309931</v>
+        <v>0.06865563790539486</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.0845644007801778</v>
+        <v>-0.08724626164848659</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,37 +842,37 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3763974167250</v>
+        <v>3752947225500</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>28.16083333333333</v>
+        <v>28.07833333333333</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.71987563340943</v>
+        <v>24.64745626585675</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.34277214929529</v>
+        <v>11.30954235487691</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.512282130804023</v>
+        <v>8.487344542222081</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.894482153905644</v>
+        <v>0.8918616782675931</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.6577974414391</v>
+        <v>18.60466041904597</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.66784937047785</v>
+        <v>11.63461957605947</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01779688090923892</v>
+        <v>0.0178491718574794</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.13919801826484</v>
+        <v>0.1391980182648402</v>
       </c>
       <c r="V3" s="4" t="n">
         <v>0.2248874130489094</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007180974363526963</v>
+        <v>0.007202073564037118</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5596168774681194</v>
+        <v>0.5569011303466421</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4347159227079213</v>
+        <v>0.4340989304501802</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>12426165661.11973</v>
+        <v>12567165071.80573</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>347.6178</v>
+        <v>349.39</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1030233435897834</v>
+        <v>0.1086466976571234</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1492675167029687</v>
+        <v>-0.1449303737059788</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4206909300594</v>
+        <v>4228356662216</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.08625124131082</v>
+        <v>17.16534260178749</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.77049451886755</v>
+        <v>20.87638515618916</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.366427486430899</v>
+        <v>9.409784187807546</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.528489386241569</v>
+        <v>6.558709421059206</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1519490260484302</v>
+        <v>0.1526523901172095</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.05422913942035</v>
+        <v>13.11384500493733</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.493920948592177</v>
+        <v>9.537277649968823</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01275642038752504</v>
+        <v>0.01269764366126457</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1773786981436588</v>
+        <v>-0.1777626982179659</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2894888778523226</v>
+        <v>0.2888869437375823</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002473981481960935</v>
+        <v>0.00246143278285011</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7754560373917703</v>
+        <v>0.770142024141324</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3800493261617421</v>
+        <v>0.3825682892334387</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8560941024.717615</v>
+        <v>8698173074.388248</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>254.9275</v>
+        <v>253.54</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1255077262693156</v>
+        <v>0.1193818984547461</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1123694289693593</v>
+        <v>-0.1172005571030641</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2742280610250</v>
+        <v>2727355134000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.23234126984127</v>
+        <v>20.12222222222222</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.62251885053139</v>
+        <v>22.4993907262407</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.535324631613552</v>
+        <v>3.516082835705446</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.970813585439251</v>
+        <v>4.943758819477176</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2290259950850053</v>
+        <v>0.2277794698251551</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.36745556148301</v>
+        <v>11.30869314991909</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.722281882026094</v>
+        <v>3.703040086117987</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004239172299344014</v>
+        <v>-0.004262371209044022</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1056547945205478</v>
+        <v>-0.105654794520548</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.178146482376863</v>
+        <v>0.1781464823768628</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8309482889059018</v>
+        <v>0.8318374772658809</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.459928867433953</v>
+        <v>0.4606663575162792</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>9381975738.114811</v>
+        <v>9478337928.275068</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>212.3</v>
+        <v>210.96</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.124172587442918</v>
+        <v>0.1170770091707865</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1024773822609283</v>
+        <v>-0.1081423860657816</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,31 +1220,31 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5142118300000</v>
+        <v>5109662160000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>26.70440251572327</v>
+        <v>26.53584905660377</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>15.90374045972344</v>
+        <v>15.8033588666192</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>16.97242391135727</v>
+        <v>16.86529697757857</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.42749275058519</v>
+        <v>22.28593438842888</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2143618705343773</v>
+        <v>0.2130088563727378</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.07643912062893</v>
+        <v>21.93754000350927</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.02661097339992</v>
+        <v>16.91948403962122</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.0246991594884155</v>
+        <v>0.02485604645141549</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
@@ -1253,7 +1253,7 @@
         <v>0.6791271577496334</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9328589725338055</v>
+        <v>0.9328589725338057</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002449364107395195</v>
+        <v>0.002464922260144103</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.326716800431758</v>
+        <v>1.329315524502224</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.414303605228308</v>
+        <v>0.4171953561352091</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>27138865933.25239</v>
+        <v>27437808210.02829</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>665.75</v>
+        <v>665.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.02358516549385681</v>
+        <v>0.02335454172393714</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1581310065756196</v>
+        <v>-0.1583206879109762</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1695989183978</v>
+        <v>1695607060992</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.74144927536232</v>
+        <v>24.73429951690822</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.1379047162463</v>
+        <v>20.1333674489426</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.430940018786584</v>
+        <v>7.428792633416284</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.481523588072935</v>
+        <v>6.479650564081755</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.071997101449271</v>
+        <v>-5.07053140096618</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.74530407023311</v>
+        <v>16.7407264363419</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.85528546759665</v>
+        <v>7.853138082226351</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02415899281162666</v>
+        <v>0.0241659762704853</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.228600970358257</v>
+        <v>0.2285227287304716</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2712460833408099</v>
+        <v>0.2711651259227765</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003154337213668795</v>
+        <v>0.003155048076923077</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7807945486452077</v>
+        <v>0.7765247561934626</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4183843080470762</v>
+        <v>0.4182632984941506</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10054200897.42441</v>
+        <v>10178323576.6413</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>360.89</v>
+        <v>358.97</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1761819025128951</v>
+        <v>-0.1805647636261851</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2765270733516428</v>
+        <v>-0.2803760800272638</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,31 +1472,31 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1425352159021</v>
+        <v>1417769028024</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>305.8389830508474</v>
+        <v>304.2118644067797</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>171.6943997048613</v>
+        <v>170.780954479354</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.75570270916531</v>
+        <v>13.68251988558083</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.44954903405558</v>
+        <v>13.37799500333878</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.141347576987343</v>
+        <v>-8.09803413702554</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>118.0273621540572</v>
+        <v>117.383773530429</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.70050967476042</v>
+        <v>13.62580248819232</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004042061821617203</v>
+        <v>0.00406413166468358</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.546418809196771</v>
+        <v>1.546711064330438</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5744128004122112</v>
+        <v>0.5751696838324828</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12725145634.4739</v>
+        <v>12819667448.53803</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>346.187</v>
+        <v>344.72</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.004122303484597856</v>
+        <v>-0.008342428968189375</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3006323232323233</v>
+        <v>-0.3035959595959595</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,31 +1598,31 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1647012347460</v>
+        <v>1640032977600</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>42.95124069478908</v>
+        <v>42.76923076923077</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.91661895366691</v>
+        <v>18.83645800017926</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.48415724838391</v>
+        <v>18.40582889208116</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.55057921556826</v>
+        <v>16.4804445781924</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.427386107903594</v>
+        <v>0.4255750190403653</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>32.19211196180854</v>
+        <v>32.05856873122477</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.88193961505656</v>
+        <v>18.80361125875381</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02392392507607291</v>
+        <v>0.02402573639565575</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
@@ -1631,7 +1631,7 @@
         <v>1.270555895849621</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8585251496160555</v>
+        <v>0.8585251496160557</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007337075049034193</v>
+        <v>0.007368298909259689</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.600406767478028</v>
+        <v>1.603839698015839</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.4034940372471656</v>
+        <v>0.4063188828354903</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8536323865.787517</v>
+        <v>8718298436.112564</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>919.0325</v>
+        <v>918.91</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07552077238150967</v>
+        <v>0.07537741369221762</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1618490652074783</v>
+        <v>-0.1619607843137255</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>407571614068</v>
+        <v>407517287890</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>46.15934203917629</v>
+        <v>46.15318935208438</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>40.54799627624607</v>
+        <v>40.54259153860747</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.388248165170801</v>
+        <v>1.388063122311274</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>12.17522649131577</v>
+        <v>12.17360362678683</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.641230240322527</v>
+        <v>3.640744892193446</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>27.42623455894955</v>
+        <v>27.42248015825847</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.351754723703706</v>
+        <v>1.351569680844179</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02160601890820294</v>
+        <v>0.02160889920914712</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006028078441186791</v>
+        <v>0.006028882045031614</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1893238290308226</v>
+        <v>-0.1908042222803441</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1875204007098069</v>
+        <v>0.1874983102170152</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1699036251.032926</v>
+        <v>1727701780.661401</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>80.605</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1141334004570258</v>
+        <v>-0.1172656128615882</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3544369694057344</v>
+        <v>-0.3567195258689733</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,37 +1850,37 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>335634383619</v>
+        <v>334447660720</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>24.95510835913313</v>
+        <v>24.86687306501548</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>21.49832110639037</v>
+        <v>21.42230818516562</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.938786073732472</v>
+        <v>6.9142521858865</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>11.19919693409258</v>
+        <v>11.15959925248205</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7334367212867178</v>
+        <v>0.7308434644717966</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>11.14046651571306</v>
+        <v>11.10100051906985</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>7.046927712760543</v>
+        <v>7.021963405829191</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03275566084268607</v>
+        <v>0.03287392704834823</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1607933584969679</v>
+        <v>0.1607933584969676</v>
       </c>
       <c r="V11" s="4" t="n">
         <v>0.1431026964010345</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09879862549608635</v>
+        <v>0.09470983751137689</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3761471406826977</v>
+        <v>0.3738594083527357</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2180220756.826574</v>
+        <v>2207519621.929148</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>515.005</v>
+        <v>514.95</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.0365401905473699</v>
+        <v>0.03642949315515032</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04227879644437837</v>
+        <v>-0.04238107635660349</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1110790385693</v>
+        <v>1110671758745</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.94225480595318</v>
+        <v>12.94483626351116</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.21625300719808</v>
+        <v>23.21377362560879</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.88653513383088</v>
+        <v>2.887110881105938</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.477938534505857</v>
+        <v>1.478233323602297</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3565261611099031</v>
+        <v>0.3565972736916762</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.67260293577646</v>
+        <v>15.67549760200748</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.117270770855267</v>
+        <v>3.117846518130324</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02180721047835266</v>
+        <v>0.02180286168728554</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4425347276349679</v>
+        <v>-0.4423639830264056</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06024522371398233</v>
+        <v>0.06056996350464527</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.0562478551022423</v>
+        <v>0.05495250038840038</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1410786097339412</v>
+        <v>0.1410426740836873</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2082475540.992599</v>
+        <v>2109431408.5975</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>350.345</v>
+        <v>350.13</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07639482663872821</v>
+        <v>0.07573426380001957</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04407912687585258</v>
+        <v>-0.04466575716234655</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>938752930950</v>
+        <v>938176836300</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.06313413585555</v>
+        <v>15.05288048151333</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.98948746659678</v>
+        <v>13.98090238673174</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.154273549757587</v>
+        <v>3.152126398282448</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.608323151618535</v>
+        <v>2.60654763506479</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7886943959068606</v>
+        <v>0.7881575222626153</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.03945791579004</v>
+        <v>20.03259807106054</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.272408971569012</v>
+        <v>6.270261820093874</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.173126594998888</v>
+        <v>-0.1732445246047693</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.0767466765185183</v>
+        <v>0.07667445670738182</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2894319492040938</v>
+        <v>-0.2894796085946888</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01712597582383079</v>
+        <v>0.01713649216005484</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7705390330702621</v>
+        <v>0.7722642455725528</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1713201326773638</v>
+        <v>0.1717842435974667</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>1963832099.704082</v>
+        <v>2015473213.400635</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>375.11</v>
+        <v>375.28</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08263099776570249</v>
+        <v>0.08312164656104293</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.02712866664937619</v>
+        <v>-0.02668776097725456</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>700348079318</v>
+        <v>700665477344</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.87128292268479</v>
+        <v>31.88445199660153</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>25.10163455802036</v>
+        <v>25.11301062870593</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.74303374001978</v>
+        <v>15.74953869232153</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.40432390627665</v>
+        <v>20.41275488316561</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.1492148023521</v>
+        <v>2.150102848455038</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.46474276671936</v>
+        <v>24.47468820345041</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>16.0015079353084</v>
+        <v>16.00801288761014</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03000245218141613</v>
+        <v>0.02999006042035009</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2696895434843873</v>
+        <v>0.2696387728262009</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1375695486202875</v>
+        <v>0.1375240610011503</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007144570925861748</v>
+        <v>0.007141334470262205</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3075508365478325</v>
+        <v>0.3051853919994814</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1918794107986126</v>
+        <v>0.1922583442671653</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2233883290.69644</v>
+        <v>2277087061.263021</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>573.13</v>
+        <v>574.42</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01775788011734258</v>
+        <v>0.02004864777101845</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.04735547355473557</v>
+        <v>-0.04521126292344013</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>502655642680</v>
+        <v>503787019120</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.47336628226249</v>
+        <v>31.54420647995606</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.86294490040217</v>
+        <v>25.9211571714777</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.3276128803124</v>
+        <v>14.35986144628452</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>90.09101051505971</v>
+        <v>90.293787203707</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.391010384796422</v>
+        <v>1.394141268533772</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.32235277807922</v>
+        <v>23.3830267281606</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.70219633554713</v>
+        <v>14.74044463472337</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03273591130842226</v>
+        <v>0.03264871736618159</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005879992322858688</v>
+        <v>0.005866787368127851</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2958611623346437</v>
+        <v>0.2935817535320609</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.2083591042955565</v>
+        <v>0.2089175877623677</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1531829315.77463</v>
+        <v>1558005584.737655</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>384.95001</v>
+        <v>383.55</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1443222859226783</v>
+        <v>0.1401605438733284</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1660889692820935</v>
+        <v>-0.1691217884840345</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,37 +2480,37 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>349590199406</v>
+        <v>348318786154</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.75403575332777</v>
+        <v>24.6640087454183</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.77857181892202</v>
+        <v>17.71391360958151</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7766444717092211</v>
+        <v>0.7738199186322142</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.542652942293518</v>
+        <v>3.529768803010757</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7500537465205449</v>
+        <v>-0.747325904675142</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.30618326305166</v>
+        <v>15.25683290587276</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8760448658184653</v>
+        <v>0.8732203127414585</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06755624167991096</v>
+        <v>0.0678028315979442</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3923523219666978</v>
+        <v>0.3923523219666976</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>0.01038134275007363</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02353552348264649</v>
+        <v>0.02362143136488072</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4258615135957727</v>
+        <v>0.4244573418377957</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.229015907648654</v>
+        <v>0.2274900484914662</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1767154420.27863</v>
+        <v>1786599094.704653</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>165.00999</v>
+        <v>165.07</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3453729143670921</v>
+        <v>0.345862192795575</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.0646222436369821</v>
+        <v>-0.0642820701774276</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,31 +2606,31 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>683877321834</v>
+        <v>684126012200</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.23680694980695</v>
+        <v>21.24453024453024</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.92781117071753</v>
+        <v>14.93324004171107</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.894082207483521</v>
+        <v>1.894770985985709</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.655282256810432</v>
+        <v>2.656247916454622</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.079437347168598</v>
+        <v>2.080193586443587</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.963902844886878</v>
+        <v>9.96736529342151</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.982100819348585</v>
+        <v>1.982789597850773</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04467614150161312</v>
+        <v>0.04465990103453049</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02496818525957126</v>
+        <v>0.02495910825710305</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5450069137685297</v>
+        <v>-0.5434105106913146</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2311005986641769</v>
+        <v>0.2310004784818244</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2211214617.743942</v>
+        <v>2246422120.522645</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>267.94</v>
+        <v>266.32</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2922111990015372</v>
+        <v>0.2843983224531217</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.04671434162308319</v>
+        <v>-0.0524780303838901</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>645708181583</v>
+        <v>641804146149</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.9757225433526</v>
+        <v>30.78843930635838</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.55816541297695</v>
+        <v>21.42782194813772</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.593636017757763</v>
+        <v>6.553770038997641</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.694394487531039</v>
+        <v>7.647873180261501</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.835283541223006</v>
+        <v>-3.812094919379379</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.99057813301909</v>
+        <v>19.87484128272856</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.885827299196356</v>
+        <v>6.845961320436235</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02897284026065148</v>
+        <v>0.02914907937608865</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01970590430693439</v>
+        <v>0.01982577350555723</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1749605068057416</v>
+        <v>-0.1737476460406477</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2117999657919614</v>
+        <v>0.2111034178170654</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1656033644.175008</v>
+        <v>1680843383.236509</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>109.595</v>
+        <v>109.08</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.02806848240750015</v>
+        <v>-0.03263570474027211</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1891461970997337</v>
+        <v>-0.1929564960047351</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>872165777600</v>
+        <v>868067366400</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>39.56498194945848</v>
+        <v>39.37906137184116</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>35.35234191979416</v>
+        <v>35.18621704102511</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.185265516416612</v>
+        <v>1.179695812133072</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.873538040269549</v>
+        <v>8.831840224760276</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.56753199868724</v>
+        <v>9.522573022645233</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.81031518009291</v>
+        <v>21.7160383388968</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.269748983474668</v>
+        <v>1.264260391389433</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01549008787339144</v>
+        <v>0.01556215625985776</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1191615548192473</v>
+        <v>0.1191615548192475</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05082221401082943</v>
+        <v>0.0508222140108292</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.008919202518363064</v>
+        <v>0.008961312797946461</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05847599473739676</v>
+        <v>-0.06001157526822717</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3133766429631844</v>
+        <v>0.3114822793533726</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2737947162.130979</v>
+        <v>2780804758.730911</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.41</v>
+        <v>146.13</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03258344687656467</v>
+        <v>0.03060869539015365</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1246038863976084</v>
+        <v>-0.1262780269058297</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,37 +2984,37 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>348047160466</v>
+        <v>347381541964</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.69037037037037</v>
+        <v>21.64888888888889</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.73066755995326</v>
+        <v>20.69102145028324</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>3.999071151599412</v>
+        <v>3.991423177268131</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.530504409788072</v>
+        <v>6.518015227117894</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.6988105820108</v>
+        <v>20.65922539682562</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.55580881085913</v>
+        <v>17.52449148226216</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.287286980260134</v>
+        <v>4.279639005928854</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04572081547424234</v>
+        <v>0.04580842122477855</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04629386910197852</v>
+        <v>0.04629386910197875</v>
       </c>
       <c r="V20" s="4" t="n">
         <v>0.02527505890851667</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02930537531589373</v>
+        <v>0.02936152740710327</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04627493880228782</v>
+        <v>-0.04674076747521385</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1612660247933156</v>
+        <v>0.160764734967262</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1275869520.073792</v>
+        <v>1296332418.248112</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>312.215</v>
+        <v>310.87</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.0971748499580386</v>
+        <v>-0.101064156451341</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2683889865260692</v>
+        <v>-0.2715407147041593</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,31 +3110,31 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>311314884155</v>
+        <v>309973761790</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.80272346368715</v>
+        <v>21.70879888268156</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.80569203590775</v>
+        <v>20.7160625953354</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.840183502122051</v>
+        <v>1.832256122558755</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.6761575494975</v>
+        <v>18.59570199193597</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.478841188125275</v>
+        <v>-7.446622872547778</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.54659770666945</v>
+        <v>15.4905189960276</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.197692841508252</v>
+        <v>2.189765461944957</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04850715712160229</v>
+        <v>0.04871702660507948</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.02975513668465641</v>
+        <v>0.0298838742882877</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7070527397636943</v>
+        <v>0.7058868672376516</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2514108575436683</v>
+        <v>0.2502242802873501</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1204074926.913289</v>
+        <v>1226694079.953125</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>497.3313</v>
+        <v>493.41</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.225494685118055</v>
+        <v>1.207947363425748</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1494684726283926</v>
+        <v>-0.1561746447078138</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,31 +3236,31 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>810948417780</v>
+        <v>804554346000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>126.2262182741117</v>
+        <v>125.2309644670051</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>36.84485069117665</v>
+        <v>36.55434069710366</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>19.63317801186297</v>
+        <v>19.47837661300085</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.06633568814709</v>
+        <v>11.97119644769725</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.019074055790993</v>
+        <v>1.01103897918316</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>75.56587288486658</v>
+        <v>74.9901423773092</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>19.60815943784046</v>
+        <v>19.45876639632006</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.01036479661397947</v>
+        <v>0.01044429135430958</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.543095872510537</v>
+        <v>2.545669055146133</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6729124485188845</v>
+        <v>0.6757380094899845</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>10186009492.09697</v>
+        <v>10291128789.90689</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1591</v>
+        <v>1575.15</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3670968395644665</v>
+        <v>0.3534774273035635</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2044840896817937</v>
+        <v>-0.2124092481849637</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>833.92</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>613200023681</v>
+        <v>607091148524</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>50.35558780841799</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>32.76313900014095</v>
+        <v>32.43674317792082</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.14070024513481</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5369585865445112</v>
+        <v>0.5524242841585354</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.289881630621726</v>
+        <v>0.3028611080328747</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004890006285355123</v>
+        <v>0.004939212138526489</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.694300974840055</v>
+        <v>1.701372357510302</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4280493768934253</v>
+        <v>0.4376047884782998</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2030300670.746045</v>
+        <v>2066909334.696265</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>209.36</v>
+        <v>210.27</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.08082716743701979</v>
+        <v>-0.07683190913728588</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1768822488696677</v>
+        <v>-0.1733045016709258</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,37 +3490,37 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>165471863200</v>
+        <v>166191099900</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>78.41198501872657</v>
+        <v>78.75280898876402</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>83.25003035686183</v>
+        <v>83.61188327826393</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.760432610245226</v>
+        <v>1.768084471514442</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.14969414809181</v>
+        <v>27.26770246713443</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4196667213465624</v>
+        <v>0.4214908363466836</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.37019614388489</v>
+        <v>29.47368343884892</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.171635333794351</v>
+        <v>2.179287195063567</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001269097935678529</v>
+        <v>-0.001263605572899876</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.05811463752501189</v>
+        <v>-0.058114637525012</v>
       </c>
       <c r="V24" s="4" t="n">
         <v>0.1529483038203576</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.244306259148119</v>
+        <v>1.242098762420381</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3373287532882038</v>
+        <v>0.3371627648070844</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1130451489.107964</v>
+        <v>1139446719.053749</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>987</v>
+        <v>988.45</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.07946712493208685</v>
+        <v>0.08105296822606012</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1447066265738871</v>
+        <v>-0.1434501165521365</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>291171909000</v>
+        <v>291599669150</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15.03656307129799</v>
+        <v>15.05865326020719</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.62905813268781</v>
+        <v>13.64908055851598</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.468876679922331</v>
+        <v>2.472503702400434</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.413181307132033</v>
+        <v>2.416726507633899</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3524362032146815</v>
+        <v>0.3529539666337912</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.941671996942</v>
+        <v>26.95529796929252</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.171455175220668</v>
+        <v>7.175082197698771</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1425790013280436</v>
+        <v>-0.1423698460324539</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.0182370820668693</v>
+        <v>0.0182103293034549</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.56529265689344</v>
+        <v>1.568896240889311</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3307767954110263</v>
+        <v>0.3297536656376204</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1820128846.091496</v>
+        <v>1844065424.760997</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>249.82001</v>
+        <v>249.09</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1429845283018868</v>
+        <v>-0.1454888507718697</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2485712266137279</v>
+        <v>-0.2507670095650604</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,37 +3742,37 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>235363922780</v>
+        <v>234676158060</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>21.81834148471616</v>
+        <v>21.75458515283843</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>19.3663142885227</v>
+        <v>19.30972313277915</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.406282802147706</v>
+        <v>3.396329190268753</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.815448374521074</v>
+        <v>6.795532654127483</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2659638913543889</v>
+        <v>0.2651867066111507</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>18.09160488132667</v>
+        <v>18.04920523149005</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.247129727484551</v>
+        <v>4.237176115605598</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.0579145683798838</v>
+        <v>0.05808429843356708</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1266130023329548</v>
+        <v>0.1266130023329546</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>0.04589294922825382</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02697942410617949</v>
+        <v>0.02705849291420772</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9009800724990913</v>
+        <v>0.8971252793196376</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3283223522132666</v>
+        <v>0.3271665812957038</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1205844276.762203</v>
+        <v>1220828464.444655</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1141.97</v>
+        <v>1137.75</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05702730153263569</v>
+        <v>0.05312119610739008</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1165667427377868</v>
+        <v>-0.119831354194871</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,40 +3868,40 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1075439969770</v>
+        <v>1071465822750</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.24051591289783</v>
+        <v>38.11557788944724</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.19299578806531</v>
+        <v>26.09620301572835</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.49359388388744</v>
+        <v>13.44950810448147</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.06748181941615</v>
+        <v>29.96924643584521</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4053653032588752</v>
+        <v>0.4040409084761278</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>31.83923970787889</v>
+        <v>31.73948599039991</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.07123196697956</v>
+        <v>14.02714618757359</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01865517331727483</v>
+        <v>0.0187163226061006</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470491333778837</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4599519742725229</v>
+        <v>0.460579451595879</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2272522672072184</v>
+        <v>0.227779731796429</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877209505000597</v>
@@ -3937,16 +3937,16 @@
         <v>33.16107129385138</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005858297503437043</v>
+        <v>0.005880026367831246</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3432028134288552</v>
+        <v>0.3407250759735089</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3269722251953026</v>
+        <v>0.325820700942637</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>3130451230.05225</v>
+        <v>3162895450.557251</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>207.02</v>
+        <v>206.6</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1380978941528219</v>
+        <v>0.1357889331077817</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1086329386437028</v>
+        <v>-0.1104413347685683</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,37 +3994,37 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>326528505600</v>
+        <v>325866048000</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.64147909967846</v>
+        <v>16.60771704180064</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.37555346314308</v>
+        <v>15.34435970189044</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.580661394620996</v>
+        <v>2.57542577590908</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.945456043906283</v>
+        <v>2.939480333644276</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4233857788037853</v>
+        <v>0.4225268181859822</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.54484293454186</v>
+        <v>23.52226966981293</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.460965514625106</v>
+        <v>5.455729895913191</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04803255988686336</v>
+        <v>-0.04813020594278052</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08233366295203259</v>
+        <v>0.08233366295203282</v>
       </c>
       <c r="V28" s="4" t="n">
         <v>-0.3273872607776852</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02004637233117573</v>
+        <v>0.02008712487899323</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.374004116147848</v>
+        <v>1.378066152786705</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2823070448686831</v>
+        <v>0.2838600492330827</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>879160524.1304927</v>
+        <v>901055652.0337336</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>929.3766000000001</v>
+        <v>924.03</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.946473148296054</v>
+        <v>1.929522416660805</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2594608764940238</v>
+        <v>-0.2637211155378486</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1049628638274</v>
+        <v>1043590241700</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.74038384289221</v>
+        <v>20.62106672617719</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.972570213205689</v>
+        <v>5.938210682417066</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.62714223667944</v>
+        <v>11.56025258324656</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.40801402644851</v>
+        <v>10.34813788173623</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02956112842472399</v>
+        <v>0.02939106654750906</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.08389378506423</v>
+        <v>14.99679925233371</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.41994156273124</v>
+        <v>11.35400272171389</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02493657227170147</v>
+        <v>0.02507880866858819</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4153,7 +4153,7 @@
         <v>2.472606114706539</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.765110056317433</v>
+        <v>1.765110056317434</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.000570274741154447</v>
+        <v>0.0005735744510459617</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.882371066500194</v>
+        <v>2.885442363676178</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8234392765072377</v>
+        <v>0.8256190424097433</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>26747478497.66545</v>
+        <v>26915220454.49057</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>142.485</v>
+        <v>142.35</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.03367241133267018</v>
+        <v>-0.03458797594978857</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2682795312387662</v>
+        <v>-0.2689728130809446</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>147309827701</v>
+        <v>147170255700</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>88.50000000000001</v>
+        <v>88.41614906832298</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>30.07824776602159</v>
+        <v>30.04974958411884</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.999309509978278</v>
+        <v>9.98983543985881</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.75990771812081</v>
+        <v>11.74876558005753</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>141.600000000003</v>
+        <v>141.4658385093198</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>43.92657715706506</v>
+        <v>43.88657371739753</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.40319221429541</v>
+        <v>10.39371814417594</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03109093311341175</v>
+        <v>0.0311204188524081</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4279,7 +4279,7 @@
         <v>1.94232565302476</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2450681773312406</v>
+        <v>0.2450681773312404</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7225149791766128</v>
+        <v>0.711253205813258</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6289425536683032</v>
+        <v>0.6283435425653637</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2235225200.689582</v>
+        <v>2258920226.575495</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.745</v>
+        <v>27.72</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1018665474081419</v>
+        <v>0.100873695950755</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05015405682985274</v>
+        <v>-0.05100992810681282</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>158130962800</v>
+        <v>157988476800</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.66094080338267</v>
+        <v>36.62790697674419</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.502344362161599</v>
+        <v>9.493782148823916</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.482588589550364</v>
+        <v>2.480351620195931</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.856071780725437</v>
+        <v>1.85439934264585</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6131785674194091</v>
+        <v>-0.6126260547437744</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.454765747782</v>
+        <v>17.44347883396705</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.459384620698317</v>
+        <v>3.457147651343883</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06947406001628417</v>
+        <v>0.06953671699681833</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06199315191926473</v>
+        <v>0.06204906204906205</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3498045768491713</v>
+        <v>0.3496282390178725</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2087462236358475</v>
+        <v>0.2088043753876717</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>977640917.3520991</v>
+        <v>988001149.972362</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>176.71</v>
+        <v>175.63</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.0517826663747083</v>
+        <v>0.04535447736624998</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1158753189573223</v>
+        <v>-0.1212788312403063</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1254384577886</v>
+        <v>1246718145063</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.414675307130095</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003669932581514144</v>
+        <v>0.003647503023548917</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.3679221533799</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2019.384609918622</v>
+        <v>2031.808543066217</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2607.991909731798</v>
+        <v>2624.035360523716</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.697696791353064</v>
+        <v>1.70813642316233</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9825162353130277</v>
+        <v>0.9855001700845949</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3307365433.320012</v>
+        <v>3333796407.208734</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>545.8599</v>
+        <v>541.5</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4622553384671757</v>
+        <v>0.4505759917150454</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1875029397317773</v>
+        <v>-0.1939925278716342</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>68800590099</v>
+        <v>68251065042</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.824524341866709</v>
+        <v>1.828293058381121</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4087014210065971</v>
+        <v>0.4137902024091694</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3834349727.93254</v>
+        <v>3886308062.686564</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>150.26</v>
+        <v>148.15</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.06641812457865315</v>
+        <v>-0.07952778621274759</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3340719730544229</v>
+        <v>-0.3434231519234178</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1964779541315</v>
+        <v>1937189465232</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-97.57142857142857</v>
+        <v>-96.20129870129871</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>136.1895656924338</v>
+        <v>134.2771473268606</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>118.5387355242836</v>
+        <v>116.874175881267</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.925773753379865</v>
+        <v>6.828519776142866</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9757142857142856</v>
+        <v>-0.9620129870129871</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>458.5124889164867</v>
+        <v>451.8914003436525</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>115.2712845438914</v>
+        <v>113.6067249008748</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01446625405157511</v>
+        <v>-0.01467228709949444</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.454987193948335</v>
+        <v>3.461529722776998</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7838497221487578</v>
+        <v>0.7855766027896656</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14229382840.13767</v>
+        <v>14309271538.60899</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>762.39</v>
+        <v>760.88</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1159594523640861</v>
+        <v>0.1137491678993505</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02178682782247199</v>
+        <v>-0.02372429013177313</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>812126971120</v>
+        <v>810518461399</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9952948421645585</v>
+        <v>0.9951782597768953</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1150564439179</v>
+        <v>0.1154451686121067</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>30011516018.29659</v>
+        <v>30486148873.09041</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>422.765</v>
+        <v>418.01</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3227527905142566</v>
+        <v>0.3078752828707778</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.117400835073069</v>
+        <v>-0.1273277661795408</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2192662217200</v>
+        <v>2168000504800</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>27.58780572620842</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6457750682770683</v>
+        <v>0.6385117885598318</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>13.89916072363153</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>41.72045652027547</v>
+        <v>42.20641563788966</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>41.69590016923872</v>
+        <v>42.18157995035575</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2601918323418448</v>
+        <v>0.2631515992440372</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.177614023658504</v>
+        <v>2.182358245656101</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3604812217091501</v>
+        <v>0.3662558302635321</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4103736969.691386</v>
+        <v>4177058875.66307</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.11</v>
+        <v>28.1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.0140301727699258</v>
+        <v>-0.01438092688847081</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06300000000000006</v>
+        <v>-0.06333333333333324</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70475612693</v>
+        <v>70450541326</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.13385826771653</v>
+        <v>-22.1259842519685</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-81.61400746981568</v>
+        <v>-81.58497367135612</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.95142219833864</v>
+        <v>1.950727989090406</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.149467385346245</v>
+        <v>2.148702722455692</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1647170847830068</v>
+        <v>0.1646584874565099</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.3850599492562</v>
+        <v>16.38091592165289</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.74483213880659</v>
+        <v>2.744137929558355</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03093268602709897</v>
+        <v>0.03094369410040947</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2531697245623366</v>
+        <v>0.2528902568169814</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1892040675167847</v>
+        <v>0.1891631311488362</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>505844800.622419</v>
+        <v>513505897.7286453</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>326.14</v>
+        <v>327.78</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1249966721569867</v>
+        <v>-0.1205967044815636</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1583266664946192</v>
+        <v>-0.1540942992077216</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>220245603400</v>
+        <v>221353111800</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.77804730139479</v>
+        <v>19.87750151607035</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.79041665809687</v>
+        <v>16.87484752618812</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.619694829493417</v>
+        <v>2.632868005185969</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.450493582263711</v>
+        <v>6.482929988331389</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.226411666724046</v>
+        <v>1.232578696629692</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.466575125384242</v>
+        <v>9.511369996764278</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.783909262188812</v>
+        <v>2.797082437881365</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.06834188636521041</v>
+        <v>0.06799994758420197</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01085423437787453</v>
+        <v>0.01079992678015742</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9619834805269214</v>
+        <v>0.9585179028789104</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2210563126348071</v>
+        <v>0.2223319342377628</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>769196088.4264648</v>
+        <v>780789981.0595449</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>143.7</v>
+        <v>144.72</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2657503700866308</v>
+        <v>-0.2605385773064524</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5638846737481031</v>
+        <v>-0.5607890743550834</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>413923539000</v>
+        <v>416861618400</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.17592592592592</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.03891865069512</v>
+        <v>16.15276483735976</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.766799099990248</v>
+        <v>5.807732538278279</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.383127658299886</v>
+        <v>6.428435871323309</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4826525054466233</v>
+        <v>0.4860784313725492</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.22362596315354</v>
+        <v>14.30196012477671</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.432541608036001</v>
+        <v>7.473475046324031</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.0693847952435486</v>
+        <v>-0.06889576476297632</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.0139178844815588</v>
+        <v>0.01381978993919292</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.073289074795495</v>
+        <v>2.074229586262845</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5846173499538706</v>
+        <v>0.5811597887336338</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4229605115.99961</v>
+        <v>4282412869.755261</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:50 ET</t>
+          <t>2026-09-14 18:42 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -446,7 +446,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -470,7 +470,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -699,55 +699,55 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>333.08</v>
+        <v>329.64999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2290320947482876</v>
+        <v>0.2163756987614149</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.03334590939431759</v>
+        <v>-0.04330037437966161</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>235.03</v>
+        <v>236.32</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4892064536480</v>
+        <v>4841686815755</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.02283105022831</v>
+        <v>37.63127739726028</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.82980592337726</v>
+        <v>34.4557922898374</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.47948480790364</v>
+        <v>10.37156870110299</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.51509390066965</v>
+        <v>45.04638600097518</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.161808726534753</v>
+        <v>1.149844587138507</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.30111425566516</v>
+        <v>29.00211184166637</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.57537339951116</v>
+        <v>10.46745729271051</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02793973770802866</v>
+        <v>0.02823045050233924</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.0916750766247576</v>
+        <v>0.09216114030149503</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1170296262044463</v>
+        <v>0.117919601370001</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003182418638165006</v>
+        <v>0.003215531721993985</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3089528812044592</v>
+        <v>0.3091698218796033</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2976224928133763</v>
+        <v>0.2956148449247202</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13912657866.93765</v>
+        <v>13293888719.37706</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>505.41</v>
+        <v>501.7073</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.06865563790539486</v>
+        <v>0.06082652643060737</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.08724626164848659</v>
+        <v>-0.09393321534349497</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3752947225500</v>
+        <v>3725452641515</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>28.07833333333333</v>
+        <v>27.87262777777778</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.64745626585675</v>
+        <v>24.45461871090728</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.30954235487691</v>
+        <v>11.22668716309717</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.487344542222081</v>
+        <v>8.425165142058875</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8918616782675931</v>
+        <v>0.8853277825470466</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.60466041904597</v>
+        <v>18.46904471879683</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.63461957605947</v>
+        <v>11.54981087515331</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.0178491718574794</v>
+        <v>0.01798403163448161</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1391980182648402</v>
+        <v>0.1397694687975646</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2248874130489094</v>
+        <v>0.2255150471434921</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007202073564037118</v>
+        <v>0.007255226304261469</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5569011303466421</v>
+        <v>0.5562011142553257</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4340989304501802</v>
+        <v>0.4348274611586234</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>12567165071.80573</v>
+        <v>11582425696.22803</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>349.39</v>
+        <v>343.66</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1086466976571234</v>
+        <v>0.09046487912317769</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1449303737059788</v>
+        <v>-0.1589535253664863</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4228356662216</v>
+        <v>4159011564547</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.16534260178749</v>
+        <v>16.88828699106256</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.87638515618916</v>
+        <v>20.55242197065229</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.409784187807546</v>
+        <v>9.257906444063909</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.558709421059206</v>
+        <v>6.452849183581066</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1526523901172095</v>
+        <v>0.1501885184571042</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.11384500493733</v>
+        <v>12.90501170215935</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.537277649968823</v>
+        <v>9.385399906225187</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01269764366126457</v>
+        <v>0.01290595095857692</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1777626982179659</v>
+        <v>-0.1782823934240892</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2888869437375823</v>
+        <v>0.2899304626314998</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.00246143278285011</v>
+        <v>0.002502473374847233</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.770142024141324</v>
+        <v>0.7724142410527388</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3825682892334387</v>
+        <v>0.3684584056345456</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8698173074.388248</v>
+        <v>8312541467.382883</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>253.54</v>
+        <v>249.49</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1193818984547461</v>
+        <v>0.1015011037527593</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1172005571030641</v>
+        <v>-0.1313022284122562</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2727355134000</v>
+        <v>2683788879000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.12222222222222</v>
+        <v>19.80079365079365</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.4993907262407</v>
+        <v>22.15156853341933</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.516082835705446</v>
+        <v>3.459917593595297</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.943758819477176</v>
+        <v>4.864788151263551</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2277794698251551</v>
+        <v>0.2241409636612682</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.30869314991909</v>
+        <v>11.13717043508388</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.703040086117987</v>
+        <v>3.646874844007839</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004262371209044022</v>
+        <v>-0.004331562773421865</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.105654794520548</v>
+        <v>-0.1061222765818658</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1781464823768628</v>
+        <v>0.1785740462863659</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8318374772658809</v>
+        <v>0.8345785311076686</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4606663575162792</v>
+        <v>0.4596911307758973</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>9478337928.275068</v>
+        <v>8741121385.194023</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>210.96</v>
+        <v>212.27</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1170770091707865</v>
+        <v>0.1240137312129448</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1081423860657816</v>
+        <v>-0.1026042107043206</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5109662160000</v>
+        <v>5141391670000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>26.53584905660377</v>
+        <v>26.7006289308176</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>15.8033588666192</v>
+        <v>15.87557250715581</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>16.86529697757857</v>
+        <v>16.97002554716819</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.28593438842888</v>
+        <v>22.42432353352199</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2130088563727378</v>
+        <v>0.2143315791725495</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>21.93754000350927</v>
+        <v>22.06992952021466</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>16.91948403962122</v>
+        <v>17.02159039769746</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02485604645141549</v>
+        <v>0.02470646785478988</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6791271577496334</v>
+        <v>0.6818687274920301</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9328589725338057</v>
+        <v>0.9361767872730502</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002464922260144103</v>
+        <v>0.00244971027465021</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.329315524502224</v>
+        <v>1.327525487399058</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4171953561352091</v>
+        <v>0.4130089407334011</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>27437808210.02829</v>
+        <v>26835566161.85361</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>665.6</v>
+        <v>668.025</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.02335454172393714</v>
+        <v>0.02708295933763982</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1583206879109762</v>
+        <v>-0.1552541729893778</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1695607060992</v>
+        <v>1701784715924</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.73429951690822</v>
+        <v>24.82441471571907</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.1333674489426</v>
+        <v>20.20271885011575</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.428792633416284</v>
+        <v>7.455858171480145</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.479650564081755</v>
+        <v>6.503258065010088</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.07053140096618</v>
+        <v>-5.089005016722404</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.7407264363419</v>
+        <v>16.79842270550657</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.853138082226351</v>
+        <v>7.880203620290211</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.0241659762704853</v>
+        <v>0.02407825127149041</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2285227287304716</v>
+        <v>0.2287660339131454</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2711651259227765</v>
+        <v>0.271779256228301</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003155048076923077</v>
+        <v>0.003143594925339621</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7765247561934626</v>
+        <v>0.7749251316420632</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4182632984941506</v>
+        <v>0.4138640761944271</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10178323576.6413</v>
+        <v>9868792832.16403</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>358.97</v>
+        <v>360.355</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1805647636261851</v>
+        <v>-0.177403168500192</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2803760800272638</v>
+        <v>-0.2775995830242768</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1417769028024</v>
+        <v>1423239151165</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>304.2118644067797</v>
+        <v>305.3898220338983</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>170.780954479354</v>
+        <v>171.3141249024022</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.68251988558083</v>
+        <v>13.73550064222778</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.37799500333878</v>
+        <v>13.42979676748256</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.09803413702554</v>
+        <v>-8.129391037240389</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>117.383773530429</v>
+        <v>117.8631831741769</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.62580248819232</v>
+        <v>13.68145192695355</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.00406413166468358</v>
+        <v>0.004047669016651527</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7812985372649175</v>
+        <v>0.7826307212430914</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1219390435997418</v>
+        <v>0.1223280851497379</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.546711064330438</v>
+        <v>1.538872399802141</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5751696838324828</v>
+        <v>0.5751269196894302</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12819667448.53803</v>
+        <v>12579569948.95085</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>344.72</v>
+        <v>339.815</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.008342428968189375</v>
+        <v>-0.0224526644808114</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3035959595959595</v>
+        <v>-0.3135050505050505</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1640032977600</v>
+        <v>1616697047700</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>42.76923076923077</v>
+        <v>42.1575682382134</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.83645800017926</v>
+        <v>18.59967808038237</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.40582889208116</v>
+        <v>18.14259862856886</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.4804445781924</v>
+        <v>16.24475012538871</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4255750190403653</v>
+        <v>0.4194886740535094</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>32.05856873122477</v>
+        <v>31.60978336873122</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.80361125875381</v>
+        <v>18.54038099524151</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02402573639565575</v>
+        <v>0.02437432487804365</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.270555895849621</v>
+        <v>1.266575155549506</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8585251496160557</v>
+        <v>0.8524380480254286</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007368298909259689</v>
+        <v>0.00747465532716331</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.603839698015839</v>
+        <v>1.605031466464408</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.4063188828354903</v>
+        <v>0.3888980769216379</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8718298436.112564</v>
+        <v>8604532715.337473</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>918.91</v>
+        <v>907.97</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07537741369221762</v>
+        <v>0.06257460503218248</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1619607843137255</v>
+        <v>-0.171937984496124</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>407517287890</v>
+        <v>402665627630</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>46.15318935208438</v>
+        <v>45.60371672526369</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>40.54259153860747</v>
+        <v>40.05991537725069</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.388063122311274</v>
+        <v>1.371537662192127</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>12.17360362678683</v>
+        <v>12.02867188844788</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.640744892193446</v>
+        <v>3.597400332747367</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>27.42248015825847</v>
+        <v>27.0871891935038</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.351569680844179</v>
+        <v>1.335044220725032</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02160889920914712</v>
+        <v>0.02186926172921724</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006028882045031614</v>
+        <v>0.00610152317807857</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1908042222803441</v>
+        <v>-0.1892386300769955</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1874983102170152</v>
+        <v>0.1726876444671286</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1727701780.661401</v>
+        <v>1679329850.192424</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>80.31999999999999</v>
+        <v>77.82859999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1172656128615882</v>
+        <v>-0.1446466443869447</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3567195258689733</v>
+        <v>-0.3766730738427039</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>334447660720</v>
+        <v>324073620606</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>24.86687306501548</v>
+        <v>24.09554179566564</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>21.42230818516562</v>
+        <v>20.75455762698772</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.9142521858865</v>
+        <v>6.699782964064823</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>11.15959925248205</v>
+        <v>10.8134460455892</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7308434644717966</v>
+        <v>0.7081738503360268</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>11.10100051906985</v>
+        <v>10.76194678079623</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>7.021963405829191</v>
+        <v>6.807494184007513</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03287392704834823</v>
+        <v>0.03392626644353429</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1607933584969676</v>
+        <v>0.1609759277323042</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1431026964010345</v>
+        <v>0.1434269861448505</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09470983751137689</v>
+        <v>0.1001273037800634</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3738594083527357</v>
+        <v>0.3823242582324036</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2207519621.929148</v>
+        <v>2152766013.596189</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>514.95</v>
+        <v>515.41998</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.03642949315515032</v>
+        <v>0.03737541243506692</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04238107635660349</v>
+        <v>-0.04150708520846502</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1110671758745</v>
+        <v>1111685443075</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.94483626351116</v>
+        <v>12.96914202743653</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.21377362560879</v>
+        <v>23.23493301977915</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.887110881105938</v>
+        <v>2.892531840790045</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.478233323602297</v>
+        <v>1.481008916082471</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3565972736916762</v>
+        <v>0.3572668355906716</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.67549760200748</v>
+        <v>15.70275238829495</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.117846518130324</v>
+        <v>3.123267477814431</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02180286168728554</v>
+        <v>0.02176200044851258</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4423639830264056</v>
+        <v>-0.4418257192135512</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06056996350464527</v>
+        <v>0.06163788923813973</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.05495250038840038</v>
+        <v>0.05420570709557663</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1410426740836873</v>
+        <v>0.1394374697778777</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2109431408.5975</v>
+        <v>2052405133.490605</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>350.13</v>
+        <v>343.58499</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07573426380001957</v>
+        <v>0.05562547131176165</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04466575716234655</v>
+        <v>-0.0625239017735334</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>938176836300</v>
+        <v>920639420454</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.05288048151333</v>
+        <v>14.77149613069647</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.98090238673174</v>
+        <v>13.71894780439785</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.152126398282448</v>
+        <v>3.093203520274969</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.60654763506479</v>
+        <v>2.557823291902253</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7881575222626153</v>
+        <v>0.7734244488807034</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.03259807106054</v>
+        <v>19.84434782471018</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.270261820093874</v>
+        <v>6.211338942086395</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1732445246047693</v>
+        <v>-0.1765446844299602</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07667445670738182</v>
+        <v>0.07672223419067215</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2894796085946888</v>
+        <v>-0.2894273564515862</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01713649216005484</v>
+        <v>0.01746292816807859</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7722642455725528</v>
+        <v>0.7774690338025343</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1717842435974667</v>
+        <v>0.1761580139505628</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2015473213.400635</v>
+        <v>1989747020.048416</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>375.28</v>
+        <v>374.875</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08312164656104293</v>
+        <v>0.08195274796037899</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.02668776097725456</v>
+        <v>-0.02773815390201517</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>700665477344</v>
+        <v>699909323224</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.88445199660153</v>
+        <v>31.8500424808836</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>25.11301062870593</v>
+        <v>25.05682103741701</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.74953869232153</v>
+        <v>15.73254188149613</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.41275488316561</v>
+        <v>20.39072555645574</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.150102848455038</v>
+        <v>2.147782469928007</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.47468820345041</v>
+        <v>24.44870173977593</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>16.00801288761014</v>
+        <v>15.99101607678475</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.02999006042035009</v>
+        <v>0.03002246048560632</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2696387728262009</v>
+        <v>0.2711126616310333</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1375240610011503</v>
+        <v>0.1378301271625042</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007141334470262205</v>
+        <v>0.007149049683227743</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3051853919994814</v>
+        <v>0.3043837886111914</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1922583442671653</v>
+        <v>0.1804852376382017</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2277087061.263021</v>
+        <v>2227520172.995125</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>574.42</v>
+        <v>572.57001</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.02004864777101845</v>
+        <v>0.01676345610309293</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.04521126292344013</v>
+        <v>-0.04828627705195965</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,40 +2354,40 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>503787019120</v>
+        <v>502164508944</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.54420647995606</v>
+        <v>31.44261449752883</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.9211571714777</v>
+        <v>25.82767643578532</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.35986144628452</v>
+        <v>14.31361368594476</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>90.293787203707</v>
+        <v>90.00298499732669</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.394141268533772</v>
+        <v>1.389651265738997</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.3830267281606</v>
+        <v>23.30966309206005</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.74044463472337</v>
+        <v>14.6941968743836</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03264871736618159</v>
+        <v>0.03275420645435186</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2169289461608479</v>
+        <v>0.2174000466400365</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1564551345566814</v>
+        <v>0.1568220736126735</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005866787368127851</v>
+        <v>0.005885743125107094</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2935817535320609</v>
+        <v>0.2932120098584461</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.2089175877623677</v>
+        <v>0.1966852027236337</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1558005584.737655</v>
+        <v>1502088672.713576</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>383.55</v>
+        <v>376.91</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1401605438733284</v>
+        <v>0.1204221368564626</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1691217884840345</v>
+        <v>-0.1835059139552012</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>348318786154</v>
+        <v>342288707312</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.6640087454183</v>
+        <v>24.23638351231432</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.71391360958151</v>
+        <v>17.39397073555487</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7738199186322142</v>
+        <v>0.760403408507339</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.529768803010757</v>
+        <v>3.468569578554958</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.747325904675142</v>
+        <v>-0.7343687484605945</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.25683290587276</v>
+        <v>15.02242075332842</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8732203127414585</v>
+        <v>0.8598038026165832</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.0678028315979442</v>
+        <v>0.06899914051299065</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3923523219666976</v>
+        <v>0.3933784229481845</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01038134275007363</v>
+        <v>0.01030214158350229</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02362143136488072</v>
+        <v>0.02403756865034093</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4244573418377957</v>
+        <v>0.4292037814150745</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2274900484914662</v>
+        <v>0.2279204356412717</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1786599094.704653</v>
+        <v>1765890067.196583</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>165.07</v>
+        <v>169.015</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.345862192795575</v>
+        <v>0.3780268886856732</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.0642820701774276</v>
+        <v>-0.04191939232469821</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>684126012200</v>
+        <v>700475904370</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.24453024453024</v>
+        <v>21.75225225225225</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.93324004171107</v>
+        <v>15.29337721023762</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.894770985985709</v>
+        <v>1.94005401974741</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.656247916454622</v>
+        <v>2.719729457803223</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.080193586443587</v>
+        <v>2.129908033033034</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.96736529342151</v>
+        <v>10.1941349112426</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.982789597850773</v>
+        <v>2.027900459757381</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04465990103453049</v>
+        <v>0.04362136014065058</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4226336806473792</v>
+        <v>0.422331506849315</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08231581936981591</v>
+        <v>0.08215438117185392</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02495910825710305</v>
+        <v>0.02437653462710411</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5434105106913146</v>
+        <v>-0.5496265863345695</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2310004784818244</v>
+        <v>0.235769764287829</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2246422120.522645</v>
+        <v>2195624573.778361</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>266.32</v>
+        <v>264.25299</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2843983224531217</v>
+        <v>0.2744296224813065</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.0524780303838901</v>
+        <v>-0.05983210588109722</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>641804146149</v>
+        <v>636822863766</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.78843930635838</v>
+        <v>30.54947861271677</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.42782194813772</v>
+        <v>21.35042362672566</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.553770038997641</v>
+        <v>6.502903774836872</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.647873180261501</v>
+        <v>7.588515151039767</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.812094919379379</v>
+        <v>-3.782507812442963</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.87484128272856</v>
+        <v>19.72716897207399</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.845961320436235</v>
+        <v>6.795095056275465</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02914907937608865</v>
+        <v>0.02937708594406598</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4368440890015042</v>
+        <v>0.430860536859609</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.08854415069248511</v>
+        <v>0.08875387185717587</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01982577350555723</v>
+        <v>0.01998085243992887</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1737476460406477</v>
+        <v>-0.170768375962891</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2111034178170654</v>
+        <v>0.2108267922654884</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1680843383.236509</v>
+        <v>1625599304.065869</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>109.08</v>
+        <v>108.3937</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.03263570474027211</v>
+        <v>-0.03872208277324563</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1929564960047351</v>
+        <v>-0.1980341817105653</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>868067366400</v>
+        <v>862605736096</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>39.37906137184116</v>
+        <v>39.13129963898917</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>35.18621704102511</v>
+        <v>34.95437599517003</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.179695812133072</v>
+        <v>1.17227350524027</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.831840224760276</v>
+        <v>8.776272825179666</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.522573022645233</v>
+        <v>9.462659730882843</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.7160383388968</v>
+        <v>21.5885463268517</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.264260391389433</v>
+        <v>1.25683808449663</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01556215625985776</v>
+        <v>0.01566068881148337</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1191615548192475</v>
+        <v>0.119496444290589</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.0508222140108292</v>
+        <v>0.05094654776722218</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.008961312797946461</v>
+        <v>0.009018051787142611</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.06001157526822717</v>
+        <v>-0.0572910695089674</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3114822793533726</v>
+        <v>0.3067937513722329</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2780804758.730911</v>
+        <v>2718864815.912511</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.13</v>
+        <v>146.8</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03060869539015365</v>
+        <v>0.03533399358978029</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1262780269058297</v>
+        <v>-0.1222720478325858</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,40 +2984,40 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>347381541964</v>
+        <v>348974271952</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.64888888888889</v>
+        <v>21.74962962962963</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.69102145028324</v>
+        <v>20.78252485599786</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>3.991423177268131</v>
+        <v>4.009996829223734</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.518015227117894</v>
+        <v>6.548346099316896</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.65922539682562</v>
+        <v>20.75536084656106</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.52449148226216</v>
+        <v>17.60054785174555</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.279639005928854</v>
+        <v>4.298212657884457</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04580842122477855</v>
+        <v>0.04559624408132944</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04629386910197875</v>
+        <v>0.04653451783807983</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02527505890851667</v>
+        <v>0.0254247114288122</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02936152740710327</v>
+        <v>0.0292275204359673</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04674076747521385</v>
+        <v>-0.04847916959282902</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.160764734967262</v>
+        <v>0.1503064794297618</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1296332418.248112</v>
+        <v>1266167775.389949</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>310.87</v>
+        <v>305.975</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.101064156451341</v>
+        <v>-0.1152189187448099</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2715407147041593</v>
+        <v>-0.2830111306385471</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,31 +3110,31 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>309973761790</v>
+        <v>305092874075</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.70879888268156</v>
+        <v>21.36696927374302</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.7160625953354</v>
+        <v>20.38986474284347</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.832256122558755</v>
+        <v>1.803405176118362</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.59570199193597</v>
+        <v>18.30289161701872</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.446622872547778</v>
+        <v>-7.329367367156067</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.4905189960276</v>
+        <v>15.28642584465816</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.189765461944957</v>
+        <v>2.160914515504563</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04871702660507948</v>
+        <v>0.04949640349937432</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.0298838742882877</v>
+        <v>0.03036195767628074</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7058868672376516</v>
+        <v>0.7093609924436535</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2502242802873501</v>
+        <v>0.246540985956761</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1226694079.953125</v>
+        <v>1204944344.503112</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>493.41</v>
+        <v>503.7806</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.207947363425748</v>
+        <v>1.254354487170996</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1561746447078138</v>
+        <v>-0.1384389376293332</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,40 +3236,40 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>804554346000</v>
+        <v>821464646360</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>125.2309644670051</v>
+        <v>127.8630964467005</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>36.55434069710366</v>
+        <v>37.26047429516517</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>19.47837661300085</v>
+        <v>19.88777742065125</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11.97119644769725</v>
+        <v>12.22280968999167</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.01103897918316</v>
+        <v>1.032289219019233</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>74.9901423773092</v>
+        <v>76.56789012502333</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>19.45876639632006</v>
+        <v>19.86816720397047</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.01044429135430958</v>
+        <v>0.01022928988756195</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.425884917599611</v>
+        <v>2.431601418538349</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.8908862032600786</v>
+        <v>0.8934119722057594</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.545669055146133</v>
+        <v>2.540662423834458</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6757380094899845</v>
+        <v>0.6645158515052284</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>10291128789.90689</v>
+        <v>10050294689.56701</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -3347,55 +3347,55 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1575.15</v>
+        <v>1591.82</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3534774273035635</v>
+        <v>0.3678014400726015</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2124092481849637</v>
+        <v>-0.2040740814816296</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>833.92</v>
+        <v>861.1799999999999</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>607091148524</v>
+        <v>613516066434</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>50.35558780841799</v>
+        <v>50.0290293904209</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>32.43674317792082</v>
+        <v>32.76890300288574</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.14070024513481</v>
+        <v>15.04251206029297</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>24.50622302454937</v>
+        <v>24.34729898512742</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.427888881122619</v>
+        <v>3.405658856237435</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>38.40744597124126</v>
+        <v>38.15616971349922</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>15.00801324492251</v>
+        <v>14.90982506008067</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01869922647784843</v>
+        <v>0.01882128342541458</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5524242841585354</v>
+        <v>0.5267227403375445</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.3028611080328747</v>
+        <v>0.2824150857016017</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004939212138526489</v>
+        <v>0.004887487278712418</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.701372357510302</v>
+        <v>1.698471322134239</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4376047884782998</v>
+        <v>0.4375226644691245</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2066909334.696265</v>
+        <v>2040826459.700114</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>210.27</v>
+        <v>210.27991</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07683190913728588</v>
+        <v>-0.07678840033536238</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1733045016709258</v>
+        <v>-0.1732655396107725</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>166191099900</v>
+        <v>166198930275</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>78.75280898876402</v>
+        <v>78.7565205992509</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>83.61188327826393</v>
+        <v>83.16396587710337</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.768084471514442</v>
+        <v>1.76816777780733</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.26770246713443</v>
+        <v>27.26898759069675</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4214908363466836</v>
+        <v>0.4215107011594871</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.47368343884892</v>
+        <v>29.47481011151079</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.179287195063567</v>
+        <v>2.179370501356455</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001263605572899876</v>
+        <v>-0.001263546038789328</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.058114637525012</v>
+        <v>-0.05299705505104968</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1529483038203576</v>
+        <v>0.1533729156417385</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.242098762420381</v>
+        <v>1.238902943540715</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3371627648070844</v>
+        <v>0.3345804216929615</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1139446719.053749</v>
+        <v>1059990284.618443</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>988.45</v>
+        <v>957.33</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.08105296822606012</v>
+        <v>0.04701749008230482</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1434501165521365</v>
+        <v>-0.1704174212948119</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>291599669150</v>
+        <v>282419051310</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15.05865326020719</v>
+        <v>14.5845521023766</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.64908055851598</v>
+        <v>13.21780872300822</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.472503702400434</v>
+        <v>2.394660295835912</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.416726507633899</v>
+        <v>2.340639169966271</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3529539666337912</v>
+        <v>0.3418416924250365</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.95529796929252</v>
+        <v>26.66285641098334</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.175082197698771</v>
+        <v>7.09723879113425</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1423698460324539</v>
+        <v>-0.1469978735762789</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1032723556468242</v>
+        <v>0.1034016611989015</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3823282959808239</v>
+        <v>-0.382285490439393</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.0182103293034549</v>
+        <v>0.01880229387985334</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.568896240889311</v>
+        <v>1.576163907424641</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3297536656376204</v>
+        <v>0.3163673996164783</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1844065424.760997</v>
+        <v>1814797433.898621</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>249.09</v>
+        <v>250.2</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1454888507718697</v>
+        <v>-0.1416809605488851</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2507670095650604</v>
+        <v>-0.247428262046562</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>234676158060</v>
+        <v>235721926800</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>21.75458515283843</v>
+        <v>21.85152838427948</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>19.30972313277915</v>
+        <v>19.3923290539268</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.396329190268753</v>
+        <v>3.411463982517331</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.795532654127483</v>
+        <v>6.825815047021944</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2651867066111507</v>
+        <v>0.2663684370874378</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>18.04920523149005</v>
+        <v>18.11367528512422</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.237176115605598</v>
+        <v>4.252310907854176</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.05808429843356708</v>
+        <v>0.05782661029902968</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1266130023329546</v>
+        <v>0.1268129951546333</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04589294922825382</v>
+        <v>0.04600047137561836</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02705849291420772</v>
+        <v>0.02693844924060752</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.8971252793196376</v>
+        <v>0.8934888010026703</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3271665812957038</v>
+        <v>0.3168137635713446</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1220828464.444655</v>
+        <v>1174690553.0539</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1137.75</v>
+        <v>1145.35999</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05312119610739008</v>
+        <v>0.06016513526024903</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.119831354194871</v>
+        <v>-0.1139442308436159</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,52 +3868,52 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1071465822750</v>
+        <v>1078632457965</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.11557788944724</v>
+        <v>38.3191699565072</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.09620301572835</v>
+        <v>26.25381288957396</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.44950810448147</v>
+        <v>13.53946684731717</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>29.96924643584521</v>
+        <v>30.16969966870332</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4040409084761278</v>
+        <v>0.4050808331259123</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>31.73948599039991</v>
+        <v>25.97057273015924</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.02714618757359</v>
+        <v>14.11710493040929</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.0187163226061006</v>
+        <v>0.01859196786812317</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.4470491333778837</v>
+        <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.460579451595879</v>
+        <v>0.4595658968730096</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.227779731796429</v>
+        <v>0.228246464557607</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.1877209505000597</v>
+        <v>0.1877328985191485</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.9257633748190075</v>
+        <v>0.9258222975894521</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.8401195996274436</v>
+        <v>0.8339940099766776</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.4392022674723658</v>
+        <v>0.4971832329556723</v>
       </c>
       <c r="AA27" s="5" t="n">
         <v>8972000000</v>
@@ -3931,22 +3931,22 @@
         <v>0.3859069600725315</v>
       </c>
       <c r="AF27" s="6" t="n">
-        <v>1.307032492615315</v>
+        <v>1.062653562653563</v>
       </c>
       <c r="AG27" s="6" t="n">
-        <v>33.16107129385138</v>
+        <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005880026367831246</v>
+        <v>0.005840958352316812</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3407250759735089</v>
+        <v>0.3386164667011203</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.325820700942637</v>
+        <v>0.3250479851309561</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>3162895450.557251</v>
+        <v>3079033823.923071</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>206.6</v>
+        <v>200.99001</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1357889331077817</v>
+        <v>0.1049478655528673</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1104413347685683</v>
+        <v>-0.1345962970936491</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,40 +3994,40 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>325866048000</v>
+        <v>317017515864</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.60771704180064</v>
+        <v>16.15675321543408</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.34435970189044</v>
+        <v>14.92526753704531</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.57542577590908</v>
+        <v>2.505492937302911</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.939480333644276</v>
+        <v>2.859662060280573</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4225268181859822</v>
+        <v>0.4110535789567702</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.52226966981293</v>
+        <v>23.21645587542168</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.455729895913191</v>
+        <v>5.384799773775182</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04813020594278052</v>
+        <v>-0.04949330728452513</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08233366295203282</v>
+        <v>0.08251012421265891</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3273872607776852</v>
+        <v>-0.3272876063513729</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02008712487899323</v>
+        <v>0.02064779239525387</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.378066152786705</v>
+        <v>1.384843569200202</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2838600492330827</v>
+        <v>0.2702874908851359</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>901055652.0337336</v>
+        <v>888563291.6675527</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>924.03</v>
+        <v>925.46</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.929522416660805</v>
+        <v>1.934056054157234</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2637211155378486</v>
+        <v>-0.2625816733067728</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,37 +4120,37 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1043590241700</v>
+        <v>1045205269400</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.62106672617719</v>
+        <v>20.65297924570408</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.938210682417066</v>
+        <v>5.945241031966287</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.56025258324656</v>
+        <v>11.57814286948623</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.34813788173623</v>
+        <v>10.36415233707955</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02939106654750906</v>
+        <v>0.02943655124515192</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>14.99679925233371</v>
+        <v>15.02042942381412</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.35400272171389</v>
+        <v>11.37189300795356</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02507880866858819</v>
+        <v>0.02504005745687068</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.472606114706539</v>
+        <v>2.473867440303503</v>
       </c>
       <c r="V29" s="4" t="n">
         <v>1.765110056317434</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005735744510459617</v>
+        <v>0.0005726881766905107</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.885442363676178</v>
+        <v>2.881697109418158</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8256190424097433</v>
+        <v>0.8123940601083595</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>26915220454.49057</v>
+        <v>26055014840.47032</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>142.35</v>
+        <v>146.26</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.03458797594978857</v>
+        <v>-0.008070511853994211</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2689728130809446</v>
+        <v>-0.2488933167630415</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,40 +4246,40 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>147170255700</v>
+        <v>151212656120</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>88.41614906832298</v>
+        <v>90.84472049689441</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>30.04974958411884</v>
+        <v>30.85835527126522</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.98983543985881</v>
+        <v>10.26423134129785</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.74876558005753</v>
+        <v>12.07147491211249</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>141.4658385093198</v>
+        <v>145.3515527950342</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>43.88657371739753</v>
+        <v>45.04518662080825</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.39371814417594</v>
+        <v>10.66811404561499</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.0311204188524081</v>
+        <v>0.03028847000984748</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.94232565302476</v>
+        <v>1.943926197566579</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2450681773312404</v>
+        <v>0.2456309996565116</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.711253205813258</v>
+        <v>0.7006968259160118</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6283435425653637</v>
+        <v>0.6291368994173632</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2258920226.575495</v>
+        <v>2194783123.786512</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.72</v>
+        <v>27.47</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.100873695950755</v>
+        <v>0.09094518137688445</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05100992810681282</v>
+        <v>-0.05956864087641223</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157988476800</v>
+        <v>156563616800</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.62790697674419</v>
+        <v>36.29756871035941</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.493782148823916</v>
+        <v>9.408847936443443</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.480351620195931</v>
+        <v>2.457981926651595</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.85439934264585</v>
+        <v>1.837674961849982</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6126260547437744</v>
+        <v>-0.6071009279874272</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.44347883396705</v>
+        <v>17.33060969581749</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.457147651343883</v>
+        <v>3.434777957799548</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06953671699681833</v>
+        <v>0.07016955934298523</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.858094319267862</v>
+        <v>2.85781223753946</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05021253784362711</v>
+        <v>-0.05031934638406588</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06204906204906205</v>
+        <v>0.06261376046596287</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3496282390178725</v>
+        <v>0.3495117154943911</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2088043753876717</v>
+        <v>0.209183226316025</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>988001149.972362</v>
+        <v>966922991.4588209</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>175.63</v>
+        <v>173.175</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.04535447736624998</v>
+        <v>0.03074225142572651</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1212788312403063</v>
+        <v>-0.1335618151798669</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,40 +4498,40 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1246718145063</v>
+        <v>1229291207489</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>7.414675307130095</v>
+        <v>7.38409031764871</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003647503023548917</v>
+        <v>0.003598314060420221</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6.3679221533799</v>
+        <v>6.341654943554526</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>4.614583589084575</v>
+        <v>4.595548771687055</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.01659311748241866</v>
+        <v>0.01652467209504274</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>7.488190590983496</v>
+        <v>7.457154914126215</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>6.337669849130638</v>
+        <v>6.311402639305264</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.07569489726394341</v>
+        <v>0.07600842642420826</v>
       </c>
       <c r="T32" s="4" t="n">
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2031.808543066217</v>
+        <v>2051.097230441963</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2624.035360523716</v>
+        <v>2653.390795539407</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.70813642316233</v>
+        <v>1.73235166738848</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9855001700845949</v>
+        <v>0.9147973844433476</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3333796407.208734</v>
+        <v>3243135688.615308</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>541.5</v>
+        <v>541.96</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4505759917150454</v>
+        <v>0.451808244635062</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1939925278716342</v>
+        <v>-0.1933078308500662</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>68251065042</v>
+        <v>68309043786</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.828293058381121</v>
+        <v>1.827574172251887</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4137902024091694</v>
+        <v>0.4040591364180168</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3886308062.686564</v>
+        <v>3799367435.75175</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>148.15</v>
+        <v>144.5801</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.07952778621274759</v>
+        <v>-0.1017079668134842</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3434231519234178</v>
+        <v>-0.3592443715653253</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1937189465232</v>
+        <v>1890509933191</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-96.20129870129871</v>
+        <v>-93.88318181818181</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>134.2771473268606</v>
+        <v>130.4648730500136</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>116.874175881267</v>
+        <v>114.0579145213273</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.828519776142866</v>
+        <v>6.663976186882977</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9620129870129871</v>
+        <v>-0.9388318181818182</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>451.8914003436525</v>
+        <v>440.6892088291337</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>113.6067249008748</v>
+        <v>110.7904635409351</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01467228709949444</v>
+        <v>-0.01503456792317652</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.194740387198083</v>
+        <v>4.204788528688608</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.461529722776998</v>
+        <v>3.471652279223203</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7855766027896656</v>
+        <v>0.7839797738368991</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14309271538.60899</v>
+        <v>14218060076.60062</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>760.88</v>
+        <v>757.21</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1137491678993505</v>
+        <v>0.1083771520148606</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02372429013177313</v>
+        <v>-0.02843322170471019</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>810518461399</v>
+        <v>806609037109</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9951782597768953</v>
+        <v>0.9952684723030731</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1154451686121067</v>
+        <v>0.1152769646468357</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>30486148873.09041</v>
+        <v>29338901279.6058</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>418.01</v>
+        <v>413.69</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3078752828707778</v>
+        <v>0.2943588090495732</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1273277661795408</v>
+        <v>-0.1363465553235909</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,40 +4914,40 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2168000504800</v>
+        <v>2145594911200</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>27.58780572620842</v>
+        <v>27.64576330126348</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6385117885598318</v>
+        <v>0.6311629187197041</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>13.89916072363153</v>
+        <v>13.92836064111815</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>9.59388616712771</v>
+        <v>9.614041390167893</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.5182494035320432</v>
+        <v>0.5193381627831609</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>18.27477474575392</v>
+        <v>18.31455399061033</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>13.41458131216091</v>
+        <v>13.44378122964753</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.01812191372746905</v>
+        <v>0.01808392229407813</v>
       </c>
       <c r="T36" s="4" t="n">
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.20641563788966</v>
+        <v>42.80131101070088</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.18157995035575</v>
+        <v>42.78428010529495</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2631515992440372</v>
+        <v>0.2658995866470062</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.182358245656101</v>
+        <v>2.182894938145429</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3662558302635321</v>
+        <v>0.3625210639033964</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4177058875.66307</v>
+        <v>4058432163.025561</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.1</v>
+        <v>27.87</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01438092688847081</v>
+        <v>-0.0224482716150064</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06333333333333324</v>
+        <v>-0.07099999999999995</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,38 +5042,38 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70450541326</v>
+        <v>69873899885</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.1259842519685</v>
+        <v>-21.94488188976378</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-81.58497367135612</v>
+        <v>-81.65673422767294</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.950727989090406</v>
+        <v>1.934761176381005</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.148702722455692</v>
+        <v>2.131115475972958</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1646584874565099</v>
+        <v>0.1633107489470793</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.38091592165289</v>
+        <v>16.28560328677686</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.744137929558355</v>
+        <v>2.728171116848955</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03094369410040947</v>
+        <v>0.03119906007232875</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02050670921914222</v>
+        <v>0.02058038420274655</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2528902568169814</v>
+        <v>0.2399821929974742</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1891631311488362</v>
+        <v>0.1904242206290057</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>513505897.7286453</v>
+        <v>505854941.2946819</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>327.78</v>
+        <v>322.32999</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1205967044815636</v>
+        <v>-0.1352185751100595</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1540942992077216</v>
+        <v>-0.1681592041084932</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,40 +5170,40 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>221353111800</v>
+        <v>217672663232</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.87750151607035</v>
+        <v>19.54699757428745</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.87484752618812</v>
+        <v>16.58836791902805</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.632868005185969</v>
+        <v>2.589091185422193</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.482929988331389</v>
+        <v>6.375138075262544</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.232578696629692</v>
+        <v>1.212084565741844</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.511369996764278</v>
+        <v>9.362508624494419</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.797082437881365</v>
+        <v>2.753305618117588</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.06799994758420197</v>
+        <v>0.06914970293700716</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1779366589963201</v>
+        <v>0.1783556809024982</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.005658273890123855</v>
+        <v>0.005891366142209531</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01079992678015742</v>
+        <v>0.01098253376919721</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9585179028789104</v>
+        <v>0.9614939136553785</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2223319342377628</v>
+        <v>0.2234581573750339</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>780789981.0595449</v>
+        <v>755198188.8363749</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>144.72</v>
+        <v>143.91499</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2605385773064524</v>
+        <v>-0.2646518570181891</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5607890743550834</v>
+        <v>-0.5632322003034902</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,40 +5296,40 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>416861618400</v>
+        <v>414542820711</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.33333333333333</v>
+        <v>22.20910339506172</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.15276483735976</v>
+        <v>16.04313808826583</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.807732538278279</v>
+        <v>5.775426957256503</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.428435871323309</v>
+        <v>6.392677474689989</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4860784313725492</v>
+        <v>0.4833746033042848</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.30196012477671</v>
+        <v>14.15972483327147</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.473475046324031</v>
+        <v>7.441169465302256</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06889576476297632</v>
+        <v>-0.06928114193544857</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3826322340605446</v>
+        <v>0.3843366100118382</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.4214263744375701</v>
+        <v>0.4232963938119607</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
@@ -5338,10 +5338,10 @@
         <v>0.425824021246188</v>
       </c>
       <c r="Y39" s="4" t="n">
-        <v>0.7443888710868384</v>
+        <v>0.6394666815275089</v>
       </c>
       <c r="Z39" s="4" t="n">
-        <v>0.3249369575212115</v>
+        <v>0.3236273458071527</v>
       </c>
       <c r="AA39" s="5" t="n">
         <v>-23686000000</v>
@@ -5359,22 +5359,22 @@
         <v>0.5141842451501851</v>
       </c>
       <c r="AF39" s="6" t="n">
-        <v>3.187724958007839</v>
+        <v>3.169724284199364</v>
       </c>
       <c r="AG39" s="6" t="n">
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01381978993919292</v>
+        <v>0.0138970929991379</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.074229586262845</v>
+        <v>2.068944190557603</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5811597887336338</v>
+        <v>0.5570941813061446</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4282412869.755261</v>
+        <v>4122497288.122352</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 18:42 ET</t>
+          <t>2026-09-15 11:57 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>329.64999</v>
+        <v>330.54</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2163756987614149</v>
+        <v>0.2196597472021709</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.04330037437966161</v>
+        <v>-0.04071741590968447</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,37 +714,37 @@
         <v>236.32</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4841686815755</v>
+        <v>4854758652240</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>37.63127739726028</v>
+        <v>37.73287671232877</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.4557922898374</v>
+        <v>34.54881822833622</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.37156870110299</v>
+        <v>10.39957039871643</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.04638600097518</v>
+        <v>45.16800509765626</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.149844587138507</v>
+        <v>1.152949010654489</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.00211184166637</v>
+        <v>29.08056767802666</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.46745729271051</v>
+        <v>10.49577361398217</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02823045050233924</v>
+        <v>0.0281535859500535</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09216114030149503</v>
+        <v>0.09216114030149525</v>
       </c>
       <c r="V2" s="4" t="n">
         <v>0.117919601370001</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003215531721993985</v>
+        <v>0.00320687360077449</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3091698218796033</v>
+        <v>0.3089245585263142</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2956148449247202</v>
+        <v>0.2951320169816031</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13293888719.37706</v>
+        <v>13334541883.37132</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>501.7073</v>
+        <v>499.4401</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.06082652643060737</v>
+        <v>0.05603268368460101</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.09393321534349497</v>
+        <v>-0.09802770353247137</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3725452641515</v>
+        <v>3708617434555</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.87262777777778</v>
+        <v>27.745</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.45461871090728</v>
+        <v>24.34410903416674</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.22668716309717</v>
+        <v>11.1752805592471</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.425165142058875</v>
+        <v>8.386586608557666</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8853277825470466</v>
+        <v>0.8812738979118314</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.46904471879683</v>
+        <v>18.38996537907373</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.54981087515331</v>
+        <v>11.50035778042967</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01798403163448161</v>
+        <v>0.01806361496263324</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1397694687975646</v>
+        <v>0.1397007777553141</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2255150471434921</v>
+        <v>0.2254411884306673</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007255226304261469</v>
+        <v>0.00728816128300471</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5562011142553257</v>
+        <v>0.557009999363542</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4348274611586234</v>
+        <v>0.4357644859792686</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>11582425696.22803</v>
+        <v>11612961037.81489</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>343.66</v>
+        <v>343.41</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09046487912317769</v>
+        <v>0.08967160606323232</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1589535253664863</v>
+        <v>-0.1595653557181664</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4159011564547</v>
+        <v>4155986036725</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.88828699106256</v>
+        <v>16.87487586891758</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.55242197065229</v>
+        <v>20.53747084019584</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.257906444063909</v>
+        <v>9.250554667404556</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.452849183581066</v>
+        <v>6.447724925056209</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1501885184571042</v>
+        <v>0.1500692525678599</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.90501170215935</v>
+        <v>12.89490294123615</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.385399906225187</v>
+        <v>9.378048129565832</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01290595095857692</v>
+        <v>0.01291620782126628</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1782823934240892</v>
+        <v>-0.1783371964239068</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2899304626314998</v>
+        <v>0.2898444330050911</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002502473374847233</v>
+        <v>0.002504295157392038</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7724142410527388</v>
+        <v>0.7727868830899939</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3684584056345456</v>
+        <v>0.3686586514585669</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8312541467.382883</v>
+        <v>8343403709.357497</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>249.49</v>
+        <v>248.505</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1015011037527593</v>
+        <v>0.0971523178807947</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1313022284122562</v>
+        <v>-0.1347318941504179</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,31 +1094,31 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2683788879000</v>
+        <v>2673193135500</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.80079365079365</v>
+        <v>19.72261904761904</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.15156853341933</v>
+        <v>22.06411294399523</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.459917593595297</v>
+        <v>3.446257651995669</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.864788151263551</v>
+        <v>4.84558170479678</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2241409636612682</v>
+        <v>0.2232560430263476</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.13717043508388</v>
+        <v>11.09503090390831</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.646874844007839</v>
+        <v>3.633076222798061</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004331562773421865</v>
+        <v>-0.004348906804326129</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8345785311076686</v>
+        <v>0.8354738263803998</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4596911307758973</v>
+        <v>0.4606698173553007</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8741121385.194023</v>
+        <v>8780433325.741096</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>212.27</v>
+        <v>211.56</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1240137312129448</v>
+        <v>0.1202541337702483</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1026042107043206</v>
+        <v>-0.1056058171979369</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,31 +1220,31 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5141391670000</v>
+        <v>5124194760000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>26.7006289308176</v>
+        <v>26.61132075471697</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>15.87557250715581</v>
+        <v>15.82247194428739</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>16.97002554716819</v>
+        <v>16.91326426136007</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.42432353352199</v>
+        <v>22.3493187296929</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2143315791725495</v>
+        <v>0.2136146836092928</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.06992952021466</v>
+        <v>21.99973363804046</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.02159039769746</v>
+        <v>16.96745132340272</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02470646785478988</v>
+        <v>0.024785552842648</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.00244971027465021</v>
+        <v>0.002457931556059747</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.327525487399058</v>
+        <v>1.327454700976176</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4130089407334011</v>
+        <v>0.4128248870097586</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26835566161.85361</v>
+        <v>26912935736.83827</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>668.025</v>
+        <v>667.6900000000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.02708295933763982</v>
+        <v>0.02656789958481909</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1552541729893778</v>
+        <v>-0.1556777946383407</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,31 +1346,31 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1701784715924</v>
+        <v>1700931307923</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.82441471571907</v>
+        <v>24.81196581196582</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.20271885011575</v>
+        <v>20.19258762626217</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.455858171480145</v>
+        <v>7.452119220860643</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.503258065010088</v>
+        <v>6.499996822613803</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.089005016722404</v>
+        <v>-5.086452991452988</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.79842270550657</v>
+        <v>16.79045229306448</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.880203620290211</v>
+        <v>7.876464669670709</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02407825127149041</v>
+        <v>0.02409033204876193</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003143594925339621</v>
+        <v>0.003145172160733274</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7749251316420632</v>
+        <v>0.7746422790702998</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4138640761944271</v>
+        <v>0.4138328542694102</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>9868792832.16403</v>
+        <v>9915542588.381979</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>360.355</v>
+        <v>357.35</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.177403168500192</v>
+        <v>-0.1842628026905235</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2775995830242768</v>
+        <v>-0.2836236794098189</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1423239151165</v>
+        <v>1411370761246</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>305.3898220338983</v>
+        <v>302.8389830508475</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>171.3141249024022</v>
+        <v>169.8855365788554</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.73550064222778</v>
+        <v>13.62077187818836</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.42979676748256</v>
+        <v>13.31762128992148</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.129391037240389</v>
+        <v>-8.061488422057767</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>117.8631831741769</v>
+        <v>116.8518258435318</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.68145192695355</v>
+        <v>13.56405448079985</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004047669016651527</v>
+        <v>0.004082555879868969</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7826307212430914</v>
+        <v>0.7826060366844672</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1223280851497379</v>
+        <v>0.122312558453592</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.538872399802141</v>
+        <v>1.539698085918128</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5751269196894302</v>
+        <v>0.5749762562376446</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12579569948.95085</v>
+        <v>12660774433.6684</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>339.815</v>
+        <v>338.11</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.0224526644808114</v>
+        <v>-0.02735744563249742</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3135050505050505</v>
+        <v>-0.3169494949494949</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1616697047700</v>
+        <v>1608585373800</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>42.1575682382134</v>
+        <v>41.94913151364764</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.59967808038237</v>
+        <v>18.50635538677835</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.14259862856886</v>
+        <v>18.05289744343688</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.24475012538871</v>
+        <v>16.16443234025479</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4194886740535094</v>
+        <v>0.4174146254575828</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>31.60978336873122</v>
+        <v>31.4568504257314</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.54038099524151</v>
+        <v>18.45067981010953</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02437432487804365</v>
+        <v>0.02449543595371462</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.266575155549506</v>
+        <v>1.266741918488052</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8524380480254286</v>
+        <v>0.8525743408863151</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.00747465532716331</v>
+        <v>0.007512348052408979</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.605031466464408</v>
+        <v>1.605762204037337</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3888980769216379</v>
+        <v>0.3900649704807758</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8604532715.337473</v>
+        <v>8653051495.002264</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>907.97</v>
+        <v>908.5700000000001</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.06257460503218248</v>
+        <v>0.06327677004095977</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.171937984496124</v>
+        <v>-0.171390788873689</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>402665627630</v>
+        <v>402931715030</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.60371672526369</v>
+        <v>45.63385233550979</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>40.05991537725069</v>
+        <v>40.08638756160298</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.371537662192127</v>
+        <v>1.37244399455698</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>12.02867188844788</v>
+        <v>12.03662061267122</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.597400332747367</v>
+        <v>3.599777548073477</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>27.0871891935038</v>
+        <v>27.10557809467865</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.335044220725032</v>
+        <v>1.335950553089885</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02186926172921724</v>
+        <v>0.02185481974121684</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.00610152317807857</v>
+        <v>0.006097493863984063</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1892386300769955</v>
+        <v>-0.1889410365998826</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1726876444671286</v>
+        <v>0.1724361417636054</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1679329850.192424</v>
+        <v>1688383985.74694</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>77.82859999999999</v>
+        <v>78.425</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1446466443869447</v>
+        <v>-0.1380920777971869</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3766730738427039</v>
+        <v>-0.3718965241069999</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,31 +1850,31 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>324073620606</v>
+        <v>326556994422</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>24.09554179566564</v>
+        <v>24.28018575851393</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.75455762698772</v>
+        <v>20.91359965226808</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.699782964064823</v>
+        <v>6.75112335256892</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.8134460455892</v>
+        <v>10.89630940458049</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7081738503360268</v>
+        <v>0.7136005814392511</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.76194678079623</v>
+        <v>10.84311064430485</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.807494184007513</v>
+        <v>6.858834572511611</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03392626644353429</v>
+        <v>0.03366826675833497</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.1001273037800634</v>
+        <v>0.09960033919145793</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3823242582324036</v>
+        <v>0.3787138989192149</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2152766013.596189</v>
+        <v>2167131638.558993</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>515.41998</v>
+        <v>514.9349999999999</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.03737541243506692</v>
+        <v>0.03639930295727201</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04150708520846502</v>
+        <v>-0.04240897087811968</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1111685443075</v>
+        <v>1110639405941</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.96914202743653</v>
+        <v>12.94107219666281</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.23493301977915</v>
+        <v>23.21307030926502</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.892531840790045</v>
+        <v>2.886271374283508</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.481008916082471</v>
+        <v>1.477803486643819</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3572668355906716</v>
+        <v>0.3564935832355907</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.70275238829495</v>
+        <v>15.67127684030374</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.123267477814431</v>
+        <v>3.117007011307894</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02176200044851258</v>
+        <v>0.02180920331243488</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4418257192135512</v>
+        <v>-0.4425092405162084</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06163788923813973</v>
+        <v>0.06033784945499487</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.05420570709557663</v>
+        <v>0.05462322429184981</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1394374697778777</v>
+        <v>0.1394831559233317</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2052405133.490605</v>
+        <v>2058681652.38444</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>343.58499</v>
+        <v>345.14001</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.05562547131176165</v>
+        <v>0.06040309189524296</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.0625239017735334</v>
+        <v>-0.05828100954979532</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>920639420454</v>
+        <v>924806120651</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>14.77149613069647</v>
+        <v>14.83834952708513</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.71894780439785</v>
+        <v>13.78103793882076</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.093203520274969</v>
+        <v>3.107202899715421</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.557823291902253</v>
+        <v>2.569399585387536</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7734244488807034</v>
+        <v>0.776924842530758</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>19.84434782471018</v>
+        <v>19.88907385842636</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.211338942086395</v>
+        <v>6.225338321526847</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1765446844299602</v>
+        <v>-0.1757492693555999</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07672223419067215</v>
+        <v>0.07672220285280162</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2894273564515862</v>
+        <v>-0.289427374123294</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01746292816807859</v>
+        <v>0.01738424936593123</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7774690338025343</v>
+        <v>0.7760824012456902</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1761580139505628</v>
+        <v>0.17336066211516</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>1989747020.048416</v>
+        <v>1997817113.647717</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>374.875</v>
+        <v>375.09</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08195274796037899</v>
+        <v>0.08257327437801543</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.02773815390201517</v>
+        <v>-0.02718053790492003</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,37 +2228,37 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>699909323224</v>
+        <v>700310738374</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.8500424808836</v>
+        <v>31.86830926083262</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>25.05682103741701</v>
+        <v>25.07119173837878</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.73254188149613</v>
+        <v>15.74156487983277</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.39072555645574</v>
+        <v>20.40242013730172</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.147782469928007</v>
+        <v>2.149014275812727</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.44870173977593</v>
+        <v>24.4637793652141</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.99101607678475</v>
+        <v>16.00087780904963</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03002246048560632</v>
+        <v>0.03000365309923089</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2711126616310333</v>
+        <v>0.2711126616310331</v>
       </c>
       <c r="V14" s="4" t="n">
         <v>0.1378301271625042</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007149049683227743</v>
+        <v>0.007144951878215896</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3043837886111914</v>
+        <v>0.3041571210899403</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1804852376382017</v>
+        <v>0.1804553510512027</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2227520172.995125</v>
+        <v>2235291208.367525</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>572.57001</v>
+        <v>571.78998</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01676345610309293</v>
+        <v>0.01537828750394787</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.04828627705195965</v>
+        <v>-0.04958282636880418</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>502164508944</v>
+        <v>501480395169</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.44261449752883</v>
+        <v>31.39977924217463</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.82767643578532</v>
+        <v>25.79249058584847</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.31361368594476</v>
+        <v>14.29411382062537</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>90.00298499732669</v>
+        <v>89.8803711210123</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.389651265738997</v>
+        <v>1.387758100435396</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.30966309206005</v>
+        <v>23.27873011254295</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.6941968743836</v>
+        <v>14.67469700906422</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03275420645435186</v>
+        <v>0.03279888936527018</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005885743125107094</v>
+        <v>0.005893772395242043</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2932120098584461</v>
+        <v>0.2936600351574814</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1966852027236337</v>
+        <v>0.196888823927035</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1502088672.713576</v>
+        <v>1506927344.18854</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>376.91</v>
+        <v>376.23</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1204221368564626</v>
+        <v>0.1184007337282293</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1835059139552012</v>
+        <v>-0.1849789870456219</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>342288707312</v>
+        <v>341671169117</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.23638351231432</v>
+        <v>24.19329946627227</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.39397073555487</v>
+        <v>17.36258950369534</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.760403408507339</v>
+        <v>0.7590516698924086</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.468569578554958</v>
+        <v>3.4624036416549</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7343687484605945</v>
+        <v>-0.7330632906164221</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.02242075332842</v>
+        <v>14.99880328832046</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8598038026165832</v>
+        <v>0.8584520640016527</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06899914051299065</v>
+        <v>0.06912201594601833</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3933784229481845</v>
+        <v>0.3934153923942698</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01030214158350229</v>
+        <v>0.01032894715891031</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02403756865034093</v>
+        <v>0.02408101427318396</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4292037814150745</v>
+        <v>0.4299634297352862</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2279204356412717</v>
+        <v>0.2286907757075497</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1765890067.196583</v>
+        <v>1774152860.888757</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>169.015</v>
+        <v>169.225</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3780268886856732</v>
+        <v>0.3797390778205074</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.04191939232469821</v>
+        <v>-0.04072898361770871</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,31 +2606,31 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>700475904370</v>
+        <v>701346243500</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.75225225225225</v>
+        <v>21.77927927927928</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>15.29337721023762</v>
+        <v>15.31237912849429</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.94005401974741</v>
+        <v>1.942464530825901</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.719729457803223</v>
+        <v>2.723108703350297</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.129908033033034</v>
+        <v>2.132554429429431</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>10.1941349112426</v>
+        <v>10.20711790462931</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>2.027900459757381</v>
+        <v>2.030483142690966</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04362136014065058</v>
+        <v>0.04356336158233091</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02437653462710411</v>
+        <v>0.02434628453242724</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5496265863345695</v>
+        <v>-0.550269401398622</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.235769764287829</v>
+        <v>0.23646778116629</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2195624573.778361</v>
+        <v>2207212313.786093</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>264.25299</v>
+        <v>265.11</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2744296224813065</v>
+        <v>0.2785627788583174</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.05983210588109722</v>
+        <v>-0.05678300779165324</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>636822863766</v>
+        <v>638888169066</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.54947861271677</v>
+        <v>30.6485549132948</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.35042362672566</v>
+        <v>21.41966608469119</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.502903774836872</v>
+        <v>6.523993598076157</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.588515151039767</v>
+        <v>7.613125784091043</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.782507812442963</v>
+        <v>-3.794775022817165</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.72716897207399</v>
+        <v>19.78839585752401</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.795095056275465</v>
+        <v>6.816184879514751</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02937708594406598</v>
+        <v>0.02928211994808027</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01998085243992887</v>
+        <v>0.01991626117460677</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.170768375962891</v>
+        <v>-0.1715966951694204</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2108267922654884</v>
+        <v>0.210161360821697</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1625599304.065869</v>
+        <v>1633273434.228108</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>108.3937</v>
+        <v>108.7578</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.03872208277324563</v>
+        <v>-0.03549310092594027</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1980341817105653</v>
+        <v>-0.1953403373779224</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,31 +2858,31 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>862605736096</v>
+        <v>865503273024</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>39.13129963898917</v>
+        <v>39.26274368231047</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.95437599517003</v>
+        <v>35.07178953765305</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.17227350524027</v>
+        <v>1.176211232093934</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.776272825179666</v>
+        <v>8.805752775911561</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.462659730882843</v>
+        <v>9.494445290449629</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.5885463268517</v>
+        <v>21.6561841551857</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.25683808449663</v>
+        <v>1.260775811350294</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01566068881148337</v>
+        <v>0.01560825986573179</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009018051787142611</v>
+        <v>0.008987861100537156</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.0572910695089674</v>
+        <v>-0.05829661623234503</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3067937513722329</v>
+        <v>0.306571484245657</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2718864815.912511</v>
+        <v>2727961800.370883</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.8</v>
+        <v>147.13</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03533399358978029</v>
+        <v>0.0376613792701932</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1222720478325858</v>
+        <v>-0.1202989536621824</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,40 +2984,40 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>348974271952</v>
+        <v>349758750901</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.74962962962963</v>
+        <v>21.79703703703704</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.78252485599786</v>
+        <v>20.82924306582401</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.009996829223734</v>
+        <v>4.018737371323192</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.548346099316896</v>
+        <v>6.562619450939956</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.75536084656106</v>
+        <v>20.80060105820128</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.60054785174555</v>
+        <v>17.63633908445469</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.298212657884457</v>
+        <v>4.306953199983914</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04559624408132944</v>
+        <v>0.04549707465219136</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04653451783807983</v>
+        <v>0.0464632328767125</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.0254247114288122</v>
+        <v>0.02535486436829393</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.0292275204359673</v>
+        <v>0.02916196560864542</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04847916959282902</v>
+        <v>-0.04923027482444151</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1503064794297618</v>
+        <v>0.1508536217588138</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1266167775.389949</v>
+        <v>1271156195.918237</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>305.975</v>
+        <v>307.3</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1152189187448099</v>
+        <v>-0.1113874458053112</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2830111306385471</v>
+        <v>-0.2799062683069713</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,31 +3110,31 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>305092874075</v>
+        <v>306414054100</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.36696927374302</v>
+        <v>21.45949720670391</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.38986474284347</v>
+        <v>20.47816140363036</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.803405176118362</v>
+        <v>1.811214676431645</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.30289161701872</v>
+        <v>18.38215080941205</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.329367367156067</v>
+        <v>-7.361106599974048</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.28642584465816</v>
+        <v>15.34167067112691</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.160914515504563</v>
+        <v>2.168724015817847</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04949640349937432</v>
+        <v>0.04928298750641412</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03036195767628074</v>
+        <v>0.03023104458184184</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7093609924436535</v>
+        <v>0.708103734946528</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.246540985956761</v>
+        <v>0.2454213031217038</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1204944344.503112</v>
+        <v>1212556730.325525</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>503.7806</v>
+        <v>502.91</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.254354487170996</v>
+        <v>1.250458662249331</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1384389376293332</v>
+        <v>-0.1399278299386041</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,31 +3236,31 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>821464646360</v>
+        <v>820045046000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>127.8630964467005</v>
+        <v>127.6421319796954</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>37.26047429516517</v>
+        <v>37.19608323103652</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>19.88777742065125</v>
+        <v>19.85340869144171</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.22280968999167</v>
+        <v>12.20168704629299</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.032289219019233</v>
+        <v>1.030505285707633</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>76.56789012502333</v>
+        <v>76.43544000746408</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>19.86816720397047</v>
+        <v>19.83379847476093</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.01022928988756195</v>
+        <v>0.01024699806551846</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.540662423834458</v>
+        <v>2.539607170605352</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6645158515052284</v>
+        <v>0.6641659753406539</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>10050294689.56701</v>
+        <v>10086206389.26477</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1591.82</v>
+        <v>1590.42</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3678014400726015</v>
+        <v>0.3665984635952979</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2040740814816296</v>
+        <v>-0.2047740954819096</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,40 +3362,40 @@
         <v>861.1799999999999</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>613516066434</v>
+        <v>612976481246</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>50.0290293904209</v>
+        <v>50.02902757619739</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>32.76890300288574</v>
+        <v>32.74008286982795</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.04251206029297</v>
+        <v>15.04251152759182</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>24.34729898512742</v>
+        <v>24.34729810221118</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.405658856237435</v>
+        <v>3.40565873273661</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>38.15616971349922</v>
+        <v>38.15616835024811</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>14.90982506008067</v>
+        <v>14.90982452737952</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01882128342541458</v>
+        <v>0.01882128409193356</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5267227403375445</v>
+        <v>0.5280666140983499</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2824150857016017</v>
+        <v>0.2835439125716808</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004887487278712418</v>
+        <v>0.004891789590171149</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.698471322134239</v>
+        <v>1.697749691823852</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4375226644691245</v>
+        <v>0.4373966797257677</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2040826459.700114</v>
+        <v>2049755767.443559</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>210.27991</v>
+        <v>210.42</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07678840033536238</v>
+        <v>-0.07617335007689019</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1732655396107725</v>
+        <v>-0.1727147631216828</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,37 +3490,37 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>166198930275</v>
+        <v>166309655400</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>78.7565205992509</v>
+        <v>78.80898876404491</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>83.16396587710337</v>
+        <v>83.21937031388347</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.76816777780733</v>
+        <v>1.769345767328049</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.26898759069675</v>
+        <v>27.28715438785574</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4215107011594871</v>
+        <v>0.4217915146434068</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.47481011151079</v>
+        <v>29.49074178417266</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.179370501356455</v>
+        <v>2.180548490877174</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001263546038789328</v>
+        <v>-0.001262704799038385</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.05299705505104968</v>
+        <v>-0.05299705505104957</v>
       </c>
       <c r="V24" s="4" t="n">
         <v>0.1533729156417385</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.238902943540715</v>
+        <v>1.238548567843496</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3345804216929615</v>
+        <v>0.33458958159499</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1059990284.618443</v>
+        <v>1065286208.996958</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>957.33</v>
+        <v>961.25</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.04701749008230482</v>
+        <v>0.05130473540118397</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1704174212948119</v>
+        <v>-0.1670205114429067</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>282419051310</v>
+        <v>283575478750</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.5845521023766</v>
+        <v>14.64427178549665</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.21780872300822</v>
+        <v>13.27193197224745</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.394660295835912</v>
+        <v>2.404465763500852</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.340639169966271</v>
+        <v>2.350223436150625</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3418416924250365</v>
+        <v>0.3432414390477331</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.66285641098334</v>
+        <v>26.69969352244131</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.09723879113425</v>
+        <v>7.107044258799189</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1469978735762789</v>
+        <v>-0.1463984128070523</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01880229387985334</v>
+        <v>0.01872561768530559</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.576163907424641</v>
+        <v>1.575157683810657</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3163673996164783</v>
+        <v>0.3144090605382871</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1814797433.898621</v>
+        <v>1824522797.139689</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>250.2</v>
+        <v>251.065</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1416809605488851</v>
+        <v>-0.1387135506003431</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.247428262046562</v>
+        <v>-0.244826445286651</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,31 +3742,31 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>235721926800</v>
+        <v>236536872710</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>21.85152838427948</v>
+        <v>21.92707423580786</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>19.3923290539268</v>
+        <v>19.45937287739462</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.411463982517331</v>
+        <v>3.423258212512844</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.825815047021944</v>
+        <v>6.849413488331592</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2663684370874378</v>
+        <v>0.2672893351613013</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>18.11367528512422</v>
+        <v>18.16391546205536</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.252310907854176</v>
+        <v>4.26410513784969</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.05782661029902968</v>
+        <v>0.05762737895292942</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02693844924060752</v>
+        <v>0.02684563758389262</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.8934888010026703</v>
+        <v>0.8922365292547589</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3168137635713446</v>
+        <v>0.3169963833418746</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1174690553.0539</v>
+        <v>1179874380.938437</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1145.35999</v>
+        <v>1141.79</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06016513526024903</v>
+        <v>0.05686069040075314</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1139442308436159</v>
+        <v>-0.1167059915677099</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,31 +3868,31 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1078632457965</v>
+        <v>1075270456390</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.3191699565072</v>
+        <v>38.19973235195718</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.25381288957396</v>
+        <v>26.1719819802564</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.53946684731717</v>
+        <v>13.4972655316334</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.16969966870332</v>
+        <v>30.07566327223353</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4050808331259123</v>
+        <v>0.4038182305065811</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.97057273015924</v>
+        <v>25.89293695825867</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.11710493040929</v>
+        <v>14.07490361472552</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01859196786812317</v>
+        <v>0.01865009856899338</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005840958352316812</v>
+        <v>0.005859221047653246</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3386164667011203</v>
+        <v>0.3395404539757896</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3250479851309561</v>
+        <v>0.3247440627848851</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>3079033823.923071</v>
+        <v>3086276713.859749</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>200.99001</v>
+        <v>202.67</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1049478655528673</v>
+        <v>0.1141836547577644</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1345962970936491</v>
+        <v>-0.1273627556512379</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,37 +3994,37 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>317017515864</v>
+        <v>319667337600</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.15675321543408</v>
+        <v>16.29180064308682</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>14.92526753704531</v>
+        <v>15.05002149974007</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.505492937302911</v>
+        <v>2.526435343676154</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.859662060280573</v>
+        <v>2.883564759049784</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4110535789567702</v>
+        <v>0.4144894009765392</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.21645587542168</v>
+        <v>23.3110484069922</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.384799773775182</v>
+        <v>5.406739463680263</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04949330728452513</v>
+        <v>-0.04906350494783863</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08251012421265891</v>
+        <v>0.08251012421265913</v>
       </c>
       <c r="V28" s="4" t="n">
         <v>-0.3272876063513729</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02064779239525387</v>
+        <v>0.02047663689741945</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.384843569200202</v>
+        <v>1.38214262173795</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2702874908851359</v>
+        <v>0.2658728935180297</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>888563291.6675527</v>
+        <v>894197077.1149739</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>925.46</v>
+        <v>924.91</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.934056054157234</v>
+        <v>1.932312347427838</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2625816733067728</v>
+        <v>-0.2630199203187251</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1045205269400</v>
+        <v>1044584104900</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.65297924570408</v>
+        <v>20.6407051997322</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.945241031966287</v>
+        <v>5.941707780861343</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.57814286948623</v>
+        <v>11.57126199016328</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.36415233707955</v>
+        <v>10.35799293117827</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02943655124515192</v>
+        <v>0.02941905713067389</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.02042942381412</v>
+        <v>15.01101040441284</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.37189300795356</v>
+        <v>11.36476191483705</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02504005745687068</v>
+        <v>0.02505548938147838</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4153,7 +4153,7 @@
         <v>2.473867440303503</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.765110056317434</v>
+        <v>1.765110056317433</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005726881766905107</v>
+        <v>0.0005730287271193955</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.881697109418158</v>
+        <v>2.880939857176743</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8123940601083595</v>
+        <v>0.8123984350281792</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>26055014840.47032</v>
+        <v>26143216729.74398</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>146.26</v>
+        <v>145.13</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.008070511853994211</v>
+        <v>-0.01573412679728003</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2488933167630415</v>
+        <v>-0.2546963425531259</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>151212656120</v>
+        <v>150044392060</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>90.84472049689441</v>
+        <v>90.14285714285715</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>30.85835527126522</v>
+        <v>30.61994462271791</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>10.26423134129785</v>
+        <v>10.18493022400217</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>12.07147491211249</v>
+        <v>11.97821108980505</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>145.3515527950342</v>
+        <v>144.2285714285745</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>45.04518662080825</v>
+        <v>44.7044181198051</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.66811404561499</v>
+        <v>10.58740936872115</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03028847000984748</v>
+        <v>0.0305285068130404</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7006968259160118</v>
+        <v>0.7028574811428264</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6291368994173632</v>
+        <v>0.6279845241431647</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2194783123.786512</v>
+        <v>2211021975.49855</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.47</v>
+        <v>27.48</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09094518137688445</v>
+        <v>0.09134232195983927</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05956864087641223</v>
+        <v>-0.05922629236562826</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>156563616800</v>
+        <v>156620608591</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.29756871035941</v>
+        <v>36.3107822410148</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.408847936443443</v>
+        <v>9.412273072204799</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.457981926651595</v>
+        <v>2.458876673433183</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.837674961849982</v>
+        <v>1.838343937081817</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6071009279874272</v>
+        <v>-0.6073219330576811</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.33060969581749</v>
+        <v>17.33512425467364</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.434777957799548</v>
+        <v>3.435672704581135</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.07016955934298523</v>
+        <v>0.07014402573730834</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06261376046596287</v>
+        <v>0.06259097525473072</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3495117154943911</v>
+        <v>0.349471422315504</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.209183226316025</v>
+        <v>0.2090637124622439</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>966922991.4588209</v>
+        <v>971346891.2394346</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>173.175</v>
+        <v>173.55499</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.03074225142572651</v>
+        <v>0.03300396211213763</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1335618151798669</v>
+        <v>-0.1316606294091159</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1229291207489</v>
+        <v>1231988604084</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.38409031764871</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003598314060420221</v>
+        <v>0.003606209676761027</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.341654943554526</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2051.097230441963</v>
+        <v>2046.604265839818</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2653.390795539407</v>
+        <v>2647.579098361404</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.73235166738848</v>
+        <v>1.728558769759371</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9147973844433476</v>
+        <v>0.9145773377026215</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3243135688.615308</v>
+        <v>3255470748.41807</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>541.96</v>
+        <v>540.72</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.451808244635062</v>
+        <v>0.4484865193724088</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1933078308500662</v>
+        <v>-0.1951535358647277</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>68309043786</v>
+        <v>68152753259</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.827574172251887</v>
+        <v>1.827355259445048</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4040591364180168</v>
+        <v>0.4040257412906711</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3799367435.75175</v>
+        <v>3821786215.378174</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>144.5801</v>
+        <v>143.72</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1017079668134842</v>
+        <v>-0.1070518625345669</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3592443715653253</v>
+        <v>-0.3630561957099805</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1890509933191</v>
+        <v>1879263381324</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-93.88318181818181</v>
+        <v>-93.32467532467533</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>130.4648730500136</v>
+        <v>129.6887438502806</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>114.0579145213273</v>
+        <v>113.37938952181</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.663976186882977</v>
+        <v>6.624332515877508</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9388318181818182</v>
+        <v>-0.9332467532467532</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>440.6892088291337</v>
+        <v>437.9902522975762</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>110.7904635409351</v>
+        <v>110.1119385414178</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01503456792317652</v>
+        <v>-0.01512454309622907</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.471652279223203</v>
+        <v>3.479191573207032</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7839797738368991</v>
+        <v>0.7852970988250992</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14218060076.60062</v>
+        <v>14275245925.48665</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>757.21</v>
+        <v>757.23</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1083771520148606</v>
+        <v>0.1084064273057843</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02843322170471019</v>
+        <v>-0.02840755995226907</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>806609037109</v>
+        <v>806630341874</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9952684723030731</v>
+        <v>0.9951926994038455</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1152769646468357</v>
+        <v>0.1152681222637806</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29338901279.6058</v>
+        <v>29461852178.78012</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>413.69</v>
+        <v>413.505</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.2943588090495732</v>
+        <v>0.2937799785734336</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1363465553235909</v>
+        <v>-0.1367327766179541</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2145594911200</v>
+        <v>2144635412400</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>27.64576330126348</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6311629187197041</v>
+        <v>0.6308806659701497</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>13.92836064111815</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.80131101070088</v>
+        <v>42.82090749088123</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.78428010529495</v>
+        <v>42.80386896593625</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2658995866470062</v>
+        <v>0.266018548747899</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.182894938145429</v>
+        <v>2.182888178698641</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3625210639033964</v>
+        <v>0.3625931373426965</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4058432163.025561</v>
+        <v>4075974924.145986</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>27.87</v>
+        <v>27.95</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.0224482716150064</v>
+        <v>-0.01964223866664627</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.07099999999999995</v>
+        <v>-0.06833333333333336</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>69873899885</v>
+        <v>70074470821</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-21.94488188976378</v>
+        <v>-22.00787401574803</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-81.65673422767294</v>
+        <v>-81.89112743679435</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.934761176381005</v>
+        <v>1.940314850366884</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.131115475972958</v>
+        <v>2.137232779097387</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1633107489470793</v>
+        <v>0.1637795275590552</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.28560328677686</v>
+        <v>16.3187555076033</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.728171116848955</v>
+        <v>2.733724790834833</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03119906007232875</v>
+        <v>0.03110976043713048</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2399821929974742</v>
+        <v>0.2397005087168364</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1904242206290057</v>
+        <v>0.1897805727521357</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>505854941.2946819</v>
+        <v>507656061.6698687</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>322.32999</v>
+        <v>324.61</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1352185751100595</v>
+        <v>-0.1291015200493023</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1681592041084932</v>
+        <v>-0.1622751554878835</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>217672663232</v>
+        <v>219212379100</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.54699757428745</v>
+        <v>19.68526379624015</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.58836791902805</v>
+        <v>16.70570619319566</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.589091185422193</v>
+        <v>2.607405220463169</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.375138075262544</v>
+        <v>6.420232788798134</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.212084565741844</v>
+        <v>1.220658279068169</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.362508624494419</v>
+        <v>9.424784788060185</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.753305618117588</v>
+        <v>2.771619653158564</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.06914970293700716</v>
+        <v>0.0686640054808839</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01098253376919721</v>
+        <v>0.01090539416530606</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9614939136553785</v>
+        <v>0.9593465801215575</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2234581573750339</v>
+        <v>0.2214287084264153</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>755198188.8363749</v>
+        <v>758068790.3711588</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>143.91499</v>
+        <v>143.08</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2646518570181891</v>
+        <v>-0.2689183225608568</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5632322003034902</v>
+        <v>-0.5657663125948407</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>414542820711</v>
+        <v>412137647600</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.20910339506172</v>
+        <v>22.08024691358025</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.04313808826583</v>
+        <v>15.9500563330413</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.775426957256503</v>
+        <v>5.741917990442621</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.392677474689989</v>
+        <v>6.355587371952316</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4833746033042848</v>
+        <v>0.4805700798838056</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.15972483327147</v>
+        <v>14.0959609650053</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.441169465302256</v>
+        <v>7.407660498488374</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06928114193544857</v>
+        <v>-0.06968545622377643</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.0138970929991379</v>
+        <v>0.01397819401733296</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.068944190557603</v>
+        <v>2.070672950189584</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5570941813061446</v>
+        <v>0.5579223453673944</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4122497288.122352</v>
+        <v>4141311523.70549</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 11:57 ET</t>
+          <t>2026-09-15 13:44 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -442,11 +442,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>330.54</v>
+        <v>331.34</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2196597472021709</v>
+        <v>0.2226116676891365</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.04071741590968447</v>
+        <v>-0.03839568157413598</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,40 +714,40 @@
         <v>236.32</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4854758652240</v>
+        <v>4866508537040</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>37.73287671232877</v>
+        <v>37.82420091324201</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.54881822833622</v>
+        <v>34.632436109932</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.39957039871643</v>
+        <v>10.42474029137382</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.16800509765626</v>
+        <v>45.27732440569197</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.152949010654489</v>
+        <v>1.15573947234906</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.08056767802666</v>
+        <v>29.14943400068848</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.49577361398217</v>
+        <v>10.52062888298134</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.0281535859500535</v>
+        <v>0.02808646054140818</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09216114030149525</v>
+        <v>0.09216114030149503</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.117919601370001</v>
+        <v>0.1179196013700008</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.00320687360077449</v>
+        <v>0.003199130802197139</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3089245585263142</v>
+        <v>0.3085138427277651</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2951320169816031</v>
+        <v>0.2948156993843422</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13334541883.37132</v>
+        <v>13507548538.13052</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>499.4401</v>
+        <v>497.12</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.05603268368460101</v>
+        <v>0.05112698742709854</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.09802770353247137</v>
+        <v>-0.1022177273712346</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3708617434555</v>
+        <v>3691389416000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.745</v>
+        <v>27.61777777777777</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.34410903416674</v>
+        <v>24.23102086329266</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.1752805592471</v>
+        <v>11.1240373072484</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.386586608557666</v>
+        <v>8.348130663875747</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8812738979118314</v>
+        <v>0.8772328950760488</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.38996537907373</v>
+        <v>18.30802343881765</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.50035778042967</v>
+        <v>11.44911452843096</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01806361496263324</v>
+        <v>0.01814682561250536</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1397007777553141</v>
+        <v>0.1397694687975644</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2254411884306673</v>
+        <v>0.2255150471434921</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.00728816128300471</v>
+        <v>0.007322175732217573</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.557009999363542</v>
+        <v>0.5579241349035604</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4357644859792686</v>
+        <v>0.4370350965003246</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>11612961037.81489</v>
+        <v>11776456198.26951</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>343.41</v>
+        <v>344.98</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.08967160606323232</v>
+        <v>0.09465336087968867</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1595653557181664</v>
+        <v>-0.1557230611096155</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4155986036725</v>
+        <v>4174986351444</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.87487586891758</v>
+        <v>16.95283018867924</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.53747084019584</v>
+        <v>20.63136393946234</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.250554667404556</v>
+        <v>9.293288060058403</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.447724925056209</v>
+        <v>6.477510507744192</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1500692525678599</v>
+        <v>0.1507625048674289</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.89490294123615</v>
+        <v>12.95366175149261</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.378048129565832</v>
+        <v>9.420781522219681</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01291620782126628</v>
+        <v>0.01285681513087965</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1783371964239068</v>
+        <v>-0.1782981368355891</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2898444330050911</v>
+        <v>0.2899057486593579</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002504295157392038</v>
+        <v>0.002492898139022552</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7727868830899939</v>
+        <v>0.772002268076359</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3686586514585669</v>
+        <v>0.3675627713635436</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8343403709.357497</v>
+        <v>8473543582.787918</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>248.505</v>
+        <v>248.42</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.0971523178807947</v>
+        <v>0.09677704194260484</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1347318941504179</v>
+        <v>-0.1350278551532034</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,37 +1094,37 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2673193135500</v>
+        <v>2672278782000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.72261904761904</v>
+        <v>19.71587301587302</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.06411294399523</v>
+        <v>22.05656601495863</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.446257651995669</v>
+        <v>3.445078875309406</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.84558170479678</v>
+        <v>4.843924295710814</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2232560430263476</v>
+        <v>0.2231796793167352</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.09503090390831</v>
+        <v>11.09185455733729</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.633076222798061</v>
+        <v>3.632036125721947</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004348906804326129</v>
+        <v>-0.004350219774337901</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1061222765818658</v>
+        <v>-0.1061222765818656</v>
       </c>
       <c r="V5" s="4" t="n">
         <v>0.1785740462863659</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8354738263803998</v>
+        <v>0.8356151450503818</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4606698173553007</v>
+        <v>0.4607508117976845</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8780433325.741096</v>
+        <v>8923821402.908955</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>211.56</v>
+        <v>212.17</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1202541337702483</v>
+        <v>0.1234842104463678</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1056058171979369</v>
+        <v>-0.1030269721822947</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,31 +1220,31 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5124194760000</v>
+        <v>5138969570000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>26.61132075471697</v>
+        <v>26.6880503144654</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>15.82247194428739</v>
+        <v>15.86809355463913</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>16.91326426136007</v>
+        <v>16.96203099987127</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.3493187296929</v>
+        <v>22.41375947664465</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2136146836092928</v>
+        <v>0.214230607966457</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>21.99973363804046</v>
+        <v>22.06296383314717</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>16.96745132340272</v>
+        <v>17.01621806191392</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.024785552842648</v>
+        <v>0.02471429306400816</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002457931556059747</v>
+        <v>0.002450864872507895</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.327454700976176</v>
+        <v>1.326698277194909</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4128248870097586</v>
+        <v>0.4129865725171606</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26912935736.83827</v>
+        <v>27161914412.29845</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>667.6900000000001</v>
+        <v>670.24</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.02656789958481909</v>
+        <v>0.03048850367345501</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1556777946383407</v>
+        <v>-0.1524532119372787</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,37 +1346,37 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1700931307923</v>
+        <v>1707427398677</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.81196581196582</v>
+        <v>24.90672612411743</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.19258762626217</v>
+        <v>20.26970589738644</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.452119220860643</v>
+        <v>7.48057988975588</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.499996822613803</v>
+        <v>6.524821205033287</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.086452991452988</v>
+        <v>-5.105878855444069</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.79045229306448</v>
+        <v>16.8511225967293</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.876464669670709</v>
+        <v>7.904925338565946</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02409033204876193</v>
+        <v>0.02399867779546601</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2287660339131454</v>
+        <v>0.2287660339131452</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>0.271779256228301</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003145172160733274</v>
+        <v>0.00313320601575555</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7746422790702998</v>
+        <v>0.7737419082192315</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4138328542694102</v>
+        <v>0.4141160903999248</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>9915542588.381979</v>
+        <v>10085256584.06548</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>357.35</v>
+        <v>356.58</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1842628026905235</v>
+        <v>-0.186020512616166</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2836236794098189</v>
+        <v>-0.2851672914620211</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,31 +1472,31 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1411370761246</v>
+        <v>1408329609753</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>302.8389830508475</v>
+        <v>302.1864406779661</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>169.8855365788554</v>
+        <v>169.5194756773143</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.62077187818836</v>
+        <v>13.59142251665235</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.31762128992148</v>
+        <v>13.2889251421861</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.061488422057767</v>
+        <v>-8.044117927906418</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>116.8518258435318</v>
+        <v>116.5989865108913</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.56405448079985</v>
+        <v>13.53470511926384</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004082555879868969</v>
+        <v>0.004091371764178535</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.539698085918128</v>
+        <v>1.539929601112977</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5749762562376446</v>
+        <v>0.575054620584088</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12660774433.6684</v>
+        <v>12770236754.12082</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>338.11</v>
+        <v>339.27</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02735744563249742</v>
+        <v>-0.02402046842665828</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3169494949494949</v>
+        <v>-0.3146060606060607</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,31 +1598,31 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1608585373800</v>
+        <v>1614104166600</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>41.94913151364764</v>
+        <v>42.09305210918114</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.50635538677835</v>
+        <v>18.56984765925968</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.05289744343688</v>
+        <v>18.11483397602801</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.16443234025479</v>
+        <v>16.21988985856154</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4174146254575828</v>
+        <v>0.4188467066309606</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>31.4568504257314</v>
+        <v>31.56244698161223</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.45067981010953</v>
+        <v>18.51261634270066</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02449543595371462</v>
+        <v>0.02441168346835987</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007512348052408979</v>
+        <v>0.007486662540159755</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.605762204037337</v>
+        <v>1.605083990203484</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3900649704807758</v>
+        <v>0.3892366707697041</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8653051495.002264</v>
+        <v>8765279017.475498</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>908.5700000000001</v>
+        <v>901.35</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.06327677004095977</v>
+        <v>0.05482738443534241</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.171390788873689</v>
+        <v>-0.1779753761969904</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>402931715030</v>
+        <v>399729796650</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.63385233550979</v>
+        <v>45.27122049221497</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>40.08638756160298</v>
+        <v>39.7678389432304</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.37244399455698</v>
+        <v>1.361537795099919</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>12.03662061267122</v>
+        <v>11.94097096451699</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.599777548073477</v>
+        <v>3.571171723649282</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>27.10557809467865</v>
+        <v>26.88429831720802</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.335950553089885</v>
+        <v>1.325044353632824</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02185481974121684</v>
+        <v>0.02202988136936526</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006097493863984063</v>
+        <v>0.006146336051478338</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1889410365998826</v>
+        <v>-0.187307937102089</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1724361417636054</v>
+        <v>0.176444822708197</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1688383985.74694</v>
+        <v>1730378059.199019</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>78.425</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1380920777971869</v>
+        <v>-0.1438619427529596</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3718965241069999</v>
+        <v>-0.3761012333813871</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,31 +1850,31 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>326556994422</v>
+        <v>324370925922</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>24.28018575851393</v>
+        <v>24.11764705882353</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.91359965226808</v>
+        <v>20.77359786945086</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.75112335256892</v>
+        <v>6.705929348604045</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.89630940458049</v>
+        <v>10.82336630687689</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7136005814392511</v>
+        <v>0.708823529411765</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.84311064430485</v>
+        <v>10.77166358135712</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.858834572511611</v>
+        <v>6.813640568546736</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03366826675833497</v>
+        <v>0.03389517099520758</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09960033919145793</v>
+        <v>0.1010625785780117</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3787138989192149</v>
+        <v>0.3818256902419801</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2167131638.558993</v>
+        <v>2197050104.863083</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>514.9349999999999</v>
+        <v>516.76</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.03639930295727201</v>
+        <v>0.04007244369910756</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04240897087811968</v>
+        <v>-0.03901513742700935</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1110639405941</v>
+        <v>1114575663752</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.94107219666281</v>
+        <v>12.97140516110474</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.21307030926502</v>
+        <v>23.2953406022426</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.886271374283508</v>
+        <v>2.893036591696626</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.477803486643819</v>
+        <v>1.481267354237733</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3564935832355907</v>
+        <v>0.3573291791599261</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.67127684030374</v>
+        <v>15.70529010834619</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.117007011307894</v>
+        <v>3.123772228721012</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02180920331243488</v>
+        <v>0.02175820361113868</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4425092405162084</v>
+        <v>-0.4431759817301831</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06033784945499487</v>
+        <v>0.05906971911748538</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.05462322429184981</v>
+        <v>0.05340833797176848</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1394831559233317</v>
+        <v>0.1395663401249826</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2058681652.38444</v>
+        <v>2101104811.616488</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>345.14001</v>
+        <v>352.49</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06040309189524296</v>
+        <v>0.08298509309933144</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.05828100954979532</v>
+        <v>-0.03822646657571616</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,31 +2102,31 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>924806120651</v>
+        <v>944500479900</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>14.83834952708513</v>
+        <v>15.15434221840069</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.78103793882076</v>
+        <v>14.07451446459346</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.107202899715421</v>
+        <v>3.173372844745038</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.569399585387536</v>
+        <v>2.624116687755941</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.776924842530758</v>
+        <v>0.793469982641731</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>19.88907385842636</v>
+        <v>20.10047745706312</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.225338321526847</v>
+        <v>6.291508266556463</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1757492693555999</v>
+        <v>-0.1720846134638369</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01738424936593123</v>
+        <v>0.01702175948253851</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7760824012456902</v>
+        <v>0.7694580071536945</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.17336066211516</v>
+        <v>0.1701887373192562</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>1997817113.647717</v>
+        <v>2109494571.052096</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>375.09</v>
+        <v>375.62</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08257327437801543</v>
+        <v>0.08410294415172404</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.02718053790492003</v>
+        <v>-0.02580594963301086</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,31 +2228,31 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>700310738374</v>
+        <v>701300273396</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.86830926083262</v>
+        <v>31.91333899745115</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>25.07119173837878</v>
+        <v>25.10661718726129</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.74156487983277</v>
+        <v>15.76380761994246</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.40242013730172</v>
+        <v>20.43124863892205</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.149014275812727</v>
+        <v>2.152050820551805</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.4637793652141</v>
+        <v>24.49650400013747</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>16.00087780904963</v>
+        <v>16.02228181523108</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03000365309923089</v>
+        <v>0.02996291431378736</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007144951878215896</v>
+        <v>0.007134870347691817</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3041571210899403</v>
+        <v>0.3037793366634721</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1804553510512027</v>
+        <v>0.1804353882007724</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2235291208.367525</v>
+        <v>2272636613.31724</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>571.78998</v>
+        <v>573.27</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01537828750394787</v>
+        <v>0.01800649056037718</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.04958282636880418</v>
+        <v>-0.04712276852498254</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>501480395169</v>
+        <v>502778427720</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.39977924217463</v>
+        <v>31.48105436573311</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.79249058584847</v>
+        <v>25.85925181506215</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.29411382062537</v>
+        <v>14.33111272468147</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.8803711210123</v>
+        <v>90.11301728747104</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.387758100435396</v>
+        <v>1.391350170628382</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.27873011254295</v>
+        <v>23.33742212515826</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.67469700906422</v>
+        <v>14.71169591312031</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03279888936527018</v>
+        <v>0.03271421185389437</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005893772395242043</v>
+        <v>0.00587855635215518</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2936600351574814</v>
+        <v>0.292833232438592</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.196888823927035</v>
+        <v>0.1965507417402079</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1506927344.18854</v>
+        <v>1532145762.413241</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>376.23</v>
+        <v>375.93</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1184007337282293</v>
+        <v>0.1175089382304795</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1849789870456219</v>
+        <v>-0.1856288722325722</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,31 +2480,31 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>341671169117</v>
+        <v>341398725796</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.19329946627227</v>
+        <v>24.17400810237284</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.36258950369534</v>
+        <v>17.34874484258084</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7590516698924086</v>
+        <v>0.7584464137969337</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.4624036416549</v>
+        <v>3.459642774386218</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7330632906164221</v>
+        <v>-0.7324787572533598</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>14.99880328832046</v>
+        <v>14.98822830400186</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8584520640016527</v>
+        <v>0.857846807906178</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06912201594601833</v>
+        <v>0.06917717675991604</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02408101427318396</v>
+        <v>0.02410023142606336</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4299634297352862</v>
+        <v>0.429900752815327</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2286907757075497</v>
+        <v>0.2290281710049149</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1774152860.888757</v>
+        <v>1805017710.513059</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>169.225</v>
+        <v>169.28</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3797390778205074</v>
+        <v>0.3801875083082022</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.04072898361770871</v>
+        <v>-0.04041720990873532</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,31 +2606,31 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>701346243500</v>
+        <v>701574188800</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.77927927927928</v>
+        <v>21.78635778635779</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>15.31237912849429</v>
+        <v>15.31735582137103</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.942464530825901</v>
+        <v>1.943095853320778</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.723108703350297</v>
+        <v>2.723993743850721</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.132554429429431</v>
+        <v>2.133247533247534</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>10.20711790462931</v>
+        <v>10.21029152523495</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>2.030483142690966</v>
+        <v>2.031114465185841</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04356336158233091</v>
+        <v>0.04354920760733665</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02434628453242724</v>
+        <v>0.02433837429111531</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.550269401398622</v>
+        <v>-0.5501222862545879</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.23646778116629</v>
+        <v>0.2367982598190592</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2207212313.786093</v>
+        <v>2242445686.619956</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>265.11</v>
+        <v>267.2</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2785627788583174</v>
+        <v>0.2886423541584338</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.05678300779165324</v>
+        <v>-0.0493471377236987</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>638888169066</v>
+        <v>643924856755</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.6485549132948</v>
+        <v>30.89017341040462</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.41966608469119</v>
+        <v>21.58852845169736</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.523993598076157</v>
+        <v>6.57542563239694</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.613125784091043</v>
+        <v>7.673144013840015</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.794775022817165</v>
+        <v>-3.824691207788263</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.78839585752401</v>
+        <v>19.93771068288272</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.816184879514751</v>
+        <v>6.867616913835534</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02928211994808027</v>
+        <v>0.02905307941407518</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2774,7 +2774,7 @@
         <v>0.2573506474441706</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.7045206220833461</v>
+        <v>0.6790736145574855</v>
       </c>
       <c r="Z18" s="4" t="n">
         <v>0.2681126121986337</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01991626117460677</v>
+        <v>0.01976047904191617</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1715966951694204</v>
+        <v>-0.1742644611003474</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.210161360821697</v>
+        <v>0.2096265966257698</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1633273434.228108</v>
+        <v>1659349928.772552</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>108.7578</v>
+        <v>108.09</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.03549310092594027</v>
+        <v>-0.04141541369064916</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1953403373779224</v>
+        <v>-0.2002811482687185</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,31 +2858,31 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>865503273024</v>
+        <v>860188867200</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>39.26274368231047</v>
+        <v>39.02166064981949</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>35.07178953765305</v>
+        <v>34.85644000821016</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.176211232093934</v>
+        <v>1.168989001956947</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.805752775911561</v>
+        <v>8.751683259024002</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.494445290449629</v>
+        <v>9.436147029865449</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.6561841551857</v>
+        <v>21.53212883587385</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.260775811350294</v>
+        <v>1.253553581213307</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01560825986573179</v>
+        <v>0.01570469058030608</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.008987861100537156</v>
+        <v>0.009043389767786104</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05829661623234503</v>
+        <v>-0.0564845450081595</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.306571484245657</v>
+        <v>0.3071438071916167</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2727961800.370883</v>
+        <v>2764095681.859236</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>147.13</v>
+        <v>146.66</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.0376613792701932</v>
+        <v>0.03434661784657456</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1202989536621824</v>
+        <v>-0.1231091180866966</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,37 +2984,37 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>349758750901</v>
+        <v>348641462700</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.79703703703704</v>
+        <v>21.72740740740741</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.82924306582401</v>
+        <v>20.76270500940494</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.018737371323192</v>
+        <v>4.005899700110304</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.562619450939956</v>
+        <v>6.541655465743587</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.80060105820128</v>
+        <v>20.73415449735472</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.63633908445469</v>
+        <v>17.5837707113955</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.306953199983914</v>
+        <v>4.294115528771027</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04549707465219136</v>
+        <v>0.04564287872350072</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.0464632328767125</v>
+        <v>0.04646323287671228</v>
       </c>
       <c r="V20" s="4" t="n">
         <v>0.02535486436829393</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02916196560864542</v>
+        <v>0.02925542070094096</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04923027482444151</v>
+        <v>-0.04817637593459839</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1508536217588138</v>
+        <v>0.1501291257052752</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1271156195.918237</v>
+        <v>1296691230.419818</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>307.3</v>
+        <v>305.48</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1113874458053112</v>
+        <v>-0.1166502992014529</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2799062683069713</v>
+        <v>-0.2841710603397773</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>306414054100</v>
+        <v>304599301160</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.45949720670391</v>
+        <v>21.33240223463687</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.47816140363036</v>
+        <v>20.35687844315328</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.811214676431645</v>
+        <v>1.800487664680569</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.38215080941205</v>
+        <v>18.27328157910573</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.361106599974048</v>
+        <v>-7.317510068858028</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.34167067112691</v>
+        <v>15.26578721137362</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.168724015817847</v>
+        <v>2.157997004066771</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04928298750641412</v>
+        <v>0.0495766075053066</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.0479210893854749</v>
+        <v>0.04792108938547468</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03023104458184184</v>
+        <v>0.03041115621317271</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.708103734946528</v>
+        <v>0.709807233714538</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2454213031217038</v>
+        <v>0.2470891658608973</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1212556730.325525</v>
+        <v>1240432383.593238</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>502.91</v>
+        <v>504.2</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.250458662249331</v>
+        <v>1.256231249142218</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1399278299386041</v>
+        <v>-0.1377216835120484</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,31 +3236,31 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>820045046000</v>
+        <v>822148520000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>127.6421319796954</v>
+        <v>127.9695431472081</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>37.19608323103652</v>
+        <v>37.29149383605141</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>19.85340869144171</v>
+        <v>19.9043340999879</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.20168704629299</v>
+        <v>12.23298524336547</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.030505285707633</v>
+        <v>1.033148605225166</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>76.43544000746408</v>
+        <v>76.63169621197984</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>19.83379847476093</v>
+        <v>19.88472388330711</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.01024699806551846</v>
+        <v>0.01022078103357773</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.539607170605352</v>
+        <v>2.538601164745802</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6641659753406539</v>
+        <v>0.6646592840893162</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>10086206389.26477</v>
+        <v>10183663363.32363</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1590.42</v>
+        <v>1591.48</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3665984635952979</v>
+        <v>0.3675092886423992</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2047740954819096</v>
+        <v>-0.2042440848816977</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>861.1799999999999</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>612976481246</v>
+        <v>613385024317</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>50.02902757619739</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>32.74008286982795</v>
+        <v>32.76190382771456</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.04251152759182</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5280666140983499</v>
+        <v>0.5270488503746813</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2835439125716808</v>
+        <v>0.2826890123849841</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004891789590171149</v>
+        <v>0.004888531429864026</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.697749691823852</v>
+        <v>1.697316872671875</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4373966797257677</v>
+        <v>0.4375157394443653</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2049755767.443559</v>
+        <v>2072147632.963916</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>210.42</v>
+        <v>209.69</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07617335007689019</v>
+        <v>-0.07937833750414935</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1727147631216828</v>
+        <v>-0.1755848240613328</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,31 +3490,31 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>166309655400</v>
+        <v>165732685300</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>78.80898876404491</v>
+        <v>78.53558052434454</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>83.21937031388347</v>
+        <v>82.93066134929298</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.769345767328049</v>
+        <v>1.763207461035161</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.28715438785574</v>
+        <v>27.19248837367869</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4217915146434068</v>
+        <v>0.4203282135993536</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.49074178417266</v>
+        <v>29.40772450359712</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.180548490877174</v>
+        <v>2.174410184584286</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001262704799038385</v>
+        <v>-0.001267100690608312</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.238548567843496</v>
+        <v>1.239882327225976</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.33458958159499</v>
+        <v>0.3346242894193652</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1065286208.996958</v>
+        <v>1079004709.662687</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>961.25</v>
+        <v>976.67</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.05130473540118397</v>
+        <v>0.0681693585688159</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1670205114429067</v>
+        <v>-0.1536581772805657</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>283575478750</v>
+        <v>288124486690</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.64427178549665</v>
+        <v>14.87918951858623</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.27193197224745</v>
+        <v>13.48483516185687</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.404465763500852</v>
+        <v>2.443037271509365</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.350223436150625</v>
+        <v>2.387924809763569</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3432414390477331</v>
+        <v>0.3487475852012999</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.69969352244131</v>
+        <v>26.8445986904724</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.107044258799189</v>
+        <v>7.145615766807702</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1463984128070523</v>
+        <v>-0.1440870245945704</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01872561768530559</v>
+        <v>0.01842997122876714</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.575157683810657</v>
+        <v>1.570100090379177</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3144090605382871</v>
+        <v>0.3090673866755244</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1824522797.139689</v>
+        <v>1862475948.847695</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>251.065</v>
+        <v>248.37</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1387135506003431</v>
+        <v>-0.1479588336192109</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.244826445286651</v>
+        <v>-0.2529326836311134</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,31 +3742,31 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>236536872710</v>
+        <v>233997821580</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>21.92707423580786</v>
+        <v>21.69170305676856</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>19.45937287739462</v>
+        <v>19.25049067595444</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.423258212512844</v>
+        <v>3.386512027729135</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.849413488331592</v>
+        <v>6.775890020898642</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2672893351613013</v>
+        <v>0.2644201787346401</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>18.16391546205536</v>
+        <v>18.00738681832193</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.26410513784969</v>
+        <v>4.22735895306598</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.05762737895292942</v>
+        <v>0.05825267905470558</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02684563758389262</v>
+        <v>0.02713693280186818</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.8922365292547589</v>
+        <v>0.8958469001438731</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3169963833418746</v>
+        <v>0.3171415193881565</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1179874380.938437</v>
+        <v>1199632443.267902</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1141.79</v>
+        <v>1136.98</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05686069040075314</v>
+        <v>0.05240847070989285</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1167059915677099</v>
+        <v>-0.1204270297450973</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,31 +3868,31 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1075270456390</v>
+        <v>1070740682180</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.19973235195718</v>
+        <v>38.03880896620944</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.1719819802564</v>
+        <v>26.0617277011639</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.4972655316334</v>
+        <v>13.4404058225738</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.07566327223353</v>
+        <v>29.94896401900882</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4038182305065811</v>
+        <v>0.4021170720722484</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.89293695825867</v>
+        <v>25.78833483078088</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.07490361472552</v>
+        <v>14.01804390566592</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01865009856899338</v>
+        <v>0.018728997911213</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005859221047653246</v>
+        <v>0.005884008513782125</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3395404539757896</v>
+        <v>0.3411813514063061</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3247440627848851</v>
+        <v>0.324628723651813</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>3086276713.859749</v>
+        <v>3123924853.497945</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>202.67</v>
+        <v>206.27</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1141836547577644</v>
+        <v>0.133974749429536</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1273627556512379</v>
+        <v>-0.1118622174381054</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,37 +3994,37 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>319667337600</v>
+        <v>325345545600</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.29180064308682</v>
+        <v>16.58118971061093</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.05002149974007</v>
+        <v>15.31735301105928</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.526435343676154</v>
+        <v>2.571312075492575</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.883564759049784</v>
+        <v>2.934785132724128</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4144894009765392</v>
+        <v>0.4218519205577083</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.3110484069922</v>
+        <v>23.5045335332402</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.406739463680263</v>
+        <v>5.451616195496685</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04906350494783863</v>
+        <v>-0.04820720680553863</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08251012421265913</v>
+        <v>0.08251012421265891</v>
       </c>
       <c r="V28" s="4" t="n">
         <v>-0.3272876063513729</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02047663689741945</v>
+        <v>0.02011926116255393</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.38214262173795</v>
+        <v>1.376706477173516</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2658728935180297</v>
+        <v>0.2623913333312874</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>894197077.1149739</v>
+        <v>922096790.9233246</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>924.91</v>
+        <v>927.6</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.932312347427838</v>
+        <v>1.940840658522518</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2630199203187251</v>
+        <v>-0.2608764940239043</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1044584104900</v>
+        <v>1047622164000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.6407051997322</v>
+        <v>20.70073644275831</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.941707780861343</v>
+        <v>5.958988590810979</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.57126199016328</v>
+        <v>11.60491574539735</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.35799293117827</v>
+        <v>10.38811802549541</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02941905713067389</v>
+        <v>0.02950461925421188</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.01101040441284</v>
+        <v>15.05579205805753</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.36476191483705</v>
+        <v>11.39866588386468</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02505548938147838</v>
+        <v>0.02498228932086626</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4153,7 +4153,7 @@
         <v>2.473867440303503</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.765110056317433</v>
+        <v>1.765110056317434</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005730287271193955</v>
+        <v>0.0005713669685209142</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.880939857176743</v>
+        <v>2.880005584881958</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8123984350281792</v>
+        <v>0.8124061229988889</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>26143216729.74398</v>
+        <v>26371464494.61606</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>145.13</v>
+        <v>141.9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.01573412679728003</v>
+        <v>-0.03763985800684921</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2546963425531259</v>
+        <v>-0.2712837525548719</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>150044392060</v>
+        <v>146705017800</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>90.14285714285715</v>
+        <v>88.13664596273293</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>30.61994462271791</v>
+        <v>29.93846993704728</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>10.18493022400217</v>
+        <v>9.958255348900353</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.97821108980505</v>
+        <v>11.7116251198466</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>144.2285714285745</v>
+        <v>141.0186335403757</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>44.7044181198051</v>
+        <v>43.75322952135282</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.58740936872115</v>
+        <v>10.36213805321749</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.0305285068130404</v>
+        <v>0.03121910939845167</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7028574811428264</v>
+        <v>0.7103996960341029</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6279845241431647</v>
+        <v>0.6278912580281349</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2211021975.49855</v>
+        <v>2235182723.005687</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.48</v>
+        <v>27.55</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09134232195983927</v>
+        <v>0.09412230604052318</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05922629236562826</v>
+        <v>-0.05682985279014041</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>156620608591</v>
+        <v>157019572000</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.3107822410148</v>
+        <v>36.40327695560254</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.412273072204799</v>
+        <v>9.436249022534287</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.458876673433183</v>
+        <v>2.465140228585782</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.838343937081817</v>
+        <v>1.84302676370466</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6073219330576811</v>
+        <v>-0.6088689685494584</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.33512425467364</v>
+        <v>17.36672782002535</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.435672704581135</v>
+        <v>3.441936259733735</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.07014402573730834</v>
+        <v>0.06996580018699834</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4405,7 +4405,7 @@
         <v>2.85781223753946</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05031934638406588</v>
+        <v>-0.05031934638406599</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06259097525473072</v>
+        <v>0.06243194192377495</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.349471422315504</v>
+        <v>0.3485226448608757</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2090637124622439</v>
+        <v>0.2082879551631476</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>971346891.2394346</v>
+        <v>990061057.8431157</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>173.55499</v>
+        <v>174.83</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.03300396211213763</v>
+        <v>0.04059285587850292</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1316606294091159</v>
+        <v>-0.1252814329314054</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1231988604084</v>
+        <v>1241039305935</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.38409031764871</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003606209676761027</v>
+        <v>0.003632702452335887</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.341654943554526</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2046.604265839818</v>
+        <v>2031.671382953652</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2647.579098361404</v>
+        <v>2628.263433149657</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.728558769759371</v>
+        <v>1.715952639707144</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9145773377026215</v>
+        <v>0.9140153423105198</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3255470748.41807</v>
+        <v>3276414380.73785</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>540.72</v>
+        <v>542.11</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4484865193724088</v>
+        <v>0.4522100662394151</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1951535358647277</v>
+        <v>-0.1930845600821637</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>68152753259</v>
+        <v>68327949898</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.827355259445048</v>
+        <v>1.826660385047441</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4040257412906711</v>
+        <v>0.4040658528778202</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3821786215.378174</v>
+        <v>3866996224.813599</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>143.72</v>
+        <v>143.49</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1070518625345669</v>
+        <v>-0.1084808777837809</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3630561957099805</v>
+        <v>-0.3640755185250841</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1879263381324</v>
+        <v>1876255932273</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-93.32467532467533</v>
+        <v>-93.17532467532467</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>129.6887438502806</v>
+        <v>129.4811985463176</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>113.37938952181</v>
+        <v>113.1979446318552</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.624332515877508</v>
+        <v>6.613731371439352</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9332467532467532</v>
+        <v>-0.9317532467532468</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>437.9902522975762</v>
+        <v>437.2685222637389</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>110.1119385414178</v>
+        <v>109.9304936514631</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01512454309622907</v>
+        <v>-0.0151487862135987</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.479191573207032</v>
+        <v>3.482105313712486</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7852970988250992</v>
+        <v>0.7857677087761391</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14275245925.48665</v>
+        <v>14385635156.2712</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>757.23</v>
+        <v>757.39</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1084064273057843</v>
+        <v>0.1086406296331734</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02840755995226907</v>
+        <v>-0.02820226593274056</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>806630341874</v>
+        <v>806800779990</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9951926994038455</v>
+        <v>0.9952239310757131</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1152681222637806</v>
+        <v>0.1152127708860105</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29461852178.78012</v>
+        <v>30114175362.7381</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>413.505</v>
+        <v>413.75</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.2937799785734336</v>
+        <v>0.2945465378526455</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1367327766179541</v>
+        <v>-0.1362212943632568</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2144635412400</v>
+        <v>2145906100000</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>27.64576330126348</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6308806659701497</v>
+        <v>0.6312544601519919</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>13.92836064111815</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.82090749088123</v>
+        <v>42.7949591589531</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.80386896593625</v>
+        <v>42.77793072328573</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.266018548747899</v>
+        <v>0.2658610271903323</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.182888178698641</v>
+        <v>2.18286906950038</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3625931373426965</v>
+        <v>0.3624691173247276</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4075974924.145986</v>
+        <v>4136072980.466634</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>27.95</v>
+        <v>28.03</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01964223866664627</v>
+        <v>-0.01683620571828592</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06833333333333336</v>
+        <v>-0.06566666666666665</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70074470821</v>
+        <v>70275041757</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.00787401574803</v>
+        <v>-22.07086614173228</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-81.89112743679435</v>
+        <v>-82.12552064591577</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.940314850366884</v>
+        <v>1.945868524352762</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.137232779097387</v>
+        <v>2.143350082221816</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1637795275590552</v>
+        <v>0.164248306171031</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.3187555076033</v>
+        <v>16.35190772842975</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.733724790834833</v>
+        <v>2.739278464820712</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03110976043713048</v>
+        <v>0.0310209705394142</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2397005087168364</v>
+        <v>0.2391619887635157</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1897805727521357</v>
+        <v>0.1893262260542644</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>507656061.6698687</v>
+        <v>517302914.2458267</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>324.61</v>
+        <v>324.43</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1291015200493023</v>
+        <v>-0.1295844433307513</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1622751554878835</v>
+        <v>-0.1627396836047382</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>219212379100</v>
+        <v>219090823300</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.68526379624015</v>
+        <v>19.67434808975137</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.70570619319566</v>
+        <v>16.69644268586448</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.607405220463169</v>
+        <v>2.605959384106669</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.420232788798134</v>
+        <v>6.416672695449241</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.220658279068169</v>
+        <v>1.219981409932183</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.424784788060185</v>
+        <v>9.419868277786767</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.771619653158564</v>
+        <v>2.770173816802065</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.0686640054808839</v>
+        <v>0.06870210159094327</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01090539416530606</v>
+        <v>0.01091144468760595</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9593465801215575</v>
+        <v>0.9594673178377636</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2214287084264153</v>
+        <v>0.2215095071081895</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>758068790.3711588</v>
+        <v>770275394.8168274</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>143.08</v>
+        <v>140.37</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2689183225608568</v>
+        <v>-0.2827653406336837</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5657663125948407</v>
+        <v>-0.5739908952959029</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,37 +5296,37 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>412137647600</v>
+        <v>404331573900</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.08024691358025</v>
+        <v>21.66203703703704</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>15.9500563330413</v>
+        <v>15.64795504241688</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.741917990442621</v>
+        <v>5.633163463226382</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.355587371952316</v>
+        <v>6.235209668723416</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4805700798838056</v>
+        <v>0.4714678649237475</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.0959609650053</v>
+        <v>13.88901309384942</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.407660498488374</v>
+        <v>7.298905971272135</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06968545622377643</v>
+        <v>-0.0710308119719166</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3843366100118382</v>
+        <v>0.3843366100118384</v>
       </c>
       <c r="V39" s="4" t="n">
         <v>0.4232963938119607</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01397819401733296</v>
+        <v>0.01424805870200185</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.070672950189584</v>
+        <v>2.076681238992412</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5579223453673944</v>
+        <v>0.5630995647140897</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4141311523.70549</v>
+        <v>4198679391.222831</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:44 ET</t>
+          <t>2026-09-15 17:41 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -442,7 +442,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -699,55 +699,55 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>331.34</v>
+        <v>333.02</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2226116676891365</v>
+        <v>0.2288107007117652</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.03839568157413598</v>
+        <v>-0.03352003946948379</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>236.32</v>
+        <v>236.65</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4866508537040</v>
+        <v>4891183295120</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>37.82420091324201</v>
+        <v>38.01598173515982</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.632436109932</v>
+        <v>34.8004258678435</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.42474029137382</v>
+        <v>10.47759706595433</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.27732440569197</v>
+        <v>45.50689495256697</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.15573947234906</v>
+        <v>1.16159944190766</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.14943400068848</v>
+        <v>29.29588390204527</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.52062888298134</v>
+        <v>10.57348565756186</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02808646054140818</v>
+        <v>0.02794477159266767</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09216114030149503</v>
+        <v>0.09239989991868391</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1179196013700008</v>
+        <v>0.118190305206118</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003199130802197139</v>
+        <v>0.003182992012491742</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3085138427277651</v>
+        <v>0.3072398750722112</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2948156993843422</v>
+        <v>0.2950645760019249</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13507548538.13052</v>
+        <v>12936506731.42503</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>497.12</v>
+        <v>494.6302</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.05112698742709854</v>
+        <v>0.04586247187090287</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1022177273712346</v>
+        <v>-0.1067142237954201</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3691389416000</v>
+        <v>3672901281610</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.61777777777777</v>
+        <v>27.47945555555555</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.23102086329266</v>
+        <v>24.08985946621722</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.1240373072484</v>
+        <v>11.06832313745521</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.348130663875747</v>
+        <v>8.306319480002802</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8772328950760488</v>
+        <v>0.8728393191544196</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.30802343881765</v>
+        <v>18.21713587189607</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.44911452843096</v>
+        <v>11.39227703494767</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01814682561250536</v>
+        <v>0.01824002173255826</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1397694687975644</v>
+        <v>0.1407063455098934</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2255150471434921</v>
+        <v>0.226123141342697</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007322175732217573</v>
+        <v>0.007359033071575492</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5579241349035604</v>
+        <v>0.554309862636615</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4370350965003246</v>
+        <v>0.4338715710278684</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>11776456198.26951</v>
+        <v>11034021304.62094</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>344.98</v>
+        <v>346.02</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09465336087968867</v>
+        <v>0.09795337680906102</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1557230611096155</v>
+        <v>-0.1531778468466264</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4174986351444</v>
+        <v>4187572547182</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.95283018867924</v>
+        <v>17.01042701092353</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.63136393946234</v>
+        <v>20.71212650332069</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.293288060058403</v>
+        <v>9.324861776926252</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.477510507744192</v>
+        <v>6.499517689857607</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1507625048674289</v>
+        <v>0.1512747167575564</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.95366175149261</v>
+        <v>12.99707590429712</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.420781522219681</v>
+        <v>9.452355239087529</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01285681513087965</v>
+        <v>0.01281328232036988</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1782981368355891</v>
+        <v>-0.178721363632251</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2899057486593579</v>
+        <v>0.2911016373680599</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002492898139022552</v>
+        <v>0.002485405467892029</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.772002268076359</v>
+        <v>0.7633398457606374</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3675627713635436</v>
+        <v>0.3637372338581698</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8473543582.787918</v>
+        <v>8096334386.816304</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>248.42</v>
+        <v>247.92</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.09677704194260484</v>
+        <v>0.09456953642384103</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1350278551532034</v>
+        <v>-0.1367688022284123</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2672278782000</v>
+        <v>2666900232000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.71587301587302</v>
+        <v>19.67619047619047</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.05656601495863</v>
+        <v>22.02367326563975</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.445078875309406</v>
+        <v>3.43814489480198</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.843924295710814</v>
+        <v>4.834174830499256</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2231796793167352</v>
+        <v>0.2227304810248973</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.09185455733729</v>
+        <v>11.07067891353048</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.632036125721947</v>
+        <v>3.625102145214522</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004350219774337901</v>
+        <v>-0.004358993208861815</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1061222765818656</v>
+        <v>-0.1065890671885193</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1785740462863659</v>
+        <v>0.1790016137663992</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8356151450503818</v>
+        <v>0.8318213742314999</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4607508117976845</v>
+        <v>0.4600177075852392</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8923821402.908955</v>
+        <v>8378234518.323593</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>212.17</v>
+        <v>216.66229</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1234842104463678</v>
+        <v>0.1472718188912288</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1030269721822947</v>
+        <v>-0.0840353005834108</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5138969570000</v>
+        <v>5247777386169</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>26.6880503144654</v>
+        <v>27.25311823899371</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>15.86809355463913</v>
+        <v>16.18266927000292</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>16.96203099987127</v>
+        <v>17.32116944693682</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.41375947664465</v>
+        <v>22.88832754733955</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.214230607966457</v>
+        <v>0.2187665273606298</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.06296383314717</v>
+        <v>22.52861716104114</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.01621806191392</v>
+        <v>17.37535650897947</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02471429306400816</v>
+        <v>0.02420186502856161</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6818687274920301</v>
+        <v>0.6840928887740156</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9361767872730502</v>
+        <v>0.9386961152552931</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002450864872507895</v>
+        <v>0.002400048480979316</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.326698277194909</v>
+        <v>1.330883068060406</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4129865725171606</v>
+        <v>0.4118331113816031</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>27161914412.29845</v>
+        <v>26479586834.7751</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>670.24</v>
+        <v>679</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.03048850367345501</v>
+        <v>0.04395693183676874</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1524532119372787</v>
+        <v>-0.1413758219524531</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1707427398677</v>
+        <v>1729743381030</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.90672612411743</v>
+        <v>25.23225566703828</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.26970589738644</v>
+        <v>20.53056884773238</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.48057988975588</v>
+        <v>7.578350658187586</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.524821205033287</v>
+        <v>6.61010025993316</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.105878855444069</v>
+        <v>-5.172612411742842</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.8511225967293</v>
+        <v>17.05954293400702</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.904925338565946</v>
+        <v>8.002696106997652</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02399867779546601</v>
+        <v>0.02368906304217234</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2287660339131452</v>
+        <v>0.229009086605275</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.271779256228301</v>
+        <v>0.2723933984855693</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.00313320601575555</v>
+        <v>0.003092783505154639</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7737419082192315</v>
+        <v>0.7739591816512366</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4141160903999248</v>
+        <v>0.4089750218803272</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10085256584.06548</v>
+        <v>9895654934.539257</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>356.58</v>
+        <v>362.4</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.186020512616166</v>
+        <v>-0.1727349648665056</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2851672914620211</v>
+        <v>-0.2734999899765451</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1408329609753</v>
+        <v>1431315975586</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>302.1864406779661</v>
+        <v>307.1186440677966</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>169.5194756773143</v>
+        <v>172.3743528501283</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.59142251665235</v>
+        <v>13.81325795062682</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.2889251421861</v>
+        <v>13.5058232977964</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.044117927906418</v>
+        <v>-8.175411792790637</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>116.5989865108913</v>
+        <v>118.510057830562</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.53470511926384</v>
+        <v>13.75654055323831</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004091371764178535</v>
+        <v>0.00402566595935671</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7826060366844672</v>
+        <v>0.7816957046668216</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.122312558453592</v>
+        <v>0.1224683805249129</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.539929601112977</v>
+        <v>1.535828499738731</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.575054620584088</v>
+        <v>0.5734854086589536</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12770236754.12082</v>
+        <v>12585173296.70041</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>339.27</v>
+        <v>342.85</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02402046842665828</v>
+        <v>-0.01372186636036121</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3146060606060607</v>
+        <v>-0.3073737373737373</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1614104166600</v>
+        <v>1631136303000</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>42.09305210918114</v>
+        <v>42.53722084367246</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.56984765925968</v>
+        <v>18.74384510101777</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.11483397602801</v>
+        <v>18.30598293005925</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.21988985856154</v>
+        <v>16.39104323402548</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4188467066309606</v>
+        <v>0.4232664054246614</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>31.56244698161223</v>
+        <v>31.89289137630828</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.51261634270066</v>
+        <v>18.70643497486084</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02441168346835987</v>
+        <v>0.02415325707293803</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.266741918488052</v>
+        <v>1.269396733403582</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8525743408863151</v>
+        <v>0.8547782329035543</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007486662540159755</v>
+        <v>0.0074084876768266</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.605083990203484</v>
+        <v>1.604331866251678</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3892366707697041</v>
+        <v>0.3900621800999269</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8765279017.475498</v>
+        <v>8448720235.190298</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>901.35</v>
+        <v>901.08</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.05482738443534241</v>
+        <v>0.05451141018139261</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1779753761969904</v>
+        <v>-0.1782216142270862</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,40 +1724,40 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>399729796650</v>
+        <v>399610057320</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.27122049221497</v>
+        <v>45.25765946760422</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.7678389432304</v>
+        <v>39.75143661554289</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.361537795099919</v>
+        <v>1.361129945535736</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.94097096451699</v>
+        <v>11.93739403861649</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.571171723649282</v>
+        <v>3.570101976752533</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.88429831720802</v>
+        <v>26.87602331167934</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.325044353632824</v>
+        <v>1.324636504068641</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02202988136936526</v>
+        <v>0.02203648241252428</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1383877448518331</v>
+        <v>0.13851632345555</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1136368918037924</v>
+        <v>0.1137619578080773</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006146336051478338</v>
+        <v>0.006148177742264838</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.187307937102089</v>
+        <v>-0.1857028973985057</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.176444822708197</v>
+        <v>0.1761879455002504</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1730378059.199019</v>
+        <v>1670251785.627592</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>77.27500000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1438619427529596</v>
+        <v>-0.15073082960507</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3761012333813871</v>
+        <v>-0.3811068396604196</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>324370925922</v>
+        <v>321768463423</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>24.11764705882353</v>
+        <v>23.92507739938081</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.77359786945086</v>
+        <v>20.60368904786809</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.705929348604045</v>
+        <v>6.652385214403478</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.82336630687689</v>
+        <v>10.73694610350234</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.708823529411765</v>
+        <v>0.7031638601525336</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.77166358135712</v>
+        <v>10.68701582300221</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.813640568546736</v>
+        <v>6.760096434346169</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03389517099520758</v>
+        <v>0.03416798856755578</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1609759277323042</v>
+        <v>0.1612035759128481</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1434269861448505</v>
+        <v>0.1437995609359888</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.1010625785780117</v>
+        <v>0.09691944164778994</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3818256902419801</v>
+        <v>0.3311391987215864</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2197050104.863083</v>
+        <v>2109589813.140972</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>516.76</v>
+        <v>520.3099999999999</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.04007244369910756</v>
+        <v>0.04721745719692438</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.03901513742700935</v>
+        <v>-0.03241343400156216</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1114575663752</v>
+        <v>1122232494014</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.97140516110474</v>
+        <v>13.08306342574169</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.2953406022426</v>
+        <v>23.45534582253936</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.893036591696626</v>
+        <v>2.917939941900818</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.481267354237733</v>
+        <v>1.494018150329856</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3573291791599261</v>
+        <v>0.3604050800013231</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.70529010834619</v>
+        <v>15.83049588872625</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.123772228721012</v>
+        <v>3.148675578925204</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02175820361113868</v>
+        <v>0.02157250679244771</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4431759817301831</v>
+        <v>-0.44221400423056</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.05906971911748538</v>
+        <v>0.06094355877574542</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.05340833797176848</v>
+        <v>0.05623404467829123</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1395663401249826</v>
+        <v>0.1395117083446725</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2101104811.616488</v>
+        <v>2040535266.620744</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>352.49</v>
+        <v>351.37</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.08298509309933144</v>
+        <v>0.07954402156745477</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.03822646657571616</v>
+        <v>-0.04128240109140513</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>944500479900</v>
+        <v>941499428700</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.15434221840069</v>
+        <v>15.10619088564059</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>14.07451446459346</v>
+        <v>14.02917206195688</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.173372844745038</v>
+        <v>3.16328978540686</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.624116687755941</v>
+        <v>2.615778832241496</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.793469982641731</v>
+        <v>0.7909488150041846</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.10047745706312</v>
+        <v>20.06826351116359</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.291508266556463</v>
+        <v>6.281425207218286</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1720846134638369</v>
+        <v>-0.1726331371484984</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07672220285280162</v>
+        <v>0.07676994899822165</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.289427374123294</v>
+        <v>-0.2893751396518991</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01702175948253851</v>
+        <v>0.0170760167344964</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7694580071536945</v>
+        <v>0.7670347220969244</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1701887373192562</v>
+        <v>0.169646219936739</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2109494571.052096</v>
+        <v>2044868972.712569</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>375.62</v>
+        <v>371.775</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08410294415172404</v>
+        <v>0.0730056228688758</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.02580594963301086</v>
+        <v>-0.03577819851129505</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>701300273396</v>
+        <v>694121476870</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.91333899745115</v>
+        <v>31.58666100254885</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>25.10661718726129</v>
+        <v>24.8621010308201</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.76380761994246</v>
+        <v>15.60244283559612</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.43124863892205</v>
+        <v>20.22210601867645</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.152050820551805</v>
+        <v>2.130021547869249</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.49650400013747</v>
+        <v>24.24979300536119</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>16.02228181523108</v>
+        <v>15.86091703088473</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.02996291431378736</v>
+        <v>0.03027279907078205</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2711126616310331</v>
+        <v>0.2704743240884069</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1378301271625042</v>
+        <v>0.1381361933238576</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007134870347691817</v>
+        <v>0.007208661152578845</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3037793366634721</v>
+        <v>0.3014679487895589</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1804353882007724</v>
+        <v>0.176358785651124</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2272636613.31724</v>
+        <v>2201177220.262569</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>573.27</v>
+        <v>570.76</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01800649056037718</v>
+        <v>0.01354926047454219</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.04712276852498254</v>
+        <v>-0.05129483727269712</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,40 +2354,40 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>502778427720</v>
+        <v>500577067360</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.48105436573311</v>
+        <v>31.34321801208127</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.85925181506215</v>
+        <v>25.73607075446453</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.33111272468147</v>
+        <v>14.26836551492176</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>90.11301728747104</v>
+        <v>89.7184672963821</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.391350170628382</v>
+        <v>1.385258296069663</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.33742212515826</v>
+        <v>23.23788512208356</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.71169591312031</v>
+        <v>14.6489487033606</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03271421185389437</v>
+        <v>0.0328580773520955</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2174000466400365</v>
+        <v>0.2178711471192254</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1568220736126735</v>
+        <v>0.1571890126686657</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.00587855635215518</v>
+        <v>0.005904408157544327</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.292833232438592</v>
+        <v>0.29062514884985</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1965507417402079</v>
+        <v>0.1932066487787013</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1532145762.413241</v>
+        <v>1480861028.262964</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>375.93</v>
+        <v>379.60999</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1175089382304795</v>
+        <v>0.1284482666096955</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1856288722325722</v>
+        <v>-0.1776569689354881</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>341398725796</v>
+        <v>344740683900</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.17400810237284</v>
+        <v>24.41064818982702</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.34874484258084</v>
+        <v>17.51259204373629</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7584464137969337</v>
+        <v>0.7658708590204141</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.459642774386218</v>
+        <v>3.493509320853149</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7324787572533598</v>
+        <v>-0.739649013689145</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>14.98822830400186</v>
+        <v>15.11794759538874</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.857846807906178</v>
+        <v>0.8652712531296584</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06917717675991604</v>
+        <v>0.06850656479770359</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3934153923942698</v>
+        <v>0.3938912143252915</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01032894715891031</v>
+        <v>0.01040690486613927</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,26 +2549,26 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02410023142606336</v>
+        <v>0.02386660056022235</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.429900752815327</v>
+        <v>0.435637936826805</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2290281710049149</v>
+        <v>0.2300048304031516</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1805017710.513059</v>
+        <v>1751533147.843852</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-27 (E)</t>
+          <t>2026-10-13 (C)</t>
         </is>
       </c>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>169.28</v>
+        <v>164.09</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3801875083082022</v>
+        <v>0.3378719768330156</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.04041720990873532</v>
+        <v>-0.06983731081004474</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>701574188800</v>
+        <v>680064441400</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.78635778635779</v>
+        <v>21.11196911196911</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>15.31735582137103</v>
+        <v>14.8510519789708</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.943095853320778</v>
+        <v>1.8829480374453</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.723993743850721</v>
+        <v>2.639673521628498</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.133247533247534</v>
+        <v>2.067213642213643</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>10.21029152523495</v>
+        <v>9.909086078663419</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>2.031114465185841</v>
+        <v>1.971196221126682</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04354920760733665</v>
+        <v>0.04493484008149426</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.422331506849315</v>
+        <v>0.4215807164276184</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08215438117185392</v>
+        <v>0.08166324800680869</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02433837429111531</v>
+        <v>0.02510817234444512</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5501222862545879</v>
+        <v>-0.5583743515301339</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2367982598190592</v>
+        <v>0.2513330320572517</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2242445686.619956</v>
+        <v>2195296767.427505</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>267.2</v>
+        <v>267.85999</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2886423541584338</v>
+        <v>0.2918253297097848</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.0493471377236987</v>
+        <v>-0.04699900380688093</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>643924856755</v>
+        <v>645515354409</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.89017341040462</v>
+        <v>30.95954913294797</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.58852845169736</v>
+        <v>21.61749441164768</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.57542563239694</v>
+        <v>6.59019327058379</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.673144013840015</v>
+        <v>7.690376999329182</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.824691207788263</v>
+        <v>-3.833281017645275</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.93771068288272</v>
+        <v>19.98058332725602</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.867616913835534</v>
+        <v>6.882384552022383</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02905307941407518</v>
+        <v>0.02898797580521503</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.430860536859609</v>
+        <v>0.4321525216292743</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.08875387185717587</v>
+        <v>0.08933884426234107</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01976047904191617</v>
+        <v>0.01971179047680843</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1742644611003474</v>
+        <v>-0.1727717519192965</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2096265966257698</v>
+        <v>0.207938150586052</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1659349928.772552</v>
+        <v>1608307061.057868</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>108.09</v>
+        <v>108.3701</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04141541369064916</v>
+        <v>-0.0389313768451941</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2002811482687185</v>
+        <v>-0.1982087895827168</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>860188867200</v>
+        <v>862417925408</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>39.02166064981949</v>
+        <v>39.1227797833935</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.85644000821016</v>
+        <v>34.93631460727707</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.168989001956947</v>
+        <v>1.172018272189606</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.751683259024002</v>
+        <v>8.774362012663124</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.436147029865449</v>
+        <v>9.460599474893344</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.53212883587385</v>
+        <v>21.58416222152711</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.253553581213307</v>
+        <v>1.256582851445966</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01570469058030608</v>
+        <v>0.01566409927484873</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.119496444290589</v>
+        <v>0.1198313337619308</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05094654776722218</v>
+        <v>0.05107088152361516</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009043389767786104</v>
+        <v>0.009020015668528497</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.0564845450081595</v>
+        <v>-0.05629082922172535</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3071438071916167</v>
+        <v>0.3070729759507302</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2764095681.859236</v>
+        <v>2669157998.060524</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.66</v>
+        <v>147.96</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03434661784657456</v>
+        <v>0.04351510689062588</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1231091180866966</v>
+        <v>-0.1153363228699551</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,40 +2984,40 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>348641462700</v>
+        <v>351731834319</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.72740740740741</v>
+        <v>21.92</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.76270500940494</v>
+        <v>20.94335688581644</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.005899700110304</v>
+        <v>4.041408152392224</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.541655465743587</v>
+        <v>6.599640956712268</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.73415449735472</v>
+        <v>20.91794285714308</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.5837707113955</v>
+        <v>17.72917259428813</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.294115528771027</v>
+        <v>4.329623981052946</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04564287872350072</v>
+        <v>0.04524185316012042</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04646323287671228</v>
+        <v>0.04663259665144603</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02535486436829393</v>
+        <v>0.02543466982807141</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02925542070094096</v>
+        <v>0.02899837793998378</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04817637593459839</v>
+        <v>-0.0442625259997273</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1501291257052752</v>
+        <v>0.1500394124977721</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1296691230.419818</v>
+        <v>1268543724.111756</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>305.48</v>
+        <v>308.04</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1166502992014529</v>
+        <v>-0.1092476043145723</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2841710603397773</v>
+        <v>-0.2781722319859402</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>304599301160</v>
+        <v>307151920680</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.33240223463687</v>
+        <v>21.51117318435754</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.35687844315328</v>
+        <v>20.52747425569247</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.800487664680569</v>
+        <v>1.815576208682083</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.27328157910573</v>
+        <v>18.42641632063549</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.317510068858028</v>
+        <v>-7.378832662076166</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.26578721137362</v>
+        <v>15.37252438553209</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.157997004066771</v>
+        <v>2.173085548068284</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.0495766075053066</v>
+        <v>0.0491645957041977</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.04792108938547468</v>
+        <v>0.0479210893854749</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03041115621317271</v>
+        <v>0.03015842098428775</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.709807233714538</v>
+        <v>0.7118905014936657</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2470891658608973</v>
+        <v>0.2413912795913898</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1240432383.593238</v>
+        <v>1200616632.192054</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>504.2</v>
+        <v>526.3273</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.256231249142218</v>
+        <v>1.355248118874754</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1377216835120484</v>
+        <v>-0.09987977357070776</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,40 +3236,40 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>822148520000</v>
+        <v>858229295380</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>127.9695431472081</v>
+        <v>133.5856091370558</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>37.29149383605141</v>
+        <v>38.77943549487809</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>19.9043340999879</v>
+        <v>20.77785486938627</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.23298524336547</v>
+        <v>12.76984151939784</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.033148605225166</v>
+        <v>1.078489321473478</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>76.63169621197984</v>
+        <v>80.02129949617466</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>19.88472388330711</v>
+        <v>20.76427279990316</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.01022078103357773</v>
+        <v>0.009788249880584051</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.431601418538349</v>
+        <v>2.444753834921077</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.8934119722057594</v>
+        <v>0.8988302387766913</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.538601164745802</v>
+        <v>2.543980070502435</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6646592840893162</v>
+        <v>0.6723667388671691</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>10183663363.32363</v>
+        <v>9526354595.547436</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1591.48</v>
+        <v>1609.3425</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3675092886423992</v>
+        <v>0.3828579795894262</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2042440848816977</v>
+        <v>-0.1953126562531251</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,40 +3362,40 @@
         <v>861.1799999999999</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>613385024317</v>
+        <v>620269553181</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>50.02902757619739</v>
+        <v>50.66037735849056</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>32.76190382771456</v>
+        <v>33.02961111517773</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.04251152759182</v>
+        <v>15.23234304816361</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>24.34729810221118</v>
+        <v>24.65455295206502</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.40565873273661</v>
+        <v>3.448637019616227</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>38.15616835024811</v>
+        <v>38.64197175080589</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>14.90982452737952</v>
+        <v>15.09965604795131</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01882128409193356</v>
+        <v>0.01858672575990359</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5270488503746813</v>
+        <v>0.5337866734740684</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2826890123849841</v>
+        <v>0.2856935401255383</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004888531429864026</v>
+        <v>0.004834272381422849</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.697316872671875</v>
+        <v>1.685865454439055</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4375157394443653</v>
+        <v>0.4362877663565686</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2072147632.963916</v>
+        <v>2024414593.658516</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>209.69</v>
+        <v>211.34</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07937833750414935</v>
+        <v>-0.07213418783979642</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1755848240613328</v>
+        <v>-0.169097700019658</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>165732685300</v>
+        <v>167036795800</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>78.53558052434454</v>
+        <v>79.15355805243443</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>82.93066134929298</v>
+        <v>83.13396862336106</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.763207461035161</v>
+        <v>1.777081714984839</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.19248837367869</v>
+        <v>27.40645950161312</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4203282135993536</v>
+        <v>0.4236356748633096</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.40772450359712</v>
+        <v>29.59536630215827</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.174410184584286</v>
+        <v>2.188284438533965</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001267100690608312</v>
+        <v>-0.001257208024101717</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.05299705505104957</v>
+        <v>-0.04787947257708691</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1533729156417385</v>
+        <v>0.1537975177777891</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.239882327225976</v>
+        <v>1.241962403843824</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3346242894193652</v>
+        <v>0.3351803178530742</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1079004709.662687</v>
+        <v>1023742467.130764</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>976.67</v>
+        <v>978.925</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.0681693585688159</v>
+        <v>0.07063561831220166</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1536581772805657</v>
+        <v>-0.1517040875570846</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>288124486690</v>
+        <v>288789727475</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.87918951858623</v>
+        <v>14.9135435709933</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.48483516185687</v>
+        <v>13.51438611179333</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.443037271509365</v>
+        <v>2.448677916811518</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.387924809763569</v>
+        <v>2.393438207785436</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3487475852012999</v>
+        <v>0.3495527965875705</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.8445986904724</v>
+        <v>26.86578942678304</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.145615766807702</v>
+        <v>7.151256412109855</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1440870245945704</v>
+        <v>-0.1437551133240841</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1034016611989015</v>
+        <v>0.1035309667509787</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.382285490439393</v>
+        <v>-0.3822426848979621</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01842997122876714</v>
+        <v>0.01838751691906939</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.570100090379177</v>
+        <v>1.568520056957277</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3090673866755244</v>
+        <v>0.3026975806733175</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1862475948.847695</v>
+        <v>1793973811.470195</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>248.37</v>
+        <v>240.94</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1479588336192109</v>
+        <v>-0.1734476843910806</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2529326836311134</v>
+        <v>-0.2752812368405221</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>233997821580</v>
+        <v>226997765960</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>21.69170305676856</v>
+        <v>21.04279475982533</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>19.25049067595444</v>
+        <v>18.67129747777815</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.386512027729135</v>
+        <v>3.285204364299463</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.775890020898642</v>
+        <v>6.573188958551028</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2644201787346401</v>
+        <v>0.2565100368978709</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>18.00738681832193</v>
+        <v>17.57584402687874</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.22735895306598</v>
+        <v>4.126051289636308</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.05825267905470558</v>
+        <v>0.06004904912765512</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1268129951546333</v>
+        <v>0.1270129879763118</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04600047137561836</v>
+        <v>0.04610799352298289</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02713693280186818</v>
+        <v>0.02797376940317092</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.8958469001438731</v>
+        <v>0.8855233417986426</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3171415193881565</v>
+        <v>0.3176603538400597</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1199632443.267902</v>
+        <v>1161328547.549453</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1136.98</v>
+        <v>1145.75</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05240847070989285</v>
+        <v>0.06052613530216844</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1204270297450973</v>
+        <v>-0.1136425173094032</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,40 +3868,40 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1070740682180</v>
+        <v>1078999750750</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.03880896620944</v>
+        <v>38.3322181331549</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.0617277011639</v>
+        <v>26.21265617928169</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.4404058225738</v>
+        <v>13.54407726715855</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>29.94896401900882</v>
+        <v>30.17997284453496</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4021170720722484</v>
+        <v>0.40521876842757</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.78833483078088</v>
+        <v>25.97905430229443</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.01804390566592</v>
+        <v>14.12171535025067</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.018728997911213</v>
+        <v>0.0185856391403805</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4595658968730096</v>
+        <v>0.4623553550232133</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.228246464557607</v>
+        <v>0.2290918506683588</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877328985191485</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005884008513782125</v>
+        <v>0.005838970106916867</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3411813514063061</v>
+        <v>0.3457100598959101</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.324628723651813</v>
+        <v>0.3246364649911769</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>3123924853.497945</v>
+        <v>2988368156.592773</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>206.27</v>
+        <v>207.415</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.133974749429536</v>
+        <v>0.1402694170404188</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1118622174381054</v>
+        <v>-0.1069321851453175</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,40 +3994,40 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>325345545600</v>
+        <v>327151531200</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.58118971061093</v>
+        <v>16.67323151125402</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.31735301105928</v>
+        <v>15.39986893249027</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.571312075492575</v>
+        <v>2.585585369361965</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.934785132724128</v>
+        <v>2.951076057128884</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4218519205577083</v>
+        <v>0.4241936108133857</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.5045335332402</v>
+        <v>23.56607255256074</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.451616195496685</v>
+        <v>5.465889489366075</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04820720680553863</v>
+        <v>-0.04794108694057062</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08251012421265891</v>
+        <v>0.08268658547328567</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3272876063513729</v>
+        <v>-0.3271879519250608</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02011926116255393</v>
+        <v>0.02000819612853458</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.376706477173516</v>
+        <v>1.377667327960806</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2623913333312874</v>
+        <v>0.2611880847700112</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>922096790.9233246</v>
+        <v>866532109.8652943</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>927.6</v>
+        <v>929.47</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.940840658522518</v>
+        <v>1.946769261402464</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2608764940239043</v>
+        <v>-0.2593864541832669</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1047622164000</v>
+        <v>1049734123300</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.70073644275831</v>
+        <v>20.74246819906271</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.958988590810979</v>
+        <v>5.95494329743573</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.60491574539735</v>
+        <v>11.62831073509538</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.38811802549541</v>
+        <v>10.40906000555975</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02950461925421188</v>
+        <v>0.02956409924343717</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.05579205805753</v>
+        <v>15.08670792366781</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.39866588386468</v>
+        <v>11.42207213318342</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02498228932086626</v>
+        <v>0.02493200333010484</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.473867440303503</v>
+        <v>2.483235215353715</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.765110056317434</v>
+        <v>1.772514181536212</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005713669685209142</v>
+        <v>0.0005702174357429503</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.880005584881958</v>
+        <v>2.877844639466991</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8124061229988889</v>
+        <v>0.8122173015895694</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>26371464494.61606</v>
+        <v>25488204420.92985</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>141.9</v>
+        <v>140.83</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.03763985800684921</v>
+        <v>-0.0448965553425269</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2712837525548719</v>
+        <v>-0.2767786530817661</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,40 +4246,40 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>146705017800</v>
+        <v>145598785460</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>88.13664596273293</v>
+        <v>87.47204968944101</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>29.93846993704728</v>
+        <v>29.69648027762235</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.958255348900353</v>
+        <v>9.883164910399131</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.7116251198466</v>
+        <v>11.62331335890061</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>141.0186335403757</v>
+        <v>139.9552795031086</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>43.75322952135282</v>
+        <v>43.43616665520207</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.36213805321749</v>
+        <v>10.28704761471626</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03121910939845167</v>
+        <v>0.03145630635262581</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.943926197566579</v>
+        <v>1.945535931251596</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2456309996565116</v>
+        <v>0.2461938219817823</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7103996960341029</v>
+        <v>0.703517495086097</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6278912580281349</v>
+        <v>0.6279114251488768</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2235182723.005687</v>
+        <v>2176582239.990946</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.55</v>
+        <v>27.605</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09412230604052318</v>
+        <v>0.09630657924677455</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05682985279014041</v>
+        <v>-0.05494693598082845</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157019572000</v>
+        <v>157333041200</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.40327695560254</v>
+        <v>36.47595137420719</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.436249022534287</v>
+        <v>9.455778672075736</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.465140228585782</v>
+        <v>2.470061561165536</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.84302676370466</v>
+        <v>1.846706127479751</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6088689685494584</v>
+        <v>-0.6100844964358547</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.36672782002535</v>
+        <v>17.39155903041825</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.441936259733735</v>
+        <v>3.446857592313489</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06996580018699834</v>
+        <v>0.06982640083868155</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.85781223753946</v>
+        <v>2.857530155811058</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05031934638406599</v>
+        <v>-0.05042615492450442</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06243194192377495</v>
+        <v>0.06230755297953269</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3485226448608757</v>
+        <v>0.3479709659284707</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2082879551631476</v>
+        <v>0.2077863857129715</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>990061057.8431157</v>
+        <v>945056547.4672413</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>174.83</v>
+        <v>179.3187</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.04059285587850292</v>
+        <v>0.06730971884356518</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1252814329314054</v>
+        <v>-0.1028233351678591</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,40 +4498,40 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1241039305935</v>
+        <v>1272902562428</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>7.38409031764871</v>
+        <v>7.685570928250936</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003632702452335887</v>
+        <v>0.003723068627362769</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6.341654943554526</v>
+        <v>6.600574583261782</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>4.595548771687055</v>
+        <v>4.78317768603404</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.01652467209504274</v>
+        <v>0.01719934805631963</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>7.457154914126215</v>
+        <v>7.763078014576559</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>6.311402639305264</v>
+        <v>6.57032227901252</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.07600842642420826</v>
+        <v>0.07302685654173505</v>
       </c>
       <c r="T32" s="4" t="n">
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2031.671382953652</v>
+        <v>2063.310840731131</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2628.263433149657</v>
+        <v>2670.248850300211</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.715952639707144</v>
+        <v>1.672998967759637</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9140153423105198</v>
+        <v>0.9154040808242494</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3276414380.73785</v>
+        <v>3140685843.304704</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>542.11</v>
+        <v>552.1356</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4522100662394151</v>
+        <v>0.4790667507501045</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1930845600821637</v>
+        <v>-0.1781617373442688</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>68327949898</v>
+        <v>69591584021</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.826660385047441</v>
+        <v>1.827958376954615</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4040658528778202</v>
+        <v>0.4033292719119316</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3866996224.813599</v>
+        <v>3720531518.062378</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>143.49</v>
+        <v>152.2995</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1084808777837809</v>
+        <v>-0.05374648718399166</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3640755185250841</v>
+        <v>-0.3250332387874491</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1876255932273</v>
+        <v>1991447762499</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-93.17532467532467</v>
+        <v>-98.89577922077922</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>129.4811985463176</v>
+        <v>136.8285069042755</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>113.1979446318552</v>
+        <v>120.1476779788235</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.613731371439352</v>
+        <v>7.019778249386908</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9317532467532468</v>
+        <v>-0.9889577922077922</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>437.2685222637389</v>
+        <v>464.9123500117591</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>109.9304936514631</v>
+        <v>116.8802269984314</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.0151487862135987</v>
+        <v>-0.01427253103758692</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.204788528688608</v>
+        <v>4.214836670179136</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.482105313712486</v>
+        <v>3.539215959670987</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7857677087761391</v>
+        <v>0.7842372976340035</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14385635156.2712</v>
+        <v>14075368301.73266</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>757.39</v>
+        <v>760.87</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1086406296331734</v>
+        <v>0.1137345302538886</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02820226593274056</v>
+        <v>-0.02373712100799363</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>806800779990</v>
+        <v>810507809017</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9952239310757131</v>
+        <v>0.995029222259491</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1152127708860105</v>
+        <v>0.1128091657703609</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>30114175362.7381</v>
+        <v>28658069989.11263</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>413.75</v>
+        <v>418.95001</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.2945465378526455</v>
+        <v>0.3108163987403776</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1362212943632568</v>
+        <v>-0.1253653235908142</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,40 +4914,40 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2145906100000</v>
+        <v>2172875859312</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>27.64576330126348</v>
+        <v>27.58780572620842</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6312544601519919</v>
+        <v>0.6385199650913073</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>13.92836064111815</v>
+        <v>13.89916072363153</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>9.614041390167893</v>
+        <v>9.59388616712771</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.5193381627831609</v>
+        <v>0.5182494035320432</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>18.31455399061033</v>
+        <v>18.27477474575392</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>13.44378122964753</v>
+        <v>13.41458131216091</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.01808392229407813</v>
+        <v>0.01812191372746905</v>
       </c>
       <c r="T36" s="4" t="n">
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.7949591589531</v>
+        <v>42.20586236056598</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.77793072328573</v>
+        <v>42.17267580496152</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2658610271903323</v>
+        <v>0.286430354781469</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.18286906950038</v>
+        <v>2.184027822511649</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3624691173247276</v>
+        <v>0.3565425843995432</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4136072980.466634</v>
+        <v>4015868130.797678</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.03</v>
+        <v>28.045</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01683620571828592</v>
+        <v>-0.0163100745404684</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06566666666666665</v>
+        <v>-0.0651666666666666</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,38 +5042,38 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70275041757</v>
+        <v>70312648808</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.07086614173228</v>
+        <v>-22.08267716535433</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-82.12552064591577</v>
+        <v>-82.92737924132929</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.945868524352762</v>
+        <v>1.946909838238959</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.143350082221816</v>
+        <v>2.144497076557647</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.164248306171031</v>
+        <v>0.1643362021607765</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.35190772842975</v>
+        <v>16.35812376991736</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.739278464820712</v>
+        <v>2.740319778706909</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.0310209705394142</v>
+        <v>0.0310043788273834</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02058038420274655</v>
+        <v>0.02065405918635133</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2391619887635157</v>
+        <v>0.2328888598444398</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1893262260542644</v>
+        <v>0.1849474654543697</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>517302914.2458267</v>
+        <v>491962398.8552333</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>324.43</v>
+        <v>317.42</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1295844433307513</v>
+        <v>-0.1483916222360665</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1627396836047382</v>
+        <v>-0.1808304730444656</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,40 +5170,40 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>219090823300</v>
+        <v>214356900200</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.67434808975137</v>
+        <v>19.24924196482717</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.69644268586448</v>
+        <v>16.3298736552132</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.605959384106669</v>
+        <v>2.549652090445208</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.416672695449241</v>
+        <v>6.278026837806301</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.219981409932183</v>
+        <v>1.193621117469635</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.419868277786767</v>
+        <v>9.228397516583078</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.770173816802065</v>
+        <v>2.713866523140604</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.06870210159094327</v>
+        <v>0.07021933973646816</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1783556809024982</v>
+        <v>0.1787747028086761</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.005891366142209531</v>
+        <v>0.006124458394295207</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01091144468760595</v>
+        <v>0.01115241635687732</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9594673178377636</v>
+        <v>0.9525098451541913</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2215095071081895</v>
+        <v>0.2235971589181255</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>770275394.8168274</v>
+        <v>750498659.687384</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>140.37</v>
+        <v>143.85</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2827653406336837</v>
+        <v>-0.2649839299718987</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5739908952959029</v>
+        <v>-0.5634294385432473</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,40 +5296,40 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>404331573900</v>
+        <v>414355609500</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>21.66203703703704</v>
+        <v>22.19907407407407</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>15.64795504241688</v>
+        <v>16.01392939571599</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.633163463226382</v>
+        <v>5.7728187232679</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.235209668723416</v>
+        <v>6.38979063080333</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4714678649237475</v>
+        <v>0.4831563180827889</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>13.88901309384942</v>
+        <v>14.15476165164369</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.298905971272135</v>
+        <v>7.438561231313653</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.0710308119719166</v>
+        <v>-0.0693124440493426</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3843366100118384</v>
+        <v>0.3862352908844917</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.4232963938119607</v>
+        <v>0.42786578758453</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01424805870200185</v>
+        <v>0.01390337156760514</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.076681238992412</v>
+        <v>2.074360657889285</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5630995647140897</v>
+        <v>0.5644469665851484</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4198679391.222831</v>
+        <v>4070435031.170095</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:41 ET</t>
+          <t>2026-09-16 11:49 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -443,10 +443,10 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>333.02</v>
+        <v>333.17</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2288107007117652</v>
+        <v>0.2293641858030715</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.03352003946948379</v>
+        <v>-0.03308471428156823</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,31 +714,31 @@
         <v>236.65</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4891183295120</v>
+        <v>4893386398520</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.01598173515982</v>
+        <v>38.03310502283105</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.8004258678435</v>
+        <v>34.81610079391454</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.47759706595433</v>
+        <v>10.48231642082759</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.50689495256697</v>
+        <v>45.52739232282367</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.16159944190766</v>
+        <v>1.162122653475392</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.29588390204527</v>
+        <v>29.30895978609498</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.57348565756186</v>
+        <v>10.57820501243512</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02794477159266767</v>
+        <v>0.02793219028060806</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
@@ -747,7 +747,7 @@
         <v>0.09239989991868391</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.118190305206118</v>
+        <v>0.1181903052061182</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003182992012491742</v>
+        <v>0.003181558963892307</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3072398750722112</v>
+        <v>0.3073909453031456</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2950645760019249</v>
+        <v>0.295121215507686</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>12936506731.42503</v>
+        <v>12980051631.23029</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>494.6302</v>
+        <v>493.65</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.04586247187090287</v>
+        <v>0.04378990453690701</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1067142237954201</v>
+        <v>-0.1084844325651955</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,31 +842,31 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3672901281610</v>
+        <v>3665622757500</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.47945555555555</v>
+        <v>27.425</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.08985946621722</v>
+        <v>24.04212101383646</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.06832313745521</v>
+        <v>11.04638923544249</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.306319480002802</v>
+        <v>8.289858992239825</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8728393191544196</v>
+        <v>0.8711096287703</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.21713587189607</v>
+        <v>18.18385814070037</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.39227703494767</v>
+        <v>11.37146645662505</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01824002173255826</v>
+        <v>0.01827438458115804</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007359033071575492</v>
+        <v>0.007373645295249672</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.554309862636615</v>
+        <v>0.5551376334446451</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4338715710278684</v>
+        <v>0.4342310741701302</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>11034021304.62094</v>
+        <v>11058390305.86168</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>346.02</v>
+        <v>345.1163</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09795337680906102</v>
+        <v>0.09508585335197095</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1531778468466264</v>
+        <v>-0.1553894912018795</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4187572547182</v>
+        <v>4176635869213</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.01042701092353</v>
+        <v>16.97120158887785</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.71212650332069</v>
+        <v>20.65803266851042</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.324861776926252</v>
+        <v>9.303358986991608</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.499517689857607</v>
+        <v>6.484530039970023</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1512747167575564</v>
+        <v>0.1509258827979006</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.99707590429712</v>
+        <v>12.96152121018984</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.452355239087529</v>
+        <v>9.42649745372152</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01281328232036988</v>
+        <v>0.01284891227647861</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.178721363632251</v>
+        <v>-0.1784696122226828</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2911016373680599</v>
+        <v>0.2914974064075679</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002485405467892029</v>
+        <v>0.002491913595503892</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7633398457606374</v>
+        <v>0.7637304034222537</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3637372338581698</v>
+        <v>0.363660526928079</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8096334386.816304</v>
+        <v>8117941626.862364</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>247.92</v>
+        <v>247.48</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.09456953642384103</v>
+        <v>0.09262693156732893</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1367688022284123</v>
+        <v>-0.1383008356545961</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,31 +1094,31 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2666900232000</v>
+        <v>2662167108000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.67619047619047</v>
+        <v>19.64126984126984</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.02367326563975</v>
+        <v>21.98458639795307</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.43814489480198</v>
+        <v>3.432042991955446</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.834174830499256</v>
+        <v>4.825595301113085</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2227304810248973</v>
+        <v>0.2223351865280799</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.07067891353048</v>
+        <v>11.05204434698048</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.625102145214522</v>
+        <v>3.619000242367987</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004358993208861815</v>
+        <v>-0.004366743156380399</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
@@ -1127,7 +1127,7 @@
         <v>-0.1065890671885193</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1790016137663992</v>
+        <v>0.1790016137663994</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8318213742314999</v>
+        <v>0.8328268405069893</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4600177075852392</v>
+        <v>0.4600876733924124</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8378234518.323593</v>
+        <v>8409213895.895597</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>216.66229</v>
+        <v>214.93</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1472718188912288</v>
+        <v>0.1380989836038924</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0840353005834108</v>
+        <v>-0.09135875539020877</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5247777386169</v>
+        <v>5205819530000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.25311823899371</v>
+        <v>27.03522012578616</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.18266927000292</v>
+        <v>16.05328322802149</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.32116944693682</v>
+        <v>17.18268050526622</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.88832754733955</v>
+        <v>22.70532744645914</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2187665273606298</v>
+        <v>0.21701741325461</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.52861716104114</v>
+        <v>22.34905455199065</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.37535650897947</v>
+        <v>17.23686756730887</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02420186502856161</v>
+        <v>0.02439692718276002</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6840928887740156</v>
+        <v>0.6840928887740154</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9386961152552931</v>
+        <v>0.9386961152552926</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002400048480979316</v>
+        <v>0.002419392360303355</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.330883068060406</v>
+        <v>1.329636861962327</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4118331113816031</v>
+        <v>0.4099954508104316</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26479586834.7751</v>
+        <v>26560966939.45884</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>679</v>
+        <v>675.33</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04395693183676874</v>
+        <v>0.03831433693273212</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1413758219524531</v>
+        <v>-0.1460166919575113</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,37 +1346,37 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1729743381030</v>
+        <v>1720394105318</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>25.23225566703828</v>
+        <v>25.0958751393534</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.53056884773238</v>
+        <v>20.41960097192799</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.578350658187586</v>
+        <v>7.53738961707441</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.61010025993316</v>
+        <v>6.574372619352962</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.172612411742842</v>
+        <v>-5.144654403567443</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>17.05954293400702</v>
+        <v>16.97222528128736</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>8.002696106997652</v>
+        <v>7.961735065884477</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02368906304217234</v>
+        <v>0.02381779841801187</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.229009086605275</v>
+        <v>0.2290090866052747</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>0.2723933984855693</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003092783505154639</v>
+        <v>0.003109590866687397</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7739591816512366</v>
+        <v>0.772962720498962</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4089750218803272</v>
+        <v>0.4082136723680519</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>9895654934.539257</v>
+        <v>9949231028.802986</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>362.4</v>
+        <v>360.61</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1727349648665056</v>
+        <v>-0.1768210697585832</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2734999899765451</v>
+        <v>-0.2770883868251709</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1431315975586</v>
+        <v>1424246285750</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>307.1186440677966</v>
+        <v>305.5932203389831</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>172.3743528501283</v>
+        <v>171.5229453125959</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.81325795062682</v>
+        <v>13.74464905351335</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.5058232977964</v>
+        <v>13.4387413939994</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.175411792790637</v>
+        <v>-8.134805442826448</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>118.510057830562</v>
+        <v>117.9190048450283</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.75654055323831</v>
+        <v>13.68793165612484</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.00402566595935671</v>
+        <v>0.004045760797758428</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7816957046668216</v>
+        <v>0.7816462968382902</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1224683805249129</v>
+        <v>0.1224372535904901</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.535828499738731</v>
+        <v>1.535600663616592</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5734854086589536</v>
+        <v>0.5726894060795944</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12585173296.70041</v>
+        <v>12633721610.01515</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>342.85</v>
+        <v>339.56</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01372186636036121</v>
+        <v>-0.02318622412519844</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3073737373737373</v>
+        <v>-0.314020202020202</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,31 +1598,31 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1631136303000</v>
+        <v>1615483864800</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>42.53722084367246</v>
+        <v>42.12903225806451</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.74384510101777</v>
+        <v>18.56397854018256</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.30598293005925</v>
+        <v>18.13031810917579</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.39104323402548</v>
+        <v>16.23375423813823</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4232664054246614</v>
+        <v>0.4192047269243051</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>31.89289137630828</v>
+        <v>31.58884612058244</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.70643497486084</v>
+        <v>18.52810047584845</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02415325707293803</v>
+        <v>0.0243908347576583</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.0074084876768266</v>
+        <v>0.007480268582871952</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.604331866251678</v>
+        <v>1.603985187995199</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3900621800999269</v>
+        <v>0.3888628033345141</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8448720235.190298</v>
+        <v>8477247786.818019</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>901.08</v>
+        <v>899.6512</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.05451141018139261</v>
+        <v>0.05283932124049162</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1782216142270862</v>
+        <v>-0.1795246694026448</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>399610057320</v>
+        <v>398976414525</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.25765946760422</v>
+        <v>45.18589653440482</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.75143661554289</v>
+        <v>39.68840463987337</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.361129945535736</v>
+        <v>1.358971666064914</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.93739403861649</v>
+        <v>11.91846547666597</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.570101976752533</v>
+        <v>3.564441034655955</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.87602331167934</v>
+        <v>26.83223320836213</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.324636504068641</v>
+        <v>1.322478224597819</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02203648241252428</v>
+        <v>0.0220714801161466</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006148177742264838</v>
+        <v>0.006157942100227288</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1857028973985057</v>
+        <v>-0.1861335977966155</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1761879455002504</v>
+        <v>0.1761941997795605</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1670251785.627592</v>
+        <v>1677501986.623104</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>77.27500000000001</v>
+        <v>77.1534</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.15073082960507</v>
+        <v>-0.1520672402310166</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3811068396604196</v>
+        <v>-0.3820807304180682</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>321768463423</v>
+        <v>321262128319</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>23.92507739938081</v>
+        <v>23.88650154798762</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.60368904786809</v>
+        <v>20.57126706678467</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.652385214403478</v>
+        <v>6.641659170795814</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.73694610350234</v>
+        <v>10.71963427498069</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7031638601525336</v>
+        <v>0.7020301064713437</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.68701582300221</v>
+        <v>10.67005905339595</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.760096434346169</v>
+        <v>6.749370390738505</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03416798856755578</v>
+        <v>0.03422316865523224</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1612035759128481</v>
+        <v>0.1611584969676407</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1437995609359888</v>
+        <v>0.1437551576299554</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09691944164778994</v>
+        <v>0.09734136717653576</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3311391987215864</v>
+        <v>0.331529085667676</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2109589813.140972</v>
+        <v>2115393626.214532</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>520.3099999999999</v>
+        <v>521.14</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.04721745719692438</v>
+        <v>0.04888798147951245</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.03241343400156216</v>
+        <v>-0.03086993714434494</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1122232494014</v>
+        <v>1124022682498</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>13.08306342574169</v>
+        <v>13.09948970953909</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.45534582253936</v>
+        <v>23.49276185727387</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.917939941900818</v>
+        <v>2.921603526492967</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.494018150329856</v>
+        <v>1.49589394694852</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3604050800013231</v>
+        <v>0.3608575822887061</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.83049588872625</v>
+        <v>15.84891517625533</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.148675578925204</v>
+        <v>3.152339163517353</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02157250679244771</v>
+        <v>0.02154545565331053</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.44221400423056</v>
+        <v>-0.4424031627646536</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06094355877574542</v>
+        <v>0.06058376751169559</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.05623404467829123</v>
+        <v>0.05568716863962286</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1395117083446725</v>
+        <v>0.1399705466182984</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2040535266.620744</v>
+        <v>2051357817.386538</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>351.37</v>
+        <v>351.445</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07954402156745477</v>
+        <v>0.07977445046467846</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04128240109140513</v>
+        <v>-0.04107776261937246</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>941499428700</v>
+        <v>941700391950</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.10619088564059</v>
+        <v>15.10576096302666</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>14.02917206195688</v>
+        <v>14.03216659166814</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.16328978540686</v>
+        <v>3.16319975809134</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.615778832241496</v>
+        <v>2.615704387102975</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7909488150041846</v>
+        <v>0.7909263045788494</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.06826351116359</v>
+        <v>20.06797588664663</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.281425207218286</v>
+        <v>6.281335179902766</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1726331371484984</v>
+        <v>-0.1726380504322287</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07676994899822165</v>
+        <v>0.07650952291258983</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2893751396518991</v>
+        <v>-0.2895470103944893</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.0170760167344964</v>
+        <v>0.01707237263298667</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7670347220969244</v>
+        <v>0.7680816077743046</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.169646219936739</v>
+        <v>0.1696582172333542</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2044868972.712569</v>
+        <v>2055091211.679513</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>371.775</v>
+        <v>371.14</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.0730056228688758</v>
+        <v>0.07117290530981002</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03577819851129505</v>
+        <v>-0.03742511087480871</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,31 +2228,31 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>694121476870</v>
+        <v>692935901891</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.58666100254885</v>
+        <v>31.53271028037383</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.8621010308201</v>
+        <v>24.81963600720482</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.60244283559612</v>
+        <v>15.5757935149029</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.22210601867645</v>
+        <v>20.18756621013133</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.130021547869249</v>
+        <v>2.126383423512052</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.24979300536119</v>
+        <v>24.20904879685889</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.86091703088473</v>
+        <v>15.83426771019151</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03027279907078205</v>
+        <v>0.03032459415460534</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007208661152578845</v>
+        <v>0.007220994772861994</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3014679487895589</v>
+        <v>0.3027942112292876</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.176358785651124</v>
+        <v>0.1771342037145193</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2201177220.262569</v>
+        <v>2210506952.644207</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>570.76</v>
+        <v>569.5599999999999</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01354926047454219</v>
+        <v>0.01141831381995972</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05129483727269712</v>
+        <v>-0.05328945181343714</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>500577067360</v>
+        <v>499524624160</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.34321801208127</v>
+        <v>31.27732015376166</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.73607075446453</v>
+        <v>25.68196169828443</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.26836551492176</v>
+        <v>14.23836684890118</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.7184672963821</v>
+        <v>89.52983781857066</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.385258296069663</v>
+        <v>1.38234584608143</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.23788512208356</v>
+        <v>23.19029771025502</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.6489487033606</v>
+        <v>14.61895003734002</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.0328580773520955</v>
+        <v>0.03292730569120379</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005904408157544327</v>
+        <v>0.005916848093264977</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.29062514884985</v>
+        <v>0.2911144575306407</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1932066487787013</v>
+        <v>0.1936677548848244</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1480861028.262964</v>
+        <v>1485001444.208325</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>379.60999</v>
+        <v>378.29999</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1284482666096955</v>
+        <v>0.1245540929361875</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1776569689354881</v>
+        <v>-0.1804948009185044</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,37 +2480,37 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>344740683900</v>
+        <v>343551016947</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.41064818982702</v>
+        <v>24.32640923413286</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.51259204373629</v>
+        <v>17.45215766060192</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7658708590204141</v>
+        <v>0.7632279123251334</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.493509320853149</v>
+        <v>3.481453533779901</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.739649013689145</v>
+        <v>-0.7370965513371065</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.11794759538874</v>
+        <v>15.07300442832745</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8652712531296584</v>
+        <v>0.8626989442737526</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06850656479770359</v>
+        <v>0.06873743126964807</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3938912143252915</v>
+        <v>0.3938912143252917</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>0.01040690486613927</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02386660056022235</v>
+        <v>0.02394924726273453</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.435637936826805</v>
+        <v>0.4343990570377064</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2300048304031516</v>
+        <v>0.229027339896481</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1751533147.843852</v>
+        <v>1755509099.510988</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>164.09</v>
+        <v>164.74</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3378719768330156</v>
+        <v>0.3431716098694071</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.06983731081004474</v>
+        <v>-0.06615271243126797</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>680064441400</v>
+        <v>682758340400</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.11196911196911</v>
+        <v>21.2020592020592</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.8510519789708</v>
+        <v>14.90988057173289</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.8829480374453</v>
+        <v>1.890983051016451</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.639673521628498</v>
+        <v>2.650937673452078</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.067213642213643</v>
+        <v>2.076034963534965</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.909086078663419</v>
+        <v>9.948323569787679</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.971196221126682</v>
+        <v>1.979001662881515</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04493484008149426</v>
+        <v>0.04474936180508649</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4215807164276184</v>
+        <v>0.422014019498951</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08166324800680869</v>
+        <v>0.0819929429738917</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02510817234444512</v>
+        <v>0.02500910525676824</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5583743515301339</v>
+        <v>-0.5542443070452834</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2513330320572517</v>
+        <v>0.2481105568062452</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2195296767.427505</v>
+        <v>2202874093.407667</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>267.85999</v>
+        <v>267.56</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2918253297097848</v>
+        <v>0.2903785489469706</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.04699900380688093</v>
+        <v>-0.0480663179990749</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>645515354409</v>
+        <v>644792420185</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.95954913294797</v>
+        <v>30.93179190751445</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.61749441164768</v>
+        <v>21.59328388230155</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.59019327058379</v>
+        <v>6.584284738790348</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.690376999329182</v>
+        <v>7.683482082122135</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.833281017645275</v>
+        <v>-3.829844234864624</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.98058332725602</v>
+        <v>19.96342998295387</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.882384552022383</v>
+        <v>6.876476020228941</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02898797580521503</v>
+        <v>0.0290139887107116</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4321525216292743</v>
+        <v>0.4324728038641219</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.08933884426234107</v>
+        <v>0.08958244178047914</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01971179047680843</v>
+        <v>0.01973389146359695</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1727717519192965</v>
+        <v>-0.1730788554631833</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.207938150586052</v>
+        <v>0.2079261879195986</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1608307061.057868</v>
+        <v>1613281392.456124</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>108.3701</v>
+        <v>108.44</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0389313768451941</v>
+        <v>-0.03831147618294017</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1982087895827168</v>
+        <v>-0.1976916247410476</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,31 +2858,31 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>862417925408</v>
+        <v>862974195200</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>39.1227797833935</v>
+        <v>39.14801444043322</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.93631460727707</v>
+        <v>34.9588489446178</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.172018272189606</v>
+        <v>1.172774237877799</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.774362012663124</v>
+        <v>8.780021580243897</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.460599474893344</v>
+        <v>9.466701673777493</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.58416222152711</v>
+        <v>21.59714734704358</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.256582851445966</v>
+        <v>1.25733881713416</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01566409927484873</v>
+        <v>0.01565400225770273</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009020015668528497</v>
+        <v>0.009014201401696792</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05629082922172535</v>
+        <v>-0.05655726834437549</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3070729759507302</v>
+        <v>0.3071195399978932</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2669157998.060524</v>
+        <v>2675558607.818647</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>147.96</v>
+        <v>148.1</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.04351510689062588</v>
+        <v>0.04450248263383139</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1153363228699551</v>
+        <v>-0.1144992526158446</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,31 +2984,31 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>351731834319</v>
+        <v>352064643570</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.92</v>
+        <v>21.94074074074074</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.94335688581644</v>
+        <v>20.96317352520556</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.041408152392224</v>
+        <v>4.045232139557864</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.599640956712268</v>
+        <v>6.605885548047357</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.91794285714308</v>
+        <v>20.93773544973567</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.72917259428813</v>
+        <v>17.74483125858662</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.329623981052946</v>
+        <v>4.333447968218587</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04524185316012042</v>
+        <v>0.0451990857094858</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
@@ -3017,7 +3017,7 @@
         <v>0.04663259665144603</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02543466982807141</v>
+        <v>0.02543466982807163</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02899837793998378</v>
+        <v>0.02897096556380824</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.0442625259997273</v>
+        <v>-0.045292058017889</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1500394124977721</v>
+        <v>0.1503810735648497</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1268543724.111756</v>
+        <v>1272470299.693518</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>308.04</v>
+        <v>308.034</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1092476043145723</v>
+        <v>-0.1092649543807135</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2781722319859402</v>
+        <v>-0.2781862917398946</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,31 +3110,31 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>307151920680</v>
+        <v>307145937978</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.51117318435754</v>
+        <v>21.51075418994413</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.52747425569247</v>
+        <v>20.52707442175683</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.815576208682083</v>
+        <v>1.815540844907079</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.42641632063549</v>
+        <v>18.42605741108503</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.378832662076166</v>
+        <v>-7.37868893724831</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.37252438553209</v>
+        <v>15.37227422028016</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.173085548068284</v>
+        <v>2.173050184293281</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.0491645957041977</v>
+        <v>0.04916555335034788</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03015842098428775</v>
+        <v>0.03015900842114831</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7118905014936657</v>
+        <v>0.7112705330733424</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2413912795913898</v>
+        <v>0.2413947795001182</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1200616632.192054</v>
+        <v>1204249115.912734</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>526.3273</v>
+        <v>520.96002</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.355248118874754</v>
+        <v>1.331230219511612</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.09987977357070776</v>
+        <v>-0.1090588476732851</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,40 +3236,40 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>858229295380</v>
+        <v>849477411829</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>133.5856091370558</v>
+        <v>132.2055837563452</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>38.77943549487809</v>
+        <v>38.38397797530244</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>20.77785486938627</v>
+        <v>20.56320624621717</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.76984151939784</v>
+        <v>12.63792083184577</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.078489321473478</v>
+        <v>1.067347832161319</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>80.02129949617466</v>
+        <v>79.170855943273</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>20.76427279990316</v>
+        <v>20.54359602953638</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009788249880584051</v>
+        <v>0.009893293780126112</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.444753834921077</v>
+        <v>2.444290840345176</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.8988302387766913</v>
+        <v>0.8985750179653031</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.543980070502435</v>
+        <v>2.542240303618909</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6723667388671691</v>
+        <v>0.668824810785113</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9526354595.547436</v>
+        <v>9563990051.388908</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1609.3425</v>
+        <v>1601.26</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3828579795894262</v>
+        <v>0.3759129386052782</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1953126562531251</v>
+        <v>-0.1993539870797416</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>861.1799999999999</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>620269553181</v>
+        <v>617154412269</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>50.66037735849056</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>33.02961111517773</v>
+        <v>32.86372856883447</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.23234304816361</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5337866734740684</v>
+        <v>0.5415285959528378</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2856935401255383</v>
+        <v>0.292183190798883</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004834272381422849</v>
+        <v>0.004858673794386921</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.685865454439055</v>
+        <v>1.686563141305556</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4362877663565686</v>
+        <v>0.4355645706920054</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2024414593.658516</v>
+        <v>2030350696.98842</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>211.34</v>
+        <v>209.77</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07213418783979642</v>
+        <v>-0.07902710600527152</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.169097700019658</v>
+        <v>-0.1752702968350697</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>167036795800</v>
+        <v>165795914900</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>79.15355805243443</v>
+        <v>78.56554307116102</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>83.13396862336106</v>
+        <v>82.51638401685648</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.777081714984839</v>
+        <v>1.763880152135752</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.40645950161312</v>
+        <v>27.20286273139672</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4236356748633096</v>
+        <v>0.420488575357606</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.59536630215827</v>
+        <v>29.41682228776978</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.188284438533965</v>
+        <v>2.175082875684877</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001257208024101717</v>
+        <v>-0.001266617456326724</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.04787947257708691</v>
+        <v>-0.04787947257708702</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1537975177777891</v>
+        <v>0.1537975177777893</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.241962403843824</v>
+        <v>1.241099396291876</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3351803178530742</v>
+        <v>0.3346224644609525</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1023742467.130764</v>
+        <v>1027151426.951191</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>978.925</v>
+        <v>983.48</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.07063561831220166</v>
+        <v>0.07561735362533817</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1517040875570846</v>
+        <v>-0.1477569129715162</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>288789727475</v>
+        <v>290133484360</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.9135435709933</v>
+        <v>14.98293723339427</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.51438611179333</v>
+        <v>13.57726940595705</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.448677916811518</v>
+        <v>2.460071770182386</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.393438207785436</v>
+        <v>2.404575027293021</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3495527965875705</v>
+        <v>0.3511792878800152</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.86578942678304</v>
+        <v>26.90859377440831</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.151256412109855</v>
+        <v>7.162650265480722</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1437551133240841</v>
+        <v>-0.143089309707141</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3649,7 +3649,7 @@
         <v>0.1035309667509787</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3822426848979621</v>
+        <v>-0.382242684897962</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01838751691906939</v>
+        <v>0.01830235490299752</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.568520056957277</v>
+        <v>1.570169884634251</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3026975806733175</v>
+        <v>0.3033121256680233</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1793973811.470195</v>
+        <v>1800924642.303914</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>240.94</v>
+        <v>239.92</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1734476843910806</v>
+        <v>-0.1769468267581475</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2752812368405221</v>
+        <v>-0.278349275100764</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>226997765960</v>
+        <v>226036789280</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>21.04279475982533</v>
+        <v>20.95021834061135</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.67129747777815</v>
+        <v>18.5922540502554</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.285204364299463</v>
+        <v>3.27075131944947</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.573188958551028</v>
+        <v>6.544270637408569</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2565100368978709</v>
+        <v>0.2553815375241191</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>17.57584402687874</v>
+        <v>17.51427802971457</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.126051289636308</v>
+        <v>4.111598244786316</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06004904912765512</v>
+        <v>0.06031439843595642</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1270129879763118</v>
+        <v>0.1268250898456054</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04610799352298289</v>
+        <v>0.04593358405423964</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02797376940317092</v>
+        <v>0.02809269756585529</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.8855233417986426</v>
+        <v>0.8894001438085999</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3176603538400597</v>
+        <v>0.3206742039625407</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1161328547.549453</v>
+        <v>1167065793.15897</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1145.75</v>
+        <v>1138.21008</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06052613530216844</v>
+        <v>0.05354705416048189</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1136425173094032</v>
+        <v>-0.1194754341855878</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,37 +3868,37 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1078999750750</v>
+        <v>1071899101782</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.3322181331549</v>
+        <v>38.07996252927401</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.21265617928169</v>
+        <v>26.04015665444705</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.54407726715855</v>
+        <v>13.45494681258457</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.17997284453496</v>
+        <v>29.98136531160896</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.40521876842757</v>
+        <v>0.4025521159323115</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.97905430229443</v>
+        <v>25.81508520491955</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.12171535025067</v>
+        <v>14.03258489567669</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.0185856391403805</v>
+        <v>0.0187087571644206</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4623553550232133</v>
+        <v>0.4623553550232131</v>
       </c>
       <c r="V27" s="4" t="n">
         <v>0.2290918506683588</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005838970106916867</v>
+        <v>0.005877649581173978</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3457100598959101</v>
+        <v>0.3442964643056499</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3246364649911769</v>
+        <v>0.3238862262068379</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2988368156.592773</v>
+        <v>2995338716.922424</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>207.415</v>
+        <v>207.94</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1402694170404188</v>
+        <v>0.1431556183467189</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1069321851453175</v>
+        <v>-0.1046716899892357</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,31 +3994,31 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>327151531200</v>
+        <v>327979603200</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.67323151125402</v>
+        <v>16.71543408360129</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.39986893249027</v>
+        <v>15.43884842379783</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.585585369361965</v>
+        <v>2.592129892751859</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.951076057128884</v>
+        <v>2.958545694956393</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4241936108133857</v>
+        <v>0.4252673115856396</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.56607255256074</v>
+        <v>23.59428913347191</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.465889489366075</v>
+        <v>5.472434012755969</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04794108694057062</v>
+        <v>-0.04782004687784194</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02000819612853458</v>
+        <v>0.01995768010002886</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.377667327960806</v>
+        <v>1.378540990024976</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2611880847700112</v>
+        <v>0.2616416850037697</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>866532109.8652943</v>
+        <v>871917450.0828471</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>929.47</v>
+        <v>932.63</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.946769261402464</v>
+        <v>1.956787649156809</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2593864541832669</v>
+        <v>-0.2568685258964144</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1049734123300</v>
+        <v>1053302995700</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.74246819906271</v>
+        <v>20.81298817228297</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.95494329743573</v>
+        <v>5.975188836097437</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.62831073509538</v>
+        <v>11.66784451447814</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.40906000555975</v>
+        <v>10.44444859219253</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02956409924343717</v>
+        <v>0.02966461088298364</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.08670792366781</v>
+        <v>15.13891077312498</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.42207213318342</v>
+        <v>11.46159465294548</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02493200333010484</v>
+        <v>0.02484755109103883</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005702174357429503</v>
+        <v>0.0005682853864876746</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.877844639466991</v>
+        <v>2.882512446595185</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8122173015895694</v>
+        <v>0.812253483866804</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25488204420.92985</v>
+        <v>25546161510.99267</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>140.83</v>
+        <v>141.13</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0448965553425269</v>
+        <v>-0.04286196730448655</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2767786530817661</v>
+        <v>-0.2752380267658145</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>145598785460</v>
+        <v>145908944060</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>87.47204968944101</v>
+        <v>87.65838509316771</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>29.69648027762235</v>
+        <v>29.75974054946277</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.883164910399131</v>
+        <v>9.904218304371437</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.62331335890061</v>
+        <v>11.64807366570789</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>139.9552795031086</v>
+        <v>140.2534161490713</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>43.43616665520207</v>
+        <v>43.52506278589853</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.28704761471626</v>
+        <v>10.30810100868857</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03145630635262581</v>
+        <v>0.03138943969135048</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.703517495086097</v>
+        <v>0.7052059814271606</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6279114251488768</v>
+        <v>0.627621340293255</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2176582239.990946</v>
+        <v>2182064502.654715</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.605</v>
+        <v>27.525</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09630657924677455</v>
+        <v>0.09312945458313604</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05494693598082845</v>
+        <v>-0.05768572406710037</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157333041200</v>
+        <v>156877083826</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.47595137420719</v>
+        <v>36.37024312896406</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.455778672075736</v>
+        <v>9.428375582281637</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.470061561165536</v>
+        <v>2.462903225100477</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.846706127479751</v>
+        <v>1.841354325625073</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6100844964358547</v>
+        <v>-0.6083164558738237</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.39155903041825</v>
+        <v>17.35544090621039</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.446857592313489</v>
+        <v>3.439699290379302</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06982640083868155</v>
+        <v>0.07002934768943885</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4405,7 +4405,7 @@
         <v>2.857530155811058</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05042615492450442</v>
+        <v>-0.05042615492450431</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06230755297953269</v>
+        <v>0.06248864668483197</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3479709659284707</v>
+        <v>0.3477023955980426</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2077863857129715</v>
+        <v>0.2079352472148128</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>945056547.4672413</v>
+        <v>947913307.6000832</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>179.3187</v>
+        <v>177.3</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.06730971884356518</v>
+        <v>0.05529436222192174</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1028233351678591</v>
+        <v>-0.1129234002101366</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1272902562428</v>
+        <v>1258572721743</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.685570928250936</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003723068627362769</v>
+        <v>0.003681155772551435</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.600574583261782</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2063.310840731131</v>
+        <v>2086.814643856816</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2670.248850300211</v>
+        <v>2700.663120205711</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.672998967759637</v>
+        <v>1.692047377326565</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9154040808242494</v>
+        <v>0.9142111589146109</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3140685843.304704</v>
+        <v>3153279962.258524</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>552.1356</v>
+        <v>548.90002</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4790667507501045</v>
+        <v>0.4703992444393506</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1781617373442688</v>
+        <v>-0.1829778068856704</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>69591584021</v>
+        <v>69183769654</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.827958376954615</v>
+        <v>1.828020121201922</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4033292719119316</v>
+        <v>0.4019387204207725</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3720531518.062378</v>
+        <v>3731184256.008455</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>152.2995</v>
+        <v>149.715</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.05374648718399166</v>
+        <v>-0.06980426940831252</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3250332387874491</v>
+        <v>-0.3364873249423861</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1991447762499</v>
+        <v>1957653194649</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-98.89577922077922</v>
+        <v>-97.21753246753246</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>136.8285069042755</v>
+        <v>134.5065473699756</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>120.1476779788235</v>
+        <v>118.1087900240724</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.019778249386908</v>
+        <v>6.900653650254669</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9889577922077922</v>
+        <v>-0.9721753246753246</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>464.9123500117591</v>
+        <v>456.7238536148308</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>116.8802269984314</v>
+        <v>114.8216167730317</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01427253103758692</v>
+        <v>-0.01452133966056344</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.214836670179136</v>
+        <v>4.214836670179135</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.539215959670987</v>
+        <v>3.505441085308753</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7842372976340035</v>
+        <v>0.7779485665244231</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14075368301.73266</v>
+        <v>14148452751.63368</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>760.87</v>
+        <v>759.4400000000001</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1137345302538886</v>
+        <v>0.1116413469528477</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02373712100799363</v>
+        <v>-0.02557193630753041</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>810507809017</v>
+        <v>808984518353</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.995029222259491</v>
+        <v>0.9950631604548276</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1128091657703609</v>
+        <v>0.1124905490063523</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>28658069989.11263</v>
+        <v>28774395592.97583</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>418.95001</v>
+        <v>417.19</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3108163987403776</v>
+        <v>0.3053096558954567</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1253653235908142</v>
+        <v>-0.1290396659707724</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2172875859312</v>
+        <v>2163747591200</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>27.58780572620842</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6385199650913073</v>
+        <v>0.6358375411816852</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>13.89916072363153</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.20586236056598</v>
+        <v>42.38813602439594</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.17267580496152</v>
+        <v>42.35480969223327</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.286430354781469</v>
+        <v>0.2876387257604449</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.184027822511649</v>
+        <v>2.183854143285995</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3565425843995432</v>
+        <v>0.355839799257699</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4015868130.797678</v>
+        <v>4028153821.240675</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.045</v>
+        <v>27.98</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.0163100745404684</v>
+        <v>-0.01858997631101111</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.0651666666666666</v>
+        <v>-0.06733333333333336</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70312648808</v>
+        <v>70149684922</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.08267716535433</v>
+        <v>-22.03149606299213</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-82.92737924132929</v>
+        <v>-82.73517814841837</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.946909838238959</v>
+        <v>1.942397478111588</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.144497076557647</v>
+        <v>2.139526767769048</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1643362021607765</v>
+        <v>0.1639553195385461</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.35812376991736</v>
+        <v>16.33118759041322</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.740319778706909</v>
+        <v>2.735807418579538</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.0310043788273834</v>
+        <v>0.03107640472546612</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2328888598444398</v>
+        <v>0.2329513225575355</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1849474654543697</v>
+        <v>0.1850855406196676</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>491962398.8552333</v>
+        <v>494329747.1355879</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>317.42</v>
+        <v>316.96</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1483916222360665</v>
+        <v>-0.1496257595108804</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1808304730444656</v>
+        <v>-0.1820176004542053</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>214356900200</v>
+        <v>214046257600</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.24924196482717</v>
+        <v>19.22134627046695</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.3298736552132</v>
+        <v>16.30620866283276</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.549652090445208</v>
+        <v>2.545957175311931</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.278026837806301</v>
+        <v>6.268928821470245</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.193621117469635</v>
+        <v>1.191891340788783</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.228397516583078</v>
+        <v>9.215833101439896</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.713866523140604</v>
+        <v>2.710171608007327</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07021933973646816</v>
+        <v>0.0703212481674335</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01115241635687732</v>
+        <v>0.0111686017163049</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9525098451541913</v>
+        <v>0.95573991499356</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2235971589181255</v>
+        <v>0.2244041645061526</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>750498659.687384</v>
+        <v>756062954.2150726</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>143.85</v>
+        <v>143</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2649839299718987</v>
+        <v>-0.2693270906220473</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5634294385432473</v>
+        <v>-0.5660091047040972</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>414355609500</v>
+        <v>411907210000</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.19907407407407</v>
+        <v>22.0679012345679</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.01392939571599</v>
+        <v>15.91930416119143</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.7728187232679</v>
+        <v>5.73870752469454</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.38979063080333</v>
+        <v>6.352033786617144</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4831563180827889</v>
+        <v>0.4803013798111839</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.15476165164369</v>
+        <v>14.0875608669141</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.438561231313653</v>
+        <v>7.403246108084763</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.0693124440493426</v>
+        <v>-0.06973907166886713</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01390337156760514</v>
+        <v>0.01398601398601399</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.074360657889285</v>
+        <v>2.071867899284275</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5644469665851484</v>
+        <v>0.5632901636292426</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4070435031.170095</v>
+        <v>4085331214.393292</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 11:49 ET</t>
+          <t>2026-09-16 13:42 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -443,7 +443,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>333.17</v>
+        <v>332.41</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2293641858030715</v>
+        <v>0.2265598613404538</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.03308471428156823</v>
+        <v>-0.03529036190033941</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,31 +714,31 @@
         <v>236.65</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4893386398520</v>
+        <v>4882224007960</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.03310502283105</v>
+        <v>37.94634703196348</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.81610079391454</v>
+        <v>34.73668116848796</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.48231642082759</v>
+        <v>10.45840502280307</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.52739232282367</v>
+        <v>45.42353898018974</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.162122653475392</v>
+        <v>1.159471714865549</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.30895978609498</v>
+        <v>29.24270864024311</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.57820501243512</v>
+        <v>10.5542936144106</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02793219028060806</v>
+        <v>0.02799605257299776</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
@@ -747,7 +747,7 @@
         <v>0.09239989991868391</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1181903052061182</v>
+        <v>0.118190305206118</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003181558963892307</v>
+        <v>0.003188833067597245</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3073909453031456</v>
+        <v>0.3070200193013617</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.295121215507686</v>
+        <v>0.2949067799982662</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>12980051631.23029</v>
+        <v>13207349211.33701</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>493.65</v>
+        <v>490.3</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.04378990453690701</v>
+        <v>0.03670655361986341</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1084844325651955</v>
+        <v>-0.114534421729394</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,31 +842,31 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3665622757500</v>
+        <v>3640747165000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.425</v>
+        <v>27.23888888888889</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.04212101383646</v>
+        <v>23.87896674381447</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.04638923544249</v>
+        <v>10.97142639954918</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.289858992239825</v>
+        <v>8.233602479277193</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8711096287703</v>
+        <v>0.8651981180716664</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.18385814070037</v>
+        <v>18.06398674338254</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.37146645662505</v>
+        <v>11.29650362073174</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01827438458115804</v>
+        <v>0.01839924525492283</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
@@ -875,7 +875,7 @@
         <v>0.1407063455098934</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.226123141342697</v>
+        <v>0.2261231413426967</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007373645295249672</v>
+        <v>0.00742402610646543</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5551376334446451</v>
+        <v>0.5568418062448269</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4342310741701302</v>
+        <v>0.4356886680199505</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>11058390305.86168</v>
+        <v>11219174471.19954</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>345.1163</v>
+        <v>342.87</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09508585335197095</v>
+        <v>0.08795813625375049</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1553894912018795</v>
+        <v>-0.1608869092777955</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4176635869213</v>
+        <v>4149450896631</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.97120158887785</v>
+        <v>16.85004965243297</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.65803266851042</v>
+        <v>20.52357324488055</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.303358986991608</v>
+        <v>9.236945306686314</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.484530039970023</v>
+        <v>6.438239070696978</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1509258827979006</v>
+        <v>0.149848471580736</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.96152121018984</v>
+        <v>12.87618994433856</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.42649745372152</v>
+        <v>9.364438768847592</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01284891227647861</v>
+        <v>0.01293523806617031</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1784696122226828</v>
+        <v>-0.1789904491102158</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2914974064075679</v>
+        <v>0.2906786180835044</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002491913595503892</v>
+        <v>0.002508239274360545</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7637304034222537</v>
+        <v>0.7646756005936947</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.363660526928079</v>
+        <v>0.3639582618317491</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8117941626.862364</v>
+        <v>8244449990.676066</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>247.48</v>
+        <v>245.96</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.09262693156732893</v>
+        <v>0.08591611479028693</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1383008356545961</v>
+        <v>-0.1435933147632311</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,31 +1094,31 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2662167108000</v>
+        <v>2645816316000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.64126984126984</v>
+        <v>19.52063492063492</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>21.98458639795307</v>
+        <v>21.84955903685363</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.432042991955446</v>
+        <v>3.410963691212872</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.825595301113085</v>
+        <v>4.795956926869946</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2223351865280799</v>
+        <v>0.2209696237208928</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.05204434698048</v>
+        <v>10.98767038980775</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.619000242367987</v>
+        <v>3.597920941625413</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004366743156380399</v>
+        <v>-0.004393729046759722</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8328268405069893</v>
+        <v>0.8342653851018501</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4600876733924124</v>
+        <v>0.4606488180473121</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8409213895.895597</v>
+        <v>8552608470.084135</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>214.93</v>
+        <v>213.9</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1380989836038924</v>
+        <v>0.1326449197081496</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.09135875539020877</v>
+        <v>-0.09571319861334227</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5205819530000</v>
+        <v>5180871900000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.03522012578616</v>
+        <v>26.90566037735849</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.05328322802149</v>
+        <v>15.97635175393754</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.18268050526622</v>
+        <v>17.10033666810796</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.70532744645914</v>
+        <v>22.59651766062257</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.21701741325461</v>
+        <v>0.2159774098318573</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.34905455199065</v>
+        <v>22.2422888127121</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.23686756730887</v>
+        <v>17.15452373015061</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02439692718276002</v>
+        <v>0.0245144065422656</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6840928887740154</v>
+        <v>0.6840928887740156</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9386961152552926</v>
+        <v>0.9386961152552931</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002419392360303355</v>
+        <v>0.002431042543244507</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.329636861962327</v>
+        <v>1.328855676123753</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4099954508104316</v>
+        <v>0.409323484252594</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26560966939.45884</v>
+        <v>26912650248.31583</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>675.33</v>
+        <v>673.3099999999999</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.03831433693273212</v>
+        <v>0.03520860349781252</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1460166919575113</v>
+        <v>-0.148571067273647</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,31 +1346,31 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1720394105318</v>
+        <v>1715248182447</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>25.0958751393534</v>
+        <v>25.02081010776663</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.41960097192799</v>
+        <v>20.35852328551795</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.53738961707441</v>
+        <v>7.514844302894221</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.574372619352962</v>
+        <v>6.554707814455958</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.144654403567443</v>
+        <v>-5.129266072092154</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.97222528128736</v>
+        <v>16.92416488388187</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.961735065884477</v>
+        <v>7.939189751704287</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02381779841801187</v>
+        <v>0.0238892542894539</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
@@ -1379,7 +1379,7 @@
         <v>0.2290090866052747</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2723933984855693</v>
+        <v>0.2723933984855695</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003109590866687397</v>
+        <v>0.003118919962572961</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.772962720498962</v>
+        <v>0.7724072583281306</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4082136723680519</v>
+        <v>0.4080010568011128</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>9949231028.802986</v>
+        <v>10138078593.51151</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>360.61</v>
+        <v>358.08</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1768210697585832</v>
+        <v>-0.1825964023714082</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2770883868251709</v>
+        <v>-0.2821602549966923</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1424246285750</v>
+        <v>1414253930844</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>305.5932203389831</v>
+        <v>303.4576271186441</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>171.5229453125959</v>
+        <v>170.3195592399943</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.74464905351335</v>
+        <v>13.64859659757381</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.4387413939994</v>
+        <v>13.3448267286836</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.134805442826448</v>
+        <v>-8.077956552876579</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>117.9190048450283</v>
+        <v>117.0915306654473</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.68793165612484</v>
+        <v>13.59187920018529</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004045760797758428</v>
+        <v>0.004074232974951922</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7816462968382902</v>
+        <v>0.7816957046668216</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1224372535904901</v>
+        <v>0.1224683805249132</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.535600663616592</v>
+        <v>1.535109374454157</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5726894060795944</v>
+        <v>0.5719937960643585</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12633721610.01515</v>
+        <v>12789598512.76878</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>339.56</v>
+        <v>339.51</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02318622412519844</v>
+        <v>-0.02333005934958809</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.314020202020202</v>
+        <v>-0.3141212121212121</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,31 +1598,31 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1615483864800</v>
+        <v>1615245985800</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>42.12903225806451</v>
+        <v>42.1228287841191</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.56397854018256</v>
+        <v>18.56124500582337</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.13031810917579</v>
+        <v>18.12764843104686</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.23375423813823</v>
+        <v>16.23136382786639</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4192047269243051</v>
+        <v>0.4191429992875215</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>31.58884612058244</v>
+        <v>31.58429454489792</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.52810047584845</v>
+        <v>18.52543079771952</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.0243908347576583</v>
+        <v>0.02439442682192116</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007480268582871952</v>
+        <v>0.007481370210008542</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.603985187995199</v>
+        <v>1.605185479351388</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3888628033345141</v>
+        <v>0.3888614920512946</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8477247786.818019</v>
+        <v>8628716383.128927</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>899.6512</v>
+        <v>893.74</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.05283932124049162</v>
+        <v>0.04592159157401987</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1795246694026448</v>
+        <v>-0.1849156406748745</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>398976414525</v>
+        <v>396354921460</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.18589653440482</v>
+        <v>44.88900050226017</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.68840463987337</v>
+        <v>39.42763013359002</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.358971666064914</v>
+        <v>1.350042479605705</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.91846547666597</v>
+        <v>11.8401546456176</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.564441034655955</v>
+        <v>3.541020709263116</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.83223320836213</v>
+        <v>26.65106575397374</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.322478224597819</v>
+        <v>1.31354903813861</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.0220714801161466</v>
+        <v>0.02221746097553805</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006157942100227288</v>
+        <v>0.006198670754358091</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1861335977966155</v>
+        <v>-0.1859168656137269</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1761941997795605</v>
+        <v>0.1771192357234746</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1677501986.623104</v>
+        <v>1715705441.000846</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>77.1534</v>
+        <v>76.41</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1520672402310166</v>
+        <v>-0.1602373690083909</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3820807304180682</v>
+        <v>-0.3880345987506006</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,31 +1850,31 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>321262128319</v>
+        <v>318166655324</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>23.88650154798762</v>
+        <v>23.65634674922601</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.57126706678467</v>
+        <v>20.37305571203624</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.641659170795814</v>
+        <v>6.577664461202226</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.71963427498069</v>
+        <v>10.61634684863239</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7020301064713437</v>
+        <v>0.695265800800423</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.67005905339595</v>
+        <v>10.56889001229465</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.749370390738505</v>
+        <v>6.685375681144917</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03422316865523224</v>
+        <v>0.03455612904753898</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
@@ -1883,7 +1883,7 @@
         <v>0.1611584969676407</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1437551576299554</v>
+        <v>0.1437551576299556</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09734136717653576</v>
+        <v>0.0988661944525397</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.331529085667676</v>
+        <v>0.3345329005052507</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2115393626.214532</v>
+        <v>2157532253.854227</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>521.14</v>
+        <v>520.67</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.04888798147951245</v>
+        <v>0.04794202194599873</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.03086993714434494</v>
+        <v>-0.03174396548517877</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1124022682498</v>
+        <v>1123008961309</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>13.09948970953909</v>
+        <v>13.07989678192819</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.49276185727387</v>
+        <v>23.47157446411095</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.921603526492967</v>
+        <v>2.917233679448487</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.49589394694852</v>
+        <v>1.49365653599084</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3608575822887061</v>
+        <v>0.3603178470284479</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.84891517625533</v>
+        <v>15.82694503549677</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.152339163517353</v>
+        <v>3.147969316472873</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02154545565331053</v>
+        <v>0.02157772949766241</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4424031627646536</v>
+        <v>-0.4427345808468063</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06058376751169559</v>
+        <v>0.05995338976402564</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.05568716863962286</v>
+        <v>0.05282987392123903</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1399705466182984</v>
+        <v>0.1393146521303358</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2051357817.386538</v>
+        <v>2110350198.758909</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>351.445</v>
+        <v>348.92</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07977445046467846</v>
+        <v>0.07201667759147434</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04107776261937246</v>
+        <v>-0.04796725784447475</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>941700391950</v>
+        <v>934934629200</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.10576096302666</v>
+        <v>15.00085984522786</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>14.03216659166814</v>
+        <v>13.9313507580556</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.16319975809134</v>
+        <v>3.141233093104595</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.615704387102975</v>
+        <v>2.597539773303648</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7909263045788494</v>
+        <v>0.7854337607970518</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.06797588664663</v>
+        <v>19.99779550450837</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.281335179902766</v>
+        <v>6.25936851491602</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1726380504322287</v>
+        <v>-0.1738453095261604</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07650952291258983</v>
+        <v>0.07676994899822165</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2895470103944893</v>
+        <v>-0.2893751396518991</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01707237263298667</v>
+        <v>0.0171959188352631</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7680816077743046</v>
+        <v>0.7708858064475166</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1696582172333542</v>
+        <v>0.1714957115652187</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2055091211.679513</v>
+        <v>2116091765.374923</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>371.14</v>
+        <v>370.93</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.07117290530981002</v>
+        <v>0.07056680973909524</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03742511087480871</v>
+        <v>-0.03796975905801792</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,31 +2228,31 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>692935901891</v>
+        <v>692543821976</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.53271028037383</v>
+        <v>31.51486830926083</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.81963600720482</v>
+        <v>24.80559245608796</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.5757935149029</v>
+        <v>15.56698035371336</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.18756621013133</v>
+        <v>20.17614359628177</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.126383423512052</v>
+        <v>2.125180264275814</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.20904879685889</v>
+        <v>24.19557433418104</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.83426771019151</v>
+        <v>15.82545454900198</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03032459415460534</v>
+        <v>0.03034176225851626</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007220994772861994</v>
+        <v>0.007225082899738495</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3027942112292876</v>
+        <v>0.3080010447724384</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1771342037145193</v>
+        <v>0.1773232932326329</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2210506952.644207</v>
+        <v>2269386064.094275</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>569.5599999999999</v>
+        <v>567.75</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01141831381995972</v>
+        <v>0.008204135949298141</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05328945181343714</v>
+        <v>-0.05629799541238656</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>499524624160</v>
+        <v>497937189000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.27732015376166</v>
+        <v>31.17792421746293</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.68196169828443</v>
+        <v>25.60034720521277</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.23836684890118</v>
+        <v>14.1931188609868</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.52983781857066</v>
+        <v>89.24532168953841</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.38234584608143</v>
+        <v>1.377952900682513</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.19029771025502</v>
+        <v>23.11852003074697</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.61895003734002</v>
+        <v>14.57370204942565</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03292730569120379</v>
+        <v>0.0330322786956971</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005916848093264977</v>
+        <v>0.005935711140466755</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2911144575306407</v>
+        <v>0.2945476222545185</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1936677548848244</v>
+        <v>0.1945693605476321</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1485001444.208325</v>
+        <v>1516304142.725171</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>378.29999</v>
+        <v>375.26</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1245540929361875</v>
+        <v>0.1155172616188378</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1804948009185044</v>
+        <v>-0.187080282483428</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,37 +2480,37 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>343551016947</v>
+        <v>340790269045</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.32640923413286</v>
+        <v>24.13092405633078</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.45215766060192</v>
+        <v>17.31191344656784</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7632279123251334</v>
+        <v>0.7570946751820034</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.481453533779901</v>
+        <v>3.45347683748616</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7370965513371065</v>
+        <v>-0.7311732994091873</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.07300442832745</v>
+        <v>14.96461083899391</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8626989442737526</v>
+        <v>0.8564950692912475</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06873743126964807</v>
+        <v>0.06930068768155311</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3938912143252917</v>
+        <v>0.3938912143252915</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>0.01040690486613927</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02394924726273453</v>
+        <v>0.02414326067260033</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4343990570377064</v>
+        <v>0.4338100090495249</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.229027339896481</v>
+        <v>0.2278803417529079</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1755509099.510988</v>
+        <v>1782957324.889425</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>164.74</v>
+        <v>163.345</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3431716098694071</v>
+        <v>0.3317977820451516</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.06615271243126797</v>
+        <v>-0.0740604274134119</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,31 +2606,31 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>682758340400</v>
+        <v>676976818700</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.2020592020592</v>
+        <v>21.02252252252252</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.90988057173289</v>
+        <v>14.78362536111271</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.890983051016451</v>
+        <v>1.874970416828228</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.650937673452078</v>
+        <v>2.62848982803223</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.076034963534965</v>
+        <v>2.058455330330331</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.948323569787679</v>
+        <v>9.867829010790116</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.979001662881515</v>
+        <v>1.962989028693292</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04474936180508649</v>
+        <v>0.04513153058722304</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
@@ -2639,7 +2639,7 @@
         <v>0.422014019498951</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.0819929429738917</v>
+        <v>0.08199294297389192</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02500910525676824</v>
+        <v>0.02522268817533442</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5542443070452834</v>
+        <v>-0.5384489964726794</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2481105568062452</v>
+        <v>0.2553168456323008</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2202874093.407667</v>
+        <v>2241902169.930573</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>267.56</v>
+        <v>267.28</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2903785489469706</v>
+        <v>0.289028175222553</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.0480663179990749</v>
+        <v>-0.0490625111182269</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>644792420185</v>
+        <v>644117648628</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.93179190751445</v>
+        <v>30.89942196531792</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.59328388230155</v>
+        <v>21.57068663500358</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.584284738790348</v>
+        <v>6.577394322703183</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.683482082122135</v>
+        <v>7.675441362347152</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.829844234864624</v>
+        <v>-3.825836324916343</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.96342998295387</v>
+        <v>19.94342608288865</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.876476020228941</v>
+        <v>6.869585604141776</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.0290139887107116</v>
+        <v>0.02904438349088694</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01973389146359695</v>
+        <v>0.01975456450164622</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1730788554631833</v>
+        <v>-0.1723926613704065</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2079261879195986</v>
+        <v>0.2079413320510723</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1613281392.456124</v>
+        <v>1640539099.46374</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>108.44</v>
+        <v>107.5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.03831147618294017</v>
+        <v>-0.04664776548935878</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1976916247410476</v>
+        <v>-0.2046463450725067</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,31 +2858,31 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>862974195200</v>
+        <v>855493600000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>39.14801444043322</v>
+        <v>38.8086642599278</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.9588489446178</v>
+        <v>34.6558120762303</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.172774237877799</v>
+        <v>1.162608175690367</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.780021580243897</v>
+        <v>8.703912946110465</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.466701673777493</v>
+        <v>9.384640630128002</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.59714734704358</v>
+        <v>21.42252620275917</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.25733881713416</v>
+        <v>1.247172754946728</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01565400225770273</v>
+        <v>0.0157908837658166</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009014201401696792</v>
+        <v>0.009093023255813954</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05655726834437549</v>
+        <v>-0.05510360733280622</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3071195399978932</v>
+        <v>0.307080509567927</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2675558607.818647</v>
+        <v>2709248419.584712</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>148.1</v>
+        <v>147.04</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.04450248263383139</v>
+        <v>0.03702663772098957</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1144992526158446</v>
+        <v>-0.1208370702541106</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,40 +2984,40 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>352064643570</v>
+        <v>349544802096</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.94074074074074</v>
+        <v>21.7837037037037</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.96317352520556</v>
+        <v>20.81313325554507</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.045232139557864</v>
+        <v>4.016279093850538</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.605885548047357</v>
+        <v>6.558605070795971</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.93773544973567</v>
+        <v>20.78787724867747</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.74483125858662</v>
+        <v>17.62627280022584</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.333447968218587</v>
+        <v>4.30449492251126</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.0451990857094858</v>
+        <v>0.04552492242648085</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04663259665144603</v>
+        <v>0.04663259665144581</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02543466982807163</v>
+        <v>0.02543466982807141</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02897096556380824</v>
+        <v>0.02917981501632209</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.045292058017889</v>
+        <v>-0.04729346856656391</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1503810735648497</v>
+        <v>0.1484728506341582</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1272470299.693518</v>
+        <v>1293885600.720227</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>308.034</v>
+        <v>302.47</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1092649543807135</v>
+        <v>-0.1253542490489179</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2781862917398946</v>
+        <v>-0.2912243702401874</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>426.75</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>307145937978</v>
+        <v>301597978990</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.51075418994413</v>
+        <v>21.12220670391061</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.52707442175683</v>
+        <v>20.15629508544118</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.815540844907079</v>
+        <v>1.78274683755379</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.42605741108503</v>
+        <v>18.09322862129145</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.37868893724831</v>
+        <v>-7.245408113550766</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.37227422028016</v>
+        <v>15.14028764332009</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.173050184293281</v>
+        <v>2.140256176939991</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04916555335034788</v>
+        <v>0.05006996416411895</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.0479210893854749</v>
+        <v>0.04792108938547468</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03015900842114831</v>
+        <v>0.03071378979733527</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7112705330733424</v>
+        <v>0.7117966030708344</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2413947795001182</v>
+        <v>0.2406043143442007</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1204249115.912734</v>
+        <v>1228364276.919541</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>520.96002</v>
+        <v>512.5</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.331230219511612</v>
+        <v>1.293372699693349</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1090588476732851</v>
+        <v>-0.123527097976844</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,40 +3236,40 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>849477411829</v>
+        <v>835682500000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>132.2055837563452</v>
+        <v>130.0761421319797</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>38.38397797530244</v>
+        <v>37.76064948773325</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>20.56320624621717</v>
+        <v>20.23199370536255</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.63792083184577</v>
+        <v>12.43436124003332</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.067347832161319</v>
+        <v>1.050156009872863</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>79.170855943273</v>
+        <v>77.89442993095727</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>20.54359602953638</v>
+        <v>20.21238348868176</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009893293780126112</v>
+        <v>0.01005525423830223</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.444290840345176</v>
+        <v>2.444753834921077</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.8985750179653031</v>
+        <v>0.8988302387766913</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.542240303618909</v>
+        <v>2.540113897603888</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.668824810785113</v>
+        <v>0.6652753068779969</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9563990051.388908</v>
+        <v>9727006093.451742</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1601.26</v>
+        <v>1602.22</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3759129386052782</v>
+        <v>0.3767378367611436</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1993539870797416</v>
+        <v>-0.1988739774795496</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>861.1799999999999</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>617154412269</v>
+        <v>617524413540</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>50.66037735849056</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>32.86372856883447</v>
+        <v>32.88343129008279</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.23234304816361</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5415285959528378</v>
+        <v>0.5406049603396792</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.292183190798883</v>
+        <v>0.2914089551371388</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004858673794386921</v>
+        <v>0.004855762629351774</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.686563141305556</v>
+        <v>1.687391075987521</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4355645706920054</v>
+        <v>0.4356364583820855</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2030350696.98842</v>
+        <v>2056543960.434692</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>209.77</v>
+        <v>201.96</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07902710600527152</v>
+        <v>-0.1133160810832085</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1752702968350697</v>
+        <v>-0.2059760172989974</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,37 +3490,37 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>165795914900</v>
+        <v>159623125200</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>78.56554307116102</v>
+        <v>75.64044943820222</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>82.51638401685648</v>
+        <v>79.44419562398977</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.763880152135752</v>
+        <v>1.698208683440608</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>27.20286273139672</v>
+        <v>26.19006605917377</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.420488575357606</v>
+        <v>0.4048332587082143</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>29.41682228776978</v>
+        <v>28.52865110791367</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.175082875684877</v>
+        <v>2.109411406989734</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001266617456326724</v>
+        <v>-0.001315598850335001</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.04787947257708702</v>
+        <v>-0.04787947257708691</v>
       </c>
       <c r="V24" s="4" t="n">
         <v>0.1537975177777893</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.241099396291876</v>
+        <v>1.250796279330109</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3346224644609525</v>
+        <v>0.3467118317299859</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1027151426.951191</v>
+        <v>1102622816.760091</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>983.48</v>
+        <v>937.98</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.07561735362533817</v>
+        <v>0.02585468474549035</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1477569129715162</v>
+        <v>-0.187185330895415</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>290133484360</v>
+        <v>276710665860</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.98293723339427</v>
+        <v>14.28976234003656</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.57726940595705</v>
+        <v>12.94912673099564</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.460071770182386</v>
+        <v>2.346258306214335</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.404575027293021</v>
+        <v>2.293329080510339</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3511792878800152</v>
+        <v>0.3349322288665724</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.90859377440831</v>
+        <v>26.48102015927118</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.162650265480722</v>
+        <v>7.048836801512672</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.143089309707141</v>
+        <v>-0.150030357055352</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3649,7 +3649,7 @@
         <v>0.1035309667509787</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.382242684897962</v>
+        <v>-0.3822426848979621</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01830235490299752</v>
+        <v>0.01919017463058914</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.570169884634251</v>
+        <v>1.579849670566597</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3033121256680233</v>
+        <v>0.3167145219979272</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1800924642.303914</v>
+        <v>1880047207.127384</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>239.92</v>
+        <v>237.49</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1769468267581475</v>
+        <v>-0.1852830188679245</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.278349275100764</v>
+        <v>-0.285658425073693</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>226036789280</v>
+        <v>223747403660</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.95021834061135</v>
+        <v>20.74148471615721</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.5922540502554</v>
+        <v>18.40394470821588</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.27075131944947</v>
+        <v>3.238163793797126</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.544270637408569</v>
+        <v>6.479068007662836</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2553815375241191</v>
+        <v>0.2528370908229242</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>17.51427802971457</v>
+        <v>17.37546413044818</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.111598244786316</v>
+        <v>4.079010719133971</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06031439843595642</v>
+        <v>0.06092137730774864</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1268250898456054</v>
+        <v>0.1270129879763118</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04593358405423964</v>
+        <v>0.04610799352298289</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02809269756585529</v>
+        <v>0.02838014232178197</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.8894001438085999</v>
+        <v>0.906225736184853</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3206742039625407</v>
+        <v>0.3287362947330283</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1167065793.15897</v>
+        <v>1191779268.202718</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1138.21008</v>
+        <v>1138.21</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05354705416048189</v>
+        <v>0.05354698011108994</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1194754341855878</v>
+        <v>-0.1194754960739567</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,31 +3868,31 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1071899101782</v>
+        <v>1071899023610</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.07996252927401</v>
+        <v>38.07995985279358</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.04015665444705</v>
+        <v>26.04015482419395</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.45494681258457</v>
+        <v>13.4549458313354</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>29.98136531160896</v>
+        <v>29.98136320434487</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4025521159323115</v>
+        <v>0.4025520876386162</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.81508520491955</v>
+        <v>25.81508339976169</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.03258489567669</v>
+        <v>14.03258391442752</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.0187087571644206</v>
+        <v>0.01870875852882241</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005877649581173978</v>
+        <v>0.005877649994289279</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3442964643056499</v>
+        <v>0.3439939232763189</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3238862262068379</v>
+        <v>0.3238698314038505</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2995338716.922424</v>
+        <v>3028410172.677368</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>207.94</v>
+        <v>202.51</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1431556183467189</v>
+        <v>0.1133040505501302</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1046716899892357</v>
+        <v>-0.1280516684607105</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,31 +3994,31 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>327979603200</v>
+        <v>319414972800</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.71543408360129</v>
+        <v>16.27893890675241</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.43884842379783</v>
+        <v>15.0356891137025</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.592129892751859</v>
+        <v>2.52444082226209</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.958545694956393</v>
+        <v>2.881288297997591</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4252673115856396</v>
+        <v>0.4141621778840429</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.59428913347191</v>
+        <v>23.30244906804784</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.472434012755969</v>
+        <v>5.4047449422662</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04782004687784194</v>
+        <v>-0.04910226925968324</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.01995768010002886</v>
+        <v>0.02049281516962126</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.378540990024976</v>
+        <v>1.382020009427655</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2616416850037697</v>
+        <v>0.2643246497965434</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>871917450.0828471</v>
+        <v>904693082.6014979</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>932.63</v>
+        <v>926.55</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.956787649156809</v>
+        <v>1.937511763857309</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2568685258964144</v>
+        <v>-0.2617131474103586</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1053302995700</v>
+        <v>1046436304500</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.81298817228297</v>
+        <v>20.67730417317563</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.975188836097437</v>
+        <v>5.936235394621748</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.66784451447814</v>
+        <v>11.59177952123535</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.44444859219253</v>
+        <v>10.37635915968389</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02966461088298364</v>
+        <v>0.02947122139929928</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.13891077312498</v>
+        <v>15.03844123284464</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.46159465294548</v>
+        <v>11.38552965970268</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02484755109103883</v>
+        <v>0.02501060015545361</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005682853864876746</v>
+        <v>0.0005720144622524419</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.882512446595185</v>
+        <v>2.885412599554037</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.812253483866804</v>
+        <v>0.8122571376334372</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25546161510.99267</v>
+        <v>25876878867.02397</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>141.13</v>
+        <v>139.82</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.04286196730448655</v>
+        <v>-0.05174633507059667</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2752380267658145</v>
+        <v>-0.2819654283454701</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>145908944060</v>
+        <v>144554584840</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>87.65838509316771</v>
+        <v>86.84472049689441</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>29.75974054946277</v>
+        <v>29.48350402909293</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.904218304371437</v>
+        <v>9.81228515069237</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.64807366570789</v>
+        <v>11.53995365931607</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>140.2534161490713</v>
+        <v>138.951552795034</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>43.52506278589853</v>
+        <v>43.1368830151906</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.30810100868857</v>
+        <v>10.2161678550095</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03138943969135048</v>
+        <v>0.03168353328308034</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7052059814271606</v>
+        <v>0.7092741804550352</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.627621340293255</v>
+        <v>0.6292117067564663</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2182064502.654715</v>
+        <v>2205532578.031082</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.525</v>
+        <v>27.46</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09312945458313604</v>
+        <v>0.09054804079392964</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05768572406710037</v>
+        <v>-0.05991098938719619</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>156877083826</v>
+        <v>156506622400</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.37024312896406</v>
+        <v>36.28435517970402</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.428375582281637</v>
+        <v>9.406110571823934</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.462903225100477</v>
+        <v>2.457087138909821</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.841354325625073</v>
+        <v>1.837005986618148</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6083164558738237</v>
+        <v>-0.6068799229171734</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.35544090621039</v>
+        <v>17.32609493029151</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.439699290379302</v>
+        <v>3.433883170057774</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.07002934768943885</v>
+        <v>0.07019511271492368</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4405,7 +4405,7 @@
         <v>2.857530155811058</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05042615492450431</v>
+        <v>-0.05042615492450442</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06248864668483197</v>
+        <v>0.06263656227239621</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3477023955980426</v>
+        <v>0.3486650696099421</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2079352472148128</v>
+        <v>0.2082359037915937</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>947913307.6000832</v>
+        <v>962789277.6907185</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>177.3</v>
+        <v>174.87</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.05529436222192174</v>
+        <v>0.04083093695289031</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1129234002101366</v>
+        <v>-0.1250813028468505</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1258572721743</v>
+        <v>1241323247892</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.685570928250936</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003681155772551435</v>
+        <v>0.003630703383790578</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.600574583261782</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2086.814643856816</v>
+        <v>2115.826993514116</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2700.663120205711</v>
+        <v>2738.205531036524</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.692047377326565</v>
+        <v>1.71556013038257</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9142111589146109</v>
+        <v>0.9138247017200472</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3153279962.258524</v>
+        <v>3192177153.981171</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>548.90002</v>
+        <v>545.5599999999999</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4703992444393506</v>
+        <v>0.4614519631395386</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1829778068856704</v>
+        <v>-0.1879493324204041</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>301.37</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>69183769654</v>
+        <v>68762790479</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.828020121201922</v>
+        <v>1.827995764366803</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4019387204207725</v>
+        <v>0.4010232887662645</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3731184256.008455</v>
+        <v>3790851939.296896</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>149.715</v>
+        <v>150.88</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.06980426940831252</v>
+        <v>-0.06256599651555428</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3364873249423861</v>
+        <v>-0.3313242332919695</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1957653194649</v>
+        <v>1972886577889</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-97.21753246753246</v>
+        <v>-97.97402597402596</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>134.5065473699756</v>
+        <v>135.5532035345952</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>118.1087900240724</v>
+        <v>119.0278478364404</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.900653650254669</v>
+        <v>6.954350751430548</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9721753246753246</v>
+        <v>-0.9797402597402596</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>456.7238536148308</v>
+        <v>460.4580220515959</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>114.8216167730317</v>
+        <v>115.7603968560483</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01452133966056344</v>
+        <v>-0.01440680894611426</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.505441085308753</v>
+        <v>3.389296132328293</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7779485665244231</v>
+        <v>0.7805915312933192</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14148452751.63368</v>
+        <v>14333385617.08179</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>759.4400000000001</v>
+        <v>754.05</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1116413469528477</v>
+        <v>0.1037516560489238</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02557193630753041</v>
+        <v>-0.03248777859039997</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>808984518353</v>
+        <v>803242884315</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9950631604548276</v>
+        <v>0.9950518300915309</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1124905490063523</v>
+        <v>0.1129920049986955</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>28774395592.97583</v>
+        <v>29850488196.7432</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>417.19</v>
+        <v>417.72</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3053096558954567</v>
+        <v>0.306967926989262</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1290396659707724</v>
+        <v>-0.1279331941544884</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2163747591200</v>
+        <v>2166496425600</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>27.58780572620842</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6358375411816852</v>
+        <v>0.6366453119739534</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>13.89916072363153</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.38813602439594</v>
+        <v>42.3330854831412</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.35480969223327</v>
+        <v>42.29980143517859</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2876387257604449</v>
+        <v>0.2872737719046251</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.183854143285995</v>
+        <v>2.178038787717862</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.355839799257699</v>
+        <v>0.3560357257084865</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4028153821.240675</v>
+        <v>4087324559.874907</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>27.98</v>
+        <v>28.07</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01858997631101111</v>
+        <v>-0.01543318924410586</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06733333333333336</v>
+        <v>-0.06433333333333335</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70149684922</v>
+        <v>70375327225</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.03149606299213</v>
+        <v>-22.10236220472441</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-82.73517814841837</v>
+        <v>-83.0013027386027</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.942397478111588</v>
+        <v>1.948645361345701</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.139526767769048</v>
+        <v>2.146408733784031</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1639553195385461</v>
+        <v>0.1644826954770189</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.33118759041322</v>
+        <v>16.36848383884297</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.735807418579538</v>
+        <v>2.742055301813651</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03107640472546612</v>
+        <v>0.03097676538014847</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2329513225575355</v>
+        <v>0.233659034991004</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1850855406196676</v>
+        <v>0.1849426260663523</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>494329747.1355879</v>
+        <v>507601729.8974198</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>316.96</v>
+        <v>312.43</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1496257595108804</v>
+        <v>-0.1617793287606775</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1820176004542053</v>
+        <v>-0.1937082247283801</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>214046257600</v>
+        <v>210987103300</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.22134627046695</v>
+        <v>18.94663432383263</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.30620866283276</v>
+        <v>16.07315993352108</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.545957175311931</v>
+        <v>2.509570293673355</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.268928821470245</v>
+        <v>6.179333138856476</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.191891340788783</v>
+        <v>1.17485680086648</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.215833101439896</v>
+        <v>9.09210092622553</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.710171608007327</v>
+        <v>2.673784726368751</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.0703212481674335</v>
+        <v>0.07134085337243454</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.0111686017163049</v>
+        <v>0.01133053804052108</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.95573991499356</v>
+        <v>0.9688452790398139</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2244041645061526</v>
+        <v>0.2350337985736363</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>756062954.2150726</v>
+        <v>786557594.6112345</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>143</v>
+        <v>143.235</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2693270906220473</v>
+        <v>-0.2681263344423002</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5660091047040972</v>
+        <v>-0.5652959028831562</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>411907210000</v>
+        <v>412584120450</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.0679012345679</v>
+        <v>22.10416666666667</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>15.91930416119143</v>
+        <v>15.94546525544234</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.73870752469454</v>
+        <v>5.748138267829527</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.352033786617144</v>
+        <v>6.362472443539208</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4803013798111839</v>
+        <v>0.4810906862745101</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.0875608669141</v>
+        <v>14.10779746686108</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.403246108084763</v>
+        <v>7.413880775875281</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06973907166886713</v>
+        <v>-0.06961004696127296</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01398601398601399</v>
+        <v>0.01396306768597061</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.071867899284275</v>
+        <v>2.059635807325663</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5632901636292426</v>
+        <v>0.5634892069469046</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4085331214.393292</v>
+        <v>4150823064.088405</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:42 ET</t>
+          <t>2026-09-16 17:37 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN39"/>
+  <dimension ref="A1:AN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>332.41</v>
+        <v>333.25</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2265598613404538</v>
+        <v>0.2296593778517679</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.03529036190033941</v>
+        <v>-0.03285254084801348</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,40 +714,40 @@
         <v>236.65</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4882224007960</v>
+        <v>4894561387000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>37.94634703196348</v>
+        <v>38.04223744292238</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.73668116848796</v>
+        <v>34.79607211064622</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.45840502280307</v>
+        <v>10.48483341009333</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.42353898018974</v>
+        <v>45.53832425362724</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.159471714865549</v>
+        <v>1.162401699644849</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.24270864024311</v>
+        <v>29.3159335909215</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.5542936144106</v>
+        <v>10.58072200170086</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02799605257299776</v>
+        <v>0.0279254848785902</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09239989991868391</v>
+        <v>0.0932911428035279</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.118190305206118</v>
+        <v>0.1193167545241032</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003188833067597245</v>
+        <v>0.0031807951987997</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3070200193013617</v>
+        <v>0.3059345400831398</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2949067799982662</v>
+        <v>0.2899507877068625</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13207349211.33701</v>
+        <v>12766832784.5418</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>490.3</v>
+        <v>496.065</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.03670655361986341</v>
+        <v>0.04889626049650708</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.114534421729394</v>
+        <v>-0.1041230224662285</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3640747165000</v>
+        <v>3683555460750</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.23888888888889</v>
+        <v>27.55916666666667</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>23.87896674381447</v>
+        <v>24.14760878035563</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>10.97142639954918</v>
+        <v>11.10042960818349</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.233602479277193</v>
+        <v>8.330414060539752</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8651981180716664</v>
+        <v>0.8753712103634942</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.06398674338254</v>
+        <v>18.2702728942892</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.29650362073174</v>
+        <v>11.42550682936605</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01839924525492283</v>
+        <v>0.01818541914565362</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1407063455098934</v>
+        <v>0.1412793257229832</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2261231413426967</v>
+        <v>0.2267520769688407</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.00742402610646543</v>
+        <v>0.007337748077368893</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5568418062448269</v>
+        <v>0.5577324893737594</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4356886680199505</v>
+        <v>0.434154881478208</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>11219174471.19954</v>
+        <v>10740454964.50076</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>342.87</v>
+        <v>345.55</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.08795813625375049</v>
+        <v>0.09646202345636401</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1608869092777955</v>
+        <v>-0.154328087907785</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4149450896631</v>
+        <v>4181884554877</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.85004965243297</v>
+        <v>16.97715988083416</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.52357324488055</v>
+        <v>20.72668875166784</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.236945306686314</v>
+        <v>9.306625233563446</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.438239070696978</v>
+        <v>6.486806645016238</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.149848471580736</v>
+        <v>0.1509788702348104</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.87618994433856</v>
+        <v>12.97200048845385</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.364438768847592</v>
+        <v>9.434118695724724</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01293523806617031</v>
+        <v>0.01283839023787929</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1789904491102158</v>
+        <v>-0.1809034195359334</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2906786180835044</v>
+        <v>0.2907051226099779</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002508239274360545</v>
+        <v>0.002488785993343944</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7646756005936947</v>
+        <v>0.762699498306213</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3639582618317491</v>
+        <v>0.3625398837283717</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8244449990.676066</v>
+        <v>7721348481.462392</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>245.96</v>
+        <v>250.51</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.08591611479028693</v>
+        <v>0.1060044150110375</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1435933147632311</v>
+        <v>-0.1277506963788301</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2645816316000</v>
+        <v>2694761121000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.52063492063492</v>
+        <v>19.89444444444444</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>21.84955903685363</v>
+        <v>22.29743425320788</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.410963691212872</v>
+        <v>3.476281787592822</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.795956926869946</v>
+        <v>4.887796889162829</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2209696237208928</v>
+        <v>0.2252010716300056</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>10.98767038980775</v>
+        <v>11.18714495446797</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.597920941625413</v>
+        <v>3.663239038005363</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004393729046759722</v>
+        <v>-0.004311172443216265</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1065890671885193</v>
+        <v>-0.1077697900787722</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1790016137663994</v>
+        <v>0.1803222819468244</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8342653851018501</v>
+        <v>0.8371813960180776</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4606488180473121</v>
+        <v>0.4622122391380389</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8552608470.084135</v>
+        <v>8206834687.93328</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>213.9</v>
+        <v>219.3</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1326449197081496</v>
+        <v>0.1612390411033062</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.09571319861334227</v>
+        <v>-0.07288407880273939</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5180871900000</v>
+        <v>5311665300000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>26.90566037735849</v>
+        <v>27.58490566037736</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>15.97635175393754</v>
+        <v>16.35811684068175</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.10033666810796</v>
+        <v>17.53204222214154</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>22.59651766062257</v>
+        <v>23.16697673199874</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2159774098318573</v>
+        <v>0.2214298549608523</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.2422888127121</v>
+        <v>22.80203152349283</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.15452373015061</v>
+        <v>17.58622928418419</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.0245144065422656</v>
+        <v>0.02391076862467219</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6840928887740156</v>
+        <v>0.6863130352373565</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9386961152552931</v>
+        <v>0.9412154432375359</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002431042543244507</v>
+        <v>0.002371181030551756</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.328855676123753</v>
+        <v>1.329916978183309</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.409323484252594</v>
+        <v>0.4133781954716744</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26912650248.31583</v>
+        <v>25936219477.06731</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>673.3099999999999</v>
+        <v>671.9299999999999</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.03520860349781252</v>
+        <v>0.03308686481455081</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.148571067273647</v>
+        <v>-0.1503161355589276</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1715248182447</v>
+        <v>1711732650980</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>25.02081010776663</v>
+        <v>24.96952805648458</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.35852328551795</v>
+        <v>20.32732684915943</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.514844302894221</v>
+        <v>7.499442058550349</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.554707814455958</v>
+        <v>6.541273442793649</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.129266072092154</v>
+        <v>-5.118753251579334</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.92416488388187</v>
+        <v>16.89133154307382</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.939189751704287</v>
+        <v>7.923787507360416</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.0238892542894539</v>
+        <v>0.0239383176902891</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2290090866052747</v>
+        <v>0.2283724388244934</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2723933984855695</v>
+        <v>0.273007539505155</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003118919962572961</v>
+        <v>0.003125325554745286</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7724072583281306</v>
+        <v>0.7681630389364189</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4080010568011128</v>
+        <v>0.4080591679147746</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10138078593.51151</v>
+        <v>9923380411.759483</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>358.08</v>
+        <v>371.9586</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1825964023714082</v>
+        <v>-0.1509151647428107</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2821602549966923</v>
+        <v>-0.2543379508048834</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1414253930844</v>
+        <v>1469068119306</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>303.4576271186441</v>
+        <v>315.2191525423729</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>170.3195592399943</v>
+        <v>176.787074434236</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.64859659757381</v>
+        <v>14.1775940638879</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.3448267286836</v>
+        <v>13.86205056759308</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.077956552876579</v>
+        <v>-8.391045046550486</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>117.0915306654473</v>
+        <v>121.6464476616229</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.59187920018529</v>
+        <v>14.12060985411942</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004074232974951922</v>
+        <v>0.003922288124775936</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7816957046668216</v>
+        <v>0.7830441142326445</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1224683805249132</v>
+        <v>0.1228443872713618</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.535109374454157</v>
+        <v>1.542491792865234</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5719937960643585</v>
+        <v>0.5752781187290299</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12789598512.76878</v>
+        <v>12645955770.24886</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>339.51</v>
+        <v>349.15</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02333005934958809</v>
+        <v>0.004401371912730934</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3141212121212121</v>
+        <v>-0.2946464646464647</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1615245985800</v>
+        <v>1661109057000</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>42.1228287841191</v>
+        <v>43.31885856079404</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.56124500582337</v>
+        <v>19.08416468427096</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.12764843104686</v>
+        <v>18.64236237430418</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.23136382786639</v>
+        <v>16.69223492827766</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4191429992875215</v>
+        <v>0.431044087659386</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>31.58429454489792</v>
+        <v>32.46183833687312</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.52543079771952</v>
+        <v>19.04014474097684</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02439442682192116</v>
+        <v>0.02372089889821123</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.269396733403582</v>
+        <v>1.269884968897651</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8547782329035543</v>
+        <v>0.855594416107851</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007481370210008542</v>
+        <v>0.00727481025347272</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.605185479351388</v>
+        <v>1.606646864702752</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3888614920512946</v>
+        <v>0.3924352387694716</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8628716383.128927</v>
+        <v>8452103139.321651</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>893.74</v>
+        <v>890.34</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04592159157401987</v>
+        <v>0.04194265652428331</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1849156406748745</v>
+        <v>-0.188016415868673</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,40 +1724,40 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>396354921460</v>
+        <v>394847092860</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>44.88900050226017</v>
+        <v>44.7182320441989</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.42763013359002</v>
+        <v>39.27749941106249</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.350042479605705</v>
+        <v>1.344906596204873</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.8401546456176</v>
+        <v>11.79511187501865</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.541020709263116</v>
+        <v>3.527549822415158</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.65106575397374</v>
+        <v>26.54686198064962</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.31354903813861</v>
+        <v>1.308413154737778</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02221746097553805</v>
+        <v>0.02230230425711232</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.13851632345555</v>
+        <v>0.1385203415369163</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1137619578080773</v>
+        <v>0.1141243314792548</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006198670754358091</v>
+        <v>0.006222342026641507</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1859168656137269</v>
+        <v>-0.1866324341762206</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1771192357234746</v>
+        <v>0.176938987211484</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1715705441.000846</v>
+        <v>1673972933.153744</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>76.41</v>
+        <v>75.88</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1602373690083909</v>
+        <v>-0.1660621850589805</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3880345987506006</v>
+        <v>-0.3922793528752203</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>318166655324</v>
+        <v>315959767124</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>23.65634674922601</v>
+        <v>23.49226006191951</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.37305571203624</v>
+        <v>20.22856225925758</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.577664461202226</v>
+        <v>6.532040038151972</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.61634684863239</v>
+        <v>10.54270905476019</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.695265800800423</v>
+        <v>0.6904432530393417</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.56889001229465</v>
+        <v>10.49676250112838</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.685375681144917</v>
+        <v>6.639751258094662</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03455612904753898</v>
+        <v>0.03479749368116578</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1611584969676407</v>
+        <v>0.1613410662029773</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1437551576299556</v>
+        <v>0.1440833291150601</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.0988661944525397</v>
+        <v>0.09619721903937392</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3345329005052507</v>
+        <v>0.3307769568007074</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2157532253.854227</v>
+        <v>2098409556.235269</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>520.67</v>
+        <v>511.2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.04794202194599873</v>
+        <v>0.02888194368562536</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.03174396548517877</v>
+        <v>-0.04935470673559716</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1123008961309</v>
+        <v>1102583557764</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>13.07989678192819</v>
+        <v>12.87376236710941</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.47157446411095</v>
+        <v>23.04464410713981</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.917233679448487</v>
+        <v>2.871259137948514</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.49365653599084</v>
+        <v>1.470117052375639</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3603178470284479</v>
+        <v>0.3546393688428563</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.82694503549677</v>
+        <v>15.59580029798468</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.147969316472873</v>
+        <v>3.1019947749729</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02157772949766241</v>
+        <v>0.02192323165285077</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4427345808468063</v>
+        <v>-0.4413555571847257</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.05995338976402564</v>
+        <v>0.06262062115746447</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.05282987392123903</v>
+        <v>0.04345626494962505</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1393146521303358</v>
+        <v>0.1458735753051842</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2110350198.758909</v>
+        <v>2062158632.583562</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>348.92</v>
+        <v>346.4</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07201667759147434</v>
+        <v>0.06427426664475133</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04796725784447475</v>
+        <v>-0.05484311050477497</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>934934629200</v>
+        <v>928182264000</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.00085984522786</v>
+        <v>14.89251934651763</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.9313507580556</v>
+        <v>13.83162337433422</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.141233093104595</v>
+        <v>3.118546209593694</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.597539773303648</v>
+        <v>2.578779598396147</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7854337607970518</v>
+        <v>0.7797611336125723</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>19.99779550450837</v>
+        <v>19.92531412623444</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.25936851491602</v>
+        <v>6.236681631405119</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1738453095261604</v>
+        <v>-0.175110004041189</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07676994899822165</v>
+        <v>0.07670075619265249</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2893751396518991</v>
+        <v>-0.2892987416862425</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.0171959188352631</v>
+        <v>0.01732101616628176</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7708858064475166</v>
+        <v>0.7629048937547521</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1714957115652187</v>
+        <v>0.171736261843984</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2116091765.374923</v>
+        <v>2067967030.863235</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>370.93</v>
+        <v>370.105</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.07056680973909524</v>
+        <v>0.06818571999700174</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03796975905801792</v>
+        <v>-0.04010944834919727</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>692543821976</v>
+        <v>691003508027</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.51486830926083</v>
+        <v>31.44477485131691</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.80559245608796</v>
+        <v>24.72162350065607</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.56698035371336</v>
+        <v>15.53235722053138</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.17614359628177</v>
+        <v>20.13126904187276</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.125180264275814</v>
+        <v>2.120453567276306</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.19557433418104</v>
+        <v>24.14263894518524</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.82545454900198</v>
+        <v>15.79083141582</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03034176225851626</v>
+        <v>0.03040939699423197</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2704743240884069</v>
+        <v>0.2719542812583653</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1381361933238576</v>
+        <v>0.1384422594852113</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007225082899738495</v>
+        <v>0.007241188311425137</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3080010447724384</v>
+        <v>0.305358848336019</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1773232932326329</v>
+        <v>0.1770610234061577</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2269386064.094275</v>
+        <v>2201657438.223872</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>567.75</v>
+        <v>565.52</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.008204135949298141</v>
+        <v>0.00424412674953234</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05629799541238656</v>
+        <v>-0.06000465410059508</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,40 +2354,40 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>497937189000</v>
+        <v>495981398720</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.17792421746293</v>
+        <v>31.05546403075233</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.60034720521277</v>
+        <v>25.48993445147995</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.1931188609868</v>
+        <v>14.13737133996523</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.24532168953841</v>
+        <v>88.89478524327214</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.377952900682513</v>
+        <v>1.372540597787714</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.11852003074697</v>
+        <v>23.03008675709893</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.57370204942565</v>
+        <v>14.51795452840407</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.0330322786956971</v>
+        <v>0.0331625340031865</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2178711471192254</v>
+        <v>0.218342247598414</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1571890126686657</v>
+        <v>0.1575559517246576</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005935711140466755</v>
+        <v>0.005959117272598671</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2945476222545185</v>
+        <v>0.291689229362848</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1945693605476321</v>
+        <v>0.1943447227578078</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1516304142.725171</v>
+        <v>1475026974.375448</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>375.26</v>
+        <v>379.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1155172616188378</v>
+        <v>0.128121304653704</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.187080282483428</v>
+        <v>-0.1778952385078636</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>340790269045</v>
+        <v>344640801318</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.13092405633078</v>
+        <v>24.40357533277603</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.31191344656784</v>
+        <v>17.45369538426162</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7570946751820034</v>
+        <v>0.7656489613377498</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.45347683748616</v>
+        <v>3.492497094883541</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7311732994091873</v>
+        <v>-0.7394347042738011</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>14.96461083899391</v>
+        <v>15.11407061747467</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8564950692912475</v>
+        <v>0.865049355446994</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06930068768155311</v>
+        <v>0.06852641912879201</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3938912143252915</v>
+        <v>0.3981895979908796</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01040690486613927</v>
+        <v>0.01048486257114667</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02414326067260033</v>
+        <v>0.02387351778656127</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4338100090495249</v>
+        <v>0.435169589702524</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2278803417529079</v>
+        <v>0.2298487125057489</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1782957324.889425</v>
+        <v>1722683059.549052</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>163.345</v>
+        <v>162.11</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3317977820451516</v>
+        <v>0.3217284792760082</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.0740604274134119</v>
+        <v>-0.08106116433308763</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>676976818700</v>
+        <v>671858410600</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.02252252252252</v>
+        <v>20.86486486486487</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.78362536111271</v>
+        <v>14.675127491552</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.874970416828228</v>
+        <v>1.860909143078713</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.62848982803223</v>
+        <v>2.608777562340967</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.058455330330331</v>
+        <v>2.04301801801802</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.867829010790116</v>
+        <v>9.797143824573617</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.962989028693292</v>
+        <v>1.948927754943777</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04513153058722304</v>
+        <v>0.04547255035634067</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.422014019498951</v>
+        <v>0.4217842316447407</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08199294297389192</v>
+        <v>0.08189823918495898</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02522268817533442</v>
+        <v>0.025414841774104</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5384489964726794</v>
+        <v>-0.538773887662406</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2553168456323008</v>
+        <v>0.256266719295899</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2241902169.930573</v>
+        <v>2190166836.893951</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>267.28</v>
+        <v>268.1</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.289028175222553</v>
+        <v>0.2929828411297759</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.0490625111182269</v>
+        <v>-0.04614508841213927</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>644117648628</v>
+        <v>646093765330</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.89942196531792</v>
+        <v>31.00520231213873</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.57068663500358</v>
+        <v>21.63110372538485</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.577394322703183</v>
+        <v>6.599911218117207</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.675441362347152</v>
+        <v>7.701717285897541</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.825836324916343</v>
+        <v>-3.838933602068762</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.94342608288865</v>
+        <v>20.00879597056208</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.869585604141776</v>
+        <v>6.892102499555801</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02904438349088694</v>
+        <v>0.02894529286317761</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4324728038641219</v>
+        <v>0.433362009898415</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.08958244178047914</v>
+        <v>0.09018004880011765</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01975456450164622</v>
+        <v>0.01969414397612831</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1723926613704065</v>
+        <v>-0.1714348386445364</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2079413320510723</v>
+        <v>0.2029502185939068</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1640539099.46374</v>
+        <v>1590417696.347237</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>107.5</v>
+        <v>106.97</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04664776548935878</v>
+        <v>-0.05134801371531816</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2046463450725067</v>
+        <v>-0.2085676235572654</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>855493600000</v>
+        <v>851275817600</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.8086642599278</v>
+        <v>38.6173285198556</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.6558120762303</v>
+        <v>34.47464110138019</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.162608175690367</v>
+        <v>1.15687624701022</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.703912946110465</v>
+        <v>8.66100063112034</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.384640630128002</v>
+        <v>9.338372169346906</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.42252620275917</v>
+        <v>21.32406960013072</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.247172754946728</v>
+        <v>1.24144082626658</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.0157908837658166</v>
+        <v>0.01586912222889861</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1198313337619308</v>
+        <v>0.1201662232332723</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05107088152361516</v>
+        <v>0.05119521528000814</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009093023255813954</v>
+        <v>0.009138076096101712</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05510360733280622</v>
+        <v>-0.05802065046066822</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.307080509567927</v>
+        <v>0.3044032628724372</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2709248419.584712</v>
+        <v>2637779378.25264</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>147.04</v>
+        <v>147.09</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03702663772098957</v>
+        <v>0.03737927191499169</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1208370702541106</v>
+        <v>-0.1205381165919283</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,40 +2984,40 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>349544802096</v>
+        <v>349663662543</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.7837037037037</v>
+        <v>21.79111111111111</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.81313325554507</v>
+        <v>20.81684209135355</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.016279093850538</v>
+        <v>4.017644803555014</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.558605070795971</v>
+        <v>6.560835281987075</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.78787724867747</v>
+        <v>20.79494603174625</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.62627280022584</v>
+        <v>17.63186518034252</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.30449492251126</v>
+        <v>4.305860632215737</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04552492242648085</v>
+        <v>0.04550944723357719</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04663259665144581</v>
+        <v>0.04680196042617957</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02543466982807141</v>
+        <v>0.02551447528784867</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02917981501632209</v>
+        <v>0.02916989598205181</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04729346856656391</v>
+        <v>-0.04587182024652679</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1484728506341582</v>
+        <v>0.1479062117411055</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1293885600.720227</v>
+        <v>1250660853.280223</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -3095,52 +3095,52 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>302.47</v>
+        <v>306.755</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1253542490489179</v>
+        <v>-0.1129634101464636</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2912243702401874</v>
+        <v>-0.2720401528275469</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>426.75</v>
+        <v>421.39</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>301597978990</v>
+        <v>305870630204</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.12220670391061</v>
+        <v>21.42143854748603</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.15629508544118</v>
+        <v>20.4418431544765</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.78274683755379</v>
+        <v>1.808002495649501</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.09322862129145</v>
+        <v>18.34954985857856</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.245408113550766</v>
+        <v>-7.348051594777218</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.14028764332009</v>
+        <v>15.31790543027389</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.140256176939991</v>
+        <v>2.165364521947557</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.05006996416411895</v>
+        <v>0.04937456889857118</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.04792108938547468</v>
+        <v>0.0479210893854749</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03071378979733527</v>
+        <v>0.03028475493471989</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7117966030708344</v>
+        <v>0.7165636912018102</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2406043143442007</v>
+        <v>0.2411228897150816</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1228364276.919541</v>
+        <v>1199237626.261287</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>512.5</v>
+        <v>534.59003</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.293372699693349</v>
+        <v>1.39222279088829</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.123527097976844</v>
+        <v>-0.0857489268551298</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,40 +3236,40 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>835682500000</v>
+        <v>871702497791</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>130.0761421319797</v>
+        <v>135.6827487309644</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>37.76064948773325</v>
+        <v>39.32269655737718</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>20.23199370536255</v>
+        <v>21.1040430405762</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.43436124003332</v>
+        <v>12.97031326505415</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.050156009872863</v>
+        <v>1.095420356727052</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>77.89442993095727</v>
+        <v>81.25513134829259</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>20.21238348868176</v>
+        <v>21.08443282389541</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.01005525423830223</v>
+        <v>0.00963975670747098</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.444753834921077</v>
+        <v>2.450494513594325</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.8988302387766913</v>
+        <v>0.9013639506361797</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.540113897603888</v>
+        <v>2.539787156299862</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6652753068779969</v>
+        <v>0.6720455582023733</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9727006093.451742</v>
+        <v>9056204706.384535</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -3347,55 +3347,55 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1602.22</v>
+        <v>1628.76</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3767378367611436</v>
+        <v>0.3995428336951732</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1988739774795496</v>
+        <v>-0.1856037120742415</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>861.1799999999999</v>
+        <v>916.03</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>617524413540</v>
+        <v>627753407021</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>50.66037735849056</v>
+        <v>51.5166908563135</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>32.88343129008279</v>
+        <v>33.40077303828817</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.23234304816361</v>
+        <v>15.48981568528766</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>24.65455295206502</v>
+        <v>25.07128941508517</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.448637019616227</v>
+        <v>3.506929408717318</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>38.64197175080589</v>
+        <v>39.30087751255025</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>15.09965604795131</v>
+        <v>15.35712868507537</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01858672575990359</v>
+        <v>0.01827777609942123</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5406049603396792</v>
+        <v>0.5423801957295591</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2914089551371388</v>
+        <v>0.2926613335233557</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004855762629351774</v>
+        <v>0.004776639897836391</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.687391075987521</v>
+        <v>1.683761660048894</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4356364583820855</v>
+        <v>0.4380186529883067</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2056543960.434692</v>
+        <v>2011817038.896167</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>201.96</v>
+        <v>200.47</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1133160810832085</v>
+        <v>-0.1198577677498059</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2059760172989974</v>
+        <v>-0.2118340868881462</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>159623125200</v>
+        <v>158445473900</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>75.64044943820222</v>
+        <v>75.11235955056178</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>79.44419562398977</v>
+        <v>78.43648954995538</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.698208683440608</v>
+        <v>1.686352502792702</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>26.19006605917377</v>
+        <v>26.00721800439344</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4048332587082143</v>
+        <v>0.4020068827190155</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>28.52865110791367</v>
+        <v>28.37569461151079</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.109411406989734</v>
+        <v>2.098101787861056</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001315598850335001</v>
+        <v>-0.001324419130242788</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.04787947257708691</v>
+        <v>-0.04237989255340768</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1537975177777893</v>
+        <v>0.1546827263367114</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.250796279330109</v>
+        <v>1.240887169138777</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3467118317299859</v>
+        <v>0.3433122505972865</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1102622816.760091</v>
+        <v>1068844576.232046</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>937.98</v>
+        <v>937.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.02585468474549035</v>
+        <v>0.02532971593093358</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.187185330895415</v>
+        <v>-0.1876012790405462</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>276710665860</v>
+        <v>276569062500</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.28976234003656</v>
+        <v>14.28244972577697</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>12.94912673099564</v>
+        <v>12.94098381920838</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.346258306214335</v>
+        <v>2.345057636704342</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.293329080510339</v>
+        <v>2.292155496895928</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3349322288665724</v>
+        <v>0.3347608313209361</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.48102015927118</v>
+        <v>26.47650949256204</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.048836801512672</v>
+        <v>7.047636132002679</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.150030357055352</v>
+        <v>-0.1501071725981643</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1035309667509787</v>
+        <v>0.1036602723030562</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3822426848979621</v>
+        <v>-0.3821998793565314</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01919017463058914</v>
+        <v>0.0192</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.579849670566597</v>
+        <v>1.571253186595629</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3167145219979272</v>
+        <v>0.3163314308983209</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1880047207.127384</v>
+        <v>1849787123.847054</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>237.49</v>
+        <v>239.24</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1852830188679245</v>
+        <v>-0.1792795883361921</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.285658425073693</v>
+        <v>-0.2803946339409251</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>223747403660</v>
+        <v>225396138160</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.74148471615721</v>
+        <v>20.89432314410481</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.40394470821588</v>
+        <v>18.5381623043999</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.238163793797126</v>
+        <v>3.262024952747587</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.479068007662836</v>
+        <v>6.526810518982934</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2528370908229242</v>
+        <v>0.2547001794116652</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>17.37546413044818</v>
+        <v>17.47710610689846</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.079010719133971</v>
+        <v>4.102871878084432</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06092137730774864</v>
+        <v>0.0604757477713477</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1270129879763118</v>
+        <v>0.1270978644493628</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04610799352298289</v>
+        <v>0.04621551567034698</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02838014232178197</v>
+        <v>0.02817254639692359</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.906225736184853</v>
+        <v>0.9065330631436457</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3287362947330283</v>
+        <v>0.3289476276953931</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1191779268.202718</v>
+        <v>1154475069.088229</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1138.21</v>
+        <v>1142</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05354698011108994</v>
+        <v>0.05705507005461619</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1194754960739567</v>
+        <v>-0.1165435345994663</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,40 +3868,40 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1071899023610</v>
+        <v>1075468222000</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.07995985279358</v>
+        <v>38.2067581130813</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.04015482419395</v>
+        <v>26.11002880644067</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.4549458313354</v>
+        <v>13.49974797215367</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>29.98136320434487</v>
+        <v>30.08119484046164</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4025520876386162</v>
+        <v>0.4038925014569365</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.81508339976169</v>
+        <v>25.89750378710905</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.03258391442752</v>
+        <v>14.07738605524579</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01870875852882241</v>
+        <v>0.01864666904123551</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4623553550232131</v>
+        <v>0.4632981984170268</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2290918506683588</v>
+        <v>0.2295582709788979</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877328985191485</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005877649994289279</v>
+        <v>0.005858143607705779</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3439939232763189</v>
+        <v>0.3459308472144155</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3238698314038505</v>
+        <v>0.3169698287472685</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>3028410172.677368</v>
+        <v>2789503758.887024</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>202.51</v>
+        <v>201.36</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1133040505501302</v>
+        <v>0.1069818953077588</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1280516684607105</v>
+        <v>-0.1330032292787944</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,40 +3994,40 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>319414972800</v>
+        <v>317601100800</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.27893890675241</v>
+        <v>16.18649517684888</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.0356891137025</v>
+        <v>14.95626223681858</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.52444082226209</v>
+        <v>2.510105199598511</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.881288297997591</v>
+        <v>2.864926234184954</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4141621778840429</v>
+        <v>0.411810261906725</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.30244906804784</v>
+        <v>23.24064131938529</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.4047449422662</v>
+        <v>5.390409319602621</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04910226925968324</v>
+        <v>-0.0493827003763332</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08268658547328567</v>
+        <v>0.08225537373915337</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3271879519250608</v>
+        <v>-0.3271714729502154</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02049281516962126</v>
+        <v>0.0206098529996027</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.382020009427655</v>
+        <v>1.371311450104973</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2643246497965434</v>
+        <v>0.2597608951352844</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>904693082.6014979</v>
+        <v>878899504.3350958</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>926.55</v>
+        <v>976.29</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.937511763857309</v>
+        <v>2.095206259712106</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2617131474103586</v>
+        <v>-0.2220796812749004</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1046436304500</v>
+        <v>1102612163100</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>20.67730417317563</v>
+        <v>21.78732425797813</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>5.936235394621748</v>
+        <v>6.245951893330358</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>11.59177952123535</v>
+        <v>12.2140612258236</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.37635915968389</v>
+        <v>10.93339343155554</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.02947122139929928</v>
+        <v>0.03105332549773018</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.03844123284464</v>
+        <v>15.85830903564217</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.38552965970268</v>
+        <v>12.00624752808117</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02501060015545361</v>
+        <v>0.02373940017726055</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.483235215353715</v>
+        <v>2.488231198393215</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.772514181536212</v>
+        <v>1.775779220960631</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005720144622524419</v>
+        <v>0.0005428714828585769</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.885412599554037</v>
+        <v>2.886543086267324</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8122571376334372</v>
+        <v>0.820553352657822</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25876878867.02397</v>
+        <v>25126493470.53228</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>139.82</v>
+        <v>139.65</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.05174633507059667</v>
+        <v>-0.05289926829215286</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2819654283454701</v>
+        <v>-0.2828384499245092</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,40 +4246,40 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>144554584840</v>
+        <v>144378828300</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>86.84472049689441</v>
+        <v>86.73913043478262</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>29.48350402909293</v>
+        <v>29.43157220450732</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.81228515069237</v>
+        <v>9.800354894108064</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.53995365931607</v>
+        <v>11.52592281879195</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>138.951552795034</v>
+        <v>138.7826086956551</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>43.1368830151906</v>
+        <v>43.08650854112926</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.2161678550095</v>
+        <v>10.2042375984252</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03168353328308034</v>
+        <v>0.03172210256813671</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.945535931251596</v>
+        <v>1.947145664936612</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2461938219817823</v>
+        <v>0.2467566443070532</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7092741804550352</v>
+        <v>0.7036776976367544</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6292117067564663</v>
+        <v>0.6293165069886928</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2205532578.031082</v>
+        <v>2158145546.582966</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.46</v>
+        <v>27.67</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09054804079392964</v>
+        <v>0.09888799303598095</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05991098938719619</v>
+        <v>-0.05272167066073263</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>156506622400</v>
+        <v>157703504800</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.28435517970402</v>
+        <v>36.56183932346723</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.406110571823934</v>
+        <v>9.478736814759447</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.457087138909821</v>
+        <v>2.475877681487063</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.837005986618148</v>
+        <v>1.851054466486677</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6068799229171734</v>
+        <v>-0.611521029392505</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.32609493029151</v>
+        <v>17.42090500633714</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.433883170057774</v>
+        <v>3.452673712635016</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.07019511271492368</v>
+        <v>0.06966237062348407</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.857530155811058</v>
+        <v>2.857248074082654</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05042615492450442</v>
+        <v>-0.05053296346494318</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06263656227239621</v>
+        <v>0.06216118539934947</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3486650696099421</v>
+        <v>0.350326043615645</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2082359037915937</v>
+        <v>0.205500723789221</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>962789277.6907185</v>
+        <v>926092622.4251246</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>174.87</v>
+        <v>183.0973</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.04083093695289031</v>
+        <v>0.08980004753556603</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1250813028468505</v>
+        <v>-0.08391804673037484</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,40 +4498,40 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1241323247892</v>
+        <v>1299725139339</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>7.685570928250936</v>
+        <v>7.624400949288165</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003630703383790578</v>
+        <v>0.003799028885083867</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6.600574583261782</v>
+        <v>6.548040163611034</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>4.78317768603404</v>
+        <v>4.745108051239</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.01719934805631963</v>
+        <v>0.0170624572815678</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>7.763078014576559</v>
+        <v>7.701006660861996</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>6.57032227901252</v>
+        <v>6.517787859361772</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.07302685654173505</v>
+        <v>0.0736127453621272</v>
       </c>
       <c r="T32" s="4" t="n">
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2115.826993514116</v>
+        <v>2005.934187635125</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2738.205531036524</v>
+        <v>2597.278524310316</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.71556013038257</v>
+        <v>1.638473095998685</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9138247017200472</v>
+        <v>0.9179793845077476</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3192177153.981171</v>
+        <v>3129659147.48306</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -4611,22 +4611,22 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>545.5599999999999</v>
+        <v>560.53</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4614519631395386</v>
+        <v>0.5015537592539878</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1879493324204041</v>
+        <v>-0.1656669097837251</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>301.37</v>
+        <v>312.6</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>68762790479</v>
+        <v>70649620476</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.827995764366803</v>
+        <v>1.827084824638465</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4010232887662645</v>
+        <v>0.4064685706510061</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3790851939.296896</v>
+        <v>3707929935.446554</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>150.88</v>
+        <v>155.23</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.06256599651555428</v>
+        <v>-0.03553896897607034</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3313242332919695</v>
+        <v>-0.3120457365715299</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1972886577889</v>
+        <v>2029766592562</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-97.97402597402596</v>
+        <v>-100.7987012987013</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>135.5532035345952</v>
+        <v>124.8406962652859</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>119.0278478364404</v>
+        <v>122.4595229298341</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.954350751430548</v>
+        <v>7.154850657108721</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9797402597402596</v>
+        <v>-1.007987012987013</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>460.4580220515959</v>
+        <v>474.1081335641949</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>115.7603968560483</v>
+        <v>119.1920719494419</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01440680894611426</v>
+        <v>-0.01400308789402435</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.214836670179135</v>
+        <v>4.22540548358437</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.389296132328293</v>
+        <v>3.379435704680966</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7805915312933192</v>
+        <v>0.7765044942046671</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14333385617.08179</v>
+        <v>13747121358.51425</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>754.05</v>
+        <v>761.4299999999999</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1037516560489238</v>
+        <v>0.1145542383997509</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.03248777859039997</v>
+        <v>-0.02301859193964362</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>803242884315</v>
+        <v>811104342423</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9950518300915309</v>
+        <v>0.9951548821037018</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1129920049986955</v>
+        <v>0.1151848510987127</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29850488196.7432</v>
+        <v>28945458724.08904</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>417.72</v>
+        <v>425.89</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.306967926989262</v>
+        <v>0.3325303323409383</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1279331941544884</v>
+        <v>-0.1108768267223382</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,40 +4914,40 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2166496425600</v>
+        <v>2208869967200</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>27.58780572620842</v>
+        <v>28.10942390170396</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6366453119739534</v>
+        <v>0.6487089672437216</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>13.89916072363153</v>
+        <v>14.16195998101111</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>9.59388616712771</v>
+        <v>9.775283174489369</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.5182494035320432</v>
+        <v>0.5280482367921029</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>18.27477474575392</v>
+        <v>18.63278794946157</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>13.41458131216091</v>
+        <v>13.67738056954049</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.01812191372746905</v>
+        <v>0.01778563079232014</v>
       </c>
       <c r="T36" s="4" t="n">
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.3330854831412</v>
+        <v>42.3313324172736</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.29980143517859</v>
+        <v>42.30502496853178</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2872737719046251</v>
+        <v>0.2817628965225762</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.178038787717862</v>
+        <v>2.177289933983538</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3560357257084865</v>
+        <v>0.3582524327454802</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4087324559.874907</v>
+        <v>3941303051.731517</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.07</v>
+        <v>28.205</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01543318924410586</v>
+        <v>-0.01069800864374804</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06433333333333335</v>
+        <v>-0.0598333333333334</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,38 +5042,38 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70375327225</v>
+        <v>70713790680</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.10236220472441</v>
+        <v>-22.20866141732283</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-83.0013027386027</v>
+        <v>-84.17691565632209</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.948645361345701</v>
+        <v>1.958017186210716</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.146408733784031</v>
+        <v>2.156731682806505</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1644826954770189</v>
+        <v>0.1652737593847281</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.36848383884297</v>
+        <v>16.42442821157025</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.742055301813651</v>
+        <v>2.751427126678665</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03097676538014847</v>
+        <v>0.03082849864272048</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02065405918635133</v>
+        <v>0.02072773416995544</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.233659034991004</v>
+        <v>0.2308629111581491</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1849426260663523</v>
+        <v>0.1565242418943464</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>507601729.8974198</v>
+        <v>492363203.8141126</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>312.43</v>
+        <v>314.505</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1617793287606775</v>
+        <v>-0.1562122964884195</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1937082247283801</v>
+        <v>-0.1883532478257504</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,40 +5170,40 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>210987103300</v>
+        <v>212388371550</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>18.94663432383263</v>
+        <v>19.07246816252274</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.07315993352108</v>
+        <v>16.17416015942142</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.509570293673355</v>
+        <v>2.526237573894116</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.179333138856476</v>
+        <v>6.220373103850642</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.17485680086648</v>
+        <v>1.182659597850758</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.09210092622553</v>
+        <v>9.148777364099661</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.673784726368751</v>
+        <v>2.690452006589512</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07134085337243454</v>
+        <v>0.0708701700104918</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1787747028086761</v>
+        <v>0.1791937247148543</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.006124458394295207</v>
+        <v>0.006357550646380439</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01133053804052108</v>
+        <v>0.01125578289693328</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9688452790398139</v>
+        <v>0.9678293910321804</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2350337985736363</v>
+        <v>0.2356061711049984</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>786557594.6112345</v>
+        <v>768638995.0475057</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>143.235</v>
+        <v>150.05</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2681263344423002</v>
+        <v>-0.2333044052296377</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5652959028831562</v>
+        <v>-0.5446130500758726</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,40 +5296,40 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>412584120450</v>
+        <v>432214523500</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.10416666666667</v>
+        <v>23.15586419753086</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>15.94546525544234</v>
+        <v>16.68949480784257</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.748138267829527</v>
+        <v>6.021629818744167</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.362472443539208</v>
+        <v>6.665193494279039</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4810906862745101</v>
+        <v>0.5039805737109662</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.10779746686108</v>
+        <v>14.62822172587487</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.413880775875281</v>
+        <v>7.687372326789919</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06961004696127296</v>
+        <v>-0.0664484843485367</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3862352908844917</v>
+        <v>0.3874514755623204</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.42786578758453</v>
+        <v>0.4294717829481378</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01396306768597061</v>
+        <v>0.01332889036987671</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.059635807325663</v>
+        <v>2.079370502183088</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5634892069469046</v>
+        <v>0.5627040552432833</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4150823064.088405</v>
+        <v>4077758386.893623</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,259 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:37 ET</t>
+          <t>2026-09-17 10:19 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="3" t="n">
+        <v>111.0801</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.4608113974564338</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>-0.1479627214850042</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>130.37</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>437814956732</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>33.05955357142857</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>21.41135533812198</v>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>6.913777445432294</v>
+      </c>
+      <c r="O40" s="6" t="n">
+        <v>8.732219057372975</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v>1.057905714285714</v>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>22.98466240731305</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>7.266165917599685</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>0.03105193139466434</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>0.1177498499664631</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>0.5440196591650359</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>0.1662824832486469</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>0.1023396098336123</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>0.2739106646984134</v>
+      </c>
+      <c r="Y40" s="4" t="n">
+        <v>0.645242795104619</v>
+      </c>
+      <c r="Z40" s="4" t="n">
+        <v>0.2426845637583893</v>
+      </c>
+      <c r="AA40" s="5" t="n">
+        <v>12767000000</v>
+      </c>
+      <c r="AB40" s="6" t="n">
+        <v>0.9311258278145695</v>
+      </c>
+      <c r="AC40" s="6" t="n">
+        <v>0.794003612281758</v>
+      </c>
+      <c r="AD40" s="6" t="n">
+        <v>0.5873123197772696</v>
+      </c>
+      <c r="AE40" s="6" t="n">
+        <v>0.2278130472010306</v>
+      </c>
+      <c r="AF40" s="6" t="n">
+        <v>1.114691043508667</v>
+      </c>
+      <c r="AG40" s="6" t="n">
+        <v>11.89047619047619</v>
+      </c>
+      <c r="AH40" s="4" t="n">
+        <v>0.01494417091810324</v>
+      </c>
+      <c r="AI40" s="6" t="n">
+        <v>0.7135542224607341</v>
+      </c>
+      <c r="AJ40" s="4" t="n">
+        <v>0.3389550718206246</v>
+      </c>
+      <c r="AK40" s="5" t="n">
+        <v>1956947392.126263</v>
+      </c>
+      <c r="AL40" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-12 (C)</t>
+        </is>
+      </c>
+      <c r="AM40" s="2" t="inlineStr"/>
+      <c r="AN40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:19 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="3" t="n">
+        <v>86.405</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>-0.09238442468673402</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>-0.1161518003273323</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>97.76000000000001</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>72.78</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>261288720000</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>12.32596291012839</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>11.1088018035119</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>2.023846636458696</v>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>1.462303565819413</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>0.655163794322141</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>15.60631191331381</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>4.004900817164324</v>
+      </c>
+      <c r="S41" s="4" t="n">
+        <v>0.0733671166516488</v>
+      </c>
+      <c r="T41" s="4" t="n">
+        <v>-0.01489668811853551</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>0.1095672718034899</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>-0.2903031514796548</v>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>0.009923315255755299</v>
+      </c>
+      <c r="X41" s="4" t="n">
+        <v>0.1256670879245121</v>
+      </c>
+      <c r="Y41" s="4" t="n">
+        <v>0.6450486038495798</v>
+      </c>
+      <c r="Z41" s="4" t="n">
+        <v>0.2117113976995469</v>
+      </c>
+      <c r="AA41" s="5" t="n">
+        <v>-19001000000</v>
+      </c>
+      <c r="AB41" s="6" t="n">
+        <v>0.5121191082899736</v>
+      </c>
+      <c r="AC41" s="6" t="n">
+        <v>0.5121191082899736</v>
+      </c>
+      <c r="AD41" s="6" t="n">
+        <v>2.548082579499417</v>
+      </c>
+      <c r="AE41" s="6" t="n">
+        <v>0.2011825426419496</v>
+      </c>
+      <c r="AF41" s="6" t="n">
+        <v>7.719779058887447</v>
+      </c>
+      <c r="AG41" s="6" t="n">
+        <v>0.6326638212402712</v>
+      </c>
+      <c r="AH41" s="4" t="n">
+        <v>0.02141079798622765</v>
+      </c>
+      <c r="AI41" s="6" t="n">
+        <v>0.7265825765145346</v>
+      </c>
+      <c r="AJ41" s="4" t="n">
+        <v>0.2275485790211614</v>
+      </c>
+      <c r="AK41" s="5" t="n">
+        <v>1069516490.984844</v>
+      </c>
+      <c r="AL41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 (C)</t>
+        </is>
+      </c>
+      <c r="AM41" s="2" t="inlineStr"/>
+      <c r="AN41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:19 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -446,7 +446,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>333.25</v>
+        <v>334.85</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2296593778517679</v>
+        <v>0.2355632188257</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.03285254084801348</v>
+        <v>-0.02820907217691604</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,40 +714,40 @@
         <v>236.65</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4894561387000</v>
+        <v>4918061156600</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.04223744292238</v>
+        <v>38.21803652968037</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.79607211064622</v>
+        <v>34.96313502250529</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.48483341009333</v>
+        <v>10.5332854534588</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.53832425362724</v>
+        <v>45.74876392159599</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.162401699644849</v>
+        <v>1.167773338406899</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.3159335909215</v>
+        <v>29.45017933383189</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.58072200170086</v>
+        <v>10.62917404506633</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.0279254848785902</v>
+        <v>0.0277970304841548</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.0932911428035279</v>
+        <v>0.09309524174762762</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1193167545241032</v>
+        <v>0.1191161900765252</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.0031807951987997</v>
+        <v>0.003165596535762281</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3059345400831398</v>
+        <v>0.307494820016682</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2899507877068625</v>
+        <v>0.2903476905773502</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>12766832784.5418</v>
+        <v>12826960054.50263</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>496.065</v>
+        <v>497.128</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.04889626049650708</v>
+        <v>0.05114390289197512</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1041230224662285</v>
+        <v>-0.1022032796359171</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3683555460750</v>
+        <v>3691448820400</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.55916666666667</v>
+        <v>27.62000555555555</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.14760878035563</v>
+        <v>24.19935383016466</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.10042960818349</v>
+        <v>11.12493462358252</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.330414060539752</v>
+        <v>8.348804062732404</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8753712103634942</v>
+        <v>0.8773036567414266</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.2702728942892</v>
+        <v>18.3094583173348</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.42550682936605</v>
+        <v>11.45001184476508</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01818541914565362</v>
+        <v>0.01814536192363117</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1412793257229832</v>
+        <v>0.1413530191507437</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2267520769688407</v>
+        <v>0.2268312894486664</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007337748077368893</v>
+        <v>0.007322057900580937</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5577324893737594</v>
+        <v>0.5584235198202734</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.434154881478208</v>
+        <v>0.434382637982257</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10740454964.50076</v>
+        <v>10783516484.97605</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>345.55</v>
+        <v>346</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09646202345636401</v>
+        <v>0.09788991496426536</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.154328087907785</v>
+        <v>-0.1532267932747609</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4181884554877</v>
+        <v>4187330504956</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.97715988083416</v>
+        <v>16.99900695134061</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.72668875166784</v>
+        <v>20.75368053270749</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.306625233563446</v>
+        <v>9.318601470995771</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.486806645016238</v>
+        <v>6.495154196852361</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1509788702348104</v>
+        <v>0.1511731575034794</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.97200048845385</v>
+        <v>12.9884679257241</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.434118695724724</v>
+        <v>9.446094933157047</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01283839023787929</v>
+        <v>0.01282189037894485</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1809034195359334</v>
+        <v>-0.1809160344089119</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2907051226099779</v>
+        <v>0.2906852445130503</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002488785993343944</v>
+        <v>0.002485549132947977</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.762699498306213</v>
+        <v>0.7627311682851862</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3625398837283717</v>
+        <v>0.3627537718930654</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>7721348481.462392</v>
+        <v>7759580886.224748</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>250.51</v>
+        <v>252.19</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1060044150110375</v>
+        <v>0.1134216335540839</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1277506963788301</v>
+        <v>-0.1219011142061281</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2694761121000</v>
+        <v>2712833075262</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.89444444444444</v>
+        <v>20.01507936507936</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.29743425320788</v>
+        <v>22.44696796262223</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.476281787592822</v>
+        <v>3.497361122192141</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.887796889162829</v>
+        <v>4.917435263405967</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2252010716300056</v>
+        <v>0.2265666344371928</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.18714495446797</v>
+        <v>11.25151901503561</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.663239038005363</v>
+        <v>3.684318372604682</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004311172443216265</v>
+        <v>-0.004285188095798073</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1077697900787722</v>
+        <v>-0.1083392911502502</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1803222819468244</v>
+        <v>0.1795688947640286</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8371813960180776</v>
+        <v>0.8395391454367772</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4622122391380389</v>
+        <v>0.4639807636505544</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8206834687.93328</v>
+        <v>8254158323.248074</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>219.3</v>
+        <v>218.84</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1612390411033062</v>
+        <v>0.1588032455770521</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07288407880273939</v>
+        <v>-0.07482878160142048</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5311665300000</v>
+        <v>5300523640000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.58490566037736</v>
+        <v>27.52704402515723</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.35811684068175</v>
+        <v>16.32380432929682</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.53204222214154</v>
+        <v>17.49526730457572</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.16697673199874</v>
+        <v>23.11838207036299</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2214298549608523</v>
+        <v>0.2209653874128268</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.80203152349283</v>
+        <v>22.75434973701892</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.58622928418419</v>
+        <v>17.54945436661837</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02391076862467219</v>
+        <v>0.02396102887676207</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6863130352373565</v>
+        <v>0.6863130352373563</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9412154432375359</v>
+        <v>0.9412154432375355</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002371181030551756</v>
+        <v>0.002376165234874794</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.329916978183309</v>
+        <v>1.328543354293291</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4133781954716744</v>
+        <v>0.4127461270773111</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>25936219477.06731</v>
+        <v>26049198503.72923</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>671.9299999999999</v>
+        <v>677.98</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.03308686481455081</v>
+        <v>0.04238869020131442</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1503161355589276</v>
+        <v>-0.142665655032878</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,37 +1346,37 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1711732650980</v>
+        <v>1727144944729</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.96952805648458</v>
+        <v>25.19435154217763</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.32732684915943</v>
+        <v>20.51035235395519</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.499442058550349</v>
+        <v>7.56696639063212</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.541273442793649</v>
+        <v>6.600170506965367</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.118753251579334</v>
+        <v>-5.16484206614641</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.89133154307382</v>
+        <v>17.0352748125467</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.923787507360416</v>
+        <v>7.991311839442186</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.0239383176902891</v>
+        <v>0.02372470250690476</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2283724388244934</v>
+        <v>0.2283724388244937</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>0.273007539505155</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003125325554745286</v>
+        <v>0.003097436502551698</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7681630389364189</v>
+        <v>0.771080780010582</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4080591679147746</v>
+        <v>0.4082474516356293</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>9923380411.759483</v>
+        <v>9984177429.071184</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>371.9586</v>
+        <v>367.8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1509151647428107</v>
+        <v>-0.1604081679853773</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2543379508048834</v>
+        <v>-0.2626746587013611</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,37 +1472,37 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1469068119306</v>
+        <v>1452643531513</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>315.2191525423729</v>
+        <v>311.6949152542373</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>176.787074434236</v>
+        <v>174.8105460578462</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>14.1775940638879</v>
+        <v>14.01908464193825</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.86205056759308</v>
+        <v>13.70706900918741</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.391045046550486</v>
+        <v>-8.297230842683215</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>121.6464476616229</v>
+        <v>120.2832167869139</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>14.12060985411942</v>
+        <v>13.96236724454975</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.003922288124775936</v>
+        <v>0.003966561565175313</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7830441142326445</v>
+        <v>0.7830441142326448</v>
       </c>
       <c r="V8" s="4" t="n">
         <v>0.1228443872713618</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.542491792865234</v>
+        <v>1.537465780199867</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5752781187290299</v>
+        <v>0.5714665824470031</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12645955770.24886</v>
+        <v>12756436695.88413</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>349.15</v>
+        <v>349.4587</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.004401371912730934</v>
+        <v>0.00528941058811272</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2946464646464647</v>
+        <v>-0.2940228282828282</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,31 +1598,31 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1661109057000</v>
+        <v>1662577721946</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>43.31885856079404</v>
+        <v>43.357158808933</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.08416468427096</v>
+        <v>19.10103789532075</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.64236237430418</v>
+        <v>18.65884496707218</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.69223492827766</v>
+        <v>16.70699332129602</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.431044087659386</v>
+        <v>0.4314251940888876</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>32.46183833687312</v>
+        <v>32.48459621529572</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.04014474097684</v>
+        <v>19.05349313162148</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02372089889821123</v>
+        <v>0.02370392630312093</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.00727481025347272</v>
+        <v>0.007268383932064075</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.606646864702752</v>
+        <v>1.606171767953301</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3924352387694716</v>
+        <v>0.3926740344888102</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8452103139.321651</v>
+        <v>8494193148.809659</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>890.34</v>
+        <v>891.1246</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04194265652428331</v>
+        <v>0.0428608543007607</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.188016415868673</v>
+        <v>-0.1873008663930689</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>394847092860</v>
+        <v>395195046483</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>44.7182320441989</v>
+        <v>44.75763937719739</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.27749941106249</v>
+        <v>39.31211217252207</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.344906596204873</v>
+        <v>1.346091776825949</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.79511187501865</v>
+        <v>11.80550615672804</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.527549822415158</v>
+        <v>3.530658427656601</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.54686198064962</v>
+        <v>26.57090853372495</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.308413154737778</v>
+        <v>1.309598335358855</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02230230425711232</v>
+        <v>0.02228266795944975</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006222342026641507</v>
+        <v>0.006216863500345519</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1866324341762206</v>
+        <v>-0.1862075281853639</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.176938987211484</v>
+        <v>0.1768703234373457</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1673972933.153744</v>
+        <v>1683859407.316933</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>75.88</v>
+        <v>75.685</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1660621850589805</v>
+        <v>-0.1682052777568389</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3922793528752203</v>
+        <v>-0.3938411020342784</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,31 +1850,31 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>315959767124</v>
+        <v>315147798824</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>23.49226006191951</v>
+        <v>23.43188854489164</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.22856225925758</v>
+        <v>20.17657794665142</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.532040038151972</v>
+        <v>6.515253693822161</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.54270905476019</v>
+        <v>10.51561590418457</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6904432530393417</v>
+        <v>0.6886689194291326</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.49676250112838</v>
+        <v>10.47022502060493</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.639751258094662</v>
+        <v>6.622964913764852</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03479749368116578</v>
+        <v>0.0348871483190658</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09619721903937392</v>
+        <v>0.09491353985868153</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3307769568007074</v>
+        <v>0.3312770426821339</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2098409556.235269</v>
+        <v>2112133090.089381</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>511.2</v>
+        <v>511.32</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02888194368562536</v>
+        <v>0.02912346526865028</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04935470673559716</v>
+        <v>-0.04913155056346941</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1102583557764</v>
+        <v>1102842380195</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.87376236710941</v>
+        <v>12.86035219797701</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.04464410713981</v>
+        <v>23.05005364801003</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.871259137948514</v>
+        <v>2.868268243013151</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.470117052375639</v>
+        <v>1.468585680446082</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3546393688428563</v>
+        <v>0.354269952833645</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.59580029798468</v>
+        <v>15.58076307081057</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.1019947749729</v>
+        <v>3.099003880037537</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02192323165285077</v>
+        <v>0.02194609216552319</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4413555571847257</v>
+        <v>-0.4420684483271354</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06262062115746447</v>
+        <v>0.06126460153157787</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.04345626494962505</v>
+        <v>0.04187500431885754</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1458735753051842</v>
+        <v>0.1460164319856381</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2062158632.583562</v>
+        <v>2076683763.379158</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>346.4</v>
+        <v>349.4</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06427426664475133</v>
+        <v>0.07349142253370711</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.05484311050477497</v>
+        <v>-0.04665757162346529</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,31 +2102,31 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>928182264000</v>
+        <v>936220794000</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>14.89251934651763</v>
+        <v>15.02149613069647</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.83162337433422</v>
+        <v>13.95141226037061</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.118546209593694</v>
+        <v>3.145554404249529</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.578779598396147</v>
+        <v>2.601113139952696</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7797611336125723</v>
+        <v>0.7865142612131431</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>19.92531412623444</v>
+        <v>20.01160148132246</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.236681631405119</v>
+        <v>6.263689826060954</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.175110004041189</v>
+        <v>-0.1736064836859413</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01732101616628176</v>
+        <v>0.01717229536348025</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7629048937547521</v>
+        <v>0.7665085670680261</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.171736261843984</v>
+        <v>0.1705758341018808</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2067967030.863235</v>
+        <v>2079387966.277783</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>370.105</v>
+        <v>370.69</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06818571999700174</v>
+        <v>0.06987412908684987</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04010944834919727</v>
+        <v>-0.03859221412454283</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,37 +2228,37 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>691003508027</v>
+        <v>692095730646</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.44477485131691</v>
+        <v>31.49447748513169</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.72162350065607</v>
+        <v>24.76069930278759</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.53235722053138</v>
+        <v>15.55690816952886</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.13126904187276</v>
+        <v>20.16308918045369</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.120453567276306</v>
+        <v>2.123805225148684</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.14263894518524</v>
+        <v>24.1801749483126</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.79083141582</v>
+        <v>15.81538236481748</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03040939699423197</v>
+        <v>0.03036140676722067</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2719542812583653</v>
+        <v>0.2719542812583655</v>
       </c>
       <c r="V14" s="4" t="n">
         <v>0.1384422594852113</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007241188311425137</v>
+        <v>0.007229760716501659</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.305358848336019</v>
+        <v>0.3055629535006044</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1770610234061577</v>
+        <v>0.1769515447465601</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2201657438.223872</v>
+        <v>2208292425.517131</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>565.52</v>
+        <v>566.16</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.00424412674953234</v>
+        <v>0.00538063163197644</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.06000465410059508</v>
+        <v>-0.05894085967886709</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>495981398720</v>
+        <v>496542701760</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.05546403075233</v>
+        <v>31.09060955518945</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.48993445147995</v>
+        <v>25.51878145609331</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.13737133996523</v>
+        <v>14.15337062850953</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>88.89478524327214</v>
+        <v>88.99538763143825</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.372540597787714</v>
+        <v>1.374093904448105</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.03008675709893</v>
+        <v>23.05546671007415</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.51795452840407</v>
+        <v>14.53395381694838</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.0331625340031865</v>
+        <v>0.03312504632874457</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005959117272598671</v>
+        <v>0.005952380952380953</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.291689229362848</v>
+        <v>0.2915658027266966</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1943447227578078</v>
+        <v>0.1942000149140474</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1475026974.375448</v>
+        <v>1480148746.370378</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>379.5</v>
+        <v>377.79001</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.128121304653704</v>
+        <v>0.1230381000430458</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1778952385078636</v>
+        <v>-0.1815995624106408</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>344640801318</v>
+        <v>343087882147</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.40357533277603</v>
+        <v>24.29361520159475</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.45369538426162</v>
+        <v>17.37505073453795</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7656489613377498</v>
+        <v>0.7621990188301575</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.492497094883541</v>
+        <v>3.476760243480959</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7394347042738011</v>
+        <v>-0.7361028835887914</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.11407061747467</v>
+        <v>15.05379350801537</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.865049355446994</v>
+        <v>0.8615994129394018</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06852641912879201</v>
+        <v>0.06883659035757206</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3981895979908796</v>
+        <v>0.3981895979908794</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01048486257114667</v>
+        <v>0.01048486257114645</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02387351778656127</v>
+        <v>0.02398157643183842</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.435169589702524</v>
+        <v>0.4322113181598834</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2298487125057489</v>
+        <v>0.2282658354730472</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1722683059.549052</v>
+        <v>1730321835.751022</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>162.11</v>
+        <v>161.89</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3217284792760082</v>
+        <v>0.3199347573252294</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.08106116433308763</v>
+        <v>-0.08230825916898143</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>671858410600</v>
+        <v>670946629400</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>20.86486486486487</v>
+        <v>20.83141698841699</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.675127491552</v>
+        <v>14.65521182905035</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.860909143078713</v>
+        <v>1.857925942519249</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.608777562340967</v>
+        <v>2.604595504601781</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.04301801801802</v>
+        <v>2.039742913449165</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.797143824573617</v>
+        <v>9.782147452920293</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.948927754943777</v>
+        <v>1.945944554384313</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04547255035634067</v>
+        <v>0.0455455638896354</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4217842316447407</v>
+        <v>0.4214340421285367</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08189823918495898</v>
+        <v>0.0816317473314494</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.025414841774104</v>
+        <v>0.02544937920810427</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.538773887662406</v>
+        <v>-0.5394711249643455</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.256266719295899</v>
+        <v>0.2565903978909659</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2190166836.893951</v>
+        <v>2198663462.421881</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>268.1</v>
+        <v>269.23001</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2929828411297759</v>
+        <v>0.2984326118880938</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.04614508841213927</v>
+        <v>-0.04212470203152241</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>646093765330</v>
+        <v>648816977016</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.00520231213873</v>
+        <v>31.12485664739884</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.63110372538485</v>
+        <v>21.72227628607386</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.599911218117207</v>
+        <v>6.625381419354839</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.701717285897541</v>
+        <v>7.731439519377199</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.838933602068762</v>
+        <v>-3.853748698052942</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20.00879597056208</v>
+        <v>20.0827397431519</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.892102499555801</v>
+        <v>6.917572700793432</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02894529286317761</v>
+        <v>0.02883401739276415</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.433362009898415</v>
+        <v>0.4328542845831023</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.09018004880011765</v>
+        <v>0.08979388535784305</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01969414397612831</v>
+        <v>0.0196114838758131</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1714348386445364</v>
+        <v>-0.1685709656295322</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2029502185939068</v>
+        <v>0.2033595034833864</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1590417696.347237</v>
+        <v>1601239215.520638</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>106.97</v>
+        <v>106.335</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.05134801371531816</v>
+        <v>-0.05697944319359038</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2085676235572654</v>
+        <v>-0.2132657591003255</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>851275817600</v>
+        <v>846222436800</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.6173285198556</v>
+        <v>38.38628158844765</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.47464110138019</v>
+        <v>34.26999122665479</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.15687624701022</v>
+        <v>1.149954692558165</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.66100063112034</v>
+        <v>8.609181986603961</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.338372169346906</v>
+        <v>9.282500820479166</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.32406960013072</v>
+        <v>21.20517894843484</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.24144082626658</v>
+        <v>1.234519271814525</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01586912222889861</v>
+        <v>0.01596463816037352</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1201662232332723</v>
+        <v>0.1201135516659035</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05119521528000814</v>
+        <v>0.0511458049142941</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009138076096101712</v>
+        <v>0.009192645883293367</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05802065046066822</v>
+        <v>-0.0620778118576816</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3044032628724372</v>
+        <v>0.3052081663229914</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2637779378.25264</v>
+        <v>2647891222.195293</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>147.09</v>
+        <v>146.835</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03737927191499169</v>
+        <v>0.0355808375255815</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1205381165919283</v>
+        <v>-0.1220627802690583</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,31 +2984,31 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>349663662543</v>
+        <v>349057474264</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.79111111111111</v>
+        <v>21.75333333333333</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.81684209135355</v>
+        <v>20.78075333798286</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.017644803555014</v>
+        <v>4.010679684070227</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.560835281987075</v>
+        <v>6.549461204912449</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.79494603174625</v>
+        <v>20.75889523809546</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.63186518034252</v>
+        <v>17.60334404178037</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.305860632215737</v>
+        <v>4.29889551273095</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04550944723357719</v>
+        <v>0.04558848090433566</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02916989598205181</v>
+        <v>0.02922055368270508</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04587182024652679</v>
+        <v>-0.04684502063108714</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1479062117411055</v>
+        <v>0.1479187006611635</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1250660853.280223</v>
+        <v>1254617399.714382</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>306.755</v>
+        <v>303.83511</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1129634101464636</v>
+        <v>-0.1214067909172658</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2720401528275469</v>
+        <v>-0.2789693395666722</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>421.39</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>305870630204</v>
+        <v>302959156893</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.42143854748603</v>
+        <v>21.21753561452514</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.4418431544765</v>
+        <v>20.24726463608781</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.808002495649501</v>
+        <v>1.790792765480919</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.34954985857856</v>
+        <v>18.17488712402961</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.348051594777218</v>
+        <v>-7.278108146842956</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.31790543027389</v>
+        <v>15.19720497148233</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.165364521947557</v>
+        <v>2.14830210486712</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04937456889857118</v>
+        <v>0.04984500272204486</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.0479210893854749</v>
+        <v>0.04792108938547468</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03028475493471989</v>
+        <v>0.03057579487768875</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7165636912018102</v>
+        <v>0.7106474672924792</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2411228897150816</v>
+        <v>0.2383717148741388</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1199237626.261287</v>
+        <v>1204978584.118602</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>534.59003</v>
+        <v>545.5364</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.39222279088829</v>
+        <v>1.441206412583397</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.0857489268551298</v>
+        <v>-0.06702854308826312</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,37 +3236,37 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>871702497791</v>
+        <v>889551653840</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>135.6827487309644</v>
+        <v>138.4610152284264</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>39.32269655737718</v>
+        <v>40.12787578212775</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>21.1040430405762</v>
+        <v>21.53617367969979</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12.97031326505415</v>
+        <v>13.23589593597525</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.095420356727052</v>
+        <v>1.117850398174451</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>81.25513134829259</v>
+        <v>82.92047526030976</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>21.08443282389541</v>
+        <v>21.516563463019</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.00963975670747098</v>
+        <v>0.009446331715225402</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.450494513594325</v>
+        <v>2.450494513594326</v>
       </c>
       <c r="V22" s="4" t="n">
         <v>0.9013639506361797</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.539787156299862</v>
+        <v>2.547286387430741</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6720455582023733</v>
+        <v>0.6813230878113947</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9056204706.384535</v>
+        <v>9175100067.032457</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1628.76</v>
+        <v>1624.4193</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3995428336951732</v>
+        <v>0.3958130051272928</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1856037120742415</v>
+        <v>-0.1877741054821096</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,40 +3362,40 @@
         <v>916.03</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>627753407021</v>
+        <v>626080423148</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>51.5166908563135</v>
+        <v>51.45137880986938</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>33.40077303828817</v>
+        <v>33.31175885846592</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.48981568528766</v>
+        <v>15.47017794177341</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>25.07128941508517</v>
+        <v>25.03950443061753</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.506929408717318</v>
+        <v>3.502483379040117</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>39.30087751255025</v>
+        <v>39.25062198833714</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>15.35712868507537</v>
+        <v>15.33749094156111</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01827777609942123</v>
+        <v>0.01830097778982211</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5423801957295591</v>
+        <v>0.5445410441542451</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2926613335233557</v>
+        <v>0.2944723300672039</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004776639897836391</v>
+        <v>0.004789403819568014</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.683761660048894</v>
+        <v>1.681166281038394</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4380186529883067</v>
+        <v>0.4372573332552659</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2011817038.896167</v>
+        <v>2030011471.559766</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>200.47</v>
+        <v>198.96</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1198577677498059</v>
+        <v>-0.1264872622911228</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2118340868881462</v>
+        <v>-0.2177707882838608</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>158445473900</v>
+        <v>157252015200</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>75.11235955056178</v>
+        <v>74.51685393258424</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>78.43648954995538</v>
+        <v>77.84568245053686</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.686352502792702</v>
+        <v>1.672982767168466</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>26.00721800439344</v>
+        <v>25.80102764474754</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4020068827190155</v>
+        <v>0.3988196927737488</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>28.37569461151079</v>
+        <v>28.18748420143885</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.098101787861056</v>
+        <v>2.084185490717591</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001324419130242788</v>
+        <v>-0.001335435986196506</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.04237989255340768</v>
+        <v>-0.04276189010312492</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1546827263367114</v>
+        <v>0.1542221199138396</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.240887169138777</v>
+        <v>1.23329301113393</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3433122505972865</v>
+        <v>0.3446769942732688</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1068844576.232046</v>
+        <v>1083637428.278135</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>937.5</v>
+        <v>946.35999</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.02532971593093358</v>
+        <v>0.0350197543627746</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1876012790405462</v>
+        <v>-0.1799235781939185</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>276569062500</v>
+        <v>279182820199</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.28244972577697</v>
+        <v>14.41742824497258</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>12.94098381920838</v>
+        <v>13.06328460558529</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.345057636704342</v>
+        <v>2.367219958104751</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.292155496895928</v>
+        <v>2.3138178699956</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3347608313209361</v>
+        <v>0.3379245407800243</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.47650949256204</v>
+        <v>26.55976874459274</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.047636132002679</v>
+        <v>7.069798453403088</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1501071725981643</v>
+        <v>-0.1487018433670393</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.01902024619616474</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.571253186595629</v>
+        <v>1.574544683584985</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3163314308983209</v>
+        <v>0.3175930766895377</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1849787123.847054</v>
+        <v>1866856727.913529</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>239.24</v>
+        <v>238.2</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1792795883361921</v>
+        <v>-0.1828473413379074</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2803946339409251</v>
+        <v>-0.2835228298141129</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>225396138160</v>
+        <v>224416318800</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.89432314410481</v>
+        <v>20.80349344978166</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.5381623043999</v>
+        <v>18.45757507485393</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.262024952747587</v>
+        <v>3.247844606857027</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.526810518982934</v>
+        <v>6.498437826541275</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2547001794116652</v>
+        <v>0.2535929724789277</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>17.47710610689846</v>
+        <v>17.4167017323223</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.102871878084432</v>
+        <v>4.088691532193873</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.0604757477713477</v>
+        <v>0.06073978965918231</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1270978644493628</v>
+        <v>0.127097864449363</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04621551567034698</v>
+        <v>0.04621551567034721</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02817254639692359</v>
+        <v>0.02829554995801847</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9065330631436457</v>
+        <v>0.9027576993381762</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3289476276953931</v>
+        <v>0.3287262397156106</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1154475069.088229</v>
+        <v>1160753951.576546</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1142</v>
+        <v>1146.24</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05705507005461619</v>
+        <v>0.06097968782784879</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1165435345994663</v>
+        <v>-0.1132634510501683</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,37 +3868,37 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1075468222000</v>
+        <v>1079461203840</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.2067581130813</v>
+        <v>38.34861157577785</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.11002880644067</v>
+        <v>26.20696971899698</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.49974797215367</v>
+        <v>13.54986962837253</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.08119484046164</v>
+        <v>30.19287983706721</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4038925014569365</v>
+        <v>0.4053920673117328</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.89750378710905</v>
+        <v>25.98971023627866</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.07738605524579</v>
+        <v>14.12750771146464</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01864666904123551</v>
+        <v>0.01857769406502212</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4632981984170268</v>
+        <v>0.4632981984170266</v>
       </c>
       <c r="V27" s="4" t="n">
         <v>0.2295582709788979</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005858143607705779</v>
+        <v>0.005836474036850922</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3459308472144155</v>
+        <v>0.3473326240337395</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3169698287472685</v>
+        <v>0.3172772832254654</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2789503758.887024</v>
+        <v>2796987141.356242</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>201.36</v>
+        <v>203.1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1069818953077588</v>
+        <v>0.1165475910657816</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1330032292787944</v>
+        <v>-0.1255113024757805</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,31 +3994,31 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>317601100800</v>
+        <v>320345568000</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.18649517684888</v>
+        <v>16.32636655948553</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>14.95626223681858</v>
+        <v>15.0855028818924</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.510105199598511</v>
+        <v>2.531795619976448</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.864926234184954</v>
+        <v>2.889682748127553</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.411810261906725</v>
+        <v>0.4153688130376234</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.24064131938529</v>
+        <v>23.33415913040515</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.390409319602621</v>
+        <v>5.412099739980558</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.0493827003763332</v>
+        <v>-0.04895962849718589</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
@@ -4027,7 +4027,7 @@
         <v>0.08225537373915337</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3271714729502154</v>
+        <v>-0.3271714729502155</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.0206098529996027</v>
+        <v>0.02043328409650419</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.371311450104973</v>
+        <v>1.373788397593307</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2597608951352844</v>
+        <v>0.2597792532014568</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>878899504.3350958</v>
+        <v>884457801.0844132</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>976.29</v>
+        <v>978.123</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.095206259712106</v>
+        <v>2.101017558684801</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2220796812749004</v>
+        <v>-0.220619123505976</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1102612163100</v>
+        <v>1104682334970</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>21.78732425797813</v>
+        <v>21.82823030573533</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.245951893330358</v>
+        <v>6.257678767333446</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.2140612258236</v>
+        <v>12.23699332000354</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.93339343155554</v>
+        <v>10.95392105158651</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03105332549773018</v>
+        <v>0.03111162861016331</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.85830903564217</v>
+        <v>15.89066419351535</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>12.00624752808117</v>
+        <v>12.03074345847088</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02373940017726055</v>
+        <v>0.02369187880668949</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005428714828585769</v>
+        <v>0.0005418541430883437</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.886543086267324</v>
+        <v>2.885937485167083</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.820553352657822</v>
+        <v>0.8212635820543983</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25126493470.53228</v>
+        <v>25251904881.10092</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>139.65</v>
+        <v>139.17999</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.05289926829215286</v>
+        <v>-0.05608685737135088</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2828384499245092</v>
+        <v>-0.2852521491737108</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>144378828300</v>
+        <v>143892905588</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>86.73913043478262</v>
+        <v>86.44719875776399</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>29.43157220450732</v>
+        <v>29.33251647051633</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.800354894108064</v>
+        <v>9.767370729568286</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.52592281879195</v>
+        <v>11.48713084611697</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>138.7826086956551</v>
+        <v>138.3155180124253</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>43.08650854112926</v>
+        <v>42.9442747320149</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.2042375984252</v>
+        <v>10.17055216806951</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03172210256813671</v>
+        <v>0.03183151270848813</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7036776976367544</v>
+        <v>0.7003721286773756</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6293165069886928</v>
+        <v>0.6296330852939583</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2158145546.582966</v>
+        <v>2164927125.677775</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.67</v>
+        <v>27.755</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09888799303598095</v>
+        <v>0.1022636879910968</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05272167066073263</v>
+        <v>-0.04981170831906889</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157703504800</v>
+        <v>158187957200</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.56183932346723</v>
+        <v>36.67415433403806</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.478736814759447</v>
+        <v>9.507854726911761</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.475877681487063</v>
+        <v>2.483483377292138</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.851054466486677</v>
+        <v>1.856740755957272</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.611521029392505</v>
+        <v>-0.613399572489663</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.42090500633714</v>
+        <v>17.45928051330798</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.452673712635016</v>
+        <v>3.460279408440091</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06966237062348407</v>
+        <v>0.06944902882910482</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.857248074082654</v>
+        <v>2.857248074082655</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05053296346494318</v>
+        <v>-0.05053296346494307</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06216118539934947</v>
+        <v>0.06197081606917672</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.350326043615645</v>
+        <v>0.3522737068710247</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.205500723789221</v>
+        <v>0.2060773297527383</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>926092622.4251246</v>
+        <v>929789396.2581302</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>183.0973</v>
+        <v>182.442</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.08980004753556603</v>
+        <v>0.0858996843344153</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.08391804673037484</v>
+        <v>-0.08719667784059637</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1299725139339</v>
+        <v>1295073460238</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.624400949288165</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003799028885083867</v>
+        <v>0.00378543226935881</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.548040163611034</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2005.934187635125</v>
+        <v>2013.142746920581</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2597.278524310316</v>
+        <v>2606.611089821998</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.638473095998685</v>
+        <v>1.644358206991811</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9179793845077476</v>
+        <v>0.9172093127091734</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3129659147.48306</v>
+        <v>3148389546.09585</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>560.53</v>
+        <v>559.6900000000001</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5015537592539878</v>
+        <v>0.4993035582696101</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1656669097837251</v>
+        <v>-0.1669172260839795</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>312.6</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>70649620476</v>
+        <v>70543746248</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.827084824638465</v>
+        <v>1.825459805417021</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4064685706510061</v>
+        <v>0.4059244807905728</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3707929935.446554</v>
+        <v>3730199471.795148</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>155.23</v>
+        <v>154.18</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.03553896897607034</v>
+        <v>-0.04206273424422158</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3120457365715299</v>
+        <v>-0.3166991668143946</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2029766592562</v>
+        <v>2016036933848</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-100.7987012987013</v>
+        <v>-100.1168831168831</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>124.8406962652859</v>
+        <v>123.9962542690316</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>122.4595229298341</v>
+        <v>121.6311875624736</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.154850657108721</v>
+        <v>7.106454128151921</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-1.007987012987013</v>
+        <v>-1.001168831168831</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>474.1081335641949</v>
+        <v>470.8132790611951</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>119.1920719494419</v>
+        <v>118.3637365820814</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01400308789402435</v>
+        <v>-0.01409845202872804</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.22540548358437</v>
+        <v>4.225405483584371</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.379435704680966</v>
+        <v>3.344649658986036</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7765044942046671</v>
+        <v>0.7755421418578198</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>13747121358.51425</v>
+        <v>13823727807.81515</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>761.4299999999999</v>
+        <v>762.165</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1145542383997509</v>
+        <v>0.115630105341195</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02301859193964362</v>
+        <v>-0.02207552253743417</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>811104342423</v>
+        <v>811887292519</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9951548821037018</v>
+        <v>0.9949016949609824</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1151848510987127</v>
+        <v>0.1156744098676479</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>28945458724.08904</v>
+        <v>29128297329.18666</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>425.89</v>
+        <v>426.2</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3325303323409383</v>
+        <v>0.333500264490145</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1108768267223382</v>
+        <v>-0.1102296450939457</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2208869967200</v>
+        <v>2210477776000</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>28.10942390170396</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6487089672437216</v>
+        <v>0.6491811543808828</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.16195998101111</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.3313324172736</v>
+        <v>42.29981502391519</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.30502496853178</v>
+        <v>42.27352671010792</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2817628965225762</v>
+        <v>0.2815579540122009</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.177289933983538</v>
+        <v>2.175548608882956</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3582524327454802</v>
+        <v>0.3584373028830186</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>3941303051.731517</v>
+        <v>3962226708.224229</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.205</v>
+        <v>28.235</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01069800864374804</v>
+        <v>-0.009645746288112989</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.0598333333333334</v>
+        <v>-0.0588333333333334</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70713790680</v>
+        <v>70789004781</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.20866141732283</v>
+        <v>-22.23228346456693</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-84.17691565632209</v>
+        <v>-84.26644969176581</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.958017186210716</v>
+        <v>1.96009981395542</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.156731682806505</v>
+        <v>2.159025671478166</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1652737593847281</v>
+        <v>0.165449551364219</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.42442821157025</v>
+        <v>16.43686029438016</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.751427126678665</v>
+        <v>2.75350975442337</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03082849864272048</v>
+        <v>0.03079574302173435</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2308629111581491</v>
+        <v>0.2311706972056922</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1565242418943464</v>
+        <v>0.1566598587424824</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>492363203.8141126</v>
+        <v>494827852.7764913</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>314.505</v>
+        <v>314.26</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1562122964884195</v>
+        <v>-0.1568696087326138</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1883532478257504</v>
+        <v>-0.1889855222070247</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>212388371550</v>
+        <v>212222920600</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.07246816252274</v>
+        <v>19.05761067313523</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.17416015942142</v>
+        <v>16.16156045754368</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.526237573894116</v>
+        <v>2.524269629964436</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.220373103850642</v>
+        <v>6.215527421236873</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.182659597850758</v>
+        <v>1.181738303748999</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.148777364099661</v>
+        <v>9.142085447338619</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.690452006589512</v>
+        <v>2.688484062659831</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.0708701700104918</v>
+        <v>0.07092542104992593</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01125578289693328</v>
+        <v>0.01126455800929167</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9678293910321804</v>
+        <v>0.9662931237539787</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2356061711049984</v>
+        <v>0.235421293356257</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>768638995.0475057</v>
+        <v>778843486.4142903</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>150.05</v>
+        <v>151.60001</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2333044052296377</v>
+        <v>-0.2253844729480649</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5446130500758726</v>
+        <v>-0.5399089226100151</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>432214523500</v>
+        <v>436679269581</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>23.15586419753086</v>
+        <v>23.39506327160494</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.68949480784257</v>
+        <v>16.86189656623714</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>6.021629818744167</v>
+        <v>6.08383283755242</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.665193494279039</v>
+        <v>6.734044654346133</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.5039805737109662</v>
+        <v>0.5091866712055194</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.62822172587487</v>
+        <v>14.74658721052492</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.687372326789919</v>
+        <v>7.749575345598172</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.0664484843485367</v>
+        <v>-0.06576909416276447</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01332889036987671</v>
+        <v>0.01319261126697815</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.079370502183088</v>
+        <v>2.08704387055119</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5627040552432833</v>
+        <v>0.5679676175542352</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4077758386.893623</v>
+        <v>4110079188.841165</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>111.0801</v>
+        <v>110.8439</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4608113974564338</v>
+        <v>0.4577051376306036</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1479627214850042</v>
+        <v>-0.1497744879957045</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,31 +5422,31 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>437814956732</v>
+        <v>436883989864</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>33.05955357142857</v>
+        <v>32.98925595238095</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.41135533812198</v>
+        <v>21.3658263718097</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.913777445432294</v>
+        <v>6.899076034172918</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.732219057372975</v>
+        <v>8.713650923734713</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.057905714285714</v>
+        <v>1.055656190476191</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.98466240731305</v>
+        <v>22.93815824286927</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.266165917599685</v>
+        <v>7.251464506340309</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.03105193139466434</v>
+        <v>0.0311181007210451</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
@@ -5455,7 +5455,7 @@
         <v>0.5440196591650359</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.1662824832486469</v>
+        <v>0.1662824832486467</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0.1023396098336123</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01494417091810324</v>
+        <v>0.01497601582044659</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7135542224607341</v>
+        <v>0.7128164736098609</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3389550718206246</v>
+        <v>0.3377503541294458</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>1956947392.126263</v>
+        <v>1964514451.361806</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>86.405</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.09238442468673402</v>
+        <v>-0.08340333196185878</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1161518003273323</v>
+        <v>-0.1074058919803601</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,31 +5548,31 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>261288720000</v>
+        <v>263874240000</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.32596291012839</v>
+        <v>12.44793152639087</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.1088018035119</v>
+        <v>11.21872629332155</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.023846636458696</v>
+        <v>2.043873126524922</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.462303565819413</v>
+        <v>1.476773440812476</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.655163794322141</v>
+        <v>0.6616468108622189</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.60631191331381</v>
+        <v>15.68435121185597</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>4.004900817164324</v>
+        <v>4.024927307230548</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.0733671166516488</v>
+        <v>0.07264824334501162</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
@@ -5581,7 +5581,7 @@
         <v>0.1095672718034899</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>-0.2903031514796548</v>
+        <v>-0.2903031514796547</v>
       </c>
       <c r="W41" s="4" t="n">
         <v>0.009923315255755299</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02141079798622765</v>
+        <v>0.02120100848040339</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.7265825765145346</v>
+        <v>0.7306324055204744</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.2275485790211614</v>
+        <v>0.2269409754412273</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1069516490.984844</v>
+        <v>1075240394.105751</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 10:19 ET</t>
+          <t>2026-09-17 11:55 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -446,7 +446,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -470,7 +470,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>334.85</v>
+        <v>335.71</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2355632188257</v>
+        <v>0.2387365333491882</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.02820907217691604</v>
+        <v>-0.02571320776620134</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,40 +714,40 @@
         <v>236.65</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4918061156600</v>
+        <v>4930692282760</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.21803652968037</v>
+        <v>38.3230593607306</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.96313502250529</v>
+        <v>35.05293133762954</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.5332854534588</v>
+        <v>10.5622308300148</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.74876392159599</v>
+        <v>45.87448112583706</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.167773338406899</v>
+        <v>1.170982369355656</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.45017933383189</v>
+        <v>29.53212154054343</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.62917404506633</v>
+        <v>10.65874866893876</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.0277970304841548</v>
+        <v>0.02771920244181391</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09309524174762762</v>
+        <v>0.09329114280352813</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1191161900765252</v>
+        <v>0.1193167545241032</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003165596535762281</v>
+        <v>0.003157487116856811</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.307494820016682</v>
+        <v>0.3087163930323565</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2903476905773502</v>
+        <v>0.2908297431618555</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>12826960054.50263</v>
+        <v>12881127653.39079</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>497.128</v>
+        <v>495.5025</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.05114390289197512</v>
+        <v>0.04770689187237664</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1022032796359171</v>
+        <v>-0.1051388788557394</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3691448820400</v>
+        <v>3679378588875</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.62000555555555</v>
+        <v>27.52984444444444</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.19935383016466</v>
+        <v>24.120227227658</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.12493462358252</v>
+        <v>11.08861906632132</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.348804062732404</v>
+        <v>8.321550720975074</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8773036567414266</v>
+        <v>0.874439838618199</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.3094583173348</v>
+        <v>18.25138692046993</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.45001184476508</v>
+        <v>11.41369628750388</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01814536192363117</v>
+        <v>0.01820478852364526</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1413530191507437</v>
+        <v>0.1413592494218596</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2268312894486664</v>
+        <v>0.2268379886144549</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007322057900580937</v>
+        <v>0.007346077971352314</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5584235198202734</v>
+        <v>0.5570718895418113</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.434382637982257</v>
+        <v>0.4340510873116192</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10783516484.97605</v>
+        <v>10804513906.35078</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>346</v>
+        <v>345.36</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09788991496426536</v>
+        <v>0.09585913593080564</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1532267932747609</v>
+        <v>-0.1547930789750618</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4187330504956</v>
+        <v>4179585153733</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.99900695134061</v>
+        <v>16.96747765640517</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.75368053270749</v>
+        <v>20.71529222189555</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.318601470995771</v>
+        <v>9.301317582883646</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.495154196852361</v>
+        <v>6.483107161816139</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1511731575034794</v>
+        <v>0.1508927656498321</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.9884679257241</v>
+        <v>12.96432802266672</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.446094933157047</v>
+        <v>9.428538758151552</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01282189037894485</v>
+        <v>0.01284609232014936</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1809160344089119</v>
+        <v>-0.1809201881076548</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2906852445130503</v>
+        <v>0.2906786992528474</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002485549132947977</v>
+        <v>0.002490155200370628</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7627311682851862</v>
+        <v>0.7619395887319947</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3627537718930654</v>
+        <v>0.3624653957099425</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>7759580886.224748</v>
+        <v>7786245226.702816</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>252.19</v>
+        <v>251.1168</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1134216335540839</v>
+        <v>0.1086834437086093</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1219011142061281</v>
+        <v>-0.1256378830083564</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,31 +1094,31 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2712833075262</v>
+        <v>2701288529280</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.01507936507936</v>
+        <v>19.92990476190476</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.44696796262223</v>
+        <v>22.35144440491778</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.497361122192141</v>
+        <v>3.482477992574258</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.917435263405967</v>
+        <v>4.896509011275878</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2265666344371928</v>
+        <v>0.225602475223592</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.25151901503561</v>
+        <v>11.20606750977374</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.684318372604682</v>
+        <v>3.669435242986799</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004285188095798073</v>
+        <v>-0.004303501782202629</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8395391454367772</v>
+        <v>0.8376754476942758</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4639807636505544</v>
+        <v>0.4626552022486072</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8254158323.248074</v>
+        <v>8281543834.25086</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>218.84</v>
+        <v>219.346</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1588032455770521</v>
+        <v>0.1614826206559317</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07482878160142048</v>
+        <v>-0.07268960852287132</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5300523640000</v>
+        <v>5312779466000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.52704402515723</v>
+        <v>27.59094339622641</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.32380432929682</v>
+        <v>16.36154809182024</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.49526730457572</v>
+        <v>17.53587960484406</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.11838207036299</v>
+        <v>23.17204747929986</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2209653874128268</v>
+        <v>0.2214783211397767</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.75434973701892</v>
+        <v>22.80700701425533</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.54945436661837</v>
+        <v>17.59006666688671</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02396102887676207</v>
+        <v>0.02390553622276297</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6863130352373563</v>
+        <v>0.6863284110639978</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9412154432375355</v>
+        <v>0.9412331432680197</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002376165234874794</v>
+        <v>0.002370683759904443</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.328543354293291</v>
+        <v>1.329488252252577</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4127461270773111</v>
+        <v>0.4134550906603844</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26049198503.72923</v>
+        <v>26144534701.49464</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>677.98</v>
+        <v>678.09</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04238869020131442</v>
+        <v>0.04255781429925554</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.142665655032878</v>
+        <v>-0.1425265553869498</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,37 +1346,37 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1727144944729</v>
+        <v>1727425168251</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>25.19435154217763</v>
+        <v>25.19843924191751</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.51035235395519</v>
+        <v>20.51368009040602</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.56696639063212</v>
+        <v>7.568194105757772</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.600170506965367</v>
+        <v>6.60124136267758</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.16484206614641</v>
+        <v>-5.165680044593084</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>17.0352748125467</v>
+        <v>17.03789196289413</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.991311839442186</v>
+        <v>7.992539554567839</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02372470250690476</v>
+        <v>0.0237208538772697</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2283724388244937</v>
+        <v>0.2283724388244934</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>0.273007539505155</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003097436502551698</v>
+        <v>0.003096934035305048</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.771080780010582</v>
+        <v>0.7711665952186683</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4082474516356293</v>
+        <v>0.4082591446211455</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>9984177429.071184</v>
+        <v>10028152950.00101</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>367.8</v>
+        <v>367.79</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1604081679853773</v>
+        <v>-0.160430995387009</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2626746587013611</v>
+        <v>-0.26269470561113</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,37 +1472,37 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1452643531513</v>
+        <v>1452604036039</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>311.6949152542373</v>
+        <v>311.6864406779661</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>174.8105460578462</v>
+        <v>174.8057931881872</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>14.01908464193825</v>
+        <v>14.0187034813982</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.70706900918741</v>
+        <v>13.70669633194409</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.297230842683215</v>
+        <v>-8.297005251850081</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>120.2832167869139</v>
+        <v>120.2799331592118</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.96236724454975</v>
+        <v>13.96198608400969</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.003966561565175313</v>
+        <v>0.003966669413718537</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7830441142326448</v>
+        <v>0.7830441142326445</v>
       </c>
       <c r="V8" s="4" t="n">
         <v>0.1228443872713618</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.537465780199867</v>
+        <v>1.537481043898858</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5714665824470031</v>
+        <v>0.5714509053007185</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12756436695.88413</v>
+        <v>12829266977.54887</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>349.4587</v>
+        <v>349.3048</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.00528941058811272</v>
+        <v>0.004846685767441405</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2940228282828282</v>
+        <v>-0.2943337373737374</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1662577721946</v>
+        <v>1661845530384</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>43.357158808933</v>
+        <v>43.34119106699752</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.10103789532075</v>
+        <v>19.09262588631342</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.65884496707218</v>
+        <v>18.65197321556832</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.70699332129602</v>
+        <v>16.70084040525629</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4314251940888876</v>
+        <v>0.4312663071518067</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>32.48459621529572</v>
+        <v>32.47822400933739</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.05349313162148</v>
+        <v>19.04975558224098</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02370392630312093</v>
+        <v>0.02370867618100493</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.269884968897651</v>
+        <v>1.270048725883573</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.855594416107851</v>
+        <v>0.8557282848072958</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007268383932064075</v>
+        <v>0.007271586305140954</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.606171767953301</v>
+        <v>1.606064809417636</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3926740344888102</v>
+        <v>0.3925099389514287</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8494193148.809659</v>
+        <v>8521232515.997333</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>891.1246</v>
+        <v>891.8049999999999</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.0428608543007607</v>
+        <v>0.04365710942071388</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1873008663930689</v>
+        <v>-0.1866803465572275</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>395195046483</v>
+        <v>395496789595</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>44.75763937719739</v>
+        <v>44.79181315921647</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.31211217252207</v>
+        <v>39.34212813339015</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.346091776825949</v>
+        <v>1.347119557729055</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.80550615672804</v>
+        <v>11.81452000999731</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.530658427656601</v>
+        <v>3.53335418983641</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.57090853372495</v>
+        <v>26.59176154768487</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.309598335358855</v>
+        <v>1.31062611626196</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02228266795944975</v>
+        <v>0.02226566746348964</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006216863500345519</v>
+        <v>0.00621212036263533</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1862075281853639</v>
+        <v>-0.1858819468101897</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1768703234373457</v>
+        <v>0.176829270064046</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1683859407.316933</v>
+        <v>1690961550.789876</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>75.685</v>
+        <v>75.67059999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1682052777568389</v>
+        <v>-0.1683635369099116</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3938411020342784</v>
+        <v>-0.3939564312029473</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>315147798824</v>
+        <v>315087838088</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>23.43188854489164</v>
+        <v>23.42724458204335</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.17657794665142</v>
+        <v>20.17273910510512</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.515253693822161</v>
+        <v>6.513962436566022</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.51561590418457</v>
+        <v>10.51353181567875</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6886689194291326</v>
+        <v>0.6885324322283473</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.47022502060493</v>
+        <v>10.46818367594929</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.622964913764852</v>
+        <v>6.621673656508713</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.0348871483190658</v>
+        <v>0.03489406396892589</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1613410662029773</v>
+        <v>0.1613318578097611</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1440833291150601</v>
+        <v>0.1440742575602207</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09491353985868153</v>
+        <v>0.09485147325057512</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3312770426821339</v>
+        <v>0.3313223450472423</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2112133090.089381</v>
+        <v>2121936879.294035</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>511.32</v>
+        <v>510.565</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02912346526865028</v>
+        <v>0.02760389197545243</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04913155056346941</v>
+        <v>-0.05053557481310678</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1102842380195</v>
+        <v>1101213960997</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.86035219797701</v>
+        <v>12.8139176434578</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.05005364801003</v>
+        <v>23.0160186200349</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.868268243013151</v>
+        <v>2.857911858050831</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.468585680446082</v>
+        <v>1.463283094576347</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.354269952833645</v>
+        <v>0.3529907991070496</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.58076307081057</v>
+        <v>15.5286946040986</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.099003880037537</v>
+        <v>3.088647495075217</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02194609216552319</v>
+        <v>0.02202561952331921</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4420684483271354</v>
+        <v>-0.4432608934238701</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06126460153157787</v>
+        <v>0.05899639749775232</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.04187500431885754</v>
+        <v>0.04094425520498445</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1460164319856381</v>
+        <v>0.1471108819524868</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2076683763.379158</v>
+        <v>2089901356.892582</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>349.4</v>
+        <v>349.72</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07349142253370711</v>
+        <v>0.07447458582852917</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04665757162346529</v>
+        <v>-0.04578444747612542</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,37 +2102,37 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>936220794000</v>
+        <v>937078237200</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.02149613069647</v>
+        <v>15.03525365434222</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.95141226037061</v>
+        <v>13.96418974154782</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.145554404249529</v>
+        <v>3.148435278346151</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.601113139952696</v>
+        <v>2.603495384385395</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7865142612131431</v>
+        <v>0.7872345948238708</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.01160148132246</v>
+        <v>20.02080546586518</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.263689826060954</v>
+        <v>6.266570700157576</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1736064836859413</v>
+        <v>-0.1734476306755916</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07670075619265249</v>
+        <v>0.07670075619265271</v>
       </c>
       <c r="V13" s="4" t="n">
         <v>-0.2892987416862425</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01717229536348025</v>
+        <v>0.01715658240878417</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7665085670680261</v>
+        <v>0.7669828061279033</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1705758341018808</v>
+        <v>0.1706057835351246</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2079387966.277783</v>
+        <v>2087553168.413064</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>370.69</v>
+        <v>371.73</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06987412908684987</v>
+        <v>0.07287574524658003</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03859221412454283</v>
+        <v>-0.03589490883626834</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,37 +2228,37 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>692095730646</v>
+        <v>694037459745</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.49447748513169</v>
+        <v>31.58283772302464</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.76069930278759</v>
+        <v>24.83016739546583</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.55690816952886</v>
+        <v>15.60055430104747</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.16308918045369</v>
+        <v>20.21965831570868</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.123805225148684</v>
+        <v>2.129763728032913</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.1801749483126</v>
+        <v>24.24690562048938</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.81538236481748</v>
+        <v>15.85902849633609</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03036140676722067</v>
+        <v>0.03027646376280684</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2719542812583655</v>
+        <v>0.2719542812583653</v>
       </c>
       <c r="V14" s="4" t="n">
         <v>0.1384422594852113</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007229760716501659</v>
+        <v>0.007209533801415005</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3055629535006044</v>
+        <v>0.3073771941405871</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1769515447465601</v>
+        <v>0.176953067551327</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2208292425.517131</v>
+        <v>2215922195.358755</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>566.16</v>
+        <v>568.83</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.00538063163197644</v>
+        <v>0.01012198793842245</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05894085967886709</v>
+        <v>-0.05450284232572045</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>496542701760</v>
+        <v>498884387880</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.09060955518945</v>
+        <v>31.23723228995058</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.51878145609331</v>
+        <v>25.63912755346468</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.15337062850953</v>
+        <v>14.22011766040532</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>88.99538763143825</v>
+        <v>89.41508821956872</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.374093904448105</v>
+        <v>1.380574105671922</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.05546671007415</v>
+        <v>23.16134870139265</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.53395381694838</v>
+        <v>14.60070084884417</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03312504632874457</v>
+        <v>0.0329695624870032</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005952380952380953</v>
+        <v>0.005924441397254013</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2915658027266966</v>
+        <v>0.2945392928189036</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1942000149140474</v>
+        <v>0.1940010080118123</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1480148746.370378</v>
+        <v>1485687391.625464</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>377.79001</v>
+        <v>378.635</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1230381000430458</v>
+        <v>0.1255499609685249</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1815995624106408</v>
+        <v>-0.179769074130237</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,37 +2480,37 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>343087882147</v>
+        <v>343855256409</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.29361520159475</v>
+        <v>24.34795190019935</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.37505073453795</v>
+        <v>17.41391291652148</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7621990188301575</v>
+        <v>0.7639038062622048</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.476760243480959</v>
+        <v>3.484536594258839</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7361028835887914</v>
+        <v>-0.7377492997436381</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.05379350801537</v>
+        <v>15.08375566242286</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8615994129394018</v>
+        <v>0.8633142879730032</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06883659035757206</v>
+        <v>0.06868206227377796</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3981895979908794</v>
+        <v>0.3981895979908796</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>0.01048486257114645</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02398157643183842</v>
+        <v>0.02392805736395209</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4322113181598834</v>
+        <v>0.4336272424393145</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2282658354730472</v>
+        <v>0.228891792358929</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1730321835.751022</v>
+        <v>1736982560.007548</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>161.89</v>
+        <v>162.65</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3199347573252294</v>
+        <v>0.3261312513370103</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.08230825916898143</v>
+        <v>-0.07800011337225776</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>670946629400</v>
+        <v>674096419000</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>20.83141698841699</v>
+        <v>20.93307593307593</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.65521182905035</v>
+        <v>14.72401139041967</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.857925942519249</v>
+        <v>1.866992796211156</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.604595504601781</v>
+        <v>2.617306134435962</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.039742913449165</v>
+        <v>2.04969701844702</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.782147452920293</v>
+        <v>9.827725986773409</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.945944554384313</v>
+        <v>1.95501140807622</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.0455455638896354</v>
+        <v>0.04532437666012879</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4214340421285367</v>
+        <v>0.4216965321485868</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.0816317473314494</v>
+        <v>0.08183150477592971</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02544937920810427</v>
+        <v>0.0253304641869044</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5394711249643455</v>
+        <v>-0.5365498125991228</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2565903978909659</v>
+        <v>0.2556097449242006</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2198663462.421881</v>
+        <v>2207618583.753525</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>269.23001</v>
+        <v>267.875</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2984326118880938</v>
+        <v>0.2918977193869403</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.04212470203152241</v>
+        <v>-0.04694560074002918</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>648816977016</v>
+        <v>645551538186</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.12485664739884</v>
+        <v>30.96820809248555</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.72227628607386</v>
+        <v>21.61295005758101</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.625381419354839</v>
+        <v>6.592036456882027</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.731439519377199</v>
+        <v>7.69252789186899</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.853748698052942</v>
+        <v>-3.83435313355644</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20.0827397431519</v>
+        <v>19.98593437050872</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.917572700793432</v>
+        <v>6.88422773832062</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02883401739276415</v>
+        <v>0.02897987053453468</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.0196114838758131</v>
+        <v>0.01971068595426972</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1685709656295322</v>
+        <v>-0.1716708096259812</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2033595034833864</v>
+        <v>0.2029143685257041</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1601239215.520638</v>
+        <v>1607116973.893585</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>106.335</v>
+        <v>106.875</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.05697944319359038</v>
+        <v>-0.0521905110388392</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2132657591003255</v>
+        <v>-0.2092704942290619</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>846222436800</v>
+        <v>850519800000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.38628158844765</v>
+        <v>38.58303249097473</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.26999122665479</v>
+        <v>34.44402419098821</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.149954692558165</v>
+        <v>1.155848825831703</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.609181986603961</v>
+        <v>8.653308801074941</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.282500820479166</v>
+        <v>9.330078765999351</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.20517894843484</v>
+        <v>21.30642171852751</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.234519271814525</v>
+        <v>1.240413405088063</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01596463816037352</v>
+        <v>0.0158832281153243</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1201135516659035</v>
+        <v>0.1201662232332723</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.0511458049142941</v>
+        <v>0.05119521528000814</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009192645883293367</v>
+        <v>0.009146198830409357</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.0620778118576816</v>
+        <v>-0.05895544842149842</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3052081663229914</v>
+        <v>0.3044828059471981</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2647891222.195293</v>
+        <v>2656171098.188821</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.835</v>
+        <v>147.365</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.0355808375255815</v>
+        <v>0.0393187599820024</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1220627802690583</v>
+        <v>-0.1188938714499252</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,31 +2984,31 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>349057474264</v>
+        <v>350317395001</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.75333333333333</v>
+        <v>21.83185185185185</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.78075333798286</v>
+        <v>20.85576133518469</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.010679684070227</v>
+        <v>4.02515620692389</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.549461204912449</v>
+        <v>6.573101443538142</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.75889523809546</v>
+        <v>20.83382433862456</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.60334404178037</v>
+        <v>17.66262327096076</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.29889551273095</v>
+        <v>4.313372035584613</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04558848090433566</v>
+        <v>0.04542452138282935</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
@@ -3017,7 +3017,7 @@
         <v>0.04680196042617957</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02551447528784867</v>
+        <v>0.02551447528784889</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02922055368270508</v>
+        <v>0.02911546160893021</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04684502063108714</v>
+        <v>-0.04448251122201943</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1479187006611635</v>
+        <v>0.1480432964863611</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1254617399.714382</v>
+        <v>1258200044.263561</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>303.83511</v>
+        <v>303.21</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1214067909172658</v>
+        <v>-0.1232144075581791</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2789693395666722</v>
+        <v>-0.2804527872042526</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>421.39</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>302959156893</v>
+        <v>302335845570</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.21753561452514</v>
+        <v>21.17388268156424</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.24726463608781</v>
+        <v>20.20560793750329</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.790792765480919</v>
+        <v>1.787108369804228</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.17488712402961</v>
+        <v>18.13749413251489</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.278108146842956</v>
+        <v>-7.263134175652882</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.19720497148233</v>
+        <v>15.17114135772528</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.14830210486712</v>
+        <v>2.144617709190429</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04984500272204486</v>
+        <v>0.04994776577527476</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.04792108938547468</v>
+        <v>0.0479210893854749</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03057579487768875</v>
+        <v>0.03063883117311434</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7106474672924792</v>
+        <v>0.7093849318460014</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2383717148741388</v>
+        <v>0.2380817993557553</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1204978584.118602</v>
+        <v>1211648190.059794</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>545.5364</v>
+        <v>546.535</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.441206412583397</v>
+        <v>1.44567502132079</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.06702854308826312</v>
+        <v>-0.06532074632736484</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,31 +3236,31 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>889551653840</v>
+        <v>891179971000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>138.4610152284264</v>
+        <v>138.7144670050761</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>40.12787578212775</v>
+        <v>40.20132953655372</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>21.53617367969979</v>
+        <v>21.57559547270306</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13.23589593597525</v>
+        <v>13.2601241372129</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.117850398174451</v>
+        <v>1.119896614352908</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>82.92047526030976</v>
+        <v>83.06555271505879</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>21.516563463019</v>
+        <v>21.55420878828229</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009446331715225402</v>
+        <v>0.009429848299383137</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.547286387430741</v>
+        <v>2.548186334181218</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6813230878113947</v>
+        <v>0.682402427557137</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9175100067.032457</v>
+        <v>9269972996.466349</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1624.4193</v>
+        <v>1623.95496</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3958130051272928</v>
+        <v>0.3954140122005276</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1877741054821096</v>
+        <v>-0.1880062801256025</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>916.03</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>626080423148</v>
+        <v>625901456637</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>51.45137880986938</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>33.31175885846592</v>
+        <v>33.30223669746454</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.47017794177341</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5445410441542451</v>
+        <v>0.5449826772081832</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2944723300672039</v>
+        <v>0.2948424637264908</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004789403819568014</v>
+        <v>0.0047907732613471</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.681166281038394</v>
+        <v>1.681175418945564</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4372573332552659</v>
+        <v>0.4372238262997493</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2030011471.559766</v>
+        <v>2039151793.483989</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>198.96</v>
+        <v>198.27</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1264872622911228</v>
+        <v>-0.1295166339689431</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2177707882838608</v>
+        <v>-0.2204835856103794</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,31 +3490,31 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>157252015200</v>
+        <v>156706659900</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>74.51685393258424</v>
+        <v>74.25842696629211</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>77.84568245053686</v>
+        <v>77.57571099451117</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.672982767168466</v>
+        <v>1.667180806425874</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>25.80102764474754</v>
+        <v>25.71154880942951</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3988196927737488</v>
+        <v>0.3974365726088218</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>28.18748420143885</v>
+        <v>28.10901581294964</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.084185490717591</v>
+        <v>2.078383529974999</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001335435986196506</v>
+        <v>-0.001340083440831477</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.23329301113393</v>
+        <v>1.230830162575411</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3446769942732688</v>
+        <v>0.3457197602298659</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1083637428.278135</v>
+        <v>1094168942.159407</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>946.35999</v>
+        <v>953.71</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.0350197543627746</v>
+        <v>0.04305835027252347</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1799235781939185</v>
+        <v>-0.1735543635560099</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>279182820199</v>
+        <v>281351125970</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.41742824497258</v>
+        <v>14.5294028031688</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.06328460558529</v>
+        <v>13.16474205676504</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.367219958104751</v>
+        <v>2.385605246614718</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.3138178699956</v>
+        <v>2.331788393540923</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3379245407800243</v>
+        <v>0.3405490692683626</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.55976874459274</v>
+        <v>26.62883846621859</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.069798453403088</v>
+        <v>7.088183741913055</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1487018433670393</v>
+        <v>-0.1475558338601662</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3649,7 +3649,7 @@
         <v>0.1036602723030562</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3821998793565314</v>
+        <v>-0.3821998793565313</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01902024619616474</v>
+        <v>0.01887366180495119</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.574544683584985</v>
+        <v>1.579440428962867</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3175930766895377</v>
+        <v>0.3198695550496338</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1866856727.913529</v>
+        <v>1879039745.070729</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>238.2</v>
+        <v>238.49</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1828473413379074</v>
+        <v>-0.1818524871355059</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2835228298141129</v>
+        <v>-0.2826505444263971</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>224416318800</v>
+        <v>224689537660</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.80349344978166</v>
+        <v>20.82882096069869</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.45757507485393</v>
+        <v>18.48004651386195</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.247844606857027</v>
+        <v>3.251798741768818</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.498437826541275</v>
+        <v>6.506349442702892</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2535929724789277</v>
+        <v>0.2539017128736333</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>17.4167017323223</v>
+        <v>17.43354525984834</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.088691532193873</v>
+        <v>4.092645667105663</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06073978965918231</v>
+        <v>0.06066593105294656</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.127097864449363</v>
+        <v>0.1270978644493628</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04621551567034721</v>
+        <v>0.04621551567034698</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02829554995801847</v>
+        <v>0.02826114302486477</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9027576993381762</v>
+        <v>0.9034871930437464</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3287262397156106</v>
+        <v>0.3287470236030156</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1160753951.576546</v>
+        <v>1164357580.35532</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1146.24</v>
+        <v>1146.53</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06097968782784879</v>
+        <v>0.06124811687365939</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1132634510501683</v>
+        <v>-0.1130391057130702</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,37 +3868,37 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1079461203840</v>
+        <v>1079734308730</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.34861157577785</v>
+        <v>38.35831381733021</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.20696971899698</v>
+        <v>26.21360011160107</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.54986962837253</v>
+        <v>13.55329776051957</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.19287983706721</v>
+        <v>30.20051866938221</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4053920673117328</v>
+        <v>0.4054946319574618</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.98971023627866</v>
+        <v>25.99601680945299</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.12750771146464</v>
+        <v>14.13093584361169</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01857769406502212</v>
+        <v>0.01857299507652739</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4632981984170266</v>
+        <v>0.4632981984170268</v>
       </c>
       <c r="V27" s="4" t="n">
         <v>0.2295582709788979</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005836474036850922</v>
+        <v>0.00583499777589771</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3473326240337395</v>
+        <v>0.3477140061425717</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3172772832254654</v>
+        <v>0.317363421515186</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2796987141.356242</v>
+        <v>2804321115.502555</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>203.1</v>
+        <v>203.665</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1165475910657816</v>
+        <v>0.1196536934239902</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1255113024757805</v>
+        <v>-0.1230785791173304</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,31 +3994,31 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>320345568000</v>
+        <v>321236731200</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.32636655948553</v>
+        <v>16.3717845659164</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.0855028818924</v>
+        <v>15.12746895342499</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.531795619976448</v>
+        <v>2.538838773719859</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.889682748127553</v>
+        <v>2.897721501218109</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4153688130376234</v>
+        <v>0.4165243195830013</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.33415913040515</v>
+        <v>23.36452554605241</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.412099739980558</v>
+        <v>5.419142893723969</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04895962849718589</v>
+        <v>-0.04882380648505366</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
@@ -4027,7 +4027,7 @@
         <v>0.08225537373915337</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3271714729502155</v>
+        <v>-0.3271714729502154</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02043328409650419</v>
+        <v>0.02037659882650431</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.373788397593307</v>
+        <v>1.375540724718137</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2597792532014568</v>
+        <v>0.2601551734066707</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>884457801.0844132</v>
+        <v>888555485.0855372</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>978.123</v>
+        <v>974.8150000000001</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.101017558684801</v>
+        <v>2.090529955301454</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.220619123505976</v>
+        <v>-0.2232549800796813</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1104682334970</v>
+        <v>1100946315607</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>21.82823030573533</v>
+        <v>21.75440749832627</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.257678767333446</v>
+        <v>6.236515374424437</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.23699332000354</v>
+        <v>12.19560798908877</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.95392105158651</v>
+        <v>10.9168750248203</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03111162861016331</v>
+        <v>0.0310064094634482</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.89066419351535</v>
+        <v>15.8360008721359</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>12.03074345847088</v>
+        <v>11.98935812755611</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02369187880668949</v>
+        <v>0.02377227629448056</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005418541430883437</v>
+        <v>0.0005436929058334146</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.885937485167083</v>
+        <v>2.884542665404855</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8212635820543983</v>
+        <v>0.8200068926288235</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25251904881.10092</v>
+        <v>25333319844.34505</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>139.17999</v>
+        <v>138.5</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.05608685737135088</v>
+        <v>-0.0606985224379748</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2852521491737108</v>
+        <v>-0.2887441841356573</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>143892905588</v>
+        <v>143189887000</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>86.44719875776399</v>
+        <v>86.0248447204969</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>29.33251647051633</v>
+        <v>29.18920694825824</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.767370729568286</v>
+        <v>9.719650217214229</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.48713084611697</v>
+        <v>11.43100830936401</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>138.3155180124253</v>
+        <v>137.639751552798</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>42.9442747320149</v>
+        <v>42.73685078876468</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.17055216806951</v>
+        <v>10.12142766779799</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03183151270848813</v>
+        <v>0.03199242857361326</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7003721286773756</v>
+        <v>0.6972145438428565</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6296330852939583</v>
+        <v>0.6303052912251551</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2164927125.677775</v>
+        <v>2170793667.364769</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.755</v>
+        <v>27.64</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1022636879910968</v>
+        <v>0.09769657128711651</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.04981170831906889</v>
+        <v>-0.05374871619308452</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>158187957200</v>
+        <v>157532521600</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.67415433403806</v>
+        <v>36.52219873150106</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.507854726911761</v>
+        <v>9.468459904588041</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.483483377292138</v>
+        <v>2.473193318261743</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.856740755957272</v>
+        <v>1.849047540791173</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.613399572489663</v>
+        <v>-0.6108580141817435</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.45928051330798</v>
+        <v>17.40736070975919</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.460279408440091</v>
+        <v>3.449989349409696</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06944902882910482</v>
+        <v>0.06973798101128091</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06197081606917672</v>
+        <v>0.06222865412445731</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3522737068710247</v>
+        <v>0.349631624305318</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2060773297527383</v>
+        <v>0.2053625253746116</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>929789396.2581302</v>
+        <v>932464647.3902593</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>182.442</v>
+        <v>183.535</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.0858996843344153</v>
+        <v>0.09240524969204955</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.08719667784059637</v>
+        <v>-0.08172812328013213</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1295073460238</v>
+        <v>1302832174197</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.624400949288165</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.00378543226935881</v>
+        <v>0.00380811058614118</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.548040163611034</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2013.142746920581</v>
+        <v>2001.14798830569</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2606.611089821998</v>
+        <v>2591.082068538258</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.644358206991811</v>
+        <v>1.63456561418803</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9172093127091734</v>
+        <v>0.9187612099390212</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3148389546.09585</v>
+        <v>3163546625.817719</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>559.6900000000001</v>
+        <v>561.29773</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4993035582696101</v>
+        <v>0.5036103625893884</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1669172260839795</v>
+        <v>-0.164524165339446</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>312.6</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>70543746248</v>
+        <v>70746385676</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.825459805417021</v>
+        <v>1.82676342947018</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4059244807905728</v>
+        <v>0.4071132574526208</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3730199471.795148</v>
+        <v>3744147858.759835</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>154.18</v>
+        <v>154.89</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.04206273424422158</v>
+        <v>-0.03765142630099561</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3166991668143946</v>
+        <v>-0.3135525616025527</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2016036933848</v>
+        <v>2025320790331</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-100.1168831168831</v>
+        <v>-100.5779220779221</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>123.9962542690316</v>
+        <v>124.567257904594</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>121.6311875624736</v>
+        <v>122.1912995674812</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.106454128151921</v>
+        <v>7.139179400113186</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-1.001168831168831</v>
+        <v>-1.005779220779221</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>470.8132790611951</v>
+        <v>473.0412282963763</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>118.3637365820814</v>
+        <v>118.923849068537</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01409845202872804</v>
+        <v>-0.01403382615914631</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.344649658986036</v>
+        <v>3.358091173596664</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7755421418578198</v>
+        <v>0.776198118854627</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>13823727807.81515</v>
+        <v>13896094518.47412</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>762.165</v>
+        <v>762.43103</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.115630105341195</v>
+        <v>0.1160195106234159</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02207552253743417</v>
+        <v>-0.02173418273733918</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>811887292519</v>
+        <v>812170678136</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9949016949609824</v>
+        <v>0.9951091276731021</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1156744098676479</v>
+        <v>0.1158705180333158</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29128297329.18666</v>
+        <v>29250954842.76344</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>426.2</v>
+        <v>429.1</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.333500264490145</v>
+        <v>0.3425738233053057</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1102296450939457</v>
+        <v>-0.1041753653444676</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2210477776000</v>
+        <v>2225518568000</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>28.10942390170396</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6491811543808828</v>
+        <v>0.6535983888898096</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.16195998101111</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.29981502391519</v>
+        <v>42.00718052480227</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.27352671010792</v>
+        <v>41.98106987613143</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2815579540122009</v>
+        <v>0.2796550920531344</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.175548608882956</v>
+        <v>2.179889478439435</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3584373028830186</v>
+        <v>0.3609925705957042</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>3962226708.224229</v>
+        <v>3980882961.413702</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.235</v>
+        <v>28.245</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.009645746288112989</v>
+        <v>-0.009294992169567862</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.0588333333333334</v>
+        <v>-0.0585</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70789004781</v>
+        <v>70814076148</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.23228346456693</v>
+        <v>-22.24015748031496</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-84.26644969176581</v>
+        <v>-84.29629437024705</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.96009981395542</v>
+        <v>1.960794023203655</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.159025671478166</v>
+        <v>2.159790334368719</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.165449551364219</v>
+        <v>0.165508148690716</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.43686029438016</v>
+        <v>16.44100432198347</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.75350975442337</v>
+        <v>2.754203963671605</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03079574302173435</v>
+        <v>0.03078483994402248</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2311706972056922</v>
+        <v>0.2312502859610314</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1566598587424824</v>
+        <v>0.1566866355788266</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>494827852.7764913</v>
+        <v>496552008.7515242</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>314.26</v>
+        <v>313.70999</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1568696087326138</v>
+        <v>-0.1583452344772233</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1889855222070247</v>
+        <v>-0.1904049394823092</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>212222920600</v>
+        <v>211851494330</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.05761067313523</v>
+        <v>19.02425651910249</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.16156045754368</v>
+        <v>16.13327489823848</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.524269629964436</v>
+        <v>2.519851728022076</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.215527421236873</v>
+        <v>6.204649160443408</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.181738303748999</v>
+        <v>1.179670054896314</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.142085447338619</v>
+        <v>9.127062543682252</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.688484062659831</v>
+        <v>2.684066160717472</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07092542104992593</v>
+        <v>0.07104977025346622</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01126455800929167</v>
+        <v>0.01128430752237122</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9662931237539787</v>
+        <v>0.9651603561422685</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.235421293356257</v>
+        <v>0.2350733092245474</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>778843486.4142903</v>
+        <v>785765946.8164337</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>151.60001</v>
+        <v>149.44901</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2253844729480649</v>
+        <v>-0.2363752241933235</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5399089226100151</v>
+        <v>-0.546436995447648</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>436679269581</v>
+        <v>430483375798</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>23.39506327160494</v>
+        <v>23.06311882716049</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.86189656623714</v>
+        <v>16.62264895989479</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>6.08383283755242</v>
+        <v>5.997511400560068</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.734044654346133</v>
+        <v>6.638497628646737</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.5091866712055194</v>
+        <v>0.5019619980029051</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.74658721052492</v>
+        <v>14.58232703600212</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.749575345598172</v>
+        <v>7.663253908605821</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06576909416276447</v>
+        <v>-0.0667157005697627</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01319261126697815</v>
+        <v>0.01338249079067168</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.08704387055119</v>
+        <v>2.07737510177524</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5679676175542352</v>
+        <v>0.5608270808254086</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4110079188.841165</v>
+        <v>4127660367.047246</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>110.8439</v>
+        <v>110.23</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4577051376306036</v>
+        <v>0.4496317552975078</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1497744879957045</v>
+        <v>-0.1544833934187313</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,31 +5422,31 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>436883989864</v>
+        <v>434464343123</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>32.98925595238095</v>
+        <v>32.80654761904762</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.3658263718097</v>
+        <v>21.24749346571695</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.899076034172918</v>
+        <v>6.860866058002369</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.713650923734713</v>
+        <v>8.665391070895895</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.055656190476191</v>
+        <v>1.049809523809524</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.93815824286927</v>
+        <v>22.81729072995654</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.251464506340309</v>
+        <v>7.21325453016976</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.0311181007210451</v>
+        <v>0.03129140564741617</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01497601582044659</v>
+        <v>0.01505942121019686</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7128164736098609</v>
+        <v>0.7105825519708762</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3377503541294458</v>
+        <v>0.3352803823404072</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>1964514451.361806</v>
+        <v>1969008784.983871</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>87.26000000000001</v>
+        <v>87.19</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.08340333196185878</v>
+        <v>-0.08413862610307665</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1074058919803601</v>
+        <v>-0.1081219312602292</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,31 +5548,31 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>263874240000</v>
+        <v>263662560000</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.44793152639087</v>
+        <v>12.43794579172611</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.21872629332155</v>
+        <v>11.20972662748918</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.043873126524922</v>
+        <v>2.042233530846985</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.476773440812476</v>
+        <v>1.475588772684389</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.6616468108622189</v>
+        <v>0.6611160375782359</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.68435121185597</v>
+        <v>15.67796202951918</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>4.024927307230548</v>
+        <v>4.023287711552612</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.07264824334501162</v>
+        <v>0.07270656857765471</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02120100848040339</v>
+        <v>0.02121802959054938</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.7306324055204744</v>
+        <v>0.7300958564413106</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.2269409754412273</v>
+        <v>0.2269026607212093</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1075240394.105751</v>
+        <v>1079104012.065905</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:55 ET</t>
+          <t>2026-09-17 13:43 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -442,11 +442,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -470,7 +470,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>335.71</v>
+        <v>337</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2387365333491882</v>
+        <v>0.2434965051344211</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.02571320776620134</v>
+        <v>-0.02196941115012918</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,31 +714,31 @@
         <v>236.65</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4930692282760</v>
+        <v>4949638972000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.3230593607306</v>
+        <v>38.4703196347032</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>35.05293133762954</v>
+        <v>35.18762581031591</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.5622308300148</v>
+        <v>10.60281728192484</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.87448112583706</v>
+        <v>46.05075851004465</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.170982369355656</v>
+        <v>1.175481988838152</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.53212154054343</v>
+        <v>29.64283069216433</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.65874866893876</v>
+        <v>10.69870587353237</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02771920244181391</v>
+        <v>0.02761474135249313</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003157487116856811</v>
+        <v>0.00314540059347181</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3087163930323565</v>
+        <v>0.3103413413725857</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2908297431618555</v>
+        <v>0.2917215924056524</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>12881127653.39079</v>
+        <v>13105224218.6762</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>495.5025</v>
+        <v>497.75</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.04770689187237664</v>
+        <v>0.05245908028612467</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1051388788557394</v>
+        <v>-0.1010799682149823</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3679378588875</v>
+        <v>3696067512500</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.52984444444444</v>
+        <v>27.65277777777778</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.120227227658</v>
+        <v>24.22963174265876</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.08861906632132</v>
+        <v>11.13813479578953</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.321550720975074</v>
+        <v>8.35871024691051</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.874439838618199</v>
+        <v>0.8783446120134039</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.25138692046993</v>
+        <v>18.33056641801474</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.41369628750388</v>
+        <v>11.46321201697209</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01820478852364526</v>
+        <v>0.01812385725462313</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1413592494218596</v>
+        <v>0.141279325722983</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2268379886144549</v>
+        <v>0.2267520769688407</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007346077971352314</v>
+        <v>0.007312908086388749</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5570718895418113</v>
+        <v>0.5589055542321191</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4340510873116192</v>
+        <v>0.4345471733432665</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10804513906.35078</v>
+        <v>10974084804.75201</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>345.36</v>
+        <v>347.33</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09585913593080564</v>
+        <v>0.1021101276431742</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1547930789750618</v>
+        <v>-0.1499718558038228</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4179585153733</v>
+        <v>4203426312966</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>16.96747765640517</v>
+        <v>17.06454816285998</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.71529222189555</v>
+        <v>20.83345624111356</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.301317582883646</v>
+        <v>9.354530183290496</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.483107161816139</v>
+        <v>6.52019685236073</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1508927656498321</v>
+        <v>0.1517560193094865</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>12.96432802266672</v>
+        <v>13.03787023753176</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.428538758151552</v>
+        <v>9.482023645451774</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01284609232014936</v>
+        <v>0.01277264429159752</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1809201881076548</v>
+        <v>-0.1809065204848667</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2906786992528474</v>
+        <v>0.2907002362377471</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002490155200370628</v>
+        <v>0.002476031439841073</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7619395887319947</v>
+        <v>0.7641258961441091</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3624653957099425</v>
+        <v>0.3634733575263296</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>7786245226.702816</v>
+        <v>7900376292.188757</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>251.1168</v>
+        <v>251.19</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1086834437086093</v>
+        <v>0.1090066225165562</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1256378830083564</v>
+        <v>-0.1253830083565459</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,31 +1094,31 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2701288529280</v>
+        <v>2702075949000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.92990476190476</v>
+        <v>19.93571428571428</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.35144440491778</v>
+        <v>22.35795980225655</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.482477992574258</v>
+        <v>3.483493127320545</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.896509011275878</v>
+        <v>4.89793633298285</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.225602475223592</v>
+        <v>0.225668237853517</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.20606750977374</v>
+        <v>11.20916762402706</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.669435242986799</v>
+        <v>3.670450377733086</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004303501782202629</v>
+        <v>-0.004302247686376931</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8376754476942758</v>
+        <v>0.8377679948319768</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4626552022486072</v>
+        <v>0.4627757144334783</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8281543834.25086</v>
+        <v>8395580226.45627</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>219.346</v>
+        <v>219.34</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1614826206559317</v>
+        <v>0.1614508494099369</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07268960852287132</v>
+        <v>-0.07271497421154982</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5312779466000</v>
+        <v>5312634140000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.59094339622641</v>
+        <v>27.58993710691823</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.36154809182024</v>
+        <v>16.36110053732391</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.53587960484406</v>
+        <v>17.53524004106031</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.17204747929986</v>
+        <v>23.17120235474967</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2214783211397767</v>
+        <v>0.2214702434432892</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.80700701425533</v>
+        <v>22.80617776579491</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.59006666688671</v>
+        <v>17.58942710310296</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02390553622276297</v>
+        <v>0.0239064081307131</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6863284110639978</v>
+        <v>0.6863130352373563</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9412331432680197</v>
+        <v>0.9412154432375359</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002370683759904443</v>
+        <v>0.002370748609464758</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.329488252252577</v>
+        <v>1.329235799282248</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4134550906603844</v>
+        <v>0.4134708612908174</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26144534701.49464</v>
+        <v>26440839904.5858</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>678.09</v>
+        <v>682.3099999999999</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04255781429925554</v>
+        <v>0.04904602969299798</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1425265553869498</v>
+        <v>-0.137190187152251</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,37 +1346,37 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1727425168251</v>
+        <v>1738175561577</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>25.19843924191751</v>
+        <v>25.35525826830175</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.51368009040602</v>
+        <v>20.64134416151976</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.568194105757772</v>
+        <v>7.615293722516737</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.60124136267758</v>
+        <v>6.642323281818843</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.165680044593084</v>
+        <v>-5.197827945001853</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>17.03789196289413</v>
+        <v>17.1382953673883</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.992539554567839</v>
+        <v>8.039639171326803</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.0237208538772697</v>
+        <v>0.02357414343279777</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2283724388244934</v>
+        <v>0.2283724388244937</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>0.273007539505155</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003096934035305048</v>
+        <v>0.00307777989476924</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7711665952186683</v>
+        <v>0.7735940337248534</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4082591446211455</v>
+        <v>0.4090935415337825</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10028152950.00101</v>
+        <v>10205541163.94253</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>367.79</v>
+        <v>366.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.160430995387009</v>
+        <v>-0.1640605522464523</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.26269470561113</v>
+        <v>-0.2658821642643786</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,37 +1472,37 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1452604036039</v>
+        <v>1446324255683</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>311.6864406779661</v>
+        <v>310.3389830508475</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>174.8057931881872</v>
+        <v>174.050086912407</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>14.0187034813982</v>
+        <v>13.9580989556259</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.70669633194409</v>
+        <v>13.64744065025674</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.297005251850081</v>
+        <v>-8.261136309381712</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>120.2799331592118</v>
+        <v>119.7578363554207</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.96198608400969</v>
+        <v>13.90138155823739</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.003966669413718537</v>
+        <v>0.00398389225469983</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7830441142326445</v>
+        <v>0.7830441142326448</v>
       </c>
       <c r="V8" s="4" t="n">
         <v>0.1228443872713618</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.537481043898858</v>
+        <v>1.535289737654368</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5714509053007185</v>
+        <v>0.5703197237714112</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12829266977.54887</v>
+        <v>12967035666.74941</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>349.3048</v>
+        <v>347.3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.004846685767441405</v>
+        <v>-0.0009205313896849532</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2943337373737374</v>
+        <v>-0.2983838383838383</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1661845530384</v>
+        <v>1652307534000</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>43.34119106699752</v>
+        <v>43.0893300248139</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.09262588631342</v>
+        <v>18.98304566761365</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.65197321556832</v>
+        <v>18.54358428353385</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.70084040525629</v>
+        <v>16.60378974821948</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4312663071518067</v>
+        <v>0.4287601650983955</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>32.47822400933739</v>
+        <v>32.29343003654593</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.04975558224098</v>
+        <v>18.9413666502065</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02370867618100493</v>
+        <v>0.02384725554365232</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.270048725883573</v>
+        <v>1.269884968897651</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8557282848072958</v>
+        <v>0.8555944161078508</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007271586305140954</v>
+        <v>0.007313561762165275</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.606064809417636</v>
+        <v>1.603180456370468</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3925099389514287</v>
+        <v>0.3900005977275804</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8521232515.997333</v>
+        <v>8661789348.470654</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>891.8049999999999</v>
+        <v>893.9299999999999</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04365710942071388</v>
+        <v>0.04614394382679921</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1866803465572275</v>
+        <v>-0.1847423620611035</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>395496789595</v>
+        <v>396439182470</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>44.79181315921647</v>
+        <v>44.89854344550477</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.34212813339015</v>
+        <v>39.43587286714187</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.347119557729055</v>
+        <v>1.350329484854575</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.81452000999731</v>
+        <v>11.84267174162165</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.53335418983641</v>
+        <v>3.541773494116385</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.59176154768487</v>
+        <v>26.65688890601244</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.31062611626196</v>
+        <v>1.31383604338748</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02226566746348964</v>
+        <v>0.02221273877403978</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.00621212036263533</v>
+        <v>0.006197353260322397</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1858819468101897</v>
+        <v>-0.1847808843101222</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.176829270064046</v>
+        <v>0.1768386631306476</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1690961550.789876</v>
+        <v>1731346165.996574</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>75.67059999999999</v>
+        <v>75.31</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1683635369099116</v>
+        <v>-0.1723266098681051</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3939564312029473</v>
+        <v>-0.3968444658016979</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>315087838088</v>
+        <v>313586321325</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>23.42724458204335</v>
+        <v>23.31578947368421</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.17273910510512</v>
+        <v>20.07660811471651</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.513962436566022</v>
+        <v>6.482972262439353</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.51353181567875</v>
+        <v>10.46351369153914</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6885324322283473</v>
+        <v>0.6852567394094996</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.46818367594929</v>
+        <v>10.41919140424638</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.621673656508713</v>
+        <v>6.590683482382044</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03489406396892589</v>
+        <v>0.03506086602739671</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1613318578097611</v>
+        <v>0.1613410662029773</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1440742575602207</v>
+        <v>0.1440833291150601</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09485147325057512</v>
+        <v>0.0926744441018264</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3313223450472423</v>
+        <v>0.3326241973936346</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2121936879.294035</v>
+        <v>2155970177.13188</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>510.565</v>
+        <v>509.2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02760389197545243</v>
+        <v>0.02485658396854551</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05053557481310678</v>
+        <v>-0.05307397627106036</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1101213960997</v>
+        <v>1098269850574</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.8139176434578</v>
+        <v>12.80563770215411</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>23.0160186200349</v>
+        <v>22.95448509263613</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.857911858050831</v>
+        <v>2.856065167359437</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.463283094576347</v>
+        <v>1.46233756812059</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3529907991070496</v>
+        <v>0.3527627078098621</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.5286946040986</v>
+        <v>15.51941005614659</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.088647495075217</v>
+        <v>3.086800804383824</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02202561952331921</v>
+        <v>0.02203986097236272</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4432608934238701</v>
+        <v>-0.4421291677650311</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.05899639749775232</v>
+        <v>0.06114910458549239</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.04094425520498445</v>
+        <v>0.03887823087399517</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1471108819524868</v>
+        <v>0.1493477437764856</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2089901356.892582</v>
+        <v>2144255896.806022</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>349.72</v>
+        <v>349.31</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07447458582852917</v>
+        <v>0.07321490785703855</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04578444747612542</v>
+        <v>-0.04690313778990451</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,37 +2102,37 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>937078237200</v>
+        <v>935979638100</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.03525365434222</v>
+        <v>15.01762682717111</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.96418974154782</v>
+        <v>13.94781859378952</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.148435278346151</v>
+        <v>3.144744158409853</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.603495384385395</v>
+        <v>2.600443133705999</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7872345948238708</v>
+        <v>0.7863116673851259</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.02080546586518</v>
+        <v>20.00901286066982</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.266570700157576</v>
+        <v>6.262879580221279</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1734476306755916</v>
+        <v>-0.173651213534877</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07670075619265271</v>
+        <v>0.07670075619265249</v>
       </c>
       <c r="V13" s="4" t="n">
         <v>-0.2892987416862425</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01715658240878417</v>
+        <v>0.01717671981907188</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7669828061279033</v>
+        <v>0.7660134893613323</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1706057835351246</v>
+        <v>0.1705710040290456</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2087553168.413064</v>
+        <v>2128423294.955566</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>371.73</v>
+        <v>369.93</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.07287574524658003</v>
+        <v>0.06768064035473964</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03589490883626834</v>
+        <v>-0.04056332183520495</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,31 +2228,31 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>694037459745</v>
+        <v>690676774765</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.58283772302464</v>
+        <v>31.42990654205607</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.83016739546583</v>
+        <v>24.7099341581381</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.60055430104747</v>
+        <v>15.52501291955134</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.21965831570868</v>
+        <v>20.12175019699812</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.129763728032913</v>
+        <v>2.119450934579441</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.24690562048938</v>
+        <v>24.13141022630421</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.85902849633609</v>
+        <v>15.78348711483996</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03027646376280684</v>
+        <v>0.03042378253872745</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007209533801415005</v>
+        <v>0.007244613845862731</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3073771941405871</v>
+        <v>0.3041296675936401</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.176953067551327</v>
+        <v>0.1771115692814877</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2215922195.358755</v>
+        <v>2252382337.061794</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>568.83</v>
+        <v>565.73</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01012198793842245</v>
+        <v>0.004617042414084338</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05450284232572045</v>
+        <v>-0.05965559655596553</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.62</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>498884387880</v>
+        <v>496165576280</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.23723228995058</v>
+        <v>31.06699615595826</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.63912755346468</v>
+        <v>25.49939987486871</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.22011766040532</v>
+        <v>14.14262110651883</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.41508821956872</v>
+        <v>88.92779540188916</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.380574105671922</v>
+        <v>1.373050276535655</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.16134870139265</v>
+        <v>23.03841455416893</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.60070084884417</v>
+        <v>14.52320429495767</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.0329695624870032</v>
+        <v>0.03315022401053865</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005924441397254013</v>
+        <v>0.005956905237480777</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2945392928189036</v>
+        <v>0.2909059922383178</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1940010080118123</v>
+        <v>0.1942915591974401</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1485687391.625464</v>
+        <v>1508107121.504842</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>378.635</v>
+        <v>375.21</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1255499609685249</v>
+        <v>0.1153686290358795</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.179769074130237</v>
+        <v>-0.187188596681253</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>343855256409</v>
+        <v>340744861825</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.34795190019935</v>
+        <v>24.12770882901421</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.41391291652148</v>
+        <v>17.25639274078736</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7639038062622048</v>
+        <v>0.7569937991664611</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.484536594258839</v>
+        <v>3.453016692941379</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7377492997436381</v>
+        <v>-0.7310758771820103</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.08375566242286</v>
+        <v>14.96284834161394</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8633142879730032</v>
+        <v>0.8563941932757053</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06868206227377796</v>
+        <v>0.06930992260164802</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3981895979908796</v>
+        <v>0.3981895979908794</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01048486257114645</v>
+        <v>0.01048486257114667</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02392805736395209</v>
+        <v>0.0241464779723355</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4336272424393145</v>
+        <v>0.4276747997915096</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.228891792358929</v>
+        <v>0.2271589811774222</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1736982560.007548</v>
+        <v>1773592635.472208</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>162.65</v>
+        <v>163.3</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3261312513370103</v>
+        <v>0.3314308843734017</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.07800011337225776</v>
+        <v>-0.07431551499348099</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,37 +2606,37 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>674096419000</v>
+        <v>676790318000</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>20.93307593307593</v>
+        <v>21.01673101673102</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.72401139041967</v>
+        <v>14.78285312053816</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.866992796211156</v>
+        <v>1.874453880241511</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.617306134435962</v>
+        <v>2.627765703986429</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.04969701844702</v>
+        <v>2.057888245388247</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.827725986773409</v>
+        <v>9.865232412112775</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.95501140807622</v>
+        <v>1.962472492106575</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04532437666012879</v>
+        <v>0.04514396732253489</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4216965321485868</v>
+        <v>0.421696532148587</v>
       </c>
       <c r="V17" s="4" t="n">
         <v>0.08183150477592971</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.0253304641869044</v>
+        <v>0.02522963870177587</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5365498125991228</v>
+        <v>-0.5338359743767092</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2556097449242006</v>
+        <v>0.2551697232515629</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2207618583.753525</v>
+        <v>2239596334.706132</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>267.875</v>
+        <v>270.22</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2918977193869403</v>
+        <v>0.3032070993289373</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.04694560074002918</v>
+        <v>-0.03860248336713257</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>645551538186</v>
+        <v>651202749972</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30.96820809248555</v>
+        <v>31.2393063583815</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.61295005758101</v>
+        <v>21.80215161758111</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.592036456882027</v>
+        <v>6.649743691572466</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.69252789186899</v>
+        <v>7.759868919984465</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.83435313355644</v>
+        <v>-3.867919379373295</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>19.98593437050872</v>
+        <v>20.15346703344006</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.88422773832062</v>
+        <v>6.941934973011059</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02897987053453468</v>
+        <v>0.02872837991056456</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01971068595426972</v>
+        <v>0.01953963437199319</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1716708096259812</v>
+        <v>-0.1659690344752618</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2029143685257041</v>
+        <v>0.2041548623999825</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1607116973.893585</v>
+        <v>1642467131.754413</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>106.875</v>
+        <v>106.79</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0521905110388392</v>
+        <v>-0.05294432443356845</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2092704942290619</v>
+        <v>-0.2098993785143533</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,37 +2858,37 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>850519800000</v>
+        <v>849843363200</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.58303249097473</v>
+        <v>38.55234657039712</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.44402419098821</v>
+        <v>34.41663011326906</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.155848825831703</v>
+        <v>1.154929554250924</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.653308801074941</v>
+        <v>8.646426637350109</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.330078765999351</v>
+        <v>9.322658352477855</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.30642171852751</v>
+        <v>21.290631508672</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.240413405088063</v>
+        <v>1.239494133507284</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.0158832281153243</v>
+        <v>0.01589587044503497</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1201662232332723</v>
+        <v>0.1201662232332725</v>
       </c>
       <c r="V19" s="4" t="n">
         <v>0.05119521528000814</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009146198830409357</v>
+        <v>0.00915347879014889</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05895544842149842</v>
+        <v>-0.05953211276586588</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3044828059471981</v>
+        <v>0.3045596561609127</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2656171098.188821</v>
+        <v>2697221653.592152</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>147.365</v>
+        <v>147.51</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.0393187599820024</v>
+        <v>0.04034139914460799</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1188938714499252</v>
+        <v>-0.1180269058295965</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,31 +2984,31 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>350317395001</v>
+        <v>350662090297</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.83185185185185</v>
+        <v>21.85333333333333</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.85576133518469</v>
+        <v>20.87628239102293</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.02515620692389</v>
+        <v>4.029116765063425</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.573101443538142</v>
+        <v>6.57956905599234</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.83382433862456</v>
+        <v>20.85432380952403</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.66262327096076</v>
+        <v>17.67884117328503</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.313372035584613</v>
+        <v>4.317332593724148</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04542452138282935</v>
+        <v>0.04537986979579737</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
@@ -3017,7 +3017,7 @@
         <v>0.04680196042617957</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02551447528784889</v>
+        <v>0.02551447528784867</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02911546160893021</v>
+        <v>0.02908684157006305</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04448251122201943</v>
+        <v>-0.04359774690612261</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1480432964863611</v>
+        <v>0.1482119462395578</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1258200044.263561</v>
+        <v>1278594925.52955</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>303.21</v>
+        <v>302.51</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1232144075581791</v>
+        <v>-0.1252385819413104</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2804527872042526</v>
+        <v>-0.2821139561926007</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>421.39</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>302335845570</v>
+        <v>301637863670</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.17388268156424</v>
+        <v>21.125</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.20560793750329</v>
+        <v>20.1589606450121</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.787108369804228</v>
+        <v>1.782982596053814</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.13749413251489</v>
+        <v>18.09562135162785</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.263134175652882</v>
+        <v>-7.246366279069798</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.17114135772528</v>
+        <v>15.14195541166632</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.144617709190429</v>
+        <v>2.140491935440015</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.04994776577527476</v>
+        <v>0.0500633435612742</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.0479210893854749</v>
+        <v>0.04792108938547468</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03063883117311434</v>
+        <v>0.03070972860401309</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7093849318460014</v>
+        <v>0.7075997509067974</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2380817993557553</v>
+        <v>0.237857828174506</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1211648190.059794</v>
+        <v>1233270114.127983</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>546.535</v>
+        <v>545.09</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.44567502132079</v>
+        <v>1.439208829026045</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.06532074632736484</v>
+        <v>-0.06779197236331291</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,31 +3236,31 @@
         <v>149.85</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>891179971000</v>
+        <v>888823754000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>138.7144670050761</v>
+        <v>138.3477157360406</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>40.20132953655372</v>
+        <v>40.0950400561356</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>21.57559547270306</v>
+        <v>21.51855111971916</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13.2601241372129</v>
+        <v>13.22506530405808</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.119896614352908</v>
+        <v>1.116935686676291</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>83.06555271505879</v>
+        <v>82.85256148535174</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>21.55420878828229</v>
+        <v>21.49894090303837</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009429848299383137</v>
+        <v>0.009454067763359979</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.548186334181218</v>
+        <v>2.546665325354219</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.682402427557137</v>
+        <v>0.6809501234510832</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9269972996.466349</v>
+        <v>9447557508.112457</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1623.95496</v>
+        <v>1629.67</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3954140122005276</v>
+        <v>0.4003247684054205</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1880062801256025</v>
+        <v>-0.1851487029740595</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>916.03</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>625901456637</v>
+        <v>628104137393</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>51.45137880986938</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>33.30223669746454</v>
+        <v>33.41943429191968</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.47017794177341</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5449826772081832</v>
+        <v>0.5395646245965797</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2948424637264908</v>
+        <v>0.2903016170625285</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.0047907732613471</v>
+        <v>0.004773972644768572</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.681175418945564</v>
+        <v>1.682070708349278</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4372238262997493</v>
+        <v>0.4380536520947686</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2039151793.483989</v>
+        <v>2063913814.663717</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>198.27</v>
+        <v>197</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1295166339689431</v>
+        <v>-0.1350924340136269</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2204835856103794</v>
+        <v>-0.2254767053273049</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,31 +3490,31 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>156706659900</v>
+        <v>155702890000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>74.25842696629211</v>
+        <v>73.78277153558049</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>77.57571099451117</v>
+        <v>77.078807010232</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.667180806425874</v>
+        <v>1.656501835204</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>25.71154880942951</v>
+        <v>25.54685588065574</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3974365726088218</v>
+        <v>0.3948908296965647</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>28.10901581294964</v>
+        <v>27.96458848920863</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.078383529974999</v>
+        <v>2.067704558753125</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001340083440831477</v>
+        <v>-0.001348722557429731</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.230830162575411</v>
+        <v>1.225929111018157</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3457197602298659</v>
+        <v>0.3480121506438135</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1094168942.159407</v>
+        <v>1127466386.077801</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>953.71</v>
+        <v>951.47</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.04305835027252347</v>
+        <v>0.04060849580459247</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1735543635560099</v>
+        <v>-0.1754954548999558</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>281351125970</v>
+        <v>280690310290</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.5294028031688</v>
+        <v>14.49527726995734</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.16474205676504</v>
+        <v>13.13382173275968</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.385605246614718</v>
+        <v>2.380002122234752</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.331788393540923</v>
+        <v>2.326311670007006</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3405490692683626</v>
+        <v>0.3397492140553931</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.62883846621859</v>
+        <v>26.6077886882426</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.088183741913055</v>
+        <v>7.08258061753309</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1475558338601662</v>
+        <v>-0.1479032174538126</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3649,7 +3649,7 @@
         <v>0.1036602723030562</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3821998793565313</v>
+        <v>-0.3821998793565314</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01887366180495119</v>
+        <v>0.01891809515801864</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.579440428962867</v>
+        <v>1.577549927393038</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3198695550496338</v>
+        <v>0.3190602947673415</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1879039745.070729</v>
+        <v>1924642858.382861</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>238.49</v>
+        <v>237.75</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1818524871355059</v>
+        <v>-0.1843910806174958</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2826505444263971</v>
+        <v>-0.2848763761053961</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,31 +3742,31 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>224689537660</v>
+        <v>223992358500</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.82882096069869</v>
+        <v>20.76419213973799</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.48004651386195</v>
+        <v>18.42270560053117</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.251798741768818</v>
+        <v>3.241708880269766</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.506349442702892</v>
+        <v>6.486161180773251</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2539017128736333</v>
+        <v>0.2531138925561086</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>17.43354525984834</v>
+        <v>17.39056522409223</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.092645667105663</v>
+        <v>4.082555805606611</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06066593105294656</v>
+        <v>0.06085475456074543</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02826114302486477</v>
+        <v>0.02834910620399579</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9034871930437464</v>
+        <v>0.9011723088955274</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3287470236030156</v>
+        <v>0.3287473900314055</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1164357580.35532</v>
+        <v>1191876703.17749</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1146.53</v>
+        <v>1152.13</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06124811687365939</v>
+        <v>0.06643157431000435</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1130391057130702</v>
+        <v>-0.1087069198932425</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,31 +3868,31 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1079734308730</v>
+        <v>1085008058330</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.35831381733021</v>
+        <v>38.5456674473068</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.21360011160107</v>
+        <v>26.34163527912828</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.55329776051957</v>
+        <v>13.61949617439353</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.20051866938221</v>
+        <v>30.34802715546504</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4054946319574618</v>
+        <v>0.407475190633608</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.99601680945299</v>
+        <v>26.11779891212983</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.13093584361169</v>
+        <v>14.19713425748565</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01857299507652739</v>
+        <v>0.01848271987110044</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.00583499777589771</v>
+        <v>0.005806636403878035</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3477140061425717</v>
+        <v>0.3510644524708125</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.317363421515186</v>
+        <v>0.3183724314684314</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2804321115.502555</v>
+        <v>2849968516.693994</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>203.665</v>
+        <v>203.46</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1196536934239902</v>
+        <v>0.1185267005329589</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1230785791173304</v>
+        <v>-0.1239612486544671</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,31 +3994,31 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>321236731200</v>
+        <v>320913388800</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.3717845659164</v>
+        <v>16.35530546623794</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.12746895342499</v>
+        <v>15.11224232570077</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.538838773719859</v>
+        <v>2.53628329315809</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.897721501218109</v>
+        <v>2.894804785494987</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4165243195830013</v>
+        <v>0.4161050649957403</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.36452554605241</v>
+        <v>23.35350764302995</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.419142893723969</v>
+        <v>5.4165874131622</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04882380648505366</v>
+        <v>-0.04887299984163204</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
@@ -4027,7 +4027,7 @@
         <v>0.08225537373915337</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3271714729502154</v>
+        <v>-0.3271714729502155</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02037659882650431</v>
+        <v>0.02039712965693502</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.375540724718137</v>
+        <v>1.374613089101811</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2601551734066707</v>
+        <v>0.2600437713250752</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>888555485.0855372</v>
+        <v>905752149.6856415</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>974.8150000000001</v>
+        <v>977.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.090529955301454</v>
+        <v>2.099042414516776</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2232549800796813</v>
+        <v>-0.2211155378486056</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1100946315607</v>
+        <v>1103978725000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>21.75440749832627</v>
+        <v>21.81432715911627</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.236515374424437</v>
+        <v>6.253693037653182</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.19560798908877</v>
+        <v>12.22919916033409</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.9168750248203</v>
+        <v>10.94694412453834</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.0310064094634482</v>
+        <v>0.03109181254958183</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.8360008721359</v>
+        <v>15.8803693705557</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>11.98935812755611</v>
+        <v>12.02294929880143</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02377227629448056</v>
+        <v>0.02370697859236372</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005436929058334146</v>
+        <v>0.0005421994884910487</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.884542665404855</v>
+        <v>2.885038377702729</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8200068926288235</v>
+        <v>0.8210021951492738</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25333319844.34505</v>
+        <v>25563845399.48759</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>138.5</v>
+        <v>138.47</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0606985224379748</v>
+        <v>-0.06090198124177881</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2887441841356573</v>
+        <v>-0.2888982467672524</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>143189887000</v>
+        <v>143158871140</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>86.0248447204969</v>
+        <v>86.00621118012423</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>29.18920694825824</v>
+        <v>29.18288437635609</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.719650217214229</v>
+        <v>9.717544877816998</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.43100830936401</v>
+        <v>11.42853227868329</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>137.639751552798</v>
+        <v>137.6099378882017</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>42.73685078876468</v>
+        <v>42.73685042705646</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.12142766779799</v>
+        <v>10.12142758213413</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03199242857361326</v>
+        <v>0.03199242885563871</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.6972145438428565</v>
+        <v>0.6967141468686718</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6303052912251551</v>
+        <v>0.6303167794631368</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2170793667.364769</v>
+        <v>2189840012.617457</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.64</v>
+        <v>27.635</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09769657128711651</v>
+        <v>0.09749800099563899</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05374871619308452</v>
+        <v>-0.05391989044847656</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157532521600</v>
+        <v>157504024400</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.52219873150106</v>
+        <v>36.51559196617337</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.468459904588041</v>
+        <v>9.466747086226141</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.473193318261743</v>
+        <v>2.472745924390856</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.849047540791173</v>
+        <v>1.848713053175255</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6108580141817435</v>
+        <v>-0.6107475116466164</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.40736070975919</v>
+        <v>17.4051033269962</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.449989349409696</v>
+        <v>3.449541955538809</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06973798101128091</v>
+        <v>0.06975059870279733</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06222865412445731</v>
+        <v>0.06223991315360955</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.349631624305318</v>
+        <v>0.3497169902670222</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2053625253746116</v>
+        <v>0.205383182098487</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>932464647.3902593</v>
+        <v>948904358.3716139</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>183.535</v>
+        <v>182.99</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.09240524969204955</v>
+        <v>0.08916139505352216</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.08172812328013213</v>
+        <v>-0.08445489568219344</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1302832174197</v>
+        <v>1298963465041</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>7.624400949288165</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.00380811058614118</v>
+        <v>0.003796802550783091</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.548040163611034</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2001.14798830569</v>
+        <v>2007.110995320426</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2591.082068538258</v>
+        <v>2598.802079070919</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.63456561418803</v>
+        <v>1.639433848844199</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9187612099390212</v>
+        <v>0.9179194720631826</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3163546625.817719</v>
+        <v>3195371538.874002</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>561.29773</v>
+        <v>560.61</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5036103625893884</v>
+        <v>0.5017680641096429</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.164524165339446</v>
+        <v>-0.1655478320408437</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>312.6</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>70746385676</v>
+        <v>70659703736</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.82676342947018</v>
+        <v>1.825747298502964</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4071132574526208</v>
+        <v>0.4065995578440564</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3744147858.759835</v>
+        <v>3788770992.865133</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>154.89</v>
+        <v>154.81</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.03765142630099561</v>
+        <v>-0.03814847508333075</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3135525616025527</v>
+        <v>-0.3139071086686757</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2025320790331</v>
+        <v>2040671353285</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-100.5779220779221</v>
+        <v>-100.525974025974</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>124.567257904594</v>
+        <v>124.5029194667842</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>122.1912995674812</v>
+        <v>123.1174270458522</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.139179400113186</v>
+        <v>7.135492045526002</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-1.005779220779221</v>
+        <v>-1.00525974025974</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>473.0412282963763</v>
+        <v>476.7250667830574</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>118.923849068537</v>
+        <v>119.84997606546</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01403382615914631</v>
+        <v>-0.0139282594202372</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.358091173596664</v>
+        <v>3.352311236959702</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.776198118854627</v>
+        <v>0.7761116655888158</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>13896094518.47412</v>
+        <v>14014369031.58549</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>762.43103</v>
+        <v>762.6</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1160195106234159</v>
+        <v>0.1162668429187845</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02173418273733918</v>
+        <v>-0.02151737942184073</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>812170678136</v>
+        <v>812350671148</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9951091276731021</v>
+        <v>0.9950494992563612</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1158705180333158</v>
+        <v>0.1159911935350224</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29250954842.76344</v>
+        <v>29967795305.13551</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>429.1</v>
+        <v>430.26</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3425738233053057</v>
+        <v>0.3462032468313698</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1041753653444676</v>
+        <v>-0.1017536534446765</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>257.98</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2225518568000</v>
+        <v>2231534884800</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>28.10942390170396</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6535983888898096</v>
+        <v>0.6553652826933801</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.16195998101111</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.00718052480227</v>
+        <v>41.89123126294021</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>41.98106987613143</v>
+        <v>41.86519100973364</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2796550920531344</v>
+        <v>0.2789011295495747</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.179889478439435</v>
+        <v>2.181320079760245</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3609925705957042</v>
+        <v>0.3622360240570155</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>3980882961.413702</v>
+        <v>4090305043.943522</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.245</v>
+        <v>28.24</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.009294992169567862</v>
+        <v>-0.009470369228840481</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.0585</v>
+        <v>-0.05866666666666676</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70814076148</v>
+        <v>70801540464</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.24015748031496</v>
+        <v>-22.23622047244094</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-84.29629437024705</v>
+        <v>-84.28137203100643</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.960794023203655</v>
+        <v>1.960446918565693</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.159790334368719</v>
+        <v>2.159408002923442</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.165508148690716</v>
+        <v>0.1654788500274675</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.44100432198347</v>
+        <v>16.43893230809917</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.754203963671605</v>
+        <v>2.753856859033643</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03078483994402248</v>
+        <v>0.03079029051788005</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2312502859610314</v>
+        <v>0.2312026372878777</v>
       </c>
       <c r="AJ37" s="4" t="n">
         <v>0.1566866355788266</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>496552008.7515242</v>
+        <v>512930202.3334476</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>313.70999</v>
+        <v>311.481</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1583452344772233</v>
+        <v>-0.1643254076167608</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1904049394823092</v>
+        <v>-0.1961573201889081</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>211851494330</v>
+        <v>210346234110</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.02425651910249</v>
+        <v>18.88908429351122</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.13327489823848</v>
+        <v>16.0186438391019</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.519851728022076</v>
+        <v>2.501947523104921</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.204649160443408</v>
+        <v>6.160563535589265</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.179670054896314</v>
+        <v>1.171288196366201</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.127062543682252</v>
+        <v>9.06617999150623</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.684066160717472</v>
+        <v>2.666161955800316</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07104977025346622</v>
+        <v>0.07155821003255326</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01128430752237122</v>
+        <v>0.01136505918499042</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9651603561422685</v>
+        <v>0.9595618726755274</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2350733092245474</v>
+        <v>0.2344650763840535</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>785765946.8164337</v>
+        <v>809555341.3908346</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>149.44901</v>
+        <v>150.58</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2363752241933235</v>
+        <v>-0.2305963168242509</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.546436995447648</v>
+        <v>-0.5430045523520486</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>430483375798</v>
+        <v>433741172600</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>23.06311882716049</v>
+        <v>23.23765432098766</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.62264895989479</v>
+        <v>16.7484447061975</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.997511400560068</v>
+        <v>6.042899154325202</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.638497628646737</v>
+        <v>6.688735997124543</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.5019619980029051</v>
+        <v>0.5057607116920845</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.58232703600212</v>
+        <v>14.66869492576882</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.663253908605821</v>
+        <v>7.708641662370955</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.0667157005697627</v>
+        <v>-0.06621460404102758</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01338249079067168</v>
+        <v>0.01328197635808208</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.07737510177524</v>
+        <v>2.082813057538501</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5608270808254086</v>
+        <v>0.5644318004989367</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4127660367.047246</v>
+        <v>4173676568.913514</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>110.23</v>
+        <v>110.24</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4496317552975078</v>
+        <v>0.4497632650276444</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1544833934187313</v>
+        <v>-0.1544066886553656</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,31 +5422,31 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>434464343123</v>
+        <v>434503757470</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>32.80654761904762</v>
+        <v>32.80952380952381</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.24749346571695</v>
+        <v>21.24942102567937</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.860866058002369</v>
+        <v>6.861488471693645</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.665391070895895</v>
+        <v>8.666177190016905</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.049809523809524</v>
+        <v>1.049904761904762</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.81729072995654</v>
+        <v>22.81925957690194</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.21325453016976</v>
+        <v>7.213876943861035</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.03129140564741617</v>
+        <v>0.03128856716719799</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
@@ -5455,7 +5455,7 @@
         <v>0.5440196591650359</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.1662824832486467</v>
+        <v>0.1662824832486469</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0.1023396098336123</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01505942121019686</v>
+        <v>0.01505805515239477</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7105825519708762</v>
+        <v>0.7104760944116318</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3352803823404072</v>
+        <v>0.3352034490599405</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>1969008784.983871</v>
+        <v>2004914121.130584</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>87.19</v>
+        <v>86.88500000000001</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.08413862610307665</v>
+        <v>-0.08734240771838298</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1081219312602292</v>
+        <v>-0.1112418166939444</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,31 +5548,31 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>263662560000</v>
+        <v>262740240000</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.43794579172611</v>
+        <v>12.3944365192582</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.20972662748918</v>
+        <v>11.170513797791</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.042233530846985</v>
+        <v>2.035089578250261</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.475588772684389</v>
+        <v>1.47042700441201</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.6611160375782359</v>
+        <v>0.6588033825551672</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.67796202951918</v>
+        <v>15.65012344933748</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>4.023287711552612</v>
+        <v>4.016143758955889</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.07270656857765471</v>
+        <v>0.07296179679214726</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
@@ -5581,7 +5581,7 @@
         <v>0.1095672718034899</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>-0.2903031514796547</v>
+        <v>-0.2903031514796548</v>
       </c>
       <c r="W41" s="4" t="n">
         <v>0.009923315255755299</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02121802959054938</v>
+        <v>0.02129251309201818</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.7300958564413106</v>
+        <v>0.7275824742256217</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.2269026607212093</v>
+        <v>0.226931730102077</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1079104012.065905</v>
+        <v>1098841160.247248</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:43 ET</t>
+          <t>2026-09-17 17:39 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -442,11 +442,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -470,7 +470,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -699,55 +699,55 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>337</v>
+        <v>334.95001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2434965051344211</v>
+        <v>0.2359322457855768</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.02196941115012918</v>
+        <v>-0.02791882636329335</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>236.65</v>
+        <v>240.21</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4949638972000</v>
+        <v>4919530071489</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.4703196347032</v>
+        <v>38.23630251141553</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>35.18762581031591</v>
+        <v>34.96592892165118</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.60281728192484</v>
+        <v>10.53831981605234</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>46.05075851004465</v>
+        <v>45.77062914969449</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.175481988838152</v>
+        <v>1.168331465626584</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.64283069216433</v>
+        <v>29.464128007603</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.69870587353237</v>
+        <v>10.63420840765986</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02761474135249313</v>
+        <v>0.02778375129611313</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09329114280352813</v>
+        <v>0.09353029336335772</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1193167545241032</v>
+        <v>0.1195887273062486</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.00314540059347181</v>
+        <v>0.003164651346032203</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3103413413725857</v>
+        <v>0.3106259292367567</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2917215924056524</v>
+        <v>0.2921115474887587</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13105224218.6762</v>
+        <v>12853530533.36324</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>497.75</v>
+        <v>493.99</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.05245908028612467</v>
+        <v>0.04450881179415922</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1010799682149823</v>
+        <v>-0.1078704038142021</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3696067512500</v>
+        <v>3668147444500</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.65277777777778</v>
+        <v>27.44388888888889</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.22963174265876</v>
+        <v>24.03453471715925</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.13813479578953</v>
+        <v>11.05399740386151</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.35871024691051</v>
+        <v>8.29556860848081</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8783446120134039</v>
+        <v>0.8717096029904599</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.33056641801474</v>
+        <v>18.19602419296546</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.46321201697209</v>
+        <v>11.37907462504407</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01812385725462313</v>
+        <v>0.01826180681489233</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.141279325722983</v>
+        <v>0.141852305936073</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2267520769688407</v>
+        <v>0.2273810125949838</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007312908086388749</v>
+        <v>0.007368570213971943</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5589055542321191</v>
+        <v>0.5592294162324398</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4345471733432665</v>
+        <v>0.4337751090459382</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10974084804.75201</v>
+        <v>10519018361.31958</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>347.33</v>
+        <v>350.89</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1021101276431742</v>
+        <v>0.113406336016795</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1499718558038228</v>
+        <v>-0.1412593915958984</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4203426312966</v>
+        <v>4246509829145</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.06454816285998</v>
+        <v>17.21896722939424</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.83345624111356</v>
+        <v>21.06602106299623</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.354530183290496</v>
+        <v>9.439180406958592</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.52019685236073</v>
+        <v>6.579198866475145</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1517560193094865</v>
+        <v>0.1531292770493972</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.03787023753176</v>
+        <v>13.15426507823563</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.482023645451774</v>
+        <v>9.566673869119869</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01277264429159752</v>
+        <v>0.01265809968608074</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1809065204848667</v>
+        <v>-0.1826189113785507</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2907002362377471</v>
+        <v>0.2898682348804311</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002476031439841073</v>
+        <v>0.002450910541765226</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7641258961441091</v>
+        <v>0.76361573303143</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3634733575263296</v>
+        <v>0.3627388231963615</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>7900376292.188757</v>
+        <v>7828933134.829708</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>251.19</v>
+        <v>253.1237</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1090066225165562</v>
+        <v>0.1175439293598235</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1253830083565459</v>
+        <v>-0.1186500696378829</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2702075949000</v>
+        <v>2722876953270</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>19.93571428571428</v>
+        <v>20.08918253968254</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.35795980225655</v>
+        <v>22.54192257048372</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.483493127320545</v>
+        <v>3.510309603534963</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.89793633298285</v>
+        <v>4.935641414742032</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.225668237853517</v>
+        <v>0.2274054673273709</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.20916762402706</v>
+        <v>11.2900585833691</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.670450377733086</v>
+        <v>3.696938183271453</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004302247686376931</v>
+        <v>-0.004269781099727464</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1083392911502502</v>
+        <v>-0.1088079343335507</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1795688947640286</v>
+        <v>0.179997197688706</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8377679948319768</v>
+        <v>0.8370649725470469</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4627757144334783</v>
+        <v>0.4624436850486459</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8395580226.45627</v>
+        <v>8302822149.937873</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>219.34</v>
+        <v>219.838</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1614508494099369</v>
+        <v>0.1640878628274902</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07271497421154982</v>
+        <v>-0.07060962205123866</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5312634140000</v>
+        <v>5324696198000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.58993710691823</v>
+        <v>27.65157232704402</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.36110053732391</v>
+        <v>16.37668653244966</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.53524004106031</v>
+        <v>17.57441332281521</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.17120235474967</v>
+        <v>23.22296623344862</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2214702434432892</v>
+        <v>0.2219650023531425</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.80617776579491</v>
+        <v>22.85696923399539</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.58942710310296</v>
+        <v>17.62860038485786</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.0239064081307131</v>
+        <v>0.02385312086335173</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6863130352373563</v>
+        <v>0.6884717352471565</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9412154432375359</v>
+        <v>0.9436640378699037</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002370748609464758</v>
+        <v>0.002365378142086445</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.329235799282248</v>
+        <v>1.327430813333441</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4134708612908174</v>
+        <v>0.411076577822255</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26440839904.5858</v>
+        <v>25969098564.80347</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>682.3099999999999</v>
+        <v>673.4400000000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04904602969299798</v>
+        <v>0.03540847743174313</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.137190187152251</v>
+        <v>-0.1484066767830045</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1738175561577</v>
+        <v>1715579355701</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>25.35525826830175</v>
+        <v>25.02564102564103</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.64134416151976</v>
+        <v>20.3688613331893</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.615293722516737</v>
+        <v>7.516295238954997</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.642323281818843</v>
+        <v>6.555973371206757</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.197827945001853</v>
+        <v>-5.130256410256407</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>17.1382953673883</v>
+        <v>16.92904264896518</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>8.039639171326803</v>
+        <v>7.94147792975185</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02357414343279777</v>
+        <v>0.02388198251828632</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2283724388244937</v>
+        <v>0.2286224848938367</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.273007539505155</v>
+        <v>0.2736216805247405</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.00307777989476924</v>
+        <v>0.00311831789023521</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7735940337248534</v>
+        <v>0.7735635086953959</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4090935415337825</v>
+        <v>0.4104482514708787</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10205541163.94253</v>
+        <v>10189928339.75648</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>366.2</v>
+        <v>363.0901</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1640605522464523</v>
+        <v>-0.1711596458799006</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2658821642643786</v>
+        <v>-0.2721165527333961</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1446324255683</v>
+        <v>1434041558242</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>310.3389830508475</v>
+        <v>307.6737288135594</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>174.050086912407</v>
+        <v>172.4382954336029</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.9580989556259</v>
+        <v>13.83822396596184</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.64744065025674</v>
+        <v>13.53023365723365</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.261136309381712</v>
+        <v>-8.190187992360942</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>119.7578363554207</v>
+        <v>118.7251354447123</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.90138155823739</v>
+        <v>13.78150656857333</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.00398389225469983</v>
+        <v>0.004018403117078524</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7830441142326448</v>
+        <v>0.7842540605026374</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1228443872713618</v>
+        <v>0.1231118120551531</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.535289737654368</v>
+        <v>1.536474236973029</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5703197237714112</v>
+        <v>0.5671256769133135</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12967035666.74941</v>
+        <v>12961748241.16383</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>347.3</v>
+        <v>357.54</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.0009205313896849532</v>
+        <v>0.02853692256530982</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2983838383838383</v>
+        <v>-0.2776969696969697</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1652307534000</v>
+        <v>1701025153200</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>43.0893300248139</v>
+        <v>44.35980148883375</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>18.98304566761365</v>
+        <v>19.52060367684623</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.54358428353385</v>
+        <v>19.0903343643383</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.60378974821948</v>
+        <v>17.09334577189287</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4287601650983955</v>
+        <v>0.4414019851116623</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>32.29343003654593</v>
+        <v>33.22559273673536</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>18.9413666502065</v>
+        <v>19.48811673101095</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02384725554365232</v>
+        <v>0.02316426651650291</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.269884968897651</v>
+        <v>1.272460535708215</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8555944161078508</v>
+        <v>0.857683211380821</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007313561762165275</v>
+        <v>0.007104100240532527</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.603180456370468</v>
+        <v>1.600346910029839</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3900005977275804</v>
+        <v>0.393113595417772</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8661789348.470654</v>
+        <v>8637120849.128256</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>893.9299999999999</v>
+        <v>895.3049999999999</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04614394382679921</v>
+        <v>0.04775307197191325</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1847423620611035</v>
+        <v>-0.1834883720930233</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>396439182470</v>
+        <v>397048966095</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>44.89854344550477</v>
+        <v>44.96760421898543</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.43587286714187</v>
+        <v>39.49653122427534</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.350329484854575</v>
+        <v>1.352406496524029</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.84267174162165</v>
+        <v>11.86088756796681</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.541773494116385</v>
+        <v>3.547221279238721</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.65688890601244</v>
+        <v>26.70176088970284</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.31383604338748</v>
+        <v>1.316047645413455</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02221273877403978</v>
+        <v>0.02217641770508916</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006197353260322397</v>
+        <v>0.006187835430384059</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1847808843101222</v>
+        <v>-0.1839456753916672</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1768386631306476</v>
+        <v>0.1763109668287718</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1731346165.996574</v>
+        <v>1695283023.777081</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>75.31</v>
+        <v>71.845</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1723266098681051</v>
+        <v>-0.2104077185762052</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3968444658016979</v>
+        <v>-0.4245955470126542</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>313586321325</v>
+        <v>299158274311</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>23.31578947368421</v>
+        <v>22.24303405572756</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>20.07660811471651</v>
+        <v>19.14987640120978</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.482972262439353</v>
+        <v>6.18469194141734</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.46351369153914</v>
+        <v>9.982089246695383</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6852567394094996</v>
+        <v>0.6537281960280905</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.41919140424638</v>
+        <v>9.948321237107983</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.590683482382044</v>
+        <v>6.292833475361275</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03506086602739671</v>
+        <v>0.03674925289529826</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1613410662029773</v>
+        <v>0.1615236354383141</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1440833291150601</v>
+        <v>0.1444115006001652</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.0926744441018264</v>
+        <v>0.09495447893104303</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3326241973936346</v>
+        <v>0.3523153787817147</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2155970177.13188</v>
+        <v>2171170761.703859</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>509.2</v>
+        <v>507.81</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02485658396854551</v>
+        <v>0.02205895896517496</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05307397627106036</v>
+        <v>-0.05565886859820735</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1098269850574</v>
+        <v>1095271824077</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.80563770215411</v>
+        <v>12.76808939621049</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.95448509263613</v>
+        <v>22.89179783164884</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.856065167359437</v>
+        <v>2.84769069892666</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.46233756812059</v>
+        <v>1.458049745859977</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3527627078098621</v>
+        <v>0.3517283476017706</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.51941005614659</v>
+        <v>15.47730600802468</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.086800804383824</v>
+        <v>3.078426335951046</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02203986097236272</v>
+        <v>0.02210467563781969</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4421291677650311</v>
+        <v>-0.44224173697017</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06114910458549239</v>
+        <v>0.06097915463345482</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.03887823087399517</v>
+        <v>0.03939255501932271</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1493477437764856</v>
+        <v>0.1492536220272904</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2144255896.806022</v>
+        <v>2108237113.600871</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>349.31</v>
+        <v>347</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07321490785703855</v>
+        <v>0.06611769782254262</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04690313778990451</v>
+        <v>-0.05320600272851295</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>935979638100</v>
+        <v>929789970000</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.01762682717111</v>
+        <v>14.9183147033534</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.94781859378952</v>
+        <v>13.85497449975836</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.144744158409853</v>
+        <v>3.123947848524861</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.600443133705999</v>
+        <v>2.583246306707457</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7863116673851259</v>
+        <v>0.7811117591326865</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.00901286066982</v>
+        <v>19.94257159725204</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.262879580221279</v>
+        <v>6.242083270336287</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.173651213534877</v>
+        <v>-0.1748072201725299</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07670075619265249</v>
+        <v>0.07674790044641289</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2892987416862425</v>
+        <v>-0.2892465869116644</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01717671981907188</v>
+        <v>0.01729106628242075</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7660134893613323</v>
+        <v>0.7674338664160787</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1705710040290456</v>
+        <v>0.1654414159399357</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2128423294.955566</v>
+        <v>2096482695.002885</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>369.93</v>
+        <v>369.98999</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06768064035473964</v>
+        <v>0.06785378165610689</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04056332183520495</v>
+        <v>-0.04040773400420161</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>690676774765</v>
+        <v>690788779365</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.42990654205607</v>
+        <v>31.43500339847068</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.7099341581381</v>
+        <v>24.70576767734846</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.52501291955134</v>
+        <v>15.52753055576785</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.12175019699812</v>
+        <v>20.12501325702115</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.119450934579441</v>
+        <v>2.119794637067926</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.13141022630421</v>
+        <v>24.13525944618187</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.78348711483996</v>
+        <v>15.78600475105647</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03042378253872745</v>
+        <v>0.0304188496219003</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2719542812583653</v>
+        <v>0.2723750910720311</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1384422594852113</v>
+        <v>0.1387483256465651</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007244613845862731</v>
+        <v>0.007243439207639105</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3041296675936401</v>
+        <v>0.3058432740746191</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1771115692814877</v>
+        <v>0.1736684649057387</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2252382337.061794</v>
+        <v>2215551708.526697</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -2339,55 +2339,55 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>565.73</v>
+        <v>567.24</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.004617042414084338</v>
+        <v>0.007298483621100527</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05965559655596553</v>
+        <v>-0.05653410508457668</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>601.62</v>
+        <v>601.23</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>496165576280</v>
+        <v>497489900640</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.06699615595826</v>
+        <v>31.1499176276771</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.49939987486871</v>
+        <v>25.55757834192488</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.14262110651883</v>
+        <v>14.18036942792806</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>88.92779540188916</v>
+        <v>89.16515416146855</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.373050276535655</v>
+        <v>1.376715109437514</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.03841455416893</v>
+        <v>23.09829538071984</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.52320429495767</v>
+        <v>14.5609526163669</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03315022401053865</v>
+        <v>0.03306197769812078</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.218342247598414</v>
+        <v>0.2188133480776031</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1575559517246576</v>
+        <v>0.1579228907806498</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005956905237480777</v>
+        <v>0.005941047880967492</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2909059922383178</v>
+        <v>0.2926366823843486</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1942915591974401</v>
+        <v>0.1892272728790046</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1508107121.504842</v>
+        <v>1466547292.951424</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>375.21</v>
+        <v>374.76999</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1153686290358795</v>
+        <v>0.1140606325793296</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.187188596681253</v>
+        <v>-0.188141783284953</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>340744861825</v>
+        <v>340345268310</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.12770882901421</v>
+        <v>24.09941418558293</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.25639274078736</v>
+        <v>17.23026590034443</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7569937991664611</v>
+        <v>0.7561060680604893</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.453016692941379</v>
+        <v>3.448967328918403</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7310758771820103</v>
+        <v>-0.7302185420984069</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>14.96284834161394</v>
+        <v>14.94733797733183</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8563941932757053</v>
+        <v>0.8555064621697335</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06930992260164802</v>
+        <v>0.06939129818748853</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3981895979908794</v>
+        <v>0.3986675728028772</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01048486257114667</v>
+        <v>0.01056282027615407</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.0241464779723355</v>
+        <v>0.02417482787242383</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4276747997915096</v>
+        <v>0.4282999180245435</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2271589811774222</v>
+        <v>0.2070963720507303</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1773592635.472208</v>
+        <v>1731751011.940075</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>163.3</v>
+        <v>163.265</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3314308843734017</v>
+        <v>0.3311455195175956</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.07431551499348099</v>
+        <v>-0.074513916444646</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>676790318000</v>
+        <v>676645261900</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.01673101673102</v>
+        <v>21.01222651222651</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.78285312053816</v>
+        <v>14.78298599456936</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.874453880241511</v>
+        <v>1.874052129562954</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.627765703986429</v>
+        <v>2.62720249639525</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.057888245388247</v>
+        <v>2.05744717932218</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.865232412112775</v>
+        <v>9.862924324399582</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.962472492106575</v>
+        <v>1.962013348473938</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04514396732253489</v>
+        <v>0.04515502795399944</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.421696532148587</v>
+        <v>0.4213790447982231</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08183150477592971</v>
+        <v>0.08167006657796794</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02522963870177587</v>
+        <v>0.02523504731571372</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5338359743767092</v>
+        <v>-0.5333224483281266</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2551697232515629</v>
+        <v>0.2502025527989721</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2239596334.706132</v>
+        <v>2208923240.115904</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>270.22</v>
+        <v>269.195</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3032070993289373</v>
+        <v>0.2982637669449086</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.03860248336713257</v>
+        <v>-0.04224926174974208</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>651202749972</v>
+        <v>648732604095</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.2393063583815</v>
+        <v>31.12080924855491</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.80215161758111</v>
+        <v>21.7136705641696</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.649743691572466</v>
+        <v>6.624519846980976</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.759868919984465</v>
+        <v>7.730434142236763</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.867919379373295</v>
+        <v>-3.853247566169766</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20.15346703344006</v>
+        <v>20.08023847073995</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.941934973011059</v>
+        <v>6.916711128419569</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02872837991056456</v>
+        <v>0.02883776748988619</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4328542845831023</v>
+        <v>0.4332357653020824</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.08979388535784305</v>
+        <v>0.09000526221088045</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01953963437199319</v>
+        <v>0.01961403443600364</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1659690344752618</v>
+        <v>-0.1651940988356478</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2041548623999825</v>
+        <v>0.2042261709506598</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1642467131.754413</v>
+        <v>1607087263.489426</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>106.79</v>
+        <v>107.22</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.05294432443356845</v>
+        <v>-0.04913091549552595</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2098993785143533</v>
+        <v>-0.2067179638946434</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>849843363200</v>
+        <v>853265337600</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.55234657039712</v>
+        <v>38.70938628158845</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.41663011326906</v>
+        <v>34.54795667197718</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.154929554250924</v>
+        <v>1.159634061752555</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.646426637350109</v>
+        <v>8.681647122294834</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.322658352477855</v>
+        <v>9.360633409911395</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.290631508672</v>
+        <v>21.37144022969724</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.239494133507284</v>
+        <v>1.244198641008915</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01589587044503497</v>
+        <v>0.01583138265166971</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1201662232332725</v>
+        <v>0.1204537116079782</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05119521528000814</v>
+        <v>0.05132784400687207</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.00915347879014889</v>
+        <v>0.009116769259466518</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05953211276586588</v>
+        <v>-0.05913344462291252</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3045596561609127</v>
+        <v>0.3024289948247972</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2697221653.592152</v>
+        <v>2648813132.931631</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>147.51</v>
+        <v>146.34</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.04034139914460799</v>
+        <v>0.03208975900496203</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1180269058295965</v>
+        <v>-0.1250224215246637</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,40 +2984,40 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>350662090297</v>
+        <v>347880755841</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.85333333333333</v>
+        <v>21.68</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.87628239102293</v>
+        <v>20.70734842384243</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.029116765063425</v>
+        <v>3.997159158022337</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.57956905599234</v>
+        <v>6.527382114120527</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.85432380952403</v>
+        <v>20.68891428571451</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.67884117328503</v>
+        <v>17.54686100268185</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.317332593724148</v>
+        <v>4.28510184473527</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04537986979579737</v>
+        <v>0.0457458114780605</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04680196042617957</v>
+        <v>0.04697132420091332</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02551447528784867</v>
+        <v>0.02559428074762593</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02908684157006305</v>
+        <v>0.02931939319393194</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04359774690612261</v>
+        <v>-0.04143308998853398</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1482119462395578</v>
+        <v>0.1486293926706055</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1278594925.52955</v>
+        <v>1250507529.617664</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -3095,46 +3095,46 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>302.51</v>
+        <v>301.09</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1252385819413104</v>
+        <v>-0.1293447642613771</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2821139561926007</v>
+        <v>-0.2806870849061112</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>421.39</v>
+        <v>418.58</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>301637863670</v>
+        <v>300221953878</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.125</v>
+        <v>21.02583798882681</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.1589606450121</v>
+        <v>20.06433328024427</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.782982596053814</v>
+        <v>1.774613147715988</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.09562135162785</v>
+        <v>18.01067942468556</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.246366279069798</v>
+        <v>-7.212351403144112</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.14195541166632</v>
+        <v>15.08274948266778</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.140491935440015</v>
+        <v>2.13212248710219</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.0500633435612742</v>
+        <v>0.05029945280462911</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03070972860401309</v>
+        <v>0.03085456175894251</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7075997509067974</v>
+        <v>0.7070411579141297</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.237857828174506</v>
+        <v>0.2378792183223306</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1233270114.127983</v>
+        <v>1227428075.027888</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -3221,55 +3221,55 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>545.09</v>
+        <v>543.03</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.439208829026045</v>
+        <v>1.429990589491667</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.06779197236331291</v>
+        <v>-0.07131496588168906</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>149.85</v>
+        <v>154.78</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>888823754000</v>
+        <v>885464718000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>138.3477157360406</v>
+        <v>137.8248730964467</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>40.0950400561356</v>
+        <v>39.87724253966871</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>21.51855111971916</v>
+        <v>21.43722837428883</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13.22506530405808</v>
+        <v>13.17508523741521</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.116935686676291</v>
+        <v>1.112714571787826</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>82.85256148535174</v>
+        <v>82.53916010449711</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>21.49894090303837</v>
+        <v>21.41761815760804</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009454067763359979</v>
+        <v>0.009489932042667791</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.450494513594326</v>
+        <v>2.456228774076907</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.9013639506361797</v>
+        <v>0.9038976624956678</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.546665325354219</v>
+        <v>2.546240113360414</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6809501234510832</v>
+        <v>0.653668679826144</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9447557508.112457</v>
+        <v>9227197779.396566</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -3347,55 +3347,55 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1629.67</v>
+        <v>1656.07</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4003247684054205</v>
+        <v>0.4230094676917195</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1851487029740595</v>
+        <v>-0.1719484389687794</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>916.03</v>
+        <v>925.87</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>628104137393</v>
+        <v>638279172355</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>51.45137880986938</v>
+        <v>52.16255370101596</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>33.41943429191968</v>
+        <v>33.93304611035687</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.47017794177341</v>
+        <v>15.68401088251362</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>25.03950443061753</v>
+        <v>25.38560724165421</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.502483379040117</v>
+        <v>3.55089565279154</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>39.25062198833714</v>
+        <v>39.79784812575609</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>15.33749094156111</v>
+        <v>15.55132388230132</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01830097778982211</v>
+        <v>0.01805146560008102</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5395646245965797</v>
+        <v>0.5372198986018875</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2903016170625285</v>
+        <v>0.2881019734108514</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004773972644768572</v>
+        <v>0.004697869051428986</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.682070708349278</v>
+        <v>1.681579670631043</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4380536520947686</v>
+        <v>0.4305795533260287</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2063913814.663717</v>
+        <v>2030263382.988037</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>197</v>
+        <v>196.385</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1350924340136269</v>
+        <v>-0.1377925261612494</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2254767053273049</v>
+        <v>-0.2278946333792019</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>155702890000</v>
+        <v>155216812450</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>73.78277153558049</v>
+        <v>73.55243445692881</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>77.078807010232</v>
+        <v>76.42957280766605</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.656501835204</v>
+        <v>1.651330522368211</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>25.54685588065574</v>
+        <v>25.46710300569836</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3948908296965647</v>
+        <v>0.3936580486799993</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>27.96458848920863</v>
+        <v>27.89464927338129</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.067704558753125</v>
+        <v>2.062533245917336</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001348722557429731</v>
+        <v>-0.001352946222031504</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.04276189010312492</v>
+        <v>-0.03764430762916227</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1542221199138396</v>
+        <v>0.1546467220498906</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.225929111018157</v>
+        <v>1.226012386886879</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3480121506438135</v>
+        <v>0.3439755139730449</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1127466386.077801</v>
+        <v>1092878111.053377</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>951.47</v>
+        <v>941.29</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.04060849580459247</v>
+        <v>0.0294747821958703</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1754954548999558</v>
+        <v>-0.1843170218112808</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>280690310290</v>
+        <v>277687139030</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.49527726995734</v>
+        <v>14.34018890920171</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.13382173275968</v>
+        <v>12.99177777803206</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.380002122234752</v>
+        <v>2.354537923043659</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.326311670007006</v>
+        <v>2.301421917518046</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3397492140553931</v>
+        <v>0.3361141577750228</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.6077886882426</v>
+        <v>26.51212496511961</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.08258061753309</v>
+        <v>7.057116418341995</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1479032174538126</v>
+        <v>-0.1495027826820417</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1036602723030562</v>
+        <v>0.1037895778551334</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3821998793565314</v>
+        <v>-0.3821570738151003</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01891809515801864</v>
+        <v>0.01912269332511766</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.577549927393038</v>
+        <v>1.57960728667643</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3190602947673415</v>
+        <v>0.3099646591195975</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1924642858.382861</v>
+        <v>1901801597.025374</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>237.75</v>
+        <v>229.87</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1843910806174958</v>
+        <v>-0.2114236706689536</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2848763761053961</v>
+        <v>-0.3085784756060879</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>223992358500</v>
+        <v>216568342580</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.76419213973799</v>
+        <v>20.07598253275109</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>18.42270560053117</v>
+        <v>17.80894327846084</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.241708880269766</v>
+        <v>3.134265490252833</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.486161180773251</v>
+        <v>6.271183472657611</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2531138925561086</v>
+        <v>0.2447246707965202</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>17.39056522409223</v>
+        <v>16.93288592441896</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>4.082555805606611</v>
+        <v>3.975112415589678</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06085475456074543</v>
+        <v>0.06294087047817125</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1270978644493628</v>
+        <v>0.127297797451696</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04621551567034698</v>
+        <v>0.04632303781771174</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02834910620399579</v>
+        <v>0.02932092052029408</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9011723088955274</v>
+        <v>0.9049354814923495</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3287473900314055</v>
+        <v>0.3390150801183113</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1191876703.17749</v>
+        <v>1184209801.843376</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1152.13</v>
+        <v>1146.73</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06643157431000435</v>
+        <v>0.06143324035352893</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1087069198932425</v>
+        <v>-0.1128843847909334</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,40 +3868,40 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1085008058330</v>
+        <v>1079922656930</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.5456674473068</v>
+        <v>38.36500501840081</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.34163527912828</v>
+        <v>26.20129058188018</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.61949617439353</v>
+        <v>13.5556619895865</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.34802715546504</v>
+        <v>30.20578682959945</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.407475190633608</v>
+        <v>0.4055653661958957</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>26.11779891212983</v>
+        <v>26.00036617026288</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.19713425748565</v>
+        <v>14.13330007267862</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01848271987110044</v>
+        <v>0.01856975577955661</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4632981984170268</v>
+        <v>0.4642410418108409</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2295582709788979</v>
+        <v>0.230024722751039</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877328985191485</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005806636403878035</v>
+        <v>0.005833980099936341</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3510644524708125</v>
+        <v>0.3509779977696696</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3183724314684314</v>
+        <v>0.312613469175804</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2849968516.693994</v>
+        <v>2748902137.458256</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>203.46</v>
+        <v>202.25</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1185267005329589</v>
+        <v>0.1118746937127244</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1239612486544671</v>
+        <v>-0.1291711517761034</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,40 +3994,40 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>320913388800</v>
+        <v>319004880000</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.35530546623794</v>
+        <v>16.258038585209</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.11224232570077</v>
+        <v>15.01994671915705</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.53628329315809</v>
+        <v>2.521199724964238</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.894804785494987</v>
+        <v>2.877589048787777</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4161050649957403</v>
+        <v>0.4136304403587362</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.35350764302995</v>
+        <v>23.28847514226327</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.4165874131622</v>
+        <v>5.401503844968348</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04887299984163204</v>
+        <v>-0.0491653920780146</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08225537373915337</v>
+        <v>0.08242984407347054</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3271714729502155</v>
+        <v>-0.3270721467871623</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02039712965693502</v>
+        <v>0.02051915945611867</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.374613089101811</v>
+        <v>1.376177867515408</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2600437713250752</v>
+        <v>0.2517194542518957</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>905752149.6856415</v>
+        <v>891502602.344251</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>977.5</v>
+        <v>991.1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.099042414516776</v>
+        <v>2.142159526370923</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2211155378486056</v>
+        <v>-0.2102788844621514</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1103978725000</v>
+        <v>1119338429000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>21.81432715911627</v>
+        <v>22.11604597188128</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.253693037653182</v>
+        <v>6.340700940785748</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.22919916033409</v>
+        <v>12.39834392912688</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>10.94694412453834</v>
+        <v>11.09835374448989</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03109181254958183</v>
+        <v>0.03152185032708219</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>15.8803693705557</v>
+        <v>16.1037822236561</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>12.02294929880143</v>
+        <v>12.19209406759421</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02370697859236372</v>
+        <v>0.02338355544523191</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.488231198393215</v>
+        <v>2.487949704365118</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.775779220960631</v>
+        <v>1.775555219220929</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005421994884910487</v>
+        <v>0.0005347593582887701</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.885038377702729</v>
+        <v>2.885542369802312</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.8210021951492738</v>
+        <v>0.7721368978843398</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25563845399.48759</v>
+        <v>24945013988.89314</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>138.47</v>
+        <v>136.73</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.06090198124177881</v>
+        <v>-0.07270259186241368</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2888982467672524</v>
+        <v>-0.297833879399772</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,40 +4246,40 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>143158871140</v>
+        <v>141359951260</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>86.00621118012423</v>
+        <v>84.92546583850933</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>29.18288437635609</v>
+        <v>28.80044437670449</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.717544877816998</v>
+        <v>9.595435192777627</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.42853227868329</v>
+        <v>11.28492249920102</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>137.6099378882017</v>
+        <v>135.8807453416178</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>42.73685042705646</v>
+        <v>42.22125286901691</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.12142758213413</v>
+        <v>9.999317897094761</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03199242885563871</v>
+        <v>0.03239955842638991</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.947145664936612</v>
+        <v>1.948755398621629</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2467566443070532</v>
+        <v>0.2473194666323242</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.6967141468686718</v>
+        <v>0.6997775735484316</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6303167794631368</v>
+        <v>0.6270241528624115</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2189840012.617457</v>
+        <v>2144377934.183103</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.635</v>
+        <v>27.45</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09749800099563899</v>
+        <v>0.09015090021097483</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05391989044847656</v>
+        <v>-0.06025333789798015</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157504024400</v>
+        <v>156449628000</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.51559196617337</v>
+        <v>36.27629492600423</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.466747086226141</v>
+        <v>9.404060528651197</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.472745924390856</v>
+        <v>2.45654126323474</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.848713053175255</v>
+        <v>1.836597911726729</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6107475116466164</v>
+        <v>-0.6067451098243185</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.4051033269962</v>
+        <v>17.32334064504119</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.449541955538809</v>
+        <v>3.433337294382693</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06975059870279733</v>
+        <v>0.0702107109892593</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.857248074082655</v>
+        <v>2.857513976593605</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05053296346494307</v>
+        <v>-0.05050491154177539</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06223991315360955</v>
+        <v>0.06265938069216757</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3497169902670222</v>
+        <v>0.3509371480600263</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.205383182098487</v>
+        <v>0.2061895175678352</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>948904358.3716139</v>
+        <v>912778413.2761378</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>182.99</v>
+        <v>183.41499</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.08916139505352216</v>
+        <v>0.0916909469486189</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.08445489568219344</v>
+        <v>-0.08232856356631824</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,40 +4498,40 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1298963465041</v>
+        <v>1301980300669</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>7.624400949288165</v>
+        <v>8.113760780990328</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003796802550783091</v>
+        <v>0.003802660961113973</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6.548040163611034</v>
+        <v>6.968315520817014</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>4.745108051239</v>
+        <v>5.049665129599325</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.0170624572815678</v>
+        <v>0.01815758347958247</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>7.701006660861996</v>
+        <v>8.197577490578496</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>6.517787859361772</v>
+        <v>6.938063216567753</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.0736127453621272</v>
+        <v>0.06917298904518683</v>
       </c>
       <c r="T32" s="4" t="n">
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2007.110995320426</v>
+        <v>2132.706071606614</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2598.802079070919</v>
+        <v>2762.495665002442</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.639433848844199</v>
+        <v>1.635635124479193</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.9179194720631826</v>
+        <v>0.8633465846030076</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3195371538.874002</v>
+        <v>3136792281.322672</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -4611,22 +4611,22 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>560.61</v>
+        <v>565.575</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5017680641096429</v>
+        <v>0.515068359213734</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1655478320408437</v>
+        <v>-0.1581575696232678</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>312.6</v>
+        <v>313.43</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>70659703736</v>
+        <v>71285496050</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.825747298502964</v>
+        <v>1.82540761846922</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4065995578440564</v>
+        <v>0.3919771357421525</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3788770992.865133</v>
+        <v>3700231626.092234</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>154.81</v>
+        <v>151.06</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.03814847508333075</v>
+        <v>-0.06144763675529974</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3139071086686757</v>
+        <v>-0.3305265023931927</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2040671353285</v>
+        <v>1991239646310</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-100.525974025974</v>
+        <v>-98.09090909090909</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>124.5029194667842</v>
+        <v>120.9805814591333</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>123.1174270458522</v>
+        <v>120.1351219493213</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.135492045526002</v>
+        <v>6.962647299251714</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-1.00525974025974</v>
+        <v>-0.980909090909091</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>476.7250667830574</v>
+        <v>465.2356919906408</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>119.84997606546</v>
+        <v>116.9615160497737</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.0139282594202372</v>
+        <v>-0.01426288111263989</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.225405483584371</v>
+        <v>4.235448666294758</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.352311236959702</v>
+        <v>3.360207879037847</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7761116655888158</v>
+        <v>0.777214118082028</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14014369031.58549</v>
+        <v>13243498224.01919</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>762.6</v>
+        <v>759.59</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1162668429187845</v>
+        <v>0.1118609116347751</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02151737942184073</v>
+        <v>-0.0253794731642224</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>812350671148</v>
+        <v>809144304087</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9950494992563612</v>
+        <v>0.9953050681130762</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1159911935350224</v>
+        <v>0.1148931228142449</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29967795305.13551</v>
+        <v>29752244927.56256</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -4899,55 +4899,55 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>430.26</v>
+        <v>431.545</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3462032468313698</v>
+        <v>0.3502237720305015</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1017536534446765</v>
+        <v>-0.09907098121085589</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>257.98</v>
+        <v>262.81</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2231534884800</v>
+        <v>2238199511600</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>28.10942390170396</v>
+        <v>28.51512692708937</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6553652826933801</v>
+        <v>0.6568678259280953</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>14.16195998101111</v>
+        <v>14.36635940341746</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>9.775283174489369</v>
+        <v>9.916369735770658</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.5280482367921029</v>
+        <v>0.535669551549927</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>18.63278794946157</v>
+        <v>18.9112426634564</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>13.67738056954049</v>
+        <v>13.88177999194684</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.01778563079232014</v>
+        <v>0.01753258319974648</v>
       </c>
       <c r="T36" s="4" t="n">
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>41.89123126294021</v>
+        <v>42.41075297271571</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>41.86519100973364</v>
+        <v>42.38729125771043</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2789011295495747</v>
+        <v>0.2780706531184465</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.181320079760245</v>
+        <v>2.181299131737951</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3622360240570155</v>
+        <v>0.3376196867388273</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4090305043.943522</v>
+        <v>3987349271.78236</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>28.24</v>
+        <v>27.945</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.009470369228840481</v>
+        <v>-0.01981761572591878</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.05866666666666676</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,38 +5042,38 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70801540464</v>
+        <v>70061934372</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.23622047244094</v>
+        <v>-22.00393700787401</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-84.28137203100643</v>
+        <v>-84.18468056003628</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.960446918565693</v>
+        <v>1.939967724546587</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.159408002923442</v>
+        <v>2.13685044765211</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1654788500274675</v>
+        <v>0.1637502288958067</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.43893230809917</v>
+        <v>16.31668336727273</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.753856859033643</v>
+        <v>2.733377665014537</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03079029051788005</v>
+        <v>0.03111532702515889</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02072773416995544</v>
+        <v>0.02080140915356021</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2312026372878777</v>
+        <v>0.2301265938031586</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1566866355788266</v>
+        <v>0.1595246601947214</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>512930202.3334476</v>
+        <v>500518907.9641965</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>311.481</v>
+        <v>310.065</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1643254076167608</v>
+        <v>-0.1681244040974922</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1961573201889081</v>
+        <v>-0.1998116080414979</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,40 +5170,40 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>210346234110</v>
+        <v>209389996799</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>18.88908429351122</v>
+        <v>18.80321406913281</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.0186438391019</v>
+        <v>15.94015843164978</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.501947523104921</v>
+        <v>2.490573630047697</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.160563535589265</v>
+        <v>6.132557467911319</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.171288196366201</v>
+        <v>1.165963492496447</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.06617999150623</v>
+        <v>9.027503510718331</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.666161955800316</v>
+        <v>2.654788062743092</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07155821003255326</v>
+        <v>0.07188500038255832</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1791937247148543</v>
+        <v>0.1796127466210324</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.006357550646380439</v>
+        <v>0.006590642898466115</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01136505918499042</v>
+        <v>0.01141696095979875</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9595618726755274</v>
+        <v>0.9625112973030167</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2344650763840535</v>
+        <v>0.2344689035074583</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>809555341.3908346</v>
+        <v>792471917.9137064</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>150.58</v>
+        <v>145.53</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2305963168242509</v>
+        <v>-0.2563998006868988</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5430045523520486</v>
+        <v>-0.5583308042488619</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,40 +5296,40 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>433741172600</v>
+        <v>419194799100</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>23.23765432098766</v>
+        <v>22.45833333333333</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.7484447061975</v>
+        <v>16.1725760427441</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>6.042899154325202</v>
+        <v>5.840238503977598</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.688735997124543</v>
+        <v>6.464415922841909</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.5057607116920845</v>
+        <v>0.4887990196078434</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.66869492576882</v>
+        <v>14.28305405885472</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.708641662370955</v>
+        <v>7.505981012023351</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06621460404102758</v>
+        <v>-0.06851230039509333</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3874514755623204</v>
+        <v>0.3886676602401486</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.4294717829481378</v>
+        <v>0.4310425747096076</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01328197635808208</v>
+        <v>0.01374287088572803</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.082813057538501</v>
+        <v>2.084383119342286</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5644318004989367</v>
+        <v>0.5630369937724207</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4173676568.913514</v>
+        <v>4128313146.163589</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>110.24</v>
+        <v>108.61</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4497632650276444</v>
+        <v>0.4283271790153527</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1544066886553656</v>
+        <v>-0.1669095650839918</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,40 +5422,40 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>434503757470</v>
+        <v>428079218966</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>32.80952380952381</v>
+        <v>32.32440476190476</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.24942102567937</v>
+        <v>20.93001124173748</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.861488471693645</v>
+        <v>6.760035040915911</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.666177190016905</v>
+        <v>8.538039773292235</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.049904761904762</v>
+        <v>1.034380952380952</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.81925957690194</v>
+        <v>22.49833752764873</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.213876943861035</v>
+        <v>7.112423513083301</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.03128856716719799</v>
+        <v>0.03175814054426168</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.5440196591650359</v>
+        <v>0.544404558056099</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.1662824832486469</v>
+        <v>0.166508857283745</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0.1023396098336123</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01505805515239477</v>
+        <v>0.01528404382653531</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7104760944116318</v>
+        <v>0.7115021341152543</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3352034490599405</v>
+        <v>0.3353961628243654</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>2004914121.130584</v>
+        <v>1975705326.379649</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>86.88500000000001</v>
+        <v>86.25</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.08734240771838298</v>
+        <v>-0.09401257599943069</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1112418166939444</v>
+        <v>-0.1177373158756138</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,40 +5548,40 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>262740240000</v>
+        <v>260820000000</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.3944365192582</v>
+        <v>12.30385164051355</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.170513797791</v>
+        <v>11.08621319741697</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.035089578250261</v>
+        <v>2.020216103171837</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.47042700441201</v>
+        <v>1.45968037210722</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.6588033825551672</v>
+        <v>0.653988510621893</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.65012344933748</v>
+        <v>15.59216443813951</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>4.016143758955889</v>
+        <v>4.001270283877464</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.07296179679214726</v>
+        <v>0.07349896480331262</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.1095672718034899</v>
+        <v>0.109833576300002</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>-0.2903031514796548</v>
+        <v>-0.2902196875898506</v>
       </c>
       <c r="W41" s="4" t="n">
         <v>0.009923315255755299</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02129251309201818</v>
+        <v>0.02144927536231884</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.7275824742256217</v>
+        <v>0.7295619626306802</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.226931730102077</v>
+        <v>0.2240177252206077</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1098841160.247248</v>
+        <v>1069867249.031316</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:39 ET</t>
+          <t>2026-09-18 11:30 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -446,7 +446,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -470,7 +470,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>334.95001</v>
+        <v>334.835</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2359322457855768</v>
+        <v>0.2355078703165692</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.02791882636329335</v>
+        <v>-0.02825260469570778</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,31 +714,31 @@
         <v>240.21</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4919530071489</v>
+        <v>4917840846260</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.23630251141553</v>
+        <v>38.22317351598173</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.96592892165118</v>
+        <v>34.95392285696923</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.53831981605234</v>
+        <v>10.53470125992078</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.77062914969449</v>
+        <v>45.754913132673</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.168331465626584</v>
+        <v>1.167930301877218</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.464128007603</v>
+        <v>29.4541020990468</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.63420840765986</v>
+        <v>10.63058985152831</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02778375129611313</v>
+        <v>0.02779329471468092</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003164651346032203</v>
+        <v>0.003165738348738931</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3106259292367567</v>
+        <v>0.3107188070342853</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2921115474887587</v>
+        <v>0.2921411097903008</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>12853530533.36324</v>
+        <v>12896900486.14602</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>493.99</v>
+        <v>493.7</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.04450881179415922</v>
+        <v>0.0438956261923853</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1078704038142021</v>
+        <v>-0.1083941342194612</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,31 +842,31 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3668147444500</v>
+        <v>3665994035000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.44388888888889</v>
+        <v>27.42777777777778</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.03453471715925</v>
+        <v>24.02042508929638</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.05399740386151</v>
+        <v>11.0475080837394</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.29556860848081</v>
+        <v>8.290698641687028</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8717096029904599</v>
+        <v>0.8711978602732647</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.19602419296546</v>
+        <v>18.18564726603347</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.37907462504407</v>
+        <v>11.37258530492197</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01826180681489233</v>
+        <v>0.018272533823149</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007368570213971943</v>
+        <v>0.007372898521369253</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5592294162324398</v>
+        <v>0.5593273839047772</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4337751090459382</v>
+        <v>0.4338780127488545</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10519018361.31958</v>
+        <v>10554708965.093</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>350.89</v>
+        <v>349.74</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.113406336016795</v>
+        <v>0.1097572799410469</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1412593915958984</v>
+        <v>-0.1440738112136267</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4246509829145</v>
+        <v>4232592401166</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.21896722939424</v>
+        <v>17.16881827209533</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>21.06602106299623</v>
+        <v>20.99697969897205</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.439180406958592</v>
+        <v>9.411689498308908</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.579198866475145</v>
+        <v>6.560037440669498</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1531292770493972</v>
+        <v>0.1526832994554069</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.15426507823563</v>
+        <v>13.11646482450411</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.566673869119869</v>
+        <v>9.539182960470185</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01265809968608074</v>
+        <v>0.01269507313938168</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1826189113785507</v>
+        <v>-0.1823196231915267</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2898682348804311</v>
+        <v>0.2903405266070767</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002450910541765226</v>
+        <v>0.002458969520215017</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.76361573303143</v>
+        <v>0.7635656952662421</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3627388231963615</v>
+        <v>0.3622794145527499</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>7828933134.829708</v>
+        <v>7863509762.425476</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>253.1237</v>
+        <v>253.2115</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1175439293598235</v>
+        <v>0.1179315673289183</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1186500696378829</v>
+        <v>-0.1183443593314762</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,31 +1094,31 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2722876953270</v>
+        <v>2723821426650</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.08918253968254</v>
+        <v>20.09615079365079</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.54192257048372</v>
+        <v>22.5497415965239</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.510309603534963</v>
+        <v>3.511527210512067</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.935641414742032</v>
+        <v>4.937353420833182</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2274054673273709</v>
+        <v>0.2274843465474176</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.2900585833691</v>
+        <v>11.29478075193802</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.696938183271453</v>
+        <v>3.698484460924608</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004269781099727464</v>
+        <v>-0.004267900930017086</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8370649725470469</v>
+        <v>0.836965608661726</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4624436850486459</v>
+        <v>0.4624511224112033</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8302822149.937873</v>
+        <v>8326029049.474432</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>219.838</v>
+        <v>219.708</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1640878628274902</v>
+        <v>0.1633994858309402</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07060962205123866</v>
+        <v>-0.071159211972605</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5324696198000</v>
+        <v>5321547468000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.65157232704402</v>
+        <v>27.63622641509433</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.37668653244966</v>
+        <v>16.36700226835875</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.57441332281521</v>
+        <v>17.56465997511297</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.22296623344862</v>
+        <v>23.21007808405827</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2219650023531425</v>
+        <v>0.2218418174817096</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.85696923399539</v>
+        <v>22.84432319497404</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.62860038485786</v>
+        <v>17.61884703715562</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02385312086335173</v>
+        <v>0.0238663660831222</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6884717352471565</v>
+        <v>0.6885331817006977</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9436640378699037</v>
+        <v>0.9437347712197781</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002365378142086445</v>
+        <v>0.00236677772315983</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.327430813333441</v>
+        <v>1.327411935064683</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.411076577822255</v>
+        <v>0.4110727686622919</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>25969098564.80347</v>
+        <v>26058316243.44726</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>673.4400000000001</v>
+        <v>671.22</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.03540847743174313</v>
+        <v>0.03199524563693079</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1484066767830045</v>
+        <v>-0.1512139605462821</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,31 +1346,31 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1715579355701</v>
+        <v>1709923935515</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>25.02564102564103</v>
+        <v>24.94314381270903</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.3688613331893</v>
+        <v>20.30171522936464</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.516295238954997</v>
+        <v>7.491517715445481</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.555973371206757</v>
+        <v>6.534361555923912</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.130256410256407</v>
+        <v>-5.113344481605347</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.92904264896518</v>
+        <v>16.87443902714995</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.94147792975185</v>
+        <v>7.915863164255547</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02388198251828632</v>
+        <v>0.02396363905372125</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.00311831789023521</v>
+        <v>0.003128631447215518</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7735635086953959</v>
+        <v>0.773777460332831</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4104482514708787</v>
+        <v>0.4112584410410082</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10189928339.75648</v>
+        <v>10278282073.38621</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>363.0901</v>
+        <v>362.4872</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1711596458799006</v>
+        <v>-0.172535909924277</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2721165527333961</v>
+        <v>-0.2733251809233607</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1434041558242</v>
+        <v>1431660376118</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>307.6737288135594</v>
+        <v>307.1925423728813</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>172.4382954336029</v>
+        <v>172.1519669208813</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.83822396596184</v>
+        <v>13.81658167052375</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.53023365723365</v>
+        <v>13.50907304335812</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.190187992360942</v>
+        <v>-8.177378944855571</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>118.7251354447123</v>
+        <v>118.5428941074992</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.78150656857333</v>
+        <v>13.76035215862921</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004018403117078524</v>
+        <v>0.004024555430817323</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7842540605026374</v>
+        <v>0.7844265614116557</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1231118120551531</v>
+        <v>0.1232203940178105</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.536474236973029</v>
+        <v>1.536586436490558</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5671256769133135</v>
+        <v>0.5672542009424821</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>12961748241.16383</v>
+        <v>13050142620.36825</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>357.54</v>
+        <v>354.67999</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.02853692256530982</v>
+        <v>0.02030951896317834</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2776969696969697</v>
+        <v>-0.2834747676767677</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1701025153200</v>
+        <v>1687418439554</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>44.35980148883375</v>
+        <v>44.00496277915632</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.52060367684623</v>
+        <v>19.36445577249478</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>19.0903343643383</v>
+        <v>18.93762877536362</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>17.09334577189287</v>
+        <v>16.95661430434346</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4414019851116623</v>
+        <v>0.4378711642876444</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>33.22559273673536</v>
+        <v>32.96524260758089</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.48811673101095</v>
+        <v>19.33541114203627</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02316426651650291</v>
+        <v>0.02335105404959528</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.272460535708215</v>
+        <v>1.272460599778944</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.857683211380821</v>
+        <v>0.8576832497428704</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007104100240532527</v>
+        <v>0.00716138511225288</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.600346910029839</v>
+        <v>1.600137469145391</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.393113595417772</v>
+        <v>0.3897093887019976</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8637120849.128256</v>
+        <v>8666116792.953856</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>895.3049999999999</v>
+        <v>896.795</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04775307197191325</v>
+        <v>0.04949678174370975</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1834883720930233</v>
+        <v>-0.1821295029639763</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,31 +1724,31 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>397048966095</v>
+        <v>397709749805</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>44.96760421898543</v>
+        <v>45.04244098442993</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.49653122427534</v>
+        <v>39.5622628258236</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.352406496524029</v>
+        <v>1.354657221896746</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.86088756796681</v>
+        <v>11.88062689978812</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.547221279238721</v>
+        <v>3.553124697298561</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.70176088970284</v>
+        <v>26.74469590912232</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.316047645413455</v>
+        <v>1.318163780429651</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02217641770508916</v>
+        <v>0.02214177551422274</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006187835430384059</v>
+        <v>0.006177554513573337</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1839456753916672</v>
+        <v>-0.1840004764619157</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1763109668287718</v>
+        <v>0.1765097002570065</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1695283023.777081</v>
+        <v>1700900406.503906</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>71.845</v>
+        <v>71.895</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2104077185762052</v>
+        <v>-0.2098582076280364</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4245955470126542</v>
+        <v>-0.4241950985103315</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,37 +1850,37 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>299158274311</v>
+        <v>299366466228</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>22.24303405572756</v>
+        <v>22.25851393188854</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>19.14987640120978</v>
+        <v>19.16320361702243</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.18469194141734</v>
+        <v>6.188996027187001</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>9.982089246695383</v>
+        <v>9.989036208381441</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6537281960280905</v>
+        <v>0.6541831533640415</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>9.948321237107983</v>
+        <v>9.954445271074931</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.292833475361275</v>
+        <v>6.296707247129692</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03674925289529826</v>
+        <v>0.03672625106790155</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1615236354383141</v>
+        <v>0.1615236354383138</v>
       </c>
       <c r="V11" s="4" t="n">
         <v>0.1444115006001652</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09495447893104303</v>
+        <v>0.09548320717656399</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3523153787817147</v>
+        <v>0.3517928521461439</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2171170761.703859</v>
+        <v>2188655773.10679</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>507.81</v>
+        <v>509.205</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02205895896517496</v>
+        <v>0.02486664736783806</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05565886859820735</v>
+        <v>-0.05306467809722171</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1095271824077</v>
+        <v>1098280634842</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.76808939621049</v>
+        <v>12.81626626695422</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.89179783164884</v>
+        <v>22.95468367079173</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.84769069892666</v>
+        <v>2.858435675913145</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.458049745859977</v>
+        <v>1.46355129522766</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3517283476017706</v>
+        <v>0.3530554977033628</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.47730600802468</v>
+        <v>15.53132818647568</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.078426335951046</v>
+        <v>3.089171312937531</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02210467563781969</v>
+        <v>0.02202158325514915</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.44224173697017</v>
+        <v>-0.4416709700398943</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06097915463345482</v>
+        <v>0.0620648791406182</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.03939255501932271</v>
+        <v>0.03913783193521956</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1492536220272904</v>
+        <v>0.1490080503669119</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2108237113.600871</v>
+        <v>2116963592.366055</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>347</v>
+        <v>347.11</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06611769782254262</v>
+        <v>0.0664556602051376</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.05320600272851295</v>
+        <v>-0.05290586630286487</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,31 +2102,31 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>929789970000</v>
+        <v>930084716100</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>14.9183147033534</v>
+        <v>14.92304385210662</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.85497449975836</v>
+        <v>13.85936656660266</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.123947848524861</v>
+        <v>3.124938148995575</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.583246306707457</v>
+        <v>2.584065203231197</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7811117591326865</v>
+        <v>0.7813593738113741</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>19.94257159725204</v>
+        <v>19.9457354669386</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.242083270336287</v>
+        <v>6.243073570807001</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1748072201725299</v>
+        <v>-0.1747518233409233</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
@@ -2135,7 +2135,7 @@
         <v>0.07674790044641289</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2892465869116644</v>
+        <v>-0.2892465869116646</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01729106628242075</v>
+        <v>0.01728558670162196</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7674338664160787</v>
+        <v>0.7675988831155752</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1654414159399357</v>
+        <v>0.1653636675908305</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2096482695.002885</v>
+        <v>2112035357.167765</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>369.98999</v>
+        <v>369.79</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06785378165610689</v>
+        <v>0.06727657664092979</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04040773400420161</v>
+        <v>-0.04092642062401108</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,37 +2228,37 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>690788779365</v>
+        <v>690415388156</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.43500339847068</v>
+        <v>31.41801189464741</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.70576767734846</v>
+        <v>24.69241351477289</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.52753055576785</v>
+        <v>15.5191374787808</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.12501325702115</v>
+        <v>20.11413512109841</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.119794637067926</v>
+        <v>2.118648828421948</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.13525944618187</v>
+        <v>24.12242725122001</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.78600475105647</v>
+        <v>15.77761167406941</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.0304188496219003</v>
+        <v>0.03043530077758361</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2723750910720311</v>
+        <v>0.2723750910720313</v>
       </c>
       <c r="V14" s="4" t="n">
         <v>0.1387483256465651</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007243439207639105</v>
+        <v>0.00724735660780443</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3058432740746191</v>
+        <v>0.3058649512080006</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1736684649057387</v>
+        <v>0.1736869764018984</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2215551708.526697</v>
+        <v>2223028838.08304</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>567.24</v>
+        <v>566.3</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.007298483621100527</v>
+        <v>0.005629242075011032</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05653410508457668</v>
+        <v>-0.05809756665502397</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.23</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>497489900640</v>
+        <v>496665486800</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.1499176276771</v>
+        <v>31.09829763866007</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.55757834192488</v>
+        <v>25.51522568054449</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.18036942792806</v>
+        <v>14.1568704728786</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.16515416146855</v>
+        <v>89.01739440384958</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.376715109437514</v>
+        <v>1.374433690280065</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.09829538071984</v>
+        <v>23.06101857478748</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.5609526163669</v>
+        <v>14.53745366131745</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03306197769812078</v>
+        <v>0.03311685719491794</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005941047880967492</v>
+        <v>0.005950909411972453</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2926366823843486</v>
+        <v>0.2926808144625126</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1892272728790046</v>
+        <v>0.1891956467987032</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1466547292.951424</v>
+        <v>1470392921.679728</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>374.76999</v>
+        <v>374.135</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1140606325793296</v>
+        <v>0.1121730285022755</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.188141783284953</v>
+        <v>-0.1895173519344916</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,31 +2480,31 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>340345268310</v>
+        <v>339768606591</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.09941418558293</v>
+        <v>24.05858144170793</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.23026590034443</v>
+        <v>17.20107186977635</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7561060680604893</v>
+        <v>0.7548249648234172</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.448967328918403</v>
+        <v>3.4431235852286</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7302185420984069</v>
+        <v>-0.7289812992977037</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>14.94733797733183</v>
+        <v>14.92495464778947</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8555064621697335</v>
+        <v>0.8542253589326615</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06939129818748853</v>
+        <v>0.06950907041399858</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
@@ -2513,7 +2513,7 @@
         <v>0.3986675728028772</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01056282027615407</v>
+        <v>0.01056282027615385</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02417482787242383</v>
+        <v>0.02421585791225093</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4282999180245435</v>
+        <v>0.4285528647058857</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2070963720507303</v>
+        <v>0.2070147679908274</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1731751011.940075</v>
+        <v>1735678195.124048</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>163.265</v>
+        <v>162.475</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3311455195175956</v>
+        <v>0.3247044270579817</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.074513916444646</v>
+        <v>-0.07899212062808236</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,31 +2606,31 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>676645261900</v>
+        <v>673371138500</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.01222651222651</v>
+        <v>20.91055341055341</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.78298599456936</v>
+        <v>14.71145468696694</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.874052129562954</v>
+        <v>1.864984042818368</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.62720249639525</v>
+        <v>2.614490096480067</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.05744717932218</v>
+        <v>2.047491688116689</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.862924324399582</v>
+        <v>9.817628103028193</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.962013348473938</v>
+        <v>1.953002654683432</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04515502795399944</v>
+        <v>0.04537319503782088</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02523504731571372</v>
+        <v>0.0253577473457455</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5333224483281266</v>
+        <v>-0.5324586158995397</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2502025527989721</v>
+        <v>0.2506514058795743</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2208923240.115904</v>
+        <v>2213786007.887808</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>269.195</v>
+        <v>269.795</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2982637669449086</v>
+        <v>0.3011574249258033</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.04224926174974208</v>
+        <v>-0.04011456220870235</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>648732604095</v>
+        <v>650178543145</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.12080924855491</v>
+        <v>31.19017341040463</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.7136705641696</v>
+        <v>21.76206745987161</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.624519846980976</v>
+        <v>6.639285024303322</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.730434142236763</v>
+        <v>7.747664256040296</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.853247566169766</v>
+        <v>-3.861835944630368</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20.08023847073995</v>
+        <v>20.12310397085853</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.916711128419569</v>
+        <v>6.931476305741915</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02883776748988619</v>
+        <v>0.02877363486882683</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01961403443600364</v>
+        <v>0.01957041457402843</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1651940988356478</v>
+        <v>-0.1652322091923143</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2042261709506598</v>
+        <v>0.2038936222219438</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1607087263.489426</v>
+        <v>1611564675.084699</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>107.22</v>
+        <v>107.2634</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04913091549552595</v>
+        <v>-0.04874602724457</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2067179638946434</v>
+        <v>-0.2063968629772122</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>853265337600</v>
+        <v>853610718272</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.70938628158845</v>
+        <v>38.72324909747293</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.54795667197718</v>
+        <v>34.56194082903337</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.159634061752555</v>
+        <v>1.160049356207871</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.681647122294834</v>
+        <v>8.684756240965818</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.360633409911395</v>
+        <v>9.36398569084346</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.37144022969724</v>
+        <v>21.37857368920843</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.244198641008915</v>
+        <v>1.244613935464231</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01583138265166971</v>
+        <v>0.0158257150605452</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1204537116079782</v>
+        <v>0.120401463824737</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05132784400687207</v>
+        <v>0.05127881962617709</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009116769259466518</v>
+        <v>0.009113080510220634</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05913344462291252</v>
+        <v>-0.05938105152903623</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3024289948247972</v>
+        <v>0.3024709219664355</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2648813132.931631</v>
+        <v>2655338070.038673</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.34</v>
+        <v>146.4</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03208975900496203</v>
+        <v>0.03251292003776451</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1250224215246637</v>
+        <v>-0.1246636771300448</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,31 +2984,31 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>347880755841</v>
+        <v>348023388377</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.68</v>
+        <v>21.68888888888889</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.70734842384243</v>
+        <v>20.71583852159718</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>3.997159158022337</v>
+        <v>3.998798009663112</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.527382114120527</v>
+        <v>6.530058367549851</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.68891428571451</v>
+        <v>20.69739682539705</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.54686100268185</v>
+        <v>17.55357185880305</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.28510184473527</v>
+        <v>4.286740696376046</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.0457458114780605</v>
+        <v>0.04572706191398881</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02931939319393194</v>
+        <v>0.02930737704918033</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04143308998853398</v>
+        <v>-0.04105688204455495</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1486293926706055</v>
+        <v>0.1485184450757981</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1250507529.617664</v>
+        <v>1254091858.333344</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>301.09</v>
+        <v>300.14</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1293447642613771</v>
+        <v>-0.1320918580670554</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2806870849061112</v>
+        <v>-0.282956663003488</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>418.58</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>300221953878</v>
+        <v>299274696380</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>21.02583798882681</v>
+        <v>20.95949720670391</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.06433328024427</v>
+        <v>20.0010262404348</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.774613147715988</v>
+        <v>1.769013904927413</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>18.01067942468556</v>
+        <v>17.953852079196</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.212351403144112</v>
+        <v>-7.189594972067069</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.08274948266778</v>
+        <v>15.04314013715241</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.13212248710219</v>
+        <v>2.126523244313614</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.05029945280462911</v>
+        <v>0.05045865949463937</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.04792108938547468</v>
+        <v>0.0479210893854749</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03085456175894251</v>
+        <v>0.03095222229626174</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7070411579141297</v>
+        <v>0.7075257194206276</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2378792183223306</v>
+        <v>0.238187445652271</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1227428075.027888</v>
+        <v>1232426384.018259</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>543.03</v>
+        <v>545.345</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.429990589491667</v>
+        <v>1.440349921783941</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.07131496588168906</v>
+        <v>-0.06735587365108686</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,40 +3236,40 @@
         <v>154.78</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>885464718000</v>
+        <v>889239557000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>137.8248730964467</v>
+        <v>138.3952335025381</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>39.87724253966871</v>
+        <v>40.04724385907894</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>21.43722837428883</v>
+        <v>21.5259420813703</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13.17508523741521</v>
+        <v>13.22960766720219</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.112714571787826</v>
+        <v>1.117319316350766</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>82.53916010449711</v>
+        <v>82.8810447537787</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>21.41761815760804</v>
+        <v>21.50633186468951</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009489932042667791</v>
+        <v>0.009450821696264655</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.456228774076907</v>
+        <v>2.455799205296948</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.9038976624956678</v>
+        <v>0.9036610361664779</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.546240113360414</v>
+        <v>2.546241384807006</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.653668679826144</v>
+        <v>0.6536067362280322</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9227197779.396566</v>
+        <v>9274735086.4007</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1656.07</v>
+        <v>1644.8317</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4230094676917195</v>
+        <v>0.4133527458739463</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1719484389687794</v>
+        <v>-0.1775677013540271</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,40 +3362,40 @@
         <v>925.87</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>638279172355</v>
+        <v>633947729347</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>52.16255370101596</v>
+        <v>52.46734397677794</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>33.93304611035687</v>
+        <v>33.70277217743011</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.68401088251362</v>
+        <v>15.77565395190715</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>25.38560724165421</v>
+        <v>25.53393752233636</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.55089565279154</v>
+        <v>3.571643840685479</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>39.79784812575609</v>
+        <v>40.03237458698251</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>15.55132388230132</v>
+        <v>15.64296695169486</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01805146560008102</v>
+        <v>0.01794660200965958</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5372198986018875</v>
+        <v>0.5567664197046081</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2881019734108514</v>
+        <v>0.3044808393003917</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004697869051428986</v>
+        <v>0.004729967205763362</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.681579670631043</v>
+        <v>1.681535031300634</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4305795533260287</v>
+        <v>0.4291426501275775</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2030263382.988037</v>
+        <v>2039732876.163163</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>196.385</v>
+        <v>197.23</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1377925261612494</v>
+        <v>-0.1340826434543535</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2278946333792019</v>
+        <v>-0.2245724395517987</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>155216812450</v>
+        <v>155884675100</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>73.55243445692881</v>
+        <v>73.86891385767787</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>76.42957280766605</v>
+        <v>76.75843188052028</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.651330522368211</v>
+        <v>1.658435822118198</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>25.46710300569836</v>
+        <v>25.57668215909508</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3936580486799993</v>
+        <v>0.3953518697515404</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>27.89464927338129</v>
+        <v>27.99074461870504</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.062533245917336</v>
+        <v>2.069638545667323</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001352946222031504</v>
+        <v>-0.001347149743008959</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.03764430762916227</v>
+        <v>-0.03764430762916238</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1546467220498906</v>
+        <v>0.1546467220498904</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.226012386886879</v>
+        <v>1.225266067601243</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3439755139730449</v>
+        <v>0.3440020379103921</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1092878111.053377</v>
+        <v>1100727654.318469</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>941.29</v>
+        <v>942.99</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.0294747821958703</v>
+        <v>0.03133404674742524</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1843170218112808</v>
+        <v>-0.1828438721306077</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,31 +3616,31 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>277687139030</v>
+        <v>278188650930</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.34018890920171</v>
+        <v>14.36608775137111</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>12.99177777803206</v>
+        <v>13.0152413463507</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.354537923043659</v>
+        <v>2.358790294224883</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.301421917518046</v>
+        <v>2.305578359485751</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3361141577750228</v>
+        <v>0.3367211907491515</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.51212496511961</v>
+        <v>26.52810024304782</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.057116418341995</v>
+        <v>7.06136878952322</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1495027826820417</v>
+        <v>-0.1492332626123067</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
@@ -3649,7 +3649,7 @@
         <v>0.1037895778551334</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3821570738151003</v>
+        <v>-0.3821570738151004</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01912269332511766</v>
+        <v>0.01908821938726816</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.57960728667643</v>
+        <v>1.579634246376577</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3099646591195975</v>
+        <v>0.3097602611010482</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1901801597.025374</v>
+        <v>1907745172.755973</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>229.87</v>
+        <v>230.03</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2114236706689536</v>
+        <v>-0.2108747855917668</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3085784756060879</v>
+        <v>-0.3080972147025206</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,37 +3742,37 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>216568342580</v>
+        <v>216719084020</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.07598253275109</v>
+        <v>20.08995633187773</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>17.80894327846084</v>
+        <v>17.82133911490994</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.134265490252833</v>
+        <v>3.136447081928304</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.271183472657611</v>
+        <v>6.27554850226402</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2447246707965202</v>
+        <v>0.2448950103246337</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>16.93288592441896</v>
+        <v>16.94217890512299</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>3.975112415589678</v>
+        <v>3.977294007265149</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06294087047817125</v>
+        <v>0.06289709123513118</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.127297797451696</v>
+        <v>0.1272977974516962</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>0.04632303781771174</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02932092052029408</v>
+        <v>0.02930052601834543</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9049354814923495</v>
+        <v>0.9063480062079311</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3390150801183113</v>
+        <v>0.3383702143838703</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1184209801.843376</v>
+        <v>1190085071.17632</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1146.73</v>
+        <v>1143.78</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06143324035352893</v>
+        <v>0.0587026690254544</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1128843847909334</v>
+        <v>-0.1151665183924497</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,31 +3868,31 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1079922656930</v>
+        <v>1077144520980</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.36500501840081</v>
+        <v>38.26630980260957</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.20129058188018</v>
+        <v>26.13388691474271</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.5556619895865</v>
+        <v>13.52078961084932</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.20578682959945</v>
+        <v>30.12808146639511</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4055653661958957</v>
+        <v>0.4045220361789972</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>26.00036617026288</v>
+        <v>25.93621309831704</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.13330007267862</v>
+        <v>14.09842769394144</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01856975577955661</v>
+        <v>0.01861765028684795</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005833980099936341</v>
+        <v>0.005849026910769554</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3509779977696696</v>
+        <v>0.3516223874189415</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.312613469175804</v>
+        <v>0.3128830000262121</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2748902137.458256</v>
+        <v>2756329166.509135</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>202.25</v>
+        <v>202.01</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1118746937127244</v>
+        <v>0.110555287401273</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1291711517761034</v>
+        <v>-0.1302045209903122</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,31 +3994,31 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>319004880000</v>
+        <v>318626332800</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.258038585209</v>
+        <v>16.2387459807074</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.01994671915705</v>
+        <v>15.00212329659785</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.521199724964238</v>
+        <v>2.518207942843143</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.877589048787777</v>
+        <v>2.874174357209488</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4136304403587362</v>
+        <v>0.4131396057199916</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.28847514226327</v>
+        <v>23.27450121647869</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.401503844968348</v>
+        <v>5.398262747670495</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.0491653920780146</v>
+        <v>-0.04922867739877446</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02051915945611867</v>
+        <v>0.02054353744864116</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.376177867515408</v>
+        <v>1.376465159083515</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2517194542518957</v>
+        <v>0.2518889976862511</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>891502602.344251</v>
+        <v>894328134.946995</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>991.1</v>
+        <v>996.65</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.142159526370923</v>
+        <v>2.15975511245846</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2102788844621514</v>
+        <v>-0.2058565737051793</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1119338429000</v>
+        <v>1125606543500</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>22.11604597188128</v>
+        <v>22.24168712340995</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.340700940785748</v>
+        <v>6.376207842431758</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.39834392912688</v>
+        <v>12.46877886766954</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>11.09835374448989</v>
+        <v>11.16140343910091</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03152185032708219</v>
+        <v>0.03170092580822581</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>16.1037822236561</v>
+        <v>16.19681537324788</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>12.19209406759421</v>
+        <v>12.26252900613687</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02338355544523191</v>
+        <v>0.02325146397836306</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.487949704365118</v>
+        <v>2.488231198393215</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.775555219220929</v>
+        <v>1.775779220960631</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005347593582887701</v>
+        <v>0.0005317814679175238</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.885542369802312</v>
+        <v>2.885321025899236</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.7721368978843398</v>
+        <v>0.7728570669088352</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>24945013988.89314</v>
+        <v>25086389113.42723</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>136.73</v>
+        <v>136.72</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.07270259186241368</v>
+        <v>-0.07277041146368168</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.297833879399772</v>
+        <v>-0.2978852336103037</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>141359951260</v>
+        <v>141349612640</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>84.92546583850933</v>
+        <v>84.9192546583851</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>28.80044437670449</v>
+        <v>28.79833800324025</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.595435192777627</v>
+        <v>9.594733412978551</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.28492249920102</v>
+        <v>11.28409715564078</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>135.8807453416178</v>
+        <v>135.870807453419</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>42.22125286901691</v>
+        <v>42.21828966466036</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>9.999317897094761</v>
+        <v>9.998616117295683</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03239955842638991</v>
+        <v>0.03240192820099688</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.6997775735484316</v>
+        <v>0.7002455359113148</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6270241528624115</v>
+        <v>0.6270240038221295</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2144377934.183103</v>
+        <v>2150035842.611379</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.45</v>
+        <v>27.505</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09015090021097483</v>
+        <v>0.09233517341722641</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.06025333789798015</v>
+        <v>-0.0583704210886683</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>156449628000</v>
+        <v>156763097200</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.27629492600423</v>
+        <v>36.34381606765328</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.404060528651197</v>
+        <v>9.422902908581099</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.45654126323474</v>
+        <v>2.461113683747802</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.836597911726729</v>
+        <v>1.840016375161404</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6067451098243185</v>
+        <v>-0.6078744457333158</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.32334064504119</v>
+        <v>17.34641137515843</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.433337294382693</v>
+        <v>3.437909714895755</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.0702107109892593</v>
+        <v>0.07008026886572639</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.857513976593605</v>
+        <v>2.856965992354253</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05050491154177539</v>
+        <v>-0.05063977200538161</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06265938069216757</v>
+        <v>0.06253408471187057</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3509371480600263</v>
+        <v>0.3509967713407846</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2061895175678352</v>
+        <v>0.2057973852744562</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>912778413.2761378</v>
+        <v>915873185.0029954</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>183.41499</v>
+        <v>184.86</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.0916909469486189</v>
+        <v>0.1002916852811306</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.08232856356631824</v>
+        <v>-0.07509881422924891</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1301980300669</v>
+        <v>1312237751503</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>8.113760780990328</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003802660961113973</v>
+        <v>0.003832619707208932</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.968315520817014</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2132.706071606614</v>
+        <v>2116.027360092321</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2762.495665002442</v>
+        <v>2740.894075746785</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.635635124479193</v>
+        <v>1.622849724115547</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.8633465846030076</v>
+        <v>0.8636009620560741</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3136792281.322672</v>
+        <v>3153588301.495565</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>565.575</v>
+        <v>564.38</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.515068359213734</v>
+        <v>0.5118671804323867</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1581575696232678</v>
+        <v>-0.1599362934075585</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>313.43</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>71285496050</v>
+        <v>71134877356</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.82540761846922</v>
+        <v>1.825352834830912</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.3919771357421525</v>
+        <v>0.3916864181733605</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3700231626.092234</v>
+        <v>3712538712.750047</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>151.06</v>
+        <v>151.8</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.06144763675529974</v>
+        <v>-0.05684993551869777</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3305265023931927</v>
+        <v>-0.3272469420315546</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1991239646310</v>
+        <v>2000994195651</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-98.09090909090909</v>
+        <v>-98.57142857142858</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>120.9805814591333</v>
+        <v>121.5732309380142</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>120.1351219493213</v>
+        <v>120.7236317134842</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.962647299251714</v>
+        <v>6.996755329183173</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.980909090909091</v>
+        <v>-0.9857142857142859</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>465.2356919906408</v>
+        <v>467.2033106913847</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>116.9615160497737</v>
+        <v>117.456180733092</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01426288111263989</v>
+        <v>-0.01420443900425854</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.360207879037847</v>
+        <v>3.36022150412568</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.777214118082028</v>
+        <v>0.7761601261188797</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>13243498224.01919</v>
+        <v>13342531663.91755</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>759.59</v>
+        <v>759.21</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1118609116347751</v>
+        <v>0.1113046811072258</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.0253794731642224</v>
+        <v>-0.02586704646060278</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>809144304087</v>
+        <v>808739513561</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9953050681130762</v>
+        <v>0.9954109491331716</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1148931228142449</v>
+        <v>0.1150244482454095</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29752244927.56256</v>
+        <v>29882618301.15575</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>431.545</v>
+        <v>429.84</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3502237720305015</v>
+        <v>0.3448891452098637</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.09907098121085589</v>
+        <v>-0.1026304801670147</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>262.81</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2238199511600</v>
+        <v>2229356563200</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>28.51512692708937</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6568678259280953</v>
+        <v>0.6542725933493203</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.36635940341746</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.41075297271571</v>
+        <v>42.58294572773731</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.38729125771043</v>
+        <v>42.55939094967581</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2780706531184465</v>
+        <v>0.2791736460078169</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.181299131737951</v>
+        <v>2.181401872113908</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3376196867388273</v>
+        <v>0.3375740463334496</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>3987349271.78236</v>
+        <v>3999456192.476538</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>27.945</v>
+        <v>27.955</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01981761572591878</v>
+        <v>-0.01946686160737376</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.06816666666666671</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70061934372</v>
+        <v>70087006313</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.00393700787401</v>
+        <v>-22.01181102362204</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-84.18468056003628</v>
+        <v>-84.214805691745</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.939967724546587</v>
+        <v>1.940661949688495</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.13685044765211</v>
+        <v>2.137615110542664</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1637502288958067</v>
+        <v>0.1638088262223037</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.31668336727273</v>
+        <v>16.32082748975207</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.733377665014537</v>
+        <v>2.734071890156445</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03111532702515889</v>
+        <v>0.03110419626520195</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2301265938031586</v>
+        <v>0.2302678767516122</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1595246601947214</v>
+        <v>0.1593563858443711</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>500518907.9641965</v>
+        <v>502982889.4132234</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>310.065</v>
+        <v>311.25</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1681244040974922</v>
+        <v>-0.1649451591612869</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1998116080414979</v>
+        <v>-0.1967534646055382</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>209389996799</v>
+        <v>210190237500</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>18.80321406913281</v>
+        <v>18.87507580351728</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>15.94015843164978</v>
+        <v>16.00107819925175</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.490573630047697</v>
+        <v>2.500092033114079</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.132557467911319</v>
+        <v>6.155994749124854</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.165963492496447</v>
+        <v>1.170419547641685</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.027503510718331</v>
+        <v>9.059870469988676</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.654788062743092</v>
+        <v>2.664306465809475</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07188500038255832</v>
+        <v>0.07161131829445694</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01141696095979875</v>
+        <v>0.01137349397590362</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9625112973030167</v>
+        <v>0.9619228569819732</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2344689035074583</v>
+        <v>0.2345931210938006</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>792471917.9137064</v>
+        <v>796387792.335734</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>145.53</v>
+        <v>145.6</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2563998006868988</v>
+        <v>-0.2560421286333573</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5583308042488619</v>
+        <v>-0.5581183611532625</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>419194799100</v>
+        <v>419396432000</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.45833333333333</v>
+        <v>22.46913580246913</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.1725760427441</v>
+        <v>16.18035505959968</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.840238503977598</v>
+        <v>5.843047661507168</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.464415922841909</v>
+        <v>6.467525310010183</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4887990196078434</v>
+        <v>0.4890341321713872</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.28305405885472</v>
+        <v>14.28839957582185</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.505981012023351</v>
+        <v>7.508790169552921</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06851230039509333</v>
+        <v>-0.06847936178913415</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01374287088572803</v>
+        <v>0.01373626373626374</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.084383119342286</v>
+        <v>2.085549571233289</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5630369937724207</v>
+        <v>0.5629532711629709</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4128313146.163589</v>
+        <v>4147522932.392493</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>108.61</v>
+        <v>108.765</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4283271790153527</v>
+        <v>0.4303655798324724</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1669095650839918</v>
+        <v>-0.1657206412518217</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,37 +5422,37 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>428079218966</v>
+        <v>428690141339</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>32.32440476190476</v>
+        <v>32.37053571428572</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>20.93001124173748</v>
+        <v>20.9598809751181</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.760035040915911</v>
+        <v>6.769682453043822</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.538039773292235</v>
+        <v>8.550224619667894</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.034380952380952</v>
+        <v>1.035857142857143</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.49833752764873</v>
+        <v>22.52885465502772</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.112423513083301</v>
+        <v>7.122070925211212</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.03175814054426168</v>
+        <v>0.03171288231060423</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.544404558056099</v>
+        <v>0.5444045580560992</v>
       </c>
       <c r="V40" s="4" t="n">
         <v>0.166508857283745</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01528404382653531</v>
+        <v>0.01526226267641245</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7115021341152543</v>
+        <v>0.7116709206384128</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3353961628243654</v>
+        <v>0.3350370560091954</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>1975705326.379649</v>
+        <v>1981790917.794049</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>86.25</v>
+        <v>86.105</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.09401257599943069</v>
+        <v>-0.09553568529195333</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1177373158756138</v>
+        <v>-0.1192205400981997</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,37 +5548,37 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>260820000000</v>
+        <v>260381530151</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.30385164051355</v>
+        <v>12.28316690442226</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.08621319741697</v>
+        <v>11.06757550566479</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.020216103171837</v>
+        <v>2.016819876464893</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.45968037210722</v>
+        <v>1.45722641669904</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.653988510621893</v>
+        <v>0.6528890516764997</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.59216443813951</v>
+        <v>15.57893000968881</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>4.001270283877464</v>
+        <v>3.99787405717052</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.07349896480331262</v>
+        <v>0.07362273348990217</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.109833576300002</v>
+        <v>0.1098335763000022</v>
       </c>
       <c r="V41" s="4" t="n">
         <v>-0.2902196875898506</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02144927536231884</v>
+        <v>0.02148539573776204</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.7295619626306802</v>
+        <v>0.7300563939504189</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.2240177252206077</v>
+        <v>0.2243778026656516</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1069867249.031316</v>
+        <v>1072418318.106382</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30 ET</t>
+          <t>2026-09-18 13:09 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -443,10 +443,10 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>334.835</v>
+        <v>336.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2355078703165692</v>
+        <v>0.240544584647455</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.02825260469570778</v>
+        <v>-0.02429114548567779</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,31 +714,31 @@
         <v>240.21</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4917840846260</v>
+        <v>4937889087200</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.22317351598173</v>
+        <v>38.37899543378995</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>34.95392285696923</v>
+        <v>35.09641723390044</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.53470125992078</v>
+        <v>10.57764738926745</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.754913132673</v>
+        <v>45.94143920200894</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.167930301877218</v>
+        <v>1.172691527143581</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.4541020990468</v>
+        <v>29.57309264389919</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.63058985152831</v>
+        <v>10.67353598087498</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02779329471468092</v>
+        <v>0.02768045162340924</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003165738348738931</v>
+        <v>0.00315288518738846</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3107188070342853</v>
+        <v>0.3100537800948155</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2921411097903008</v>
+        <v>0.2917465145752744</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>12896900486.14602</v>
+        <v>12991193528.28819</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>493.7</v>
+        <v>493.7863</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.0438956261923853</v>
+        <v>0.0440781017697407</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1083941342194612</v>
+        <v>-0.1082382792747237</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,31 +842,31 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3665994035000</v>
+        <v>3666634859965</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.42777777777778</v>
+        <v>27.43257222222222</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.02042508929638</v>
+        <v>24.02462391993281</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.0475080837394</v>
+        <v>11.04943921589988</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.290698641687028</v>
+        <v>8.292147876632901</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8711978602732647</v>
+        <v>0.8713501478473817</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.18564726603347</v>
+        <v>18.18873529635841</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.37258530492197</v>
+        <v>11.37451643708244</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.018272533823149</v>
+        <v>0.01826934029657904</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
@@ -875,7 +875,7 @@
         <v>0.141852305936073</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2273810125949838</v>
+        <v>0.227381012594984</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007372898521369253</v>
+        <v>0.00737160994543591</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5593273839047772</v>
+        <v>0.5582010347179622</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4338780127488545</v>
+        <v>0.4337879675422517</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10554708965.093</v>
+        <v>10618505318.93155</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>349.74</v>
+        <v>349.78</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1097572799410469</v>
+        <v>0.109884203630638</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1440738112136267</v>
+        <v>-0.143975918357358</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4232592401166</v>
+        <v>4233076485617</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.16881827209533</v>
+        <v>17.15491559086395</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.99697969897205</v>
+        <v>20.99938113772071</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.411689498308908</v>
+        <v>9.404068256305706</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.560037440669498</v>
+        <v>6.554725362228329</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1526832994554069</v>
+        <v>0.1525596621026175</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.11646482450411</v>
+        <v>13.1059855462401</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.539182960470185</v>
+        <v>9.531561718466984</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01269507313938168</v>
+        <v>0.01270536147651478</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1823196231915267</v>
+        <v>-0.1830751831038981</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2903405266070767</v>
+        <v>0.2891482152799802</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002458969520215017</v>
+        <v>0.002458688318371548</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7635656952662421</v>
+        <v>0.7639422798140121</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3622794145527499</v>
+        <v>0.3622859847015646</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>7863509762.425476</v>
+        <v>7930389977.807666</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>253.2115</v>
+        <v>253.84</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1179315673289183</v>
+        <v>0.1207064017660044</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1183443593314762</v>
+        <v>-0.1161559888579387</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,37 +1094,37 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2723821426650</v>
+        <v>2730582264000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.09615079365079</v>
+        <v>20.14603174603175</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.5497415965239</v>
+        <v>22.60571264283663</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.511527210512067</v>
+        <v>3.520243224009901</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.937353420833182</v>
+        <v>4.949608498604111</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2274843465474176</v>
+        <v>0.2280489888002578</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.29478075193802</v>
+        <v>11.32309258770773</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.698484460924608</v>
+        <v>3.707755192863036</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004267900930017086</v>
+        <v>-0.004256662975976923</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1088079343335507</v>
+        <v>-0.1088079343335506</v>
       </c>
       <c r="V5" s="4" t="n">
         <v>0.179997197688706</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.836965608661726</v>
+        <v>0.8380302743492216</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4624511224112033</v>
+        <v>0.4631250225014107</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8326029049.474432</v>
+        <v>8372734468.453293</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>219.708</v>
+        <v>220.58</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1633994858309402</v>
+        <v>0.1680169069154915</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.071159211972605</v>
+        <v>-0.06747273188467062</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,31 +1220,31 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5321547468000</v>
+        <v>5342668180000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.63622641509433</v>
+        <v>27.74591194968553</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.36700226835875</v>
+        <v>16.43196133210704</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.56465997511297</v>
+        <v>17.63437242754209</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.21007808405827</v>
+        <v>23.30219666002865</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2218418174817096</v>
+        <v>0.2227222863988363</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.84432319497404</v>
+        <v>22.93471127715938</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.61884703715562</v>
+        <v>17.68855948958474</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.0238663660831222</v>
+        <v>0.02377201722454715</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.00236677772315983</v>
+        <v>0.002357421343730166</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.327411935064683</v>
+        <v>1.32757200663413</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4110727686622919</v>
+        <v>0.411357244292535</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26058316243.44726</v>
+        <v>26232323242.23933</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>671.22</v>
+        <v>666.26</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.03199524563693079</v>
+        <v>0.02436928631158408</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1512139605462821</v>
+        <v>-0.1574860900354071</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1709923935515</v>
+        <v>1697288402128</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.94314381270903</v>
+        <v>24.75882571534746</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.30171522936464</v>
+        <v>20.15169510550413</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.491517715445481</v>
+        <v>7.436158924187726</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.534361555923912</v>
+        <v>6.486075698355033</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.113344481605347</v>
+        <v>-5.075559271646224</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.87443902714995</v>
+        <v>16.75642933846384</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.915863164255547</v>
+        <v>7.860504372997792</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02396363905372125</v>
+        <v>0.02414203735123963</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2286224848938367</v>
+        <v>0.228622484893837</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2736216805247405</v>
+        <v>0.2736216805247407</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003128631447215518</v>
+        <v>0.003151922672830427</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.773777460332831</v>
+        <v>0.7708869468135293</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4112584410410082</v>
+        <v>0.4136044229202094</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10278282073.38621</v>
+        <v>10383135938.78237</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>362.4872</v>
+        <v>365.42</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.172535909924277</v>
+        <v>-0.1658410895737263</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2733251809233607</v>
+        <v>-0.2674458232263496</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1431660376118</v>
+        <v>1443243608715</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>307.1925423728813</v>
+        <v>309.5932203389831</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>172.1519669208813</v>
+        <v>173.5448086228382</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.81658167052375</v>
+        <v>13.92455682814928</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.50907304335812</v>
+        <v>13.61464505284487</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.177378944855571</v>
+        <v>-8.241284316065883</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>118.5428941074992</v>
+        <v>119.4623098626538</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.76035215862921</v>
+        <v>13.86707710968066</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.004024555430817323</v>
+        <v>0.003993707483360202</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7844265614116557</v>
+        <v>0.7839382393270924</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1232203940178105</v>
+        <v>0.1229130160984628</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.536586436490558</v>
+        <v>1.535683387402444</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5672542009424821</v>
+        <v>0.5667998468307686</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>13050142620.36825</v>
+        <v>13176844852.79364</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>354.67999</v>
+        <v>356.975</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.02030951896317834</v>
+        <v>0.02691158452970699</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2834747676767677</v>
+        <v>-0.2788383838383838</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1687418439554</v>
+        <v>1698337120500</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>44.00496277915632</v>
+        <v>44.28970223325062</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.36445577249478</v>
+        <v>19.48975638401908</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>18.93762877536362</v>
+        <v>19.06016700148141</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>16.95661430434346</v>
+        <v>17.06633413582104</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4378711642876444</v>
+        <v>0.4407044628160084</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>32.96524260758089</v>
+        <v>33.18144245259553</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.33541114203627</v>
+        <v>19.46222085316035</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02335105404959528</v>
+        <v>0.02319573133077664</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.272460599778944</v>
+        <v>1.272460535708215</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8576832497428704</v>
+        <v>0.857683211380821</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.00716138511225288</v>
+        <v>0.007115344211779536</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.600137469145391</v>
+        <v>1.602707345413127</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3897093887019976</v>
+        <v>0.3925035147436929</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8666116792.953856</v>
+        <v>8726089082.55924</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>896.795</v>
+        <v>896.895</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04949678174370975</v>
+        <v>0.04961380924517256</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1821295029639763</v>
+        <v>-0.1820383036935704</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,40 +1724,40 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>397709749805</v>
+        <v>397754097705</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.04244098442993</v>
+        <v>45.04319437468608</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.5622628258236</v>
+        <v>39.56667434270604</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.354657221896746</v>
+        <v>1.354679880205867</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.88062689978812</v>
+        <v>11.8808256178937</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.553124697298561</v>
+        <v>3.553184127681714</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.74469590912232</v>
+        <v>26.74515563165169</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.318163780429651</v>
+        <v>1.318186438738773</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02214177551422274</v>
+        <v>0.02214140517197331</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1385203415369163</v>
+        <v>0.138412442363623</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1141243314792548</v>
+        <v>0.1140187443501308</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006177554513573337</v>
+        <v>0.006176865742366721</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1840004764619157</v>
+        <v>-0.1835311703353185</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1765097002570065</v>
+        <v>0.1764920483004075</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1700900406.503906</v>
+        <v>1714044398.323975</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>71.895</v>
+        <v>71.8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2098582076280364</v>
+        <v>-0.2109022784295572</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4241950985103315</v>
+        <v>-0.4249559506647446</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,37 +1850,37 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>299366466228</v>
+        <v>298970891928</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>22.25851393188854</v>
+        <v>22.22910216718266</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>19.16320361702243</v>
+        <v>19.13788190697838</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.188996027187001</v>
+        <v>6.180818064564786</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>9.989036208381441</v>
+        <v>9.975836981177931</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6541831533640415</v>
+        <v>0.6533187344257345</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>9.954445271074931</v>
+        <v>9.941516754922485</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.296707247129692</v>
+        <v>6.288529284507477</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03672625106790155</v>
+        <v>0.0367748442970421</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1615236354383138</v>
+        <v>0.1615236354383141</v>
       </c>
       <c r="V11" s="4" t="n">
         <v>0.1444115006001652</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09548320717656399</v>
+        <v>0.09015660905514743</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3517928521461439</v>
+        <v>0.3529625042741945</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2188655773.10679</v>
+        <v>2224196886.446198</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>509.205</v>
+        <v>508.96</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02486664736783806</v>
+        <v>0.02437354080249587</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05306467809722171</v>
+        <v>-0.05352028861531599</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1098280634842</v>
+        <v>1097752205711</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.81626626695422</v>
+        <v>12.80093760550032</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.95468367079173</v>
+        <v>22.94363920441896</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.858435675913145</v>
+        <v>2.855016896071351</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.46355129522766</v>
+        <v>1.461800841401429</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3530554977033628</v>
+        <v>0.3526332321163337</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.53132818647568</v>
+        <v>15.51413969599028</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.089171312937531</v>
+        <v>3.085752533095738</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02202158325514915</v>
+        <v>0.02204795330746677</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4416709700398943</v>
+        <v>-0.4420703057850193</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.0620648791406182</v>
+        <v>0.06130525453407087</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.03913783193521956</v>
+        <v>0.03911907307699093</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1490080503669119</v>
+        <v>0.1490255769318704</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2116963592.366055</v>
+        <v>2144817563.720947</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>347.11</v>
+        <v>348.755</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.0664556602051376</v>
+        <v>0.07150973401758165</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.05290586630286487</v>
+        <v>-0.04841746248294676</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,31 +2102,31 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>930084716100</v>
+        <v>934492510050</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>14.92304385210662</v>
+        <v>14.99376612209802</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.85936656660266</v>
+        <v>13.9250479298652</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.124938148995575</v>
+        <v>3.139747642398524</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.584065203231197</v>
+        <v>2.596311428518038</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7813593738113741</v>
+        <v>0.7850623387790203</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>19.9457354669386</v>
+        <v>19.99304969997853</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.243073570807001</v>
+        <v>6.25788306420995</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1747518233409233</v>
+        <v>-0.1739275577407288</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
@@ -2135,7 +2135,7 @@
         <v>0.07674790044641289</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2892465869116646</v>
+        <v>-0.2892465869116644</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01728558670162196</v>
+        <v>0.01720405442215882</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7675988831155752</v>
+        <v>0.7668354593375404</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1653636675908305</v>
+        <v>0.164616470233544</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2112035357.167765</v>
+        <v>2132541692.304957</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>369.79</v>
+        <v>368.84</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06727657664092979</v>
+        <v>0.06453471572579161</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04092642062401108</v>
+        <v>-0.04339030526233889</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,31 +2228,31 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>690415388156</v>
+        <v>688641693305</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.41801189464741</v>
+        <v>31.33729821580289</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.69241351477289</v>
+        <v>24.62897807076674</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.5191374787808</v>
+        <v>15.47926841631451</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.11413512109841</v>
+        <v>20.06246139177895</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.118648828421948</v>
+        <v>2.113205965210393</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.12242725122001</v>
+        <v>24.06596283627741</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.77761167406941</v>
+        <v>15.74068033199964</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03043530077758361</v>
+        <v>0.03050790131616888</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.00724735660780443</v>
+        <v>0.007266023207895023</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3058649512080006</v>
+        <v>0.3058199398892936</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1736869764018984</v>
+        <v>0.1739239191531709</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2223028838.08304</v>
+        <v>2244048875.587618</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>566.3</v>
+        <v>565.9</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.005629242075011032</v>
+        <v>0.004918926523483469</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05809756665502397</v>
+        <v>-0.05876286945095899</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.23</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>496665486800</v>
+        <v>496314672400</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.09829763866007</v>
+        <v>31.07633168588687</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.51522568054449</v>
+        <v>25.49720327144646</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.1568704728786</v>
+        <v>14.14687091753841</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.01739440384958</v>
+        <v>88.95451791124576</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.374433690280065</v>
+        <v>1.373462873617321</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.06101857478748</v>
+        <v>23.0507079688913</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.53745366131745</v>
+        <v>14.53095395034632</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03311685719491794</v>
+        <v>0.03313206881047634</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005950909411972453</v>
+        <v>0.005955115744831243</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2926808144625126</v>
+        <v>0.2929495295054146</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1891956467987032</v>
+        <v>0.1892123701042264</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1470392921.679728</v>
+        <v>1482031342.379022</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>374.135</v>
+        <v>377.58</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1121730285022755</v>
+        <v>0.1224138134681041</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1895173519344916</v>
+        <v>-0.1820545037043456</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>339768606591</v>
+        <v>342897164062</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.05858144170793</v>
+        <v>24.27303710372324</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.20107186977635</v>
+        <v>17.35945772673007</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7548249648234172</v>
+        <v>0.7615533950889634</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.4431235852286</v>
+        <v>3.473815226365455</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7289812992977037</v>
+        <v>-0.735479361850413</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>14.92495464778947</v>
+        <v>15.04251322353763</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8542253589326615</v>
+        <v>0.8609537891982075</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06950907041399858</v>
+        <v>0.06889494810016018</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3986675728028772</v>
+        <v>0.3982601003917106</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01056282027615385</v>
+        <v>0.01026841403180612</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02421585791225093</v>
+        <v>0.02399491498490386</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4285528647058857</v>
+        <v>0.4282802710404795</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2070147679908274</v>
+        <v>0.208504715997248</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1735678195.124048</v>
+        <v>1746645439.662369</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>162.475</v>
+        <v>162.76</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3247044270579817</v>
+        <v>0.3270281123123995</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.07899212062808236</v>
+        <v>-0.07737656595431097</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>673371138500</v>
+        <v>674552309600</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>20.91055341055341</v>
+        <v>20.94851994851995</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.71145468696694</v>
+        <v>14.73726028527921</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.864984042818368</v>
+        <v>1.868370227109068</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.614490096480067</v>
+        <v>2.619237131891433</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.047491688116689</v>
+        <v>2.051209244959247</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.817628103028193</v>
+        <v>9.834650249912983</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.953002654683432</v>
+        <v>1.956388838974132</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04537319503782088</v>
+        <v>0.04529096187116759</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4213790447982231</v>
+        <v>0.4214663745502998</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08167006657796794</v>
+        <v>0.08173652455699099</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.0253577473457455</v>
+        <v>0.0253133448021627</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5324586158995397</v>
+        <v>-0.533623678586268</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2506514058795743</v>
+        <v>0.2504661472028754</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2213786007.887808</v>
+        <v>2234192800.051252</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>269.795</v>
+        <v>270.54</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3011574249258033</v>
+        <v>0.3047503835854144</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.04011456220870235</v>
+        <v>-0.03746397694524484</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>650178543145</v>
+        <v>651973917465</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.19017341040463</v>
+        <v>31.27630057803468</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.76206745987161</v>
+        <v>21.82216027203493</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.639285024303322</v>
+        <v>6.657618452807647</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.747664256040296</v>
+        <v>7.769058314013017</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.861835944630368</v>
+        <v>-3.872499847885616</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20.12310397085853</v>
+        <v>20.17632863349342</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.931476305741915</v>
+        <v>6.94980973424624</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02877363486882683</v>
+        <v>0.02869439942128407</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01957041457402843</v>
+        <v>0.01951652251053449</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1652322091923143</v>
+        <v>-0.1657701297219941</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2038936222219438</v>
+        <v>0.2037439017414996</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1611564675.084699</v>
+        <v>1636745130.11503</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>107.2634</v>
+        <v>107.03</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04874602724457</v>
+        <v>-0.05081591014256803</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2063968629772122</v>
+        <v>-0.2081237052382361</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>853610718272</v>
+        <v>851753302400</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.72324909747293</v>
+        <v>38.72393501805054</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.56194082903337</v>
+        <v>34.48673570790634</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.160049356207871</v>
+        <v>1.160069904631442</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.684756240965818</v>
+        <v>8.684910077566725</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.36398569084346</v>
+        <v>9.364151558910409</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.37857368920843</v>
+        <v>21.3789266468405</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.244613935464231</v>
+        <v>1.244634483887802</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.0158257150605452</v>
+        <v>0.01582543473821715</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.120401463824737</v>
+        <v>0.1228646093394332</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05127881962617709</v>
+        <v>0.053590002530578</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009113080510220634</v>
+        <v>0.009132953377557694</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05938105152903623</v>
+        <v>-0.05874921969177545</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3024709219664355</v>
+        <v>0.3022903094301135</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2655338070.038673</v>
+        <v>2670418352.014382</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.4</v>
+        <v>146.145</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03251292003776451</v>
+        <v>0.03071448564835433</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1246636771300448</v>
+        <v>-0.1261883408071748</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,37 +2984,37 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>348023388377</v>
+        <v>347417200098</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.68888888888889</v>
+        <v>21.65111111111111</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.71583852159718</v>
+        <v>20.67975560613948</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>3.998798009663112</v>
+        <v>3.991832890178325</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.530058367549851</v>
+        <v>6.518684290475226</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.69739682539705</v>
+        <v>20.66134603174625</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.55357185880305</v>
+        <v>17.52616919629246</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.286740696376046</v>
+        <v>4.280048718839048</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04572706191398881</v>
+        <v>0.04580371954961135</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04697132420091332</v>
+        <v>0.0469713242009131</v>
       </c>
       <c r="V20" s="4" t="n">
         <v>0.02559428074762593</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02930737704918033</v>
+        <v>0.02935851380478292</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04105688204455495</v>
+        <v>-0.04234112358032071</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1485184450757981</v>
+        <v>0.1490285887018052</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1254091858.333344</v>
+        <v>1262485327.122565</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>300.14</v>
+        <v>299.85</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1320918580670554</v>
+        <v>-0.1329304445972097</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.282956663003488</v>
+        <v>-0.2836494815805819</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>418.58</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>299274696380</v>
+        <v>298985532450</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>20.95949720670391</v>
+        <v>20.93924581005587</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>20.0010262404348</v>
+        <v>19.9817009335456</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.769013904927413</v>
+        <v>1.767304655802241</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>17.953852079196</v>
+        <v>17.93650478425709</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.189594972067069</v>
+        <v>-7.182648272054078</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.04314013715241</v>
+        <v>15.03104881664227</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.126523244313614</v>
+        <v>2.124813995188443</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.05045865949463937</v>
+        <v>0.05050746059936988</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.0479210893854749</v>
+        <v>0.04792108938547468</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03095222229626174</v>
+        <v>0.03098215774553943</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7075257194206276</v>
+        <v>0.7066984552760949</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.238187445652271</v>
+        <v>0.2382936415908705</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1232426384.018259</v>
+        <v>1247262395.590235</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>545.345</v>
+        <v>556.8099999999999</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.440349921783941</v>
+        <v>1.491654347153666</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.06735587365108686</v>
+        <v>-0.04774853351119335</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,40 +3236,40 @@
         <v>154.78</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>889239557000</v>
+        <v>907934386000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>138.3952335025381</v>
+        <v>141.3223350253807</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>40.04724385907894</v>
+        <v>40.88917263965699</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>21.5259420813703</v>
+        <v>21.98122227333253</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13.22960766720219</v>
+        <v>13.5094179162204</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.117319316350766</v>
+        <v>1.140950961672798</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>82.8810447537787</v>
+        <v>84.63560235118493</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>21.50633186468951</v>
+        <v>21.96161205665174</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009450821696264655</v>
+        <v>0.009255074077566658</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.455799205296948</v>
+        <v>2.456228774076907</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.9036610361664779</v>
+        <v>0.9038976624956678</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.546241384807006</v>
+        <v>2.546781223666731</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6536067362280322</v>
+        <v>0.6557376936892084</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9274735086.4007</v>
+        <v>9381118117.115662</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1644.8317</v>
+        <v>1678.57</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4133527458739463</v>
+        <v>0.4423430182198154</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1775677013540271</v>
+        <v>-0.1606982139642793</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>925.87</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>633947729347</v>
+        <v>646951077153</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>52.46734397677794</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>33.70277217743011</v>
+        <v>34.39407344463805</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.77565395190715</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5567664197046081</v>
+        <v>0.5254763022248963</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.3044808393003917</v>
+        <v>0.2782615181512065</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004729967205763362</v>
+        <v>0.004634897561614946</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.681535031300634</v>
+        <v>1.683729028827948</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4291426501275775</v>
+        <v>0.4353468110970209</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2039732876.163163</v>
+        <v>2060004173.352702</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>197.23</v>
+        <v>198.57</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1340826434543535</v>
+        <v>-0.1281995158481517</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2245724395517987</v>
+        <v>-0.2193041085118931</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,31 +3490,31 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>155884675100</v>
+        <v>156943770900</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>73.86891385767787</v>
+        <v>74.3707865168539</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>76.75843188052028</v>
+        <v>77.27993620907017</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.658435822118198</v>
+        <v>1.669703398053088</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>25.57668215909508</v>
+        <v>25.75045265087213</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3953518697515404</v>
+        <v>0.3980379292022683</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>27.99074461870504</v>
+        <v>28.14313250359712</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.069638545667323</v>
+        <v>2.080906121602213</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001347149743008959</v>
+        <v>-0.001338058839772659</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.225266067601243</v>
+        <v>1.226071078831882</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3440020379103921</v>
+        <v>0.344660329767266</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1100727654.318469</v>
+        <v>1114853216.855952</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>942.99</v>
+        <v>942.5700000000001</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.03133404674742524</v>
+        <v>0.0308746990346882</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1828438721306077</v>
+        <v>-0.1832078267575975</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>278188650930</v>
+        <v>278064747990</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.36608775137111</v>
+        <v>14.35778503961</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.0152413463507</v>
+        <v>13.00944446476609</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.358790294224883</v>
+        <v>2.357427052375421</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.305578359485751</v>
+        <v>2.30424587753988</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3367211907491515</v>
+        <v>0.3365265866899925</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.52810024304782</v>
+        <v>26.52297882572548</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.06136878952322</v>
+        <v>7.060005547673757</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1492332626123067</v>
+        <v>-0.1493195605228697</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1037895778551334</v>
+        <v>0.1036432092466097</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3821570738151004</v>
+        <v>-0.3822390049607122</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01908821938726816</v>
+        <v>0.01909672491167765</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.579634246376577</v>
+        <v>1.578594488743073</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3097602611010482</v>
+        <v>0.3098206260427906</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1907745172.755973</v>
+        <v>1927355402.634725</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>230.03</v>
+        <v>230.495</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2108747855917668</v>
+        <v>-0.2092795883361921</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3080972147025206</v>
+        <v>-0.3066985502015279</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,37 +3742,37 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>216719084020</v>
+        <v>217157176330</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.08995633187773</v>
+        <v>20.13056768558952</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>17.82133911490994</v>
+        <v>17.85736451459012</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.136447081928304</v>
+        <v>3.142787332735141</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.27554850226402</v>
+        <v>6.288234369557646</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2448950103246337</v>
+        <v>0.2453900595782134</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>16.94217890512299</v>
+        <v>16.96918663029406</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>3.977294007265149</v>
+        <v>3.983634258071986</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06289709123513118</v>
+        <v>0.06277020281054785</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1272977974516962</v>
+        <v>0.127297797451696</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>0.04632303781771174</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02930052601834543</v>
+        <v>0.02924141521508059</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9063480062079311</v>
+        <v>0.9014098705981924</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3383702143838703</v>
+        <v>0.3371713026824387</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1190085071.17632</v>
+        <v>1203153949.425537</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1143.78</v>
+        <v>1151.55005</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.0587026690254544</v>
+        <v>0.06589476249925297</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1151665183924497</v>
+        <v>-0.1091555718872085</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,31 +3868,31 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1077144520980</v>
+        <v>1084461894533</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.26630980260957</v>
+        <v>38.52626463700235</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.13388691474271</v>
+        <v>26.31142246180762</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.52078961084932</v>
+        <v>13.61264048729819</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.12808146639511</v>
+        <v>30.33275080787508</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4045220361789972</v>
+        <v>0.4072700790257096</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>25.93621309831704</v>
+        <v>26.10388095753819</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.09842769394144</v>
+        <v>14.18956872447148</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01861765028684795</v>
+        <v>0.01849299259662781</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005849026910769554</v>
+        <v>0.005809560774193011</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3516223874189415</v>
+        <v>0.350323275556163</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3128830000262121</v>
+        <v>0.3124112426613143</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2756329166.509135</v>
+        <v>2777874152.538623</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>202.01</v>
+        <v>202.52</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.110555287401273</v>
+        <v>0.1133590258131074</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1302045209903122</v>
+        <v>-0.1280086114101183</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,40 +3994,40 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>318626332800</v>
+        <v>319430745600</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.2387459807074</v>
+        <v>16.28014469453376</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.00212329659785</v>
+        <v>15.03999806953615</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.518207942843143</v>
+        <v>2.524627808644659</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.874174357209488</v>
+        <v>2.881501716221234</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4131396057199916</v>
+        <v>0.4141928550489644</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.27450121647869</v>
+        <v>23.30325525607388</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.398262747670495</v>
+        <v>5.404931928648769</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04922867739877446</v>
+        <v>-0.04909863250353514</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08242984407347054</v>
+        <v>0.08245656809687762</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3270721467871623</v>
+        <v>-0.3270555329254892</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02054353744864116</v>
+        <v>0.02049180327868853</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.376465159083515</v>
+        <v>1.375590821887104</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2518889976862511</v>
+        <v>0.2516001176663703</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>894328134.946995</v>
+        <v>902565595.0897374</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>996.65</v>
+        <v>1014.04999</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.15975511245846</v>
+        <v>2.214919620921036</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2058565737051793</v>
+        <v>-0.1919920398406375</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1125606543500</v>
+        <v>1145257915714</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>22.24168712340995</v>
+        <v>22.62921222941307</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.376207842431758</v>
+        <v>6.487526713345554</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.46877886766954</v>
+        <v>12.68602699392959</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>11.16140343910091</v>
+        <v>11.35587268178388</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03170092580822581</v>
+        <v>0.03225326271351839</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>16.19681537324788</v>
+        <v>16.48376497307816</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>12.26252900613687</v>
+        <v>12.47977713239692</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02325146397836306</v>
+        <v>0.02285328281537802</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.488231198393215</v>
+        <v>2.488110836270208</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.775779220960631</v>
+        <v>1.775683448177134</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005317814679175238</v>
+        <v>0.0005226566788881878</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.885321025899236</v>
+        <v>2.887346356521891</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.7728570669088352</v>
+        <v>0.7765953688079688</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25086389113.42723</v>
+        <v>25396725336.12331</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>136.72</v>
+        <v>135.42</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.07277041146368168</v>
+        <v>-0.0815869596285238</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2978852336103037</v>
+        <v>-0.3045612809794276</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>141349612640</v>
+        <v>140005592040</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>84.9192546583851</v>
+        <v>84.11180124223603</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>28.79833800324025</v>
+        <v>28.52450945288761</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.594733412978551</v>
+        <v>9.503502039098562</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.28409715564078</v>
+        <v>11.1768024928092</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>135.870807453419</v>
+        <v>134.5788819875805</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>42.21828966466036</v>
+        <v>41.83455470048725</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>9.998616117295683</v>
+        <v>9.907735633315232</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03240192820099688</v>
+        <v>0.03271177126557351</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.7002455359113148</v>
+        <v>0.6984344625389985</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6270240038221295</v>
+        <v>0.6293102900679443</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2150035842.611379</v>
+        <v>2165299958.742249</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.505</v>
+        <v>27.525</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09233517341722641</v>
+        <v>0.09312945458313604</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.0583704210886683</v>
+        <v>-0.05768572406710037</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>156763097200</v>
+        <v>156877086000</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.34381606765328</v>
+        <v>36.37024312896406</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.422902908581099</v>
+        <v>9.429754683101063</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.461113683747802</v>
+        <v>2.462903259231349</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.840016375161404</v>
+        <v>1.841354325625073</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6078744457333158</v>
+        <v>-0.6083164558738237</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.34641137515843</v>
+        <v>17.35544090621039</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.437909714895755</v>
+        <v>3.439699290379302</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.07008026886572639</v>
+        <v>0.07002934768943885</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4405,7 +4405,7 @@
         <v>2.856965992354253</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05063977200538161</v>
+        <v>-0.05063977200538172</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06253408471187057</v>
+        <v>0.06248864668483197</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3509967713407846</v>
+        <v>0.350231438586782</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2057973852744562</v>
+        <v>0.2056481392028983</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>915873185.0029954</v>
+        <v>922795432.2719091</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>184.86</v>
+        <v>187.56</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1002916852811306</v>
+        <v>0.1163621578022767</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.07509881422924891</v>
+        <v>-0.06159003352178916</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1312237751503</v>
+        <v>1331403833560</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>8.113760780990328</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003832619707208932</v>
+        <v>0.003888597599719286</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.968315520817014</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2116.027360092321</v>
+        <v>2085.551918248381</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2740.894075746785</v>
+        <v>2701.423431662151</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.622849724115547</v>
+        <v>1.599488163787588</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.8636009620560741</v>
+        <v>0.8652646860929261</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3153588301.495565</v>
+        <v>3233958452.709249</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>564.38</v>
+        <v>571.6</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5118671804323867</v>
+        <v>0.531208193655254</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1599362934075585</v>
+        <v>-0.1491895271125137</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>313.43</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>71134877356</v>
+        <v>72044891557</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.825352834830912</v>
+        <v>1.826435715393559</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.3916864181733605</v>
+        <v>0.3944226601182411</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3712538712.750047</v>
+        <v>3756089378.837296</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>151.8</v>
+        <v>152.84</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.05684993551869777</v>
+        <v>-0.05038830134833849</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3272469420315546</v>
+        <v>-0.3226378301719552</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2000994195651</v>
+        <v>2014703246794</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-98.57142857142858</v>
+        <v>-99.24675324675324</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>121.5732309380142</v>
+        <v>122.4061437191443</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>120.7236317134842</v>
+        <v>121.5507237884766</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>6.996755329183173</v>
+        <v>7.044690938816576</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9857142857142859</v>
+        <v>-0.9924675324675324</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>467.2033106913847</v>
+        <v>470.4932197729782</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>117.456180733092</v>
+        <v>118.2832728080845</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01420443900425854</v>
+        <v>-0.01410778487860659</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.36022150412568</v>
+        <v>3.350539605680813</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7761601261188797</v>
+        <v>0.7750722587956251</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>13342531663.91755</v>
+        <v>13552560968.73255</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>759.21</v>
+        <v>761.6</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1113046811072258</v>
+        <v>0.114803078372602</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02586704646060278</v>
+        <v>-0.02280046704389438</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>808739513561</v>
+        <v>811285432922</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9954109491331716</v>
+        <v>0.9949899115174288</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1150244482454095</v>
+        <v>0.1144748591753932</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>29882618301.15575</v>
+        <v>30313236321.26533</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>429.84</v>
+        <v>432.905</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3448891452098637</v>
+        <v>0.3544789582334731</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.1026304801670147</v>
+        <v>-0.09623173277661801</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>262.81</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2229356563200</v>
+        <v>2245253124400</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>28.51512692708937</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6542725933493203</v>
+        <v>0.6589379234689362</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.36635940341746</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.58294572773731</v>
+        <v>42.27437518996225</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.55939094967581</v>
+        <v>42.25098718150321</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2791736460078169</v>
+        <v>0.2771970755708528</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.181401872113908</v>
+        <v>2.181743752284683</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3375740463334496</v>
+        <v>0.3378386981429733</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>3999456192.476538</v>
+        <v>4032137559.084684</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>27.955</v>
+        <v>27.785</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.01946686160737376</v>
+        <v>-0.02542968162263914</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.06816666666666671</v>
+        <v>-0.07383333333333331</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>70087006313</v>
+        <v>69660793265</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-22.01181102362204</v>
+        <v>-21.87795275590551</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-84.214805691745</v>
+        <v>-83.70267845269666</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.940661949688495</v>
+        <v>1.928860397757165</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.137615110542664</v>
+        <v>2.124615841403252</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1638088262223037</v>
+        <v>0.162812671671855</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.32082748975207</v>
+        <v>16.25037905206612</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.734071890156445</v>
+        <v>2.722270338225114</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03110419626520195</v>
+        <v>0.03129450438077781</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2302678767516122</v>
+        <v>0.2281754905119234</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1593563858443711</v>
+        <v>0.1628478387281664</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>502982889.4132234</v>
+        <v>512921677.7885841</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>311.25</v>
+        <v>311.945</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1649451591612869</v>
+        <v>-0.1630805387134704</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1967534646055382</v>
+        <v>-0.1949598699321273</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>210190237500</v>
+        <v>210659577950</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>18.87507580351728</v>
+        <v>18.91722255912675</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.00107819925175</v>
+        <v>16.03680751442759</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.500092033114079</v>
+        <v>2.505674567935009</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.155994749124854</v>
+        <v>6.169740665110852</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.170419547641685</v>
+        <v>1.173033014583408</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.059870469988676</v>
+        <v>9.078717092703446</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.664306465809475</v>
+        <v>2.669848838509391</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07161131829445694</v>
+        <v>0.07145291664791217</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01137349397590362</v>
+        <v>0.01134815432207601</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9619228569819732</v>
+        <v>0.962369697447938</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2345931210938006</v>
+        <v>0.2348380311758343</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>796387792.335734</v>
+        <v>804518829.2742085</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>145.6</v>
+        <v>147.65</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2560421286333573</v>
+        <v>-0.2455674470653516</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5581183611532625</v>
+        <v>-0.551896813353566</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>419396432000</v>
+        <v>425301395500</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.46913580246913</v>
+        <v>22.78549382716049</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.18035505959968</v>
+        <v>16.40816912465585</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.843047661507168</v>
+        <v>5.92531584630174</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.467525310010183</v>
+        <v>6.558585934223926</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4890341321713872</v>
+        <v>0.4959195715323169</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.28839957582185</v>
+        <v>14.44494685843054</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.508790169552921</v>
+        <v>7.591058354347493</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06847936178913415</v>
+        <v>-0.06752858162206524</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01373626373626374</v>
+        <v>0.01354554690145615</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.085549571233289</v>
+        <v>2.08144647420547</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5629532711629709</v>
+        <v>0.5580451944419919</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4147522932.392493</v>
+        <v>4183163699.936793</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>108.765</v>
+        <v>109.755</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4303655798324724</v>
+        <v>0.4433850431160116</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1657206412518217</v>
+        <v>-0.1581268696786071</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,40 +5422,40 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>428690141339</v>
+        <v>432592161657</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>32.37053571428572</v>
+        <v>32.64732142857142</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>20.9598809751181</v>
+        <v>21.15066185283949</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.769682453043822</v>
+        <v>6.827566925811292</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.550224619667894</v>
+        <v>8.623333697921845</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.035857142857143</v>
+        <v>1.044714285714285</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.52885465502772</v>
+        <v>22.71589511314252</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.122070925211212</v>
+        <v>7.181200225345441</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.03171288231060423</v>
+        <v>0.03143828687525745</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.5444045580560992</v>
+        <v>0.5435602751215325</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.166508857283745</v>
+        <v>0.1658711593978481</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0.1023396098336123</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01526226267641245</v>
+        <v>0.01512459569040135</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7116709206384128</v>
+        <v>0.7104229440262755</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3350370560091954</v>
+        <v>0.3336878824100721</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>1981790917.794049</v>
+        <v>1996854323.029983</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>86.105</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.09553568529195333</v>
+        <v>-0.09506299620117042</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1192205400981997</v>
+        <v>-0.1187602291325696</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,37 +5548,37 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>260381530151</v>
+        <v>260517600000</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.28316690442226</v>
+        <v>12.28958630527818</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.06757550566479</v>
+        <v>11.07335961689822</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.016819876464893</v>
+        <v>2.017873823631927</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.45722641669904</v>
+        <v>1.457987989067096</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.6528890516764997</v>
+        <v>0.653230263073346</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.57893000968881</v>
+        <v>15.58303703480124</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>3.99787405717052</v>
+        <v>3.998928004337555</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.07362273348990217</v>
+        <v>0.07358427991045519</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.1098335763000022</v>
+        <v>0.109833576300002</v>
       </c>
       <c r="V41" s="4" t="n">
         <v>-0.2902196875898506</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02148539573776204</v>
+        <v>0.02147417295414974</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.7300563939504189</v>
+        <v>0.7288060149510324</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.2243778026656516</v>
+        <v>0.2241820964238002</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1072418318.106382</v>
+        <v>1079462179.585685</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:09 ET</t>
+          <t>2026-09-18 15:54 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -443,10 +443,10 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -470,7 +470,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>336.2</v>
+        <v>336.13</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.240544584647455</v>
+        <v>0.2402862916048456</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.02429114548567779</v>
+        <v>-0.02449429724003827</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,31 +714,31 @@
         <v>240.21</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4937889087200</v>
+        <v>4936860972280</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.37899543378995</v>
+        <v>38.37100456621005</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>35.09641723390044</v>
+        <v>35.08910982995525</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.57764738926745</v>
+        <v>10.57544502365993</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.94143920200894</v>
+        <v>45.93187376255581</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.172691527143581</v>
+        <v>1.172447361745306</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.57309264389919</v>
+        <v>29.56699056467599</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.67353598087498</v>
+        <v>10.67133361526746</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02768045162340924</v>
+        <v>0.02768621615383984</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.00315288518738846</v>
+        <v>0.003153541784428644</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3100537800948155</v>
+        <v>0.3096765658979816</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2917465145752744</v>
+        <v>0.291748504721329</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>12991193528.28819</v>
+        <v>13594114828.82618</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>493.7863</v>
+        <v>493.78</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.0440781017697407</v>
+        <v>0.04406478084115051</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1082382792747237</v>
+        <v>-0.1082496568662863</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,31 +842,31 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3666634859965</v>
+        <v>3666588079000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.43257222222222</v>
+        <v>27.43222222222222</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.02462391993281</v>
+        <v>24.02431740043097</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.04943921589988</v>
+        <v>11.04929824101447</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.292147876632901</v>
+        <v>8.292042080802554</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8713501478473817</v>
+        <v>0.8713390306780081</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.18873529635841</v>
+        <v>18.18850986656644</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.37451643708244</v>
+        <v>11.37437546219703</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01826934029657904</v>
+        <v>0.01826957338994829</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.00737160994543591</v>
+        <v>0.007371703997731784</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5582010347179622</v>
+        <v>0.5574561254179546</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4337879675422517</v>
+        <v>0.4338476357762108</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10618505318.93155</v>
+        <v>11015710913.17164</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>349.78</v>
+        <v>349.54</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.109884203630638</v>
+        <v>0.1091226614930907</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.143975918357358</v>
+        <v>-0.1445632754949707</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4233076485617</v>
+        <v>4230171978908</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.15491559086395</v>
+        <v>17.10079443892751</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.99938113772071</v>
+        <v>20.98497250522871</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.404068256305706</v>
+        <v>9.374399849939218</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.554725362228329</v>
+        <v>6.534046199725207</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1525596621026175</v>
+        <v>0.1520783595506874</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.1059855462401</v>
+        <v>13.06519121300237</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.531561718466984</v>
+        <v>9.501893312100496</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01270536147651478</v>
+        <v>0.01274557181886761</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1830751831038981</v>
+        <v>-0.1850933121467472</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2891482152799802</v>
+        <v>0.2859635067242161</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002458688318371548</v>
+        <v>0.002460376494821765</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7639422798140121</v>
+        <v>0.7637474871723581</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3622859847015646</v>
+        <v>0.3622167366566593</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>7930389977.807666</v>
+        <v>8153408895.182483</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>253.84</v>
+        <v>253.71</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1207064017660044</v>
+        <v>0.1201324503311259</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1161559888579387</v>
+        <v>-0.116608635097493</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,31 +1094,31 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2730582264000</v>
+        <v>2729183841000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.14603174603175</v>
+        <v>20.13571428571429</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.60571264283663</v>
+        <v>22.59413549721904</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.520243224009901</v>
+        <v>3.51844038907797</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.949608498604111</v>
+        <v>4.947073637649106</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2280489888002578</v>
+        <v>0.22793219724438</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.32309258770773</v>
+        <v>11.31589286881341</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.707755192863036</v>
+        <v>3.705397639490512</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004256662975976923</v>
+        <v>-0.004259515180091527</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8380302743492216</v>
+        <v>0.8378168744020118</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4631250225014107</v>
+        <v>0.4627066709514093</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8372734468.453293</v>
+        <v>8563813948.280845</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>220.58</v>
+        <v>222.27</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1680169069154915</v>
+        <v>0.1769658078706424</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.06747273188467062</v>
+        <v>-0.06032806290690784</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,31 +1220,31 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5342668180000</v>
+        <v>5383601670000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.74591194968553</v>
+        <v>27.95849056603773</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.43196133210704</v>
+        <v>16.55785676528892</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.63437242754209</v>
+        <v>17.76948027686001</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.30219666002865</v>
+        <v>23.48072922125563</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2227222863988363</v>
+        <v>0.2244286997817995</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>22.93471127715938</v>
+        <v>23.10989001442223</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.68855948958474</v>
+        <v>17.82366733890266</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02377201722454715</v>
+        <v>0.02359126989423049</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002357421343730166</v>
+        <v>0.002339497008143249</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.32757200663413</v>
+        <v>1.328091171552411</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.411357244292535</v>
+        <v>0.4121028150628047</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26232323242.23933</v>
+        <v>27017728029.57898</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>666.26</v>
+        <v>665.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.02436928631158408</v>
+        <v>0.02358516549385681</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1574860900354071</v>
+        <v>-0.1581310065756196</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>790.8</v>
@@ -1346,31 +1346,31 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1697288402128</v>
+        <v>1695989183978</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.75882571534746</v>
+        <v>24.73987365291713</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.15169510550413</v>
+        <v>20.13626964922009</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.436158924187726</v>
+        <v>7.430466790412184</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.486075698355033</v>
+        <v>6.481110821871137</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.075559271646224</v>
+        <v>-5.071674098848008</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.75642933846384</v>
+        <v>16.74429527773834</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.860504372997792</v>
+        <v>7.85481223922225</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02414203735123963</v>
+        <v>0.02416053143917428</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
@@ -1379,7 +1379,7 @@
         <v>0.228622484893837</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2736216805247407</v>
+        <v>0.2736216805247405</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003151922672830427</v>
+        <v>0.003154337213668795</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7708869468135293</v>
+        <v>0.769151071197354</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4136044229202094</v>
+        <v>0.4138640308670974</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10383135938.78237</v>
+        <v>10585494580.24203</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>365.42</v>
+        <v>364.27</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1658410895737263</v>
+        <v>-0.1684662407613742</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2674458232263496</v>
+        <v>-0.2697512178497685</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1443243608715</v>
+        <v>1438701629212</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>309.5932203389831</v>
+        <v>308.7033898305085</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>173.5448086228382</v>
+        <v>172.998652063492</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.92455682814928</v>
+        <v>13.88453497150137</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.61464505284487</v>
+        <v>13.57551394229662</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.241284316065883</v>
+        <v>-8.217597278586773</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>119.4623098626538</v>
+        <v>119.1240962098437</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.86707710968066</v>
+        <v>13.82781757411286</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.003993707483360202</v>
+        <v>0.00400499998262735</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7839382393270924</v>
+        <v>0.7844265614116559</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1229130160984628</v>
+        <v>0.1232203940178107</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.535683387402444</v>
+        <v>1.53428605529164</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5667998468307686</v>
+        <v>0.5669001191480243</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>13176844852.79364</v>
+        <v>13320249859.17986</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>356.975</v>
+        <v>357.61</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.02691158452970699</v>
+        <v>0.0287382918794552</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2788383838383838</v>
+        <v>-0.2775555555555556</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,31 +1598,31 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1698337120500</v>
+        <v>1701358183800</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>44.28970223325062</v>
+        <v>44.36848635235732</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.48975638401908</v>
+        <v>19.52442546533809</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>19.06016700148141</v>
+        <v>19.0940719137188</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>17.06633413582104</v>
+        <v>17.09669234627345</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4407044628160084</v>
+        <v>0.4414884038031592</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>33.18144245259553</v>
+        <v>33.23196494269368</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.46222085316035</v>
+        <v>19.49185428039145</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02319573133077664</v>
+        <v>0.02315973225108485</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007115344211779536</v>
+        <v>0.007102709655770252</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.602707345413127</v>
+        <v>1.603588744680662</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3925035147436929</v>
+        <v>0.3932084614129385</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8726089082.55924</v>
+        <v>9006536579.43968</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>896.895</v>
+        <v>895.3099999999999</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04961380924517256</v>
+        <v>0.04775892334698639</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1820383036935704</v>
+        <v>-0.183483812129503</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,40 +1724,40 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>397754097705</v>
+        <v>397051183490</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.04319437468608</v>
+        <v>44.96785534907082</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.56667434270604</v>
+        <v>39.49675180011946</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.354679880205867</v>
+        <v>1.352414049293736</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.8808256178937</v>
+        <v>11.86095380733534</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.553184127681714</v>
+        <v>3.547241089366438</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.74515563165169</v>
+        <v>26.69918337871458</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.318186438738773</v>
+        <v>1.315920607826641</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02214140517197331</v>
+        <v>0.02217850082348838</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.138412442363623</v>
+        <v>0.1385203415369163</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1140187443501308</v>
+        <v>0.1141243314792548</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006176865742366721</v>
+        <v>0.006187800873440485</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1835311703353185</v>
+        <v>-0.1835038483254343</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1764920483004075</v>
+        <v>0.1763090659402758</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1714044398.323975</v>
+        <v>1789294524.128361</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>71.8</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2109022784295572</v>
+        <v>-0.2110121806191908</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4249559506647446</v>
+        <v>-0.425036040365209</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,37 +1850,37 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>298970891928</v>
+        <v>298929252528</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>22.22910216718266</v>
+        <v>22.22600619195047</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>19.13788190697838</v>
+        <v>19.13521646381585</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.180818064564786</v>
+        <v>6.179957226394026</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>9.975836981177931</v>
+        <v>9.974447588840722</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6533187344257345</v>
+        <v>0.6532277429585444</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>9.941516754922485</v>
+        <v>9.940155858485387</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.288529284507477</v>
+        <v>6.287668446336717</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.0367748442970421</v>
+        <v>0.03677996685510115</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1615236354383141</v>
+        <v>0.1615236354383138</v>
       </c>
       <c r="V11" s="4" t="n">
         <v>0.1444115006001652</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.09015660905514743</v>
+        <v>0.08771628690465143</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3529625042741945</v>
+        <v>0.3530217611262856</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2224196886.446198</v>
+        <v>2357773889.265933</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>508.96</v>
+        <v>509.77</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02437354080249587</v>
+        <v>0.02600381148791331</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05352028861531599</v>
+        <v>-0.0520139844534534</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1097752205711</v>
+        <v>1099499257123</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.80093760550032</v>
+        <v>12.80000643688118</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.94363920441896</v>
+        <v>22.98015356263096</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.855016896071351</v>
+        <v>2.854809215804017</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.461800841401429</v>
+        <v>1.461694506763071</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3526332321163337</v>
+        <v>0.3526075807921941</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.51413969599028</v>
+        <v>15.51309554852707</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.085752533095738</v>
+        <v>3.085544852828403</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02204795330746677</v>
+        <v>0.02204955724121188</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4420703057850193</v>
+        <v>-0.4429973497785569</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06130525453407087</v>
+        <v>0.05954181252370994</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.03911907307699093</v>
+        <v>0.03918452948205382</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1490255769318704</v>
+        <v>0.14899060627112</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2144817563.720947</v>
+        <v>2282909512.691259</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>348.755</v>
+        <v>349.67</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07150973401758165</v>
+        <v>0.07432096656371323</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04841746248294676</v>
+        <v>-0.04592087312414728</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,31 +2102,31 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>934492510050</v>
+        <v>936944261700</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>14.99376612209802</v>
+        <v>15.03310404127257</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.9250479298652</v>
+        <v>13.96158194043373</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.139747642398524</v>
+        <v>3.147985141768554</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.596311428518038</v>
+        <v>2.603123158692786</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7850623387790203</v>
+        <v>0.7871220426971945</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>19.99304969997853</v>
+        <v>20.01936734328038</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.25788306420995</v>
+        <v>6.266120563579979</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1739275577407288</v>
+        <v>-0.1734724322929273</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01720405442215882</v>
+        <v>0.01715903566219578</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7668354593375404</v>
+        <v>0.7668452127602949</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.164616470233544</v>
+        <v>0.1645804732340038</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2132541692.304957</v>
+        <v>2272143514.789128</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>368.84</v>
+        <v>368.29</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06453471572579161</v>
+        <v>0.06294732256439617</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04339030526233889</v>
+        <v>-0.04481676478979169</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,31 +2228,31 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>688641693305</v>
+        <v>687614817339</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.33729821580289</v>
+        <v>31.29056924384027</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.62897807076674</v>
+        <v>24.59225228739476</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.47926841631451</v>
+        <v>15.45618632752652</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.06246139177895</v>
+        <v>20.03254502217295</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.113205965210393</v>
+        <v>2.110054833877388</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.06596283627741</v>
+        <v>24.02618108938758</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.74068033199964</v>
+        <v>15.71466052281514</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03050790131616888</v>
+        <v>0.03055926002484675</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007266023207895023</v>
+        <v>0.007276874202394852</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3058199398892936</v>
+        <v>0.3055468132238942</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1739239191531709</v>
+        <v>0.1741592411990704</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2244048875.587618</v>
+        <v>2431162237.331487</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>565.9</v>
+        <v>565.24</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.004918926523483469</v>
+        <v>0.003746905863463379</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05876286945095899</v>
+        <v>-0.05986061906425166</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.23</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>496314672400</v>
+        <v>495735828640</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.07633168588687</v>
+        <v>31.04008786381109</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.49720327144646</v>
+        <v>25.4674662964347</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.14687091753841</v>
+        <v>14.13037165122709</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>88.95451791124576</v>
+        <v>88.85077169844948</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.373462873617321</v>
+        <v>1.371861026123793</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.0507079688913</v>
+        <v>23.01898302767227</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.53095395034632</v>
+        <v>14.51095483966593</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03313206881047634</v>
+        <v>0.03317896155523677</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005955115744831243</v>
+        <v>0.005962069209539311</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2929495295054146</v>
+        <v>0.2928800069420453</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1892123701042264</v>
+        <v>0.1892630957122217</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1482031342.379022</v>
+        <v>1553689433.673885</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>377.58</v>
+        <v>376.9</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1224138134681041</v>
+        <v>0.1203924103398708</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1820545037043456</v>
+        <v>-0.1835275767947663</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>342897164062</v>
+        <v>342279625868</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.27303710372324</v>
+        <v>24.23638351231432</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.35945772673007</v>
+        <v>17.32819433551714</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7615533950889634</v>
+        <v>0.760403408507339</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.473815226365455</v>
+        <v>3.468569578554958</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.735479361850413</v>
+        <v>-0.7343687484605945</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.04251322353763</v>
+        <v>15.02242075332842</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8609537891982075</v>
+        <v>0.8598038026165832</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06889494810016018</v>
+        <v>0.06899914051299065</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3982601003917106</v>
+        <v>0.398667572802877</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01026841403180612</v>
+        <v>0.01056282027615407</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02399491498490386</v>
+        <v>0.02403820642080128</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4282802710404795</v>
+        <v>0.4284111499557166</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.208504715997248</v>
+        <v>0.2079717007585567</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1746645439.662369</v>
+        <v>1819232989.747476</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>162.76</v>
+        <v>163.18</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3270281123123995</v>
+        <v>0.3304524905820678</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.07737656595431097</v>
+        <v>-0.07499574854033209</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>674552309600</v>
+        <v>676292982800</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>20.94851994851995</v>
+        <v>21.001287001287</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.73726028527921</v>
+        <v>14.77528958805518</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.868370227109068</v>
+        <v>1.873076449343599</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.619237131891433</v>
+        <v>2.625834706530958</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.051209244959247</v>
+        <v>2.056376018876021</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.834650249912983</v>
+        <v>9.858308148973199</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.956388838974132</v>
+        <v>1.961095061208663</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04529096187116759</v>
+        <v>0.04517716548455662</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4214663745502998</v>
+        <v>0.4213790447982231</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08173652455699099</v>
+        <v>0.08167006657796794</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.0253133448021627</v>
+        <v>0.02524819218041427</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.533623678586268</v>
+        <v>-0.5335105066356072</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2504661472028754</v>
+        <v>0.250161637469347</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2234192800.051252</v>
+        <v>2383481130.017454</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>270.54</v>
+        <v>269.99</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3047503835854144</v>
+        <v>0.3020978637695941</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.03746397694524484</v>
+        <v>-0.03942078485786449</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,31 +2732,31 @@
         <v>173.33</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>651973917465</v>
+        <v>650648473336</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.27630057803468</v>
+        <v>31.21271676300578</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.82216027203493</v>
+        <v>21.77779645097476</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.657618452807647</v>
+        <v>6.644083706930531</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.769058314013017</v>
+        <v>7.753264043026444</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.872499847885616</v>
+        <v>-3.864627167630064</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20.17632863349342</v>
+        <v>20.13703525838966</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.94980973424624</v>
+        <v>6.936274988369124</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02869439942128407</v>
+        <v>0.02875285314062213</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01951652251053449</v>
+        <v>0.01955627986221712</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1657701297219941</v>
+        <v>-0.1659156819489056</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2037439017414996</v>
+        <v>0.2038433219200969</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1636745130.11503</v>
+        <v>1729617379.845727</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>107.03</v>
+        <v>106.73</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.05081591014256803</v>
+        <v>-0.05347642800631869</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2081237052382361</v>
+        <v>-0.2103432968333826</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>851753302400</v>
+        <v>849365878400</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.72393501805054</v>
+        <v>38.53068592057762</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.48673570790634</v>
+        <v>34.39007102779449</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.160069904631442</v>
+        <v>1.154280656664492</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.684910077566725</v>
+        <v>8.641568639426698</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.364151558910409</v>
+        <v>9.317420413521504</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.3789266468405</v>
+        <v>21.27948547818577</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.244634483887802</v>
+        <v>1.238845235920852</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01582543473821715</v>
+        <v>0.01590480656633828</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1228646093394332</v>
+        <v>0.1204014638247368</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.053590002530578</v>
+        <v>0.05127881962617709</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009132953377557694</v>
+        <v>0.009158624566663543</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05874921969177545</v>
+        <v>-0.05882571029802023</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3022903094301135</v>
+        <v>0.3021983656671209</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2670418352.014382</v>
+        <v>2766554545.643186</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.145</v>
+        <v>146.335</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03071448564835433</v>
+        <v>0.03205449558556195</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1261883408071748</v>
+        <v>-0.1250523168908819</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,31 +2984,31 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>347417200098</v>
+        <v>347868869796</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.65111111111111</v>
+        <v>21.67925925925926</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.67975560613948</v>
+        <v>20.7066409156962</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>3.991832890178325</v>
+        <v>3.997022587048442</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.518684290475226</v>
+        <v>6.527159093001417</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.66134603174625</v>
+        <v>20.68820740740763</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.52616919629246</v>
+        <v>17.54742024070763</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.280048718839048</v>
+        <v>4.285238415709165</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04580371954961135</v>
+        <v>0.04574424842709216</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02935851380478292</v>
+        <v>0.0293203949841118</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04234112358032071</v>
+        <v>-0.04268400994052118</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1490285887018052</v>
+        <v>0.1484968291390396</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1262485327.122565</v>
+        <v>1299735702.618421</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>299.85</v>
+        <v>299.98</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1329304445972097</v>
+        <v>-0.1325545264974853</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2836494815805819</v>
+        <v>-0.2833389077356777</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>418.58</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>298985532450</v>
+        <v>299115157660</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>20.93924581005587</v>
+        <v>20.94832402234637</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>19.9817009335456</v>
+        <v>19.99036400215111</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.767304655802241</v>
+        <v>1.768070870927318</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>17.93650478425709</v>
+        <v>17.94428115785039</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.182648272054078</v>
+        <v>-7.185762309990937</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.03104881664227</v>
+        <v>15.03646906376751</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.124813995188443</v>
+        <v>2.12558021031352</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.05050746059936988</v>
+        <v>0.05048557257390845</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.04792108938547468</v>
+        <v>0.0479210893854749</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03098215774553943</v>
+        <v>0.03096873124874991</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7066984552760949</v>
+        <v>0.7063059258783332</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2382936415908705</v>
+        <v>0.2382806161863175</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1247262395.590235</v>
+        <v>1284599331.473999</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>556.8099999999999</v>
+        <v>559.8200000000001</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.491654347153666</v>
+        <v>1.505123716570402</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.04774853351119335</v>
+        <v>-0.04260085851589612</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>584.73</v>
@@ -3236,31 +3236,31 @@
         <v>154.78</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>907934386000</v>
+        <v>912842492000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>141.3223350253807</v>
+        <v>142.0862944162436</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>40.88917263965699</v>
+        <v>41.1102110722379</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>21.98122227333253</v>
+        <v>22.10004822660695</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13.5094179162204</v>
+        <v>13.58244704272284</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.140950961672798</v>
+        <v>1.14711870721371</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>84.63560235118493</v>
+        <v>85.09353349505504</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>21.96161205665174</v>
+        <v>22.08043800992616</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009255074077566658</v>
+        <v>0.009205312059465348</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.546781223666731</v>
+        <v>2.547107438065864</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6557376936892084</v>
+        <v>0.6568543593127123</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9381118117.115662</v>
+        <v>9638713874.855129</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1678.57</v>
+        <v>1679.92</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4423430182198154</v>
+        <v>0.4435030312515014</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1606982139642793</v>
+        <v>-0.1600232004640093</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>925.87</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>646951077153</v>
+        <v>647471391441</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>52.46734397677794</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>34.39407344463805</v>
+        <v>34.42173508469492</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.77565395190715</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5254763022248963</v>
+        <v>0.5242504146778677</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2782615181512065</v>
+        <v>0.2772342948012847</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004634897561614946</v>
+        <v>0.004631172912995857</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.683729028827948</v>
+        <v>1.684420144898762</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4353468110970209</v>
+        <v>0.4356624008892414</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2060004173.352702</v>
+        <v>2144072722.60616</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>198.57</v>
+        <v>198.2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1281995158481517</v>
+        <v>-0.1298239615304612</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2193041085118931</v>
+        <v>-0.2207587969333595</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>156943770900</v>
+        <v>156651334000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>74.3707865168539</v>
+        <v>74.23220973782769</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>77.27993620907017</v>
+        <v>77.13593874521685</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.669703398053088</v>
+        <v>1.666592201712857</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>25.75045265087213</v>
+        <v>25.70247124642623</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3980379292022683</v>
+        <v>0.3972962560703509</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>28.14313250359712</v>
+        <v>28.10105525179856</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.080906121602213</v>
+        <v>2.077794925261982</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001338058839772659</v>
+        <v>-0.001340556729634999</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.03764430762916238</v>
+        <v>-0.03764430762916227</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1546467220498904</v>
+        <v>0.1546467220498906</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.226071078831882</v>
+        <v>1.22626418528472</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.344660329767266</v>
+        <v>0.3443784423467804</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1114853216.855952</v>
+        <v>1137354153.473872</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>942.5700000000001</v>
+        <v>942</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.0308746990346882</v>
+        <v>0.03025129856740216</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1832078267575975</v>
+        <v>-0.1837017651799409</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>278064747990</v>
+        <v>277896594000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.35778503961</v>
+        <v>14.35100548446069</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.00944446476609</v>
+        <v>13.00157726832984</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.357427052375421</v>
+        <v>2.356313913360523</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.30424587753988</v>
+        <v>2.303157843281028</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3365265866899925</v>
+        <v>0.3363676833112766</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.52297882572548</v>
+        <v>26.51879699296022</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.060005547673757</v>
+        <v>7.05889240865886</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1493195605228697</v>
+        <v>-0.1493901001175998</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1036432092466097</v>
+        <v>0.1037895778551334</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3822390049607122</v>
+        <v>-0.3821570738151003</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01909672491167765</v>
+        <v>0.01910828025477707</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.578594488743073</v>
+        <v>1.577960615288972</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3098206260427906</v>
+        <v>0.3098876404351355</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1927355402.634725</v>
+        <v>1990542610.318058</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>230.495</v>
+        <v>229.55</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2092795883361921</v>
+        <v>-0.2125214408233276</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3066985502015279</v>
+        <v>-0.3095409974132226</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,37 +3742,37 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>217157176330</v>
+        <v>216266859700</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.13056768558952</v>
+        <v>20.04803493449782</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>17.85736451459012</v>
+        <v>17.78415160556265</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.142787332735141</v>
+        <v>3.129902306901892</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.288234369557646</v>
+        <v>6.262453413444794</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2453900595782134</v>
+        <v>0.2443839917402933</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>16.96918663029406</v>
+        <v>16.91429996301091</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>3.983634258071986</v>
+        <v>3.970749232238737</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06277020281054785</v>
+        <v>0.06302861205322251</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.127297797451696</v>
+        <v>0.1272977974516962</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>0.04632303781771174</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02924141521508059</v>
+        <v>0.02936179481594424</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.9014098705981924</v>
+        <v>0.8996161912189466</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3371713026824387</v>
+        <v>0.3397939648974554</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1203153949.425537</v>
+        <v>1262584088.404345</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1151.55005</v>
+        <v>1152.22</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06589476249925297</v>
+        <v>0.06651487987594562</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1091555718872085</v>
+        <v>-0.108637295478281</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,31 +3868,31 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1084461894533</v>
+        <v>1085092815020</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.52626463700235</v>
+        <v>38.54867848778856</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.31142246180762</v>
+        <v>26.32672994885804</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.61264048729819</v>
+        <v>13.62056007747365</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.33275080787508</v>
+        <v>30.35039782756279</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4072700790257096</v>
+        <v>0.4075070210409032</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>26.10388095753819</v>
+        <v>26.11975612449428</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.18956872447148</v>
+        <v>14.19819816056576</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01849299259662781</v>
+        <v>0.01848127618431459</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005809560774193011</v>
+        <v>0.005806182847025742</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.350323275556163</v>
+        <v>0.350247177976581</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3124112426613143</v>
+        <v>0.3124183205632644</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2777874152.538623</v>
+        <v>2888317711.147994</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -3997,37 +3997,37 @@
         <v>319430745600</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.28014469453376</v>
+        <v>16.27974276527331</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>15.03999806953615</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.524627808644659</v>
+        <v>2.524565479850469</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.881501716221234</v>
+        <v>2.881430576813353</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4141928550489644</v>
+        <v>0.4141826293273239</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.30325525607388</v>
+        <v>23.30298652673186</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.404931928648769</v>
+        <v>5.404869599854579</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04909863250353514</v>
+        <v>-0.04909984469572612</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08245656809687762</v>
+        <v>0.08242984407347032</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3270555329254892</v>
+        <v>-0.3270721467871623</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4066,13 +4066,13 @@
         <v>0.02049180327868853</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.375590821887104</v>
+        <v>1.375227679397425</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2516001176663703</v>
+        <v>0.2515769412288019</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>902565595.0897374</v>
+        <v>930258124.2022237</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>1014.04999</v>
+        <v>1015.8</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.214919620921036</v>
+        <v>2.220467810400145</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1919920398406375</v>
+        <v>-0.190597609561753</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1145257915714</v>
+        <v>1147234362000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>22.62921222941307</v>
+        <v>22.66904708770364</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.487526713345554</v>
+        <v>6.498722647210335</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.68602699392959</v>
+        <v>12.70835857500498</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>11.35587268178388</v>
+        <v>11.37586275366348</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03225326271351839</v>
+        <v>0.03231003906686979</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>16.48376497307816</v>
+        <v>16.51326137594007</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>12.47977713239692</v>
+        <v>12.50210871347232</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02285328281537802</v>
+        <v>0.02281312421149394</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.488110836270208</v>
+        <v>2.488231198393215</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.775683448177134</v>
+        <v>1.775779220960631</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005226566788881878</v>
+        <v>0.0005217562512305573</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.887346356521891</v>
+        <v>2.887672519638909</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.7765953688079688</v>
+        <v>0.7770948884887525</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25396725336.12331</v>
+        <v>25714651977.77043</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>135.42</v>
+        <v>135.47</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0815869596285238</v>
+        <v>-0.08124786162218367</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3045612809794276</v>
+        <v>-0.3043045099267689</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>140005592040</v>
+        <v>140057285140</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>84.11180124223603</v>
+        <v>84.14285714285715</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>28.52450945288761</v>
+        <v>28.53504132020887</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.503502039098562</v>
+        <v>9.507010938093945</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.1768024928092</v>
+        <v>11.18092921061042</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>134.5788819875805</v>
+        <v>134.6285714285743</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>41.83455470048725</v>
+        <v>41.84788912009171</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>9.907735633315232</v>
+        <v>9.910893642411079</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03271177126557351</v>
+        <v>0.03270090517192214</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.6984344625389985</v>
+        <v>0.6973746617483811</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6293102900679443</v>
+        <v>0.6292376666408013</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2165299958.742249</v>
+        <v>2212118088.143447</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.525</v>
+        <v>27.6</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09312945458313604</v>
+        <v>0.09610800895529725</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05768572406710037</v>
+        <v>-0.05511811023622049</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,31 +4372,31 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>156877086000</v>
+        <v>157304544000</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.37024312896406</v>
+        <v>36.4693446088795</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.429754683101063</v>
+        <v>9.45544883755093</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.462903259231349</v>
+        <v>2.46961416729465</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.841354325625073</v>
+        <v>1.846371639863834</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6083164558738237</v>
+        <v>-0.6099739939007278</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.35544090621039</v>
+        <v>17.38930164765526</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.439699290379302</v>
+        <v>3.446410198442602</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.07002934768943885</v>
+        <v>0.06983905054897842</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
@@ -4405,7 +4405,7 @@
         <v>2.856965992354253</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05063977200538172</v>
+        <v>-0.05063977200538161</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06248864668483197</v>
+        <v>0.06231884057971014</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.350231438586782</v>
+        <v>0.3502851110013918</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2056481392028983</v>
+        <v>0.2050434135637993</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>922795432.2719091</v>
+        <v>973988281.7226467</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>187.56</v>
+        <v>187.5</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1163621578022767</v>
+        <v>0.1160050361906955</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.06159003352178916</v>
+        <v>-0.06189022864862159</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1331403833560</v>
+        <v>1330977920625</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>8.113760780990328</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003888597599719286</v>
+        <v>0.003887353646552389</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.968315520817014</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2085.551918248381</v>
+        <v>2086.219614862221</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2701.423431662151</v>
+        <v>2702.288207161095</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.599488163787588</v>
+        <v>1.6</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.8652646860929261</v>
+        <v>0.8651532945538819</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3233958452.709249</v>
+        <v>3530852861.059164</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>571.6</v>
+        <v>573</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.531208193655254</v>
+        <v>0.5349585286292171</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1491895271125137</v>
+        <v>-0.1471056666120895</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>313.43</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>72044891557</v>
+        <v>72221348604</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.826435715393559</v>
+        <v>1.826773975279009</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.3944226601182411</v>
+        <v>0.3952270456297697</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3756089378.837296</v>
+        <v>3788902302.625822</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>152.84</v>
+        <v>152.71</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.05038830134833849</v>
+        <v>-0.05119600561963333</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3226378301719552</v>
+        <v>-0.3232139691544051</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2014703246794</v>
+        <v>2012989615401</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-99.24675324675324</v>
+        <v>-99.16233766233766</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>122.4061437191443</v>
+        <v>122.302029621503</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>121.5507237884766</v>
+        <v>121.447337279095</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.044690938816576</v>
+        <v>7.038698987612401</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9924675324675324</v>
+        <v>-0.9916233766233766</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>470.4932197729782</v>
+        <v>470.081981137749</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>118.2832728080845</v>
+        <v>118.1798862987029</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01410778487860659</v>
+        <v>-0.0141197946489843</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.350539605680813</v>
+        <v>3.346077245157795</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7750722587956251</v>
+        <v>0.7751488656668594</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>13552560968.73255</v>
+        <v>14746294264.62609</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>761.6</v>
+        <v>761.6900000000001</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.114803078372602</v>
+        <v>0.1149348171817584</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02280046704389438</v>
+        <v>-0.02268498915790951</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>811285432922</v>
+        <v>811381304362</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9949899115174288</v>
+        <v>0.9948420724730013</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1144748591753932</v>
+        <v>0.1144605303882855</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>30313236321.26533</v>
+        <v>30644354666.64014</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>432.905</v>
+        <v>434.67</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3544789582334731</v>
+        <v>0.3600013138571829</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.09623173277661801</v>
+        <v>-0.09254697286012525</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>262.81</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2245253124400</v>
+        <v>2254407261600</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>28.51512692708937</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6589379234689362</v>
+        <v>0.6616244838803953</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.36635940341746</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.27437518996225</v>
+        <v>42.0986573529588</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.25098718150321</v>
+        <v>42.07536431271689</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2771970755708528</v>
+        <v>0.2760715025191525</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.181743752284683</v>
+        <v>2.182055485317523</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3378386981429733</v>
+        <v>0.3384223806071351</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4032137559.084684</v>
+        <v>4128968528.000573</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -5027,13 +5027,13 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>27.785</v>
+        <v>27.8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.02542968162263914</v>
+        <v>-0.02490355044482162</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.07383333333333331</v>
+        <v>-0.07333333333333336</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>30</v>
@@ -5042,31 +5042,31 @@
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>69660793265</v>
+        <v>69698400316</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-21.87795275590551</v>
+        <v>-21.88976377952756</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-83.70267845269666</v>
+        <v>-83.74786615025975</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.928860397757165</v>
+        <v>1.929901711643361</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.124615841403252</v>
+        <v>2.125762835739083</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.162812671671855</v>
+        <v>0.1629005676616005</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.25037905206612</v>
+        <v>16.25659509355372</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.722270338225114</v>
+        <v>2.723311652111311</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03129450438077781</v>
+        <v>0.03127761885662041</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2281754905119234</v>
+        <v>0.2271828744710579</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1628478387281664</v>
+        <v>0.1624865549921377</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>512921677.7885841</v>
+        <v>527905689.5206326</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>311.945</v>
+        <v>311.56</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1630805387134704</v>
+        <v>-0.1641134579543472</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1949598699321273</v>
+        <v>-0.1959534439598442</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>210659577950</v>
+        <v>210399583600</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>18.91722255912675</v>
+        <v>18.89387507580352</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.03680751442759</v>
+        <v>16.01701501609278</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.505674567935009</v>
+        <v>2.50258208461694</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.169740665110852</v>
+        <v>6.162126021003501</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.173033014583408</v>
+        <v>1.171585266709216</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.078717092703446</v>
+        <v>9.06833779323734</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.669848838509391</v>
+        <v>2.666796517312336</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07145291664791217</v>
+        <v>0.07154006553841868</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01134815432207601</v>
+        <v>0.01136217742970856</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.962369697447938</v>
+        <v>0.9623591680626296</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2348380311758343</v>
+        <v>0.2346867436799534</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>804518829.2742085</v>
+        <v>837896450.1384989</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>147.65</v>
+        <v>147.6</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2455674470653516</v>
+        <v>-0.2458229271035957</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.551896813353566</v>
+        <v>-0.5520485584218513</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>425301395500</v>
+        <v>425157372000</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.78549382716049</v>
+        <v>22.77777777777778</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.40816912465585</v>
+        <v>16.40261268404473</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.92531584630174</v>
+        <v>5.92330930520919</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.558585934223926</v>
+        <v>6.556364943389444</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4959195715323169</v>
+        <v>0.4957516339869283</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.44494685843054</v>
+        <v>14.44112863202545</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.591058354347493</v>
+        <v>7.589051813254943</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06752858162206524</v>
+        <v>-0.06755145715784507</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01354554690145615</v>
+        <v>0.01355013550135501</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.08144647420547</v>
+        <v>2.080442925700819</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5580451944419919</v>
+        <v>0.5583366535191318</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4183163699.936793</v>
+        <v>4260293875.820374</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>109.755</v>
+        <v>109.51</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4433850431160116</v>
+        <v>0.4401630547276612</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1581268696786071</v>
+        <v>-0.1600061363810693</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,40 +5422,40 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>432592161657</v>
+        <v>431626510164</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>32.64732142857142</v>
+        <v>32.59226190476191</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.15066185283949</v>
+        <v>21.10344840330238</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.827566925811292</v>
+        <v>6.816052272625346</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.623333697921845</v>
+        <v>8.608790494183157</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.044714285714285</v>
+        <v>1.042952380952381</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.71589511314252</v>
+        <v>22.67553375113642</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.181200225345441</v>
+        <v>7.168440744792736</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.03143828687525745</v>
+        <v>0.0314971385674028</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.5435602751215325</v>
+        <v>0.544404558056099</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.1658711593978481</v>
+        <v>0.166508857283745</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0.1023396098336123</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01512459569040135</v>
+        <v>0.01515843301981554</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7104229440262755</v>
+        <v>0.7094121871053773</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3336878824100721</v>
+        <v>0.3338654993278114</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>1996854323.029983</v>
+        <v>2099773678.943522</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.09506299620117042</v>
+        <v>-0.0953781222616924</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1187602291325696</v>
+        <v>-0.1190671031096563</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,31 +5548,31 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>260517600000</v>
+        <v>260426880000</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.28958630527818</v>
+        <v>12.28530670470756</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.07335961689822</v>
+        <v>11.0695035427426</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.017873823631927</v>
+        <v>2.017171139769955</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.457987989067096</v>
+        <v>1.457480274155059</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.653230263073346</v>
+        <v>0.6530027888087817</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.58303703480124</v>
+        <v>15.58029881379976</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>3.998928004337555</v>
+        <v>3.998225320475582</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.07358427991045519</v>
+        <v>0.07360991307809701</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02147417295414974</v>
+        <v>0.02148165350673479</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.7288060149510324</v>
+        <v>0.728303923042646</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.2241820964238002</v>
+        <v>0.2243370392460025</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1079462179.585685</v>
+        <v>1132664655.30247</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 15:54 ET</t>
+          <t>2026-09-18 18:46 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -711,7 +711,7 @@
         <v>344.57</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>240.21</v>
+        <v>243.42</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>4936860972280</v>
@@ -720,7 +720,7 @@
         <v>38.37100456621005</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>35.08910982995525</v>
+        <v>35.08143766439387</v>
       </c>
       <c r="N2" s="6" t="n">
         <v>10.57544502365993</v>
@@ -744,10 +744,10 @@
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09353029336335772</v>
+        <v>0.09376944392318731</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1195887273062486</v>
+        <v>0.119860700088394</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -784,13 +784,13 @@
         <v>0.003153541784428644</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3096765658979816</v>
+        <v>0.3096765527226455</v>
       </c>
       <c r="AJ2" s="4" t="n">
         <v>0.291748504721329</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13594114828.82618</v>
+        <v>13596266632.27844</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         <v>27.43222222222222</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.02431740043097</v>
+        <v>24.01226807110472</v>
       </c>
       <c r="N3" s="6" t="n">
         <v>11.04929824101447</v>
@@ -872,10 +872,10 @@
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.141852305936073</v>
+        <v>0.1424252861491628</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.227381012594984</v>
+        <v>0.2280099482211277</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -914,13 +914,13 @@
         <v>0.007371703997731784</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5574561254179546</v>
+        <v>0.5574561004202877</v>
       </c>
       <c r="AJ3" s="4" t="n">
         <v>0.4338476357762108</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>11015710913.17164</v>
+        <v>11018804543.62</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>17.10079443892751</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.98497250522871</v>
+        <v>21.0039634442356</v>
       </c>
       <c r="N4" s="6" t="n">
         <v>9.374399849939218</v>
@@ -998,10 +998,10 @@
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1850933121467472</v>
+        <v>-0.1858301179999097</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2859635067242161</v>
+        <v>0.2866631499931194</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1040,13 +1040,13 @@
         <v>0.002460376494821765</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7637474871723581</v>
+        <v>0.7637474801987068</v>
       </c>
       <c r="AJ4" s="4" t="n">
         <v>0.3622167366566593</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8153408895.182483</v>
+        <v>8154185526.476135</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         <v>20.13571428571429</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.59413549721904</v>
+        <v>22.60602312396835</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>3.51844038907797</v>
@@ -1124,10 +1124,10 @@
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1088079343335506</v>
+        <v>-0.1092765775168516</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.179997197688706</v>
+        <v>0.1804255006133832</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8378168744020118</v>
+        <v>0.8378168738742139</v>
       </c>
       <c r="AJ5" s="4" t="n">
         <v>0.4627066709514093</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8563813948.280845</v>
+        <v>8564928276.458333</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         <v>27.95849056603773</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.55785676528892</v>
+        <v>16.5361144646673</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>17.76948027686001</v>
@@ -1250,10 +1250,10 @@
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6885331817006977</v>
+        <v>0.6907533281640386</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9437347712197781</v>
+        <v>0.9462540992020205</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1292,13 +1292,13 @@
         <v>0.002339497008143249</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.328091171552411</v>
+        <v>1.328091165640004</v>
       </c>
       <c r="AJ6" s="4" t="n">
         <v>0.4121028150628047</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>27017728029.57898</v>
+        <v>27024314319.52759</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -1337,10 +1337,10 @@
         <v>0.02358516549385681</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1581310065756196</v>
+        <v>-0.1526987642065341</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>790.8</v>
+        <v>785.73</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>520.26</v>
@@ -1352,7 +1352,7 @@
         <v>24.73987365291713</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.13626964922009</v>
+        <v>20.13216724768483</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>7.430466790412184</v>
@@ -1376,10 +1376,10 @@
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.228622484893837</v>
+        <v>0.2288728455582536</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2736216805247405</v>
+        <v>0.2742358205935815</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1418,13 +1418,13 @@
         <v>0.003154337213668795</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.769151071197354</v>
+        <v>0.7691510145943935</v>
       </c>
       <c r="AJ7" s="4" t="n">
         <v>0.4138640308670974</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10585494580.24203</v>
+        <v>10588895009.32536</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
         <v>308.7033898305085</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>172.998652063492</v>
+        <v>170.5690820590555</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>13.88453497150137</v>
@@ -1502,10 +1502,10 @@
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7844265614116559</v>
+        <v>0.8098437659623872</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1232203940178107</v>
+        <v>0.1235964007642594</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.53428605529164</v>
+        <v>1.534286015864648</v>
       </c>
       <c r="AJ8" s="4" t="n">
         <v>0.5669001191480243</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>13320249859.17986</v>
+        <v>13320828659.90774</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
         <v>44.36848635235732</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.52442546533809</v>
+        <v>19.50232187666616</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>19.0940719137188</v>
@@ -1628,10 +1628,10 @@
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.272460535708215</v>
+        <v>1.27503610251878</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.857683211380821</v>
+        <v>0.8597720066537917</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1670,13 +1670,13 @@
         <v>0.007102709655770252</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.603588744680662</v>
+        <v>1.60358876268177</v>
       </c>
       <c r="AJ9" s="4" t="n">
         <v>0.3932084614129385</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>9006536579.43968</v>
+        <v>9007092889.453226</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -1796,13 +1796,13 @@
         <v>0.006187800873440485</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1835038483254343</v>
+        <v>-0.1835038416372886</v>
       </c>
       <c r="AJ10" s="4" t="n">
         <v>0.1763090659402758</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1789294524.128361</v>
+        <v>1789685237.411296</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
         <v>22.22600619195047</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>19.13521646381585</v>
+        <v>19.13220924751302</v>
       </c>
       <c r="N11" s="6" t="n">
         <v>6.179957226394026</v>
@@ -1880,10 +1880,10 @@
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1615236354383138</v>
+        <v>0.1617062046736504</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1444115006001652</v>
+        <v>0.1447396720852696</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.08771628690465143</v>
+        <v>0.08771620800657744</v>
       </c>
       <c r="AJ11" s="4" t="n">
         <v>0.3530217611262856</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2357773889.265933</v>
+        <v>2359371527.876307</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>12.80000643688118</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.98015356263096</v>
+        <v>22.98012671355498</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>2.854809215804017</v>
@@ -2006,10 +2006,10 @@
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4429973497785569</v>
+        <v>-0.4429966989985737</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.05954181252370994</v>
+        <v>0.05958716313017343</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2054,7 +2054,7 @@
         <v>0.14899060627112</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2282909512.691259</v>
+        <v>2283300251.387838</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
         <v>15.03310404127257</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.96158194043373</v>
+        <v>13.96097067428319</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>3.147985141768554</v>
@@ -2132,10 +2132,10 @@
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07674790044641289</v>
+        <v>0.07679504470017307</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2892465869116644</v>
+        <v>-0.2891944321370867</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2180,7 +2180,7 @@
         <v>0.1645804732340038</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2272143514.789128</v>
+        <v>2272708907.889506</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>31.29056924384027</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.59225228739476</v>
+        <v>24.58412163495041</v>
       </c>
       <c r="N14" s="6" t="n">
         <v>15.45618632752652</v>
@@ -2258,10 +2258,10 @@
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2723750910720313</v>
+        <v>0.2727959008856973</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1387483256465651</v>
+        <v>0.1390543918079188</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2306,7 +2306,7 @@
         <v>0.1741592411990704</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2431162237.331487</v>
+        <v>2431231782.761434</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>31.04008786381109</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.4674662964347</v>
+        <v>25.4576263156245</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>14.13037165122709</v>
@@ -2384,10 +2384,10 @@
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2188133480776031</v>
+        <v>0.2192844485567917</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1579228907806498</v>
+        <v>0.1582898298366417</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2432,7 +2432,7 @@
         <v>0.1892630957122217</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1553689433.673885</v>
+        <v>1553690111.961873</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
         <v>24.23638351231432</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.32819433551714</v>
+        <v>17.32227469374443</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>0.760403408507339</v>
@@ -2510,10 +2510,10 @@
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.398667572802877</v>
+        <v>0.3991455476148742</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01056282027615407</v>
+        <v>0.01064077798116125</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2558,7 +2558,7 @@
         <v>0.2079717007585567</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1819232989.747476</v>
+        <v>1819773200.508728</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         <v>21.001287001287</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.77528958805518</v>
+        <v>14.77859061855424</v>
       </c>
       <c r="N17" s="6" t="n">
         <v>1.873076449343599</v>
@@ -2636,10 +2636,10 @@
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4213790447982231</v>
+        <v>0.4210615574478587</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08167006657796794</v>
+        <v>0.08150862838000572</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2684,7 +2684,7 @@
         <v>0.250161637469347</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2383481130.017454</v>
+        <v>2383692668.998769</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
         <v>281.07</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>173.33</v>
+        <v>174.12</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>650648473336</v>
@@ -2738,7 +2738,7 @@
         <v>31.21271676300578</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.77779645097476</v>
+        <v>21.77200145271355</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>6.644083706930531</v>
@@ -2762,10 +2762,10 @@
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4332357653020824</v>
+        <v>0.4336172460210626</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.09000526221088045</v>
+        <v>0.09021663906391786</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2810,7 +2810,7 @@
         <v>0.2038433219200969</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1729617379.845727</v>
+        <v>1732490820.314128</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
         <v>38.53068592057762</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.39007102779449</v>
+        <v>34.37980093004954</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>1.154280656664492</v>
@@ -2888,10 +2888,10 @@
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1204014638247368</v>
+        <v>0.1207361554819246</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05127881962617709</v>
+        <v>0.05140285797353572</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2936,7 +2936,7 @@
         <v>0.3021983656671209</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2766554545.643186</v>
+        <v>2771984633.79331</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         <v>21.67925925925926</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.7066409156962</v>
+        <v>20.70329183862584</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>3.997022587048442</v>
@@ -3014,10 +3014,10 @@
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.0469713242009131</v>
+        <v>0.04714068797564686</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02559428074762593</v>
+        <v>0.02567408620740341</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3062,7 +3062,7 @@
         <v>0.1484968291390396</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1299735702.618421</v>
+        <v>1300175287.388255</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -3101,10 +3101,10 @@
         <v>-0.1325545264974853</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2833389077356777</v>
+        <v>-0.276947551099113</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>418.58</v>
+        <v>414.88</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>289.1</v>
@@ -3188,7 +3188,7 @@
         <v>0.2382806161863175</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1284599331.473999</v>
+        <v>1284660327.409566</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
         <v>142.0862944162436</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>41.1102110722379</v>
+        <v>41.0421177227628</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>22.10004822660695</v>
@@ -3266,10 +3266,10 @@
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.456228774076907</v>
+        <v>2.461963034559488</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.9038976624956678</v>
+        <v>0.9064313743551562</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.547107438065864</v>
+        <v>2.54710742323953</v>
       </c>
       <c r="AJ22" s="4" t="n">
         <v>0.6568543593127123</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9638713874.855129</v>
+        <v>9640699873.652445</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
         <v>1999.96</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>925.87</v>
+        <v>935.41</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>647471391441</v>
@@ -3368,7 +3368,7 @@
         <v>52.46734397677794</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>34.42173508469492</v>
+        <v>34.39361158387129</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.77565395190715</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5242504146778677</v>
+        <v>0.5254967873563541</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2772342948012847</v>
+        <v>0.2780463161960551</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3432,13 +3432,13 @@
         <v>0.004631172912995857</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.684420144898762</v>
+        <v>1.684420158995621</v>
       </c>
       <c r="AJ23" s="4" t="n">
         <v>0.4356624008892414</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2144072722.60616</v>
+        <v>2144411058.503011</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
         <v>74.23220973782769</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>77.13593874521685</v>
+        <v>76.72791762618546</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1.666592201712857</v>
@@ -3520,10 +3520,10 @@
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.03764430762916227</v>
+        <v>-0.03252672515520005</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1546467220498906</v>
+        <v>0.1550713241859412</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3568,7 +3568,7 @@
         <v>0.3443784423467804</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1137354153.473872</v>
+        <v>1137444493.032481</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
         <v>14.35100548446069</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.00157726832984</v>
+        <v>13.00005435197084</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>2.356313913360523</v>
@@ -3646,10 +3646,10 @@
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1037895778551334</v>
+        <v>0.1039188834072107</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3821570738151003</v>
+        <v>-0.3821142682736697</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3694,7 +3694,7 @@
         <v>0.3098876404351355</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1990542610.318058</v>
+        <v>1991869448.718058</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
         <v>20.04803493449782</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>17.78415160556265</v>
+        <v>17.78099803928185</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>3.129902306901892</v>
@@ -3772,10 +3772,10 @@
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1272977974516962</v>
+        <v>0.127497730454029</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04632303781771174</v>
+        <v>0.04643055996507583</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3820,7 +3820,7 @@
         <v>0.3397939648974554</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1262584088.404345</v>
+        <v>1263032973.435313</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
         <v>38.54867848778856</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.32672994885804</v>
+        <v>26.29556379699387</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>13.62056007747365</v>
@@ -3898,10 +3898,10 @@
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4642410418108409</v>
+        <v>0.4659764964687874</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.230024722751039</v>
+        <v>0.2311671946536107</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877328985191485</v>
@@ -3946,7 +3946,7 @@
         <v>0.3124183205632644</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2888317711.147994</v>
+        <v>2888595298.273926</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
         <v>16.27974276527331</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.03999806953615</v>
+        <v>15.03757425369097</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>2.524565479850469</v>
@@ -4024,10 +4024,10 @@
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08242984407347032</v>
+        <v>0.08260431440778748</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3270721467871623</v>
+        <v>-0.3269728206241095</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4072,7 +4072,7 @@
         <v>0.2515769412288019</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>930258124.2022237</v>
+        <v>930398066.4674886</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4192,13 +4192,13 @@
         <v>0.0005217562512305573</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.887672519638909</v>
+        <v>2.887672514345583</v>
       </c>
       <c r="AJ29" s="4" t="n">
         <v>0.7770948884887525</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25714651977.77043</v>
+        <v>25726528135.60771</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>84.14285714285715</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>28.53504132020887</v>
+        <v>28.51947246172641</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>9.507010938093945</v>
@@ -4276,10 +4276,10 @@
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.948755398621629</v>
+        <v>1.950365132306645</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2473194666323242</v>
+        <v>0.2478822889575949</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4324,7 +4324,7 @@
         <v>0.6292376666408013</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2212118088.143447</v>
+        <v>2213456242.752838</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
         <v>36.4693446088795</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.45544883755093</v>
+        <v>9.456140418560089</v>
       </c>
       <c r="N31" s="6" t="n">
         <v>2.46961416729465</v>
@@ -4402,10 +4402,10 @@
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.856965992354253</v>
+        <v>2.85668391062585</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05063977200538161</v>
+        <v>-0.05074658054582049</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4450,7 +4450,7 @@
         <v>0.2050434135637993</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>973988281.7226467</v>
+        <v>974085769.3921089</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
         <v>8.113760780990328</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003887353646552389</v>
+        <v>0.003884332858249072</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.968315520817014</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2086.219614862221</v>
+        <v>2087.842814734405</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2702.288207161095</v>
+        <v>2705.457791183441</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4574,7 +4574,7 @@
         <v>0.8651532945538819</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3530852861.059164</v>
+        <v>3534679079.809164</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
         <v>671.83</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>313.43</v>
+        <v>313.6</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>72221348604</v>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.826773975279009</v>
+        <v>1.826773971888191</v>
       </c>
       <c r="AJ33" s="4" t="n">
         <v>0.3952270456297697</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3788902302.625822</v>
+        <v>3790890765.425822</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
         <v>-99.16233766233766</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>122.302029621503</v>
+        <v>121.7942751010598</v>
       </c>
       <c r="N34" s="6" t="n">
         <v>121.447337279095</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.235448666294758</v>
+        <v>4.245491849005145</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4782,7 +4782,7 @@
         <v>0.7751488656668594</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14746294264.62609</v>
+        <v>14747168834.83454</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
         <v>0.1144605303882855</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>30644354666.64014</v>
+        <v>30651027451.90654</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
         <v>479</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>262.81</v>
+        <v>265.45</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>2254407261600</v>
@@ -4920,7 +4920,7 @@
         <v>28.51512692708937</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6616244838803953</v>
+        <v>0.6609707103451463</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.36635940341746</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.0986573529588</v>
+        <v>42.1412867178325</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.07536431271689</v>
+        <v>42.12152275071068</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4990,7 +4990,7 @@
         <v>0.3384223806071351</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4128968528.000573</v>
+        <v>4129131543.744608</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
         <v>-21.88976377952756</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-83.74786615025975</v>
+        <v>-84.54231820018896</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>1.929901711643361</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02080140915356021</v>
+        <v>0.02087508413716432</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2271828744710579</v>
+        <v>0.2271828399419369</v>
       </c>
       <c r="AJ37" s="4" t="n">
         <v>0.1624865549921377</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>527905689.5206326</v>
+        <v>528269668.4239769</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
         <v>18.89387507580352</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.01701501609278</v>
+        <v>16.01132747416185</v>
       </c>
       <c r="N38" s="6" t="n">
         <v>2.50258208461694</v>
@@ -5200,10 +5200,10 @@
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1796127466210324</v>
+        <v>0.1800317685272104</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.006590642898466115</v>
+        <v>0.006823735150551569</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5248,7 +5248,7 @@
         <v>0.2346867436799534</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>837896450.1384989</v>
+        <v>838049893.4372965</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.40261268404473</v>
+        <v>16.38825996939477</v>
       </c>
       <c r="N39" s="6" t="n">
         <v>5.92330930520919</v>
@@ -5326,10 +5326,10 @@
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3886676602401486</v>
+        <v>0.3898838449179773</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.4310425747096076</v>
+        <v>0.4326133664710774</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
@@ -5374,7 +5374,7 @@
         <v>0.5583366535191318</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4260293875.820374</v>
+        <v>4260749803.749593</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>32.59226190476191</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.10344840330238</v>
+        <v>21.09819027971051</v>
       </c>
       <c r="N40" s="6" t="n">
         <v>6.816052272625346</v>
@@ -5452,10 +5452,10 @@
         <v>0.1177498499664631</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.544404558056099</v>
+        <v>0.5447894569471623</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.166508857283745</v>
+        <v>0.1667352313188437</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0.1023396098336123</v>
@@ -5494,13 +5494,13 @@
         <v>0.01515843301981554</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7094121871053773</v>
+        <v>0.7094121578490867</v>
       </c>
       <c r="AJ40" s="4" t="n">
         <v>0.3338654993278114</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>2099773678.943522</v>
+        <v>2099847167.455622</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
         <v>12.28530670470756</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.0695035427426</v>
+        <v>11.06684805325145</v>
       </c>
       <c r="N41" s="6" t="n">
         <v>2.017171139769955</v>
@@ -5578,10 +5578,10 @@
         <v>-0.01489668811853551</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.109833576300002</v>
+        <v>0.1100998807965139</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>-0.2902196875898506</v>
+        <v>-0.2901362237000468</v>
       </c>
       <c r="W41" s="4" t="n">
         <v>0.009923315255755299</v>
@@ -5626,7 +5626,7 @@
         <v>0.2243370392460025</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1132664655.30247</v>
+        <v>1132677059.453532</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:46 ET</t>
+          <t>2026-09-19 11:04 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -720,7 +720,7 @@
         <v>38.37100456621005</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>35.08143766439387</v>
+        <v>35.04041588562982</v>
       </c>
       <c r="N2" s="6" t="n">
         <v>10.57544502365993</v>
@@ -744,10 +744,10 @@
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09376944392318731</v>
+        <v>0.09504991868393065</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.119860700088394</v>
+        <v>0.1201326728705394</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         <v>27.43222222222222</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.01226807110472</v>
+        <v>23.99611740230289</v>
       </c>
       <c r="N3" s="6" t="n">
         <v>11.04929824101447</v>
@@ -872,10 +872,10 @@
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1424252861491628</v>
+        <v>0.1431941993911721</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2280099482211277</v>
+        <v>0.228638883847271</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>17.10079443892751</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>21.0039634442356</v>
+        <v>20.98435250321343</v>
       </c>
       <c r="N4" s="6" t="n">
         <v>9.374399849939218</v>
@@ -998,10 +998,10 @@
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1858301179999097</v>
+        <v>-0.1850692349783587</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2866631499931194</v>
+        <v>0.2865650075664814</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         <v>20.13571428571429</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.60602312396835</v>
+        <v>22.60671328362403</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>3.51844038907797</v>
@@ -1124,10 +1124,10 @@
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1092765775168516</v>
+        <v>-0.1093037703848662</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1804255006133832</v>
+        <v>0.1808538035380607</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         <v>27.95849056603773</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.5361144646673</v>
+        <v>16.50246367594439</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>17.76948027686001</v>
@@ -1250,10 +1250,10 @@
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6907533281640386</v>
+        <v>0.6942010062893076</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9462540992020205</v>
+        <v>0.9491140480986955</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
         <v>24.73987365291713</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.13216724768483</v>
+        <v>20.12807171920323</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>7.430466790412184</v>
@@ -1376,10 +1376,10 @@
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2288728455582536</v>
+        <v>0.2291228885732759</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2742358205935815</v>
+        <v>0.2748499616223978</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
         <v>308.7033898305085</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>170.5690820590555</v>
+        <v>170.4397970293183</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>13.88453497150137</v>
@@ -1502,10 +1502,10 @@
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.8098437659623872</v>
+        <v>0.8112166008822852</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1235964007642594</v>
+        <v>0.1239724075107083</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
         <v>44.36848635235732</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.50232187666616</v>
+        <v>19.48032505772298</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>19.0940719137188</v>
@@ -1628,10 +1628,10 @@
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.27503610251878</v>
+        <v>1.277605030762432</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8597720066537917</v>
+        <v>0.8596106943360324</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>44.96785534907082</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.49675180011946</v>
+        <v>39.5141661094671</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>1.352414049293736</v>
@@ -1754,10 +1754,10 @@
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1385203415369163</v>
+        <v>0.1380185836263184</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1141243314792548</v>
+        <v>0.114432509886337</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
         <v>22.22600619195047</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>19.13220924751302</v>
+        <v>19.13709820116455</v>
       </c>
       <c r="N11" s="6" t="n">
         <v>6.179957226394026</v>
@@ -1880,10 +1880,10 @@
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1617062046736504</v>
+        <v>0.1614094236396795</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1447396720852696</v>
+        <v>0.1450676707331524</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>12.80000643688118</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.98012671355498</v>
+        <v>22.98009986454174</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>2.854809215804017</v>
@@ -2006,10 +2006,10 @@
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4429966989985737</v>
+        <v>-0.4429960482185905</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.05958716313017343</v>
+        <v>0.05963251373663692</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
         <v>15.03310404127257</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.96097067428319</v>
+        <v>13.96035946165523</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>3.147985141768554</v>
@@ -2132,10 +2132,10 @@
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07679504470017307</v>
+        <v>0.07684218895393347</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2891944321370867</v>
+        <v>-0.2891422773625089</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>31.29056924384027</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.58412163495041</v>
+        <v>24.57599635701665</v>
       </c>
       <c r="N14" s="6" t="n">
         <v>15.45618632752652</v>
@@ -2258,10 +2258,10 @@
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2727959008856973</v>
+        <v>0.2732167106993633</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1390543918079188</v>
+        <v>0.1393604579692722</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>31.04008786381109</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.4576263156245</v>
+        <v>25.44779393571381</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>14.13037165122709</v>
@@ -2384,10 +2384,10 @@
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2192844485567917</v>
+        <v>0.2197555490359804</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1582898298366417</v>
+        <v>0.1586567688926339</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
         <v>24.23638351231432</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.32227469374443</v>
+        <v>17.31678331622206</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>0.760403408507339</v>
@@ -2510,10 +2510,10 @@
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3991455476148742</v>
+        <v>0.399589234890414</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01064077798116125</v>
+        <v>0.01071873568616866</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         <v>21.001287001287</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.77859061855424</v>
+        <v>14.78189312438647</v>
       </c>
       <c r="N17" s="6" t="n">
         <v>1.873076449343599</v>
@@ -2636,10 +2636,10 @@
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4210615574478587</v>
+        <v>0.4207440700974949</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08150862838000572</v>
+        <v>0.08134719018204395</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
         <v>31.21271676300578</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.77200145271355</v>
+        <v>21.78939291273559</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>6.644083706930531</v>
@@ -2762,10 +2762,10 @@
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4336172460210626</v>
+        <v>0.4324729875682951</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.09021663906391786</v>
+        <v>0.09040105275409904</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
         <v>38.53068592057762</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.37980093004954</v>
+        <v>34.36953696450584</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>1.154280656664492</v>
@@ -2888,10 +2888,10 @@
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1207361554819246</v>
+        <v>0.1210708471391129</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05140285797353572</v>
+        <v>0.05152689632089458</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,7 +2927,7 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009158624566663543</v>
+        <v>0.009163309285111965</v>
       </c>
       <c r="AI19" s="6" t="n">
         <v>-0.05882571029802023</v>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         <v>21.67925925925926</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.70329183862584</v>
+        <v>20.69994384473488</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>3.997022587048442</v>
@@ -3014,10 +3014,10 @@
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04714068797564686</v>
+        <v>0.04731005175038039</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02567408620740341</v>
+        <v>0.02575389166718089</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
         <v>142.0862944162436</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>41.0421177227628</v>
+        <v>40.9741537717905</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>22.10004822660695</v>
@@ -3266,10 +3266,10 @@
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.461963034559488</v>
+        <v>2.467705402962242</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.9064313743551562</v>
+        <v>0.9135852965836171</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
         <v>52.46734397677794</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>34.39361158387129</v>
+        <v>34.26854356414675</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>15.77565395190715</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5254967873563541</v>
+        <v>0.5310643091255145</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2780463161960551</v>
+        <v>0.2810928551907987</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
         <v>74.23220973782769</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>76.72791762618546</v>
+        <v>76.3241903614753</v>
       </c>
       <c r="N24" s="6" t="n">
         <v>1.666592201712857</v>
@@ -3520,10 +3520,10 @@
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.03252672515520005</v>
+        <v>-0.02740914268123762</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1550713241859412</v>
+        <v>0.1554959263219917</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
         <v>14.35100548446069</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.00005435197084</v>
+        <v>13.01185074089099</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>2.356313913360523</v>
@@ -3646,10 +3646,10 @@
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1039188834072107</v>
+        <v>0.1029180836943728</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3821142682736697</v>
+        <v>-0.3820415698249855</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
         <v>20.04803493449782</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>17.78099803928185</v>
+        <v>17.77784559121205</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>3.129902306901892</v>
@@ -3772,10 +3772,10 @@
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.127497730454029</v>
+        <v>0.1276976634563622</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04643055996507583</v>
+        <v>0.04653808211244037</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
         <v>38.54867848778856</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.29556379699387</v>
+        <v>26.27867849323994</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>13.62056007747365</v>
@@ -3898,10 +3898,10 @@
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4659764964687874</v>
+        <v>0.4669184562574189</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2311671946536107</v>
+        <v>0.2316358049677185</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877328985191485</v>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
         <v>16.27974276527331</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.03757425369097</v>
+        <v>15.03565888435984</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>2.524565479850469</v>
@@ -4024,10 +4024,10 @@
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08260431440778748</v>
+        <v>0.08274222569704426</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3269728206241095</v>
+        <v>-0.3268734944610564</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
         <v>22.66904708770364</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.498722647210335</v>
+        <v>6.474647909946941</v>
       </c>
       <c r="N29" s="6" t="n">
         <v>12.70835857500498</v>
@@ -4150,10 +4150,10 @@
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.488231198393215</v>
+        <v>2.501201517518411</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.775779220960631</v>
+        <v>1.784318972372998</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>84.14285714285715</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>28.51947246172641</v>
+        <v>28.50428043394301</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>9.507010938093945</v>
@@ -4276,10 +4276,10 @@
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.950365132306645</v>
+        <v>1.951937598910916</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2478822889575949</v>
+        <v>0.2489068021146772</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
         <v>36.4693446088795</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.456140418560089</v>
+        <v>9.456832100742504</v>
       </c>
       <c r="N31" s="6" t="n">
         <v>2.46961416729465</v>
@@ -4402,10 +4402,10 @@
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.85668391062585</v>
+        <v>2.856401828897448</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05074658054582049</v>
+        <v>-0.05085331782783276</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
         <v>8.113760780990328</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003884332858249072</v>
+        <v>0.003878990629858609</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>6.968315520817014</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2087.842814734405</v>
+        <v>2090.719613482562</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2705.457791183441</v>
+        <v>2709.926668716981</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
         <v>-99.16233766233766</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>121.7942751010598</v>
+        <v>134.8342969109074</v>
       </c>
       <c r="N34" s="6" t="n">
         <v>121.447337279095</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.245491849005145</v>
+        <v>4.295094526746421</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
         <v>28.51512692708937</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6609707103451463</v>
+        <v>0.6605140703029319</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.36635940341746</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.1412867178325</v>
+        <v>42.17111203098439</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.12152275071068</v>
+        <v>42.15420560240253</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
         <v>-21.88976377952756</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-84.54231820018896</v>
+        <v>-87.36095804432952</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>1.929901711643361</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02087508413716432</v>
+        <v>0.02094875164040277</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
         <v>18.89387507580352</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.01132747416185</v>
+        <v>16.00561869427619</v>
       </c>
       <c r="N38" s="6" t="n">
         <v>2.50258208461694</v>
@@ -5200,10 +5200,10 @@
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1800317685272104</v>
+        <v>0.1804526545768712</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.006823735150551569</v>
+        <v>0.007056827402637245</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.38825996939477</v>
+        <v>16.36102450346003</v>
       </c>
       <c r="N39" s="6" t="n">
         <v>5.92330930520919</v>
@@ -5326,10 +5326,10 @@
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3898838449179773</v>
+        <v>0.3921975224082528</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.4326133664710774</v>
+        <v>0.43520912853463</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>32.59226190476191</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.09819027971051</v>
+        <v>21.08743235214967</v>
       </c>
       <c r="N40" s="6" t="n">
         <v>6.816052272625346</v>
@@ -5452,10 +5452,10 @@
         <v>0.1177498499664631</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.5447894569471623</v>
+        <v>0.5455775440313109</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.1667352313188437</v>
+        <v>0.1669616053539418</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0.1023396098336123</v>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
         <v>12.28530670470756</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.06684805325145</v>
+        <v>11.06339943310153</v>
       </c>
       <c r="N41" s="6" t="n">
         <v>2.017171139769955</v>
@@ -5578,10 +5578,10 @@
         <v>-0.01489668811853551</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.1100998807965139</v>
+        <v>0.1104459148379029</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>-0.2901362237000468</v>
+        <v>-0.2900527598102426</v>
       </c>
       <c r="W41" s="4" t="n">
         <v>0.009923315255755299</v>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 11:04 ET</t>
+          <t>2026-09-20 11:09 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -446,7 +446,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -454,7 +454,7 @@
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
     <col width="24" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>336.13</v>
+        <v>338.73001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2402862916048456</v>
+        <v>0.2498800700864909</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.02449429724003827</v>
+        <v>-0.01694863162782601</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,40 +714,40 @@
         <v>243.42</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4936860972280</v>
+        <v>4975048259240</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.37100456621005</v>
+        <v>38.66780936073059</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>35.04041588562982</v>
+        <v>35.30365975903797</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.57544502365993</v>
+        <v>10.65724752045208</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>45.93187376255581</v>
+        <v>46.28716288016323</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.172447361745306</v>
+        <v>1.181516397133433</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.56699056467599</v>
+        <v>29.79364017924338</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.67133361526746</v>
+        <v>10.7531361120596</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02768621615383984</v>
+        <v>0.02747370334471489</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.09504991868393065</v>
+        <v>0.09529180896978762</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1201326728705394</v>
+        <v>0.1204046456526846</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003153541784428644</v>
+        <v>0.003129335956976472</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3096765527226455</v>
+        <v>0.3109023404336923</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.291748504721329</v>
+        <v>0.2918276013444279</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13596266632.27844</v>
+        <v>13426178369.28659</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>493.78</v>
+        <v>497.21</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.04406478084115051</v>
+        <v>0.05131728640695932</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1082496568662863</v>
+        <v>-0.1020551903489129</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,40 +842,40 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3666588079000</v>
+        <v>3692057715500</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.43222222222222</v>
+        <v>27.62277777777777</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>23.99611740230289</v>
+        <v>24.15071427882669</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.04929824101447</v>
+        <v>11.12605123418284</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.292042080802554</v>
+        <v>8.349642032880713</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8713390306780081</v>
+        <v>0.8773917117813853</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.18850986656644</v>
+        <v>18.31213842708379</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.37437546219703</v>
+        <v>11.45168787951386</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01826957338994829</v>
+        <v>0.01814262863331959</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1431941993911721</v>
+        <v>0.1437664931506848</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.228638883847271</v>
+        <v>0.2292678194734146</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.1763623848855976</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007371703997731784</v>
+        <v>0.00732085034492468</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5574561004202877</v>
+        <v>0.5552190936757947</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4338476357762108</v>
+        <v>0.4296743117557364</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>11018804543.62</v>
+        <v>10717377452.03641</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>349.54</v>
+        <v>355.99</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1091226614930907</v>
+        <v>0.1295891064396788</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1445632754949707</v>
+        <v>-0.1287780524216245</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4230171978908</v>
+        <v>4308230596703</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.10079443892751</v>
+        <v>17.48108738828202</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>20.98435250321343</v>
+        <v>21.39083141810268</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.374399849939218</v>
+        <v>9.582870759293151</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.534046199725207</v>
+        <v>6.679352413970772</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1520783595506874</v>
+        <v>0.1554603268676488</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.06519121300237</v>
+        <v>13.35184064207868</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.501893312100496</v>
+        <v>9.710364221454428</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01274557181886761</v>
+        <v>0.01246829781465144</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1850692349783587</v>
+        <v>-0.1827766276775904</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2865650075664814</v>
+        <v>0.2920481943604654</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002460376494821765</v>
+        <v>0.002415798196578555</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7637474801987068</v>
+        <v>0.7624166777559729</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3622167366566593</v>
+        <v>0.3629042708997856</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8154185526.476135</v>
+        <v>8089666871.93655</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>253.71</v>
+        <v>257.575</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1201324503311259</v>
+        <v>0.1371964679911699</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.116608635097493</v>
+        <v>-0.1031511142061281</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2729183841000</v>
+        <v>2770760032500</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.13571428571429</v>
+        <v>20.44319841269841</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.60671328362403</v>
+        <v>22.96315303847702</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.51844038907797</v>
+        <v>3.57216903043781</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>4.947073637649106</v>
+        <v>5.022618343787389</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.22793219724438</v>
+        <v>0.231412855128515</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.31589286881341</v>
+        <v>11.47997446241491</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.705397639490512</v>
+        <v>3.759126280850351</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004259515180091527</v>
+        <v>-0.004195448233223147</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1093037703848662</v>
+        <v>-0.1097390511466859</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1808538035380607</v>
+        <v>0.1813247578209447</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8378168738742139</v>
+        <v>0.8364343821079248</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4627066709514093</v>
+        <v>0.4630905271732186</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8564928276.458333</v>
+        <v>8437203402.756631</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>222.27</v>
+        <v>227.27</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1769658078706424</v>
+        <v>0.2034418461994911</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.06032806290690784</v>
+        <v>-0.03918998900820148</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5383601670000</v>
+        <v>5504706670000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>27.95849056603773</v>
+        <v>28.58742138364779</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.50246367594439</v>
+        <v>16.85156152217641</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17.76948027686001</v>
+        <v>18.16920764170592</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>23.48072922125563</v>
+        <v>24.00893206512245</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2244286997817995</v>
+        <v>0.2294772600864245</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>23.10989001442223</v>
+        <v>23.62817030218216</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>17.82366733890266</v>
+        <v>18.22339470374857</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02359126989423049</v>
+        <v>0.02307225572838743</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6942010062893076</v>
+        <v>0.6964256603773582</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9491140480986955</v>
+        <v>0.9516327173898933</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002339497008143249</v>
+        <v>0.002288027456329476</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.328091165640004</v>
+        <v>1.316562868039854</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4121028150628047</v>
+        <v>0.4119391543254972</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>27024314319.52759</v>
+        <v>26685025267.72803</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>665.75</v>
+        <v>737.5309999999999</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.02358516549385681</v>
+        <v>0.1339478643512575</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1526987642065341</v>
+        <v>-0.06134295495908271</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>785.73</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1695989183978</v>
+        <v>1878850317459</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>24.73987365291713</v>
+        <v>27.40732069862505</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>20.12807171920323</v>
+        <v>22.29374016167409</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>7.430466790412184</v>
+        <v>8.231617878180751</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>6.481110821871137</v>
+        <v>7.179902584401713</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.071674098848008</v>
+        <v>-5.61850074321813</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>16.74429527773834</v>
+        <v>18.45212863735617</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>7.85481223922225</v>
+        <v>8.655963326990818</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02416053143917428</v>
+        <v>0.02180908165979761</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2291228885732759</v>
+        <v>0.2293729315882977</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2748499616223978</v>
+        <v>0.2754641026512139</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.003154337213668795</v>
+        <v>0.002847337942405133</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.7691510145943935</v>
+        <v>0.8244058033176008</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4138640308670974</v>
+        <v>0.4774682281582845</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>10588895009.32536</v>
+        <v>11033935205.32499</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>364.27</v>
+        <v>373.1022</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1684662407613742</v>
+        <v>-0.1483046230922074</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2697512178497685</v>
+        <v>-0.2520453862037167</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,40 +1472,40 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1438701629212</v>
+        <v>1473584821706</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>308.7033898305085</v>
+        <v>316.1883050847458</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>170.4397970293183</v>
+        <v>174.4401124928839</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>13.88453497150137</v>
+        <v>14.22118358318455</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.57551394229662</v>
+        <v>13.90466993713878</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.217597278586773</v>
+        <v>-8.416843614227735</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>119.1240962098437</v>
+        <v>122.024262970735</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>13.82781757411286</v>
+        <v>14.16446631420878</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.00400499998262735</v>
+        <v>0.0039101922489268</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.8112166008822852</v>
+        <v>0.8125894358021826</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1239724075107083</v>
+        <v>0.1243484142571567</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.534286015864648</v>
+        <v>1.534176558605315</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5669001191480243</v>
+        <v>0.5692931213186111</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>13320828659.90774</v>
+        <v>13184996020.47722</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>357.61</v>
+        <v>359.223</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0287382918794552</v>
+        <v>0.03337841621826443</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2775555555555556</v>
+        <v>-0.2742969696969697</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1701358183800</v>
+        <v>1709032160340</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>44.36848635235732</v>
+        <v>44.5854094292804</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.48032505772298</v>
+        <v>19.54608832275813</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>19.0940719137188</v>
+        <v>19.18742521853115</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>17.09669234627345</v>
+        <v>17.18028021265924</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4414884038031592</v>
+        <v>0.4436468958062057</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>33.23196494269368</v>
+        <v>33.39112444122993</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.49185428039145</v>
+        <v>19.58520758520381</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02315973225108485</v>
+        <v>0.02304705233079414</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.277605030762432</v>
+        <v>1.28104000621793</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8596106943360324</v>
+        <v>0.8623942193149883</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007102709655770252</v>
+        <v>0.007237843901977323</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.60358876268177</v>
+        <v>1.586250399704904</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3932084614129385</v>
+        <v>0.3872302666399897</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>9007092889.453226</v>
+        <v>8946248609.782087</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>895.3099999999999</v>
+        <v>897.3899</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04775892334698639</v>
+        <v>0.05019297834991221</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.183483812129503</v>
+        <v>-0.1815869585043319</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,40 +1724,40 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>397051183490</v>
+        <v>397973575462</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>44.96785534907082</v>
+        <v>45.07081868407835</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.5141661094671</v>
+        <v>39.60596170439074</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.352414049293736</v>
+        <v>1.355510684873649</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.86095380733534</v>
+        <v>11.88811194843176</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.547241089366438</v>
+        <v>3.555363241730649</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.69918337871458</v>
+        <v>26.7620121243953</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.315920607826641</v>
+        <v>1.319017243406554</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02217850082348838</v>
+        <v>0.02212783450597016</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1380185836263184</v>
+        <v>0.1379806661551608</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.114432509886337</v>
+        <v>0.1143953782763263</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006187800873440485</v>
+        <v>0.006173459273388301</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1835038416372886</v>
+        <v>-0.1773280087527101</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1763090659402758</v>
+        <v>0.1764326601584382</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1789685237.411296</v>
+        <v>1770592802.520325</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>71.79000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2110121806191908</v>
+        <v>-0.1909000799162116</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.425036040365209</v>
+        <v>-0.4103796251802018</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>298929252528</v>
+        <v>306549262726</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>22.22600619195047</v>
+        <v>22.79256965944273</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>19.13709820116455</v>
+        <v>19.62186658715291</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.179957226394026</v>
+        <v>6.33749061160167</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>9.974447588840722</v>
+        <v>10.22870638655041</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6532277429585444</v>
+        <v>0.6698791814543534</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>9.940155858485387</v>
+        <v>10.18919990640924</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.287668446336717</v>
+        <v>6.44520183154436</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03677996685510115</v>
+        <v>0.03586571340028701</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1614094236396795</v>
+        <v>0.1615902879681073</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1450676707331524</v>
+        <v>0.1453958417687611</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.08771620800657744</v>
+        <v>0.1067428780225328</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3530217611262856</v>
+        <v>0.3578414218266984</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2359371527.876307</v>
+        <v>2342091763.981251</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>509.77</v>
+        <v>507.64499</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02600381148791331</v>
+        <v>0.02172684666171731</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.0520139844534534</v>
+        <v>-0.0559657269312307</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1099499257123</v>
+        <v>1094915919538</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.80000643688118</v>
+        <v>12.77318609861637</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.98009986454174</v>
+        <v>22.8842790595741</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.854809215804017</v>
+        <v>2.848827425933291</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.461694506763071</v>
+        <v>1.458631762903955</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3526075807921941</v>
+        <v>0.3518687487737715</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.51309554852707</v>
+        <v>15.48302109417884</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.085544852828403</v>
+        <v>3.079563062957677</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02204955724121188</v>
+        <v>0.02209585552413306</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4429960482185905</v>
+        <v>-0.4418357657077925</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.05963251373663692</v>
+        <v>0.06188401707386548</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.03918452948205382</v>
+        <v>0.03626418744575198</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.14899060627112</v>
+        <v>0.1494815903370572</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2283300251.387838</v>
+        <v>2251531071.274144</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>349.67</v>
+        <v>352.255</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07432096656371323</v>
+        <v>0.08226308255469661</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04592087312414728</v>
+        <v>-0.03886766712141887</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,40 +2102,40 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>936944261700</v>
+        <v>943870808134</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.03310404127257</v>
+        <v>15.14423903697335</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>13.96035946165523</v>
+        <v>14.06294831787748</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.147985141768554</v>
+        <v>3.17125724679051</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.603123158692786</v>
+        <v>2.622367227000678</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7871220426971945</v>
+        <v>0.7929409876463529</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.01936734328038</v>
+        <v>20.0937184213611</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.266120563579979</v>
+        <v>6.289392668601936</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1734724322929273</v>
+        <v>-0.1721994139445038</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.07684218895393347</v>
+        <v>0.07688933320769409</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2891422773625089</v>
+        <v>-0.2890901225879311</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>0.01297429806050525</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01715903566219578</v>
+        <v>0.01703311521483017</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7668452127602949</v>
+        <v>0.763789019754343</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1645804732340038</v>
+        <v>0.1642307875462587</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2272708907.889506</v>
+        <v>2246023087.747815</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>368.29</v>
+        <v>368.25</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06294732256439617</v>
+        <v>0.06283187578902183</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04481676478979169</v>
+        <v>-0.04492050730087915</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>687614817339</v>
+        <v>687540135451</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.29056924384027</v>
+        <v>31.28632115548004</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.57599635701665</v>
+        <v>24.56520812966425</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.45618632752652</v>
+        <v>15.45408795583079</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.03254502217295</v>
+        <v>20.02982535220877</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.110054833877388</v>
+        <v>2.109768367392569</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.02618108938758</v>
+        <v>24.02297288401265</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.71466052281514</v>
+        <v>15.7125621511194</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03055926002484675</v>
+        <v>0.03056340939208615</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2732167106993633</v>
+        <v>0.2736029342938711</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1393604579692722</v>
+        <v>0.1396355759563579</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007276874202394852</v>
+        <v>0.007277664630006789</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3055468132238942</v>
+        <v>0.3079912209734742</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1741592411990704</v>
+        <v>0.1731368413704722</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2431231782.761434</v>
+        <v>2393201495.369767</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>565.24</v>
+        <v>565.23</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.003746905863463379</v>
+        <v>0.003729147974675051</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05986061906425166</v>
+        <v>-0.05987725163415003</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.23</v>
@@ -2354,40 +2354,40 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>495735828640</v>
+        <v>495727058280</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.04008786381109</v>
+        <v>31.03953871499176</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.44779393571381</v>
+        <v>25.43751910952335</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.13037165122709</v>
+        <v>14.13012166234359</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>88.85077169844948</v>
+        <v>88.84919978613438</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.371861026123793</v>
+        <v>1.371836755707224</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.01898302767227</v>
+        <v>23.01858646590703</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.51095483966593</v>
+        <v>14.51070485078243</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03317896155523677</v>
+        <v>0.03317954855453891</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2197555490359804</v>
+        <v>0.2202266495151692</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1586567688926339</v>
+        <v>0.1590237079486261</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>0.2817943873394463</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005962069209539311</v>
+        <v>0.005962174689949224</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2928800069420453</v>
+        <v>0.2950387562166457</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1892630957122217</v>
+        <v>0.1864926849625038</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1553690111.961873</v>
+        <v>1512409281.778219</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>376.9</v>
+        <v>377.315</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1203924103398708</v>
+        <v>0.121626060778425</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1835275767947663</v>
+        <v>-0.1826285689528183</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,40 +2480,40 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>342279625868</v>
+        <v>342656508012</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.23638351231432</v>
+        <v>24.26306989904187</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.31678331622206</v>
+        <v>17.32993387047288</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.760403408507339</v>
+        <v>0.7612406843638156</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.468569578554958</v>
+        <v>3.472388778276636</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7343687484605945</v>
+        <v>-0.735177352946164</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.02242075332842</v>
+        <v>15.03704956767457</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8598038026165832</v>
+        <v>0.8606410784730599</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06899914051299065</v>
+        <v>0.06892324951602238</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.399589234890414</v>
+        <v>0.4000670793315502</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.01071873568616866</v>
+        <v>0.01079669339117584</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>0.0455949917185134</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02403820642080128</v>
+        <v>0.0240117673561878</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4284111499557166</v>
+        <v>0.4297623421872889</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2079717007585567</v>
+        <v>0.2072665871450886</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1819773200.508728</v>
+        <v>1787935432.073832</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>163.18</v>
+        <v>158.325</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3304524905820678</v>
+        <v>0.2908683084410213</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.07499574854033209</v>
+        <v>-0.102516864123349</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,40 +2606,40 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>676292982800</v>
+        <v>656171616852</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>21.001287001287</v>
+        <v>20.37644787644788</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.78189312438647</v>
+        <v>14.34530170298521</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.873076449343599</v>
+        <v>1.817347855902066</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.625834706530958</v>
+        <v>2.547709767811705</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>2.056376018876021</v>
+        <v>1.995193854568856</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.858308148973199</v>
+        <v>9.578163826689872</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.961095061208663</v>
+        <v>1.90536646776713</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04517716548455662</v>
+        <v>0.04656251385358421</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4207440700974949</v>
+        <v>0.4204265827471307</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.08134719018204395</v>
+        <v>0.08118575198408196</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>0.07052372320132966</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02524819218041427</v>
+        <v>0.02602242223274909</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.5335105066356072</v>
+        <v>-0.551854144028243</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.250161637469347</v>
+        <v>0.2603882970005258</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2383692668.998769</v>
+        <v>2318966523.51605</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>269.99</v>
+        <v>270.88</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3020978637695941</v>
+        <v>0.3063901231079211</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.03942078485786449</v>
+        <v>-0.03625431387198919</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>174.12</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>650648473336</v>
+        <v>652793282926</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.21271676300578</v>
+        <v>31.31560693641618</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.78939291273559</v>
+        <v>21.85550363721279</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.644083706930531</v>
+        <v>6.665985386616835</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.753264043026444</v>
+        <v>7.778822045168351</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.864627167630064</v>
+        <v>-3.877366595679957</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20.13703525838966</v>
+        <v>20.20061908354085</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.936274988369124</v>
+        <v>6.958176668055428</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02875285314062213</v>
+        <v>0.02865838311960805</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4324729875682951</v>
+        <v>0.43284764589437</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.09040105275409904</v>
+        <v>0.09061244409666647</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01955627986221712</v>
+        <v>0.01949202598936799</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1659156819489056</v>
+        <v>-0.1582184663195926</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.2038433219200969</v>
+        <v>0.1988117512032154</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1732490820.314128</v>
+        <v>1690795642.735026</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>106.73</v>
+        <v>107.7035</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.05347642800631869</v>
+        <v>-0.04484304753844781</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2103432968333826</v>
+        <v>-0.2031407221071322</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,40 +2858,40 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>849365878400</v>
+        <v>857113069280</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.53068592057762</v>
+        <v>38.88212996389892</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.36953696450584</v>
+        <v>34.6726751551757</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.154280656664492</v>
+        <v>1.164809020004349</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.641568639426698</v>
+        <v>8.720389655734033</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.317420413521504</v>
+        <v>9.402405973088291</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.27948547818577</v>
+        <v>21.460329822825</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.238845235920852</v>
+        <v>1.249373599260709</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01590480656633828</v>
+        <v>0.01576104773591652</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1210708471391129</v>
+        <v>0.1214055387963009</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.05152689632089458</v>
+        <v>0.05165093466825343</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>0.07511040644542281</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009163309285111965</v>
+        <v>0.009075842474942782</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.05882571029802023</v>
+        <v>-0.04943727187952437</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3021983656671209</v>
+        <v>0.3023135323099588</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2771984633.79331</v>
+        <v>2729666069.604243</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.335</v>
+        <v>146.67</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03205449558556195</v>
+        <v>0.03441714468537493</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1250523168908819</v>
+        <v>-0.1230493273542602</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,40 +2984,40 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>347868869796</v>
+        <v>348665230437</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.67925925925926</v>
+        <v>21.72888888888889</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.69994384473488</v>
+        <v>20.74397698593049</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>3.997022587048442</v>
+        <v>4.006172792042007</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.527159093001417</v>
+        <v>6.542101507981807</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.68820740740763</v>
+        <v>20.73556825396847</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.54742024070763</v>
+        <v>17.58488898263856</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.285238415709165</v>
+        <v>4.29438862070273</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04574424842709216</v>
+        <v>0.04563976734948713</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04731005175038039</v>
+        <v>0.04747941552511414</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02575389166718089</v>
+        <v>0.02583369712695816</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>0.1268247958836873</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.0293203949841118</v>
+        <v>0.02925342605849868</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.04268400994052118</v>
+        <v>-0.03592844684359042</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1484968291390396</v>
+        <v>0.1475051370718759</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1300175287.388255</v>
+        <v>1273994170.671572</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>299.98</v>
+        <v>299.0801</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1325545264974853</v>
+        <v>-0.1351567472508853</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.276947551099113</v>
+        <v>-0.2791166120323949</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>414.88</v>
@@ -3110,31 +3110,31 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>299115157660</v>
+        <v>298217852072</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>20.94832402234637</v>
+        <v>20.88548184357542</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>19.99036400215111</v>
+        <v>19.93039557570422</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.768070870927318</v>
+        <v>1.76276689407481</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>17.94428115785039</v>
+        <v>17.89045070710718</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.185762309990937</v>
+        <v>-7.164205981226483</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>15.03646906376751</v>
+        <v>14.99894844541083</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.12558021031352</v>
+        <v>2.120276233461011</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.05048557257390845</v>
+        <v>0.0506374782565133</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03096873124874991</v>
+        <v>0.03106191284542167</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.7063059258783332</v>
+        <v>0.6973263151319282</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2382806161863175</v>
+        <v>0.2382353227908371</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1284660327.409566</v>
+        <v>1262761881.639897</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -3221,55 +3221,55 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>559.8200000000001</v>
+        <v>606.64001</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.505123716570402</v>
+        <v>1.714637341416001</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.04260085851589612</v>
+        <v>-0.01517880160392227</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>584.73</v>
+        <v>615.99</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>154.78</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>912842492000</v>
+        <v>989187207886</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>142.0862944162436</v>
+        <v>153.9695456852792</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>40.9741537717905</v>
+        <v>44.32768658139424</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>22.10004822660695</v>
+        <v>23.94836479569059</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>13.58244704272284</v>
+        <v>14.71840200389742</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.14711870721371</v>
+        <v>1.243056882596749</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>85.09353349505504</v>
+        <v>92.21230893823474</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>22.08043800992616</v>
+        <v>23.92764864302143</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.009205312059465348</v>
+        <v>0.008495245391007581</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.467705402962242</v>
+        <v>2.473439684305681</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.9135852965836171</v>
+        <v>0.9161344104613689</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>0.07617446486076908</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.54710742323953</v>
+        <v>2.564944611511842</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6568543593127123</v>
+        <v>0.6845070365174124</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9640699873.652445</v>
+        <v>9816473311.898008</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1679.92</v>
+        <v>1710.1299</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4435030312515014</v>
+        <v>0.4694614591669999</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1600232004640093</v>
+        <v>-0.1449179483589672</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,40 +3362,40 @@
         <v>935.41</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>647471391441</v>
+        <v>659114830407</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>52.46734397677794</v>
+        <v>53.75181422351234</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>34.26854356414675</v>
+        <v>34.9922796659698</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>15.77565395190715</v>
+        <v>16.16186290756493</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>25.53393752233636</v>
+        <v>26.15904221686658</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>3.571643840685479</v>
+        <v>3.659082424337115</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>40.03237458698251</v>
+        <v>41.0207332295266</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>15.64296695169486</v>
+        <v>16.02917590735263</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01794660200965958</v>
+        <v>0.01751774436748071</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5310643091255145</v>
+        <v>0.5361049561965605</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2810928551907987</v>
+        <v>0.2850763763526722</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004631172912995857</v>
+        <v>0.004549362010453125</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.684420158995621</v>
+        <v>1.658503110145121</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4356624008892414</v>
+        <v>0.4382365466804631</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2144411058.503011</v>
+        <v>2126492654.149658</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>198.2</v>
+        <v>200.71</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1298239615304612</v>
+        <v>-0.1188040732531728</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2207587969333595</v>
+        <v>-0.2108905052093571</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,40 +3490,40 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>156651334000</v>
+        <v>158635162700</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>74.23220973782769</v>
+        <v>75.17228464419473</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>76.3241903614753</v>
+        <v>76.88619795501751</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.666592201712857</v>
+        <v>1.687697884993883</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>25.70247124642623</v>
+        <v>26.02796671982951</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3972962560703509</v>
+        <v>0.4023276062355203</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>28.10105525179856</v>
+        <v>28.38649823021583</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.077794925261982</v>
+        <v>2.098900608543008</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001340556729634999</v>
+        <v>-0.001323792256557505</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.02740914268123762</v>
+        <v>-0.02229156020727541</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1554959263219917</v>
+        <v>0.1559205284580425</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>0.01468017121842407</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.22626418528472</v>
+        <v>1.223270381950688</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3443784423467804</v>
+        <v>0.3425999429553007</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1137444493.032481</v>
+        <v>1131035388.394091</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>942</v>
+        <v>953.635</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.03025129856740216</v>
+        <v>0.04297632389524897</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1837017651799409</v>
+        <v>-0.1736193554536868</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>277896594000</v>
+        <v>281329000445</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.35100548446069</v>
+        <v>14.52780316879951</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.01185074089099</v>
+        <v>13.17505273292933</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.356313913360523</v>
+        <v>2.385342600159407</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.303157843281028</v>
+        <v>2.331531672125271</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3363676833112766</v>
+        <v>0.3405115760552547</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.51879699296022</v>
+        <v>26.62785175787596</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.05889240865886</v>
+        <v>7.087921095457744</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1493901001175998</v>
+        <v>-0.1475720810092009</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1029180836943728</v>
+        <v>0.1026751439475575</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3820415698249855</v>
+        <v>-0.3821630148620359</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01910828025477707</v>
+        <v>0.01887514615130527</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.577960615288972</v>
+        <v>1.568739059563203</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3098876404351355</v>
+        <v>0.3100899717742037</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1991869448.718058</v>
+        <v>1969286600.109009</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>229.55</v>
+        <v>228.765</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2125214408233276</v>
+        <v>-0.2152144082332762</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3095409974132226</v>
+        <v>-0.3119021837213499</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,40 +3742,40 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>216266859700</v>
+        <v>215527284510</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>20.04803493449782</v>
+        <v>19.97947598253275</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>17.77784559121205</v>
+        <v>17.71390952978631</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.129902306901892</v>
+        <v>3.119198872744113</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.262453413444794</v>
+        <v>6.24103748693835</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2443839917402933</v>
+        <v>0.2435482634304865</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>16.91429996301091</v>
+        <v>16.86870627643179</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>3.970749232238737</v>
+        <v>3.960045798080959</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.06302861205322251</v>
+        <v>0.0632448927800023</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.1276976634563622</v>
+        <v>0.1278975964586948</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.04653808211244037</v>
+        <v>0.04664560425980491</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>0.07051328411100664</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02936179481594424</v>
+        <v>0.02946254890389701</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.8996161912189466</v>
+        <v>0.8823698743961197</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3397939648974554</v>
+        <v>0.3343853572537092</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1263032973.435313</v>
+        <v>1256225166.119612</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1152.22</v>
+        <v>1167.33</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.06651487987594562</v>
+        <v>0.08050095878008312</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.108637295478281</v>
+        <v>-0.09694812981085377</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,40 +3868,40 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1085092815020</v>
+        <v>1099322521530</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>38.54867848778856</v>
+        <v>39.0541987286718</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.27867849323994</v>
+        <v>26.60614431054024</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.62056007747365</v>
+        <v>13.79917758347999</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.35039782756279</v>
+        <v>30.74840733197556</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4075070210409032</v>
+        <v>0.4128509927545759</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>26.11975612449428</v>
+        <v>26.44835033368125</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.19819816056576</v>
+        <v>14.3768156665721</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01848127618431459</v>
+        <v>0.01824205327121804</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4669184562574189</v>
+        <v>0.4678638991370185</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2316358049677185</v>
+        <v>0.2321044287935796</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0.1877328985191485</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005806182847025742</v>
+        <v>0.005731027215954358</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.350247177976581</v>
+        <v>0.3548820357182461</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3124183205632644</v>
+        <v>0.3129111703445646</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2888595298.273926</v>
+        <v>2811762385.221431</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>202.52</v>
+        <v>205.62</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1133590258131074</v>
+        <v>0.1304013573360217</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1280086114101183</v>
+        <v>-0.1146609257265877</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,40 +3994,40 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>319430745600</v>
+        <v>324320313600</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.27974276527331</v>
+        <v>16.52893890675241</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.03565888435984</v>
+        <v>15.26334534500181</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.524565479850469</v>
+        <v>2.563209332247943</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.881430576813353</v>
+        <v>2.925537009699593</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4141826293273239</v>
+        <v>0.4205225767444417</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.30298652673186</v>
+        <v>23.46959871877875</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.404869599854579</v>
+        <v>5.443513452252053</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04909984469572612</v>
+        <v>-0.04835959803413313</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.08274222569704426</v>
+        <v>0.08291718054882602</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3268734944610564</v>
+        <v>-0.3267741682980033</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02049180327868853</v>
+        <v>0.02018286158933956</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.375227679397425</v>
+        <v>1.370230159780131</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2515769412288019</v>
+        <v>0.2533154516306673</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>930398066.4674886</v>
+        <v>904113498.0990347</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>1015.8</v>
+        <v>1040.34</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.220467810400145</v>
+        <v>2.298268834289906</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.190597609561753</v>
+        <v>-0.1710438247011953</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,31 +4120,31 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1147234362000</v>
+        <v>1174949592600</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>22.66904708770364</v>
+        <v>23.21669270252175</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.474647909946941</v>
+        <v>6.63106438928352</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12.70835857500498</v>
+        <v>13.01537089970534</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>11.37586275366348</v>
+        <v>11.65068424605854</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03231003906686979</v>
+        <v>0.03309059464739843</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>16.51326137594007</v>
+        <v>16.91877494805841</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>12.50210871347232</v>
+        <v>12.80912103817267</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02281312421149394</v>
+        <v>0.02227499814871632</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
@@ -4153,7 +4153,7 @@
         <v>2.501201517518411</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.784318972372998</v>
+        <v>1.784318972372997</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.0005217562512305573</v>
+        <v>0.000509448834035027</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.887672514345583</v>
+        <v>2.849763739789576</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.7770948884887525</v>
+        <v>0.7784115439297378</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25726528135.60771</v>
+        <v>25346216338.7304</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>135.47</v>
+        <v>137.405</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.08124786162218367</v>
+        <v>-0.0681247687768225</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3043045099267689</v>
+        <v>-0.2943674701888808</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,40 +4246,40 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>140057285140</v>
+        <v>142057806848</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>84.14285714285715</v>
+        <v>85.34472049689442</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>28.50428043394301</v>
+        <v>28.89566710342278</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.507010938093945</v>
+        <v>9.642805243551452</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.18092921061042</v>
+        <v>11.34063318951742</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>134.6285714285743</v>
+        <v>136.551552795034</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>41.84788912009171</v>
+        <v>42.42126880137575</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>9.910893642411079</v>
+        <v>10.04668794786859</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03270090517192214</v>
+        <v>0.03224039636836391</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.951937598910916</v>
+        <v>1.953547332595934</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2489068021146772</v>
+        <v>0.2494717167744058</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.6973746617483811</v>
+        <v>0.703082710186232</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6292376666408013</v>
+        <v>0.6016878335038168</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2213456242.752838</v>
+        <v>2132357723.640202</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.6</v>
+        <v>27.7137</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.09610800895529725</v>
+        <v>0.1006234973834934</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05511811023622049</v>
+        <v>-0.05122560766860673</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157304544000</v>
+        <v>157952566571</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.4693446088795</v>
+        <v>36.61958245243129</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.456832100742504</v>
+        <v>9.49648477055605</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.46961416729465</v>
+        <v>2.479787844935318</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.846371639863834</v>
+        <v>1.853977888249795</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6099739939007278</v>
+        <v>-0.6124868215495144</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.38930164765526</v>
+        <v>17.44063423407795</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.446410198442602</v>
+        <v>3.456583876083271</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06983905054897842</v>
+        <v>0.06955252604307491</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.856401828897448</v>
+        <v>2.856119747169046</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05085331782783276</v>
+        <v>-0.05096012505918535</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06231884057971014</v>
+        <v>0.06206316731436077</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3502851110013918</v>
+        <v>0.3470077692005</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2050434135637993</v>
+        <v>0.2042335836475987</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>974085769.3921089</v>
+        <v>949503793.4137268</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>187.5</v>
+        <v>187.42</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1160050361906955</v>
+        <v>0.1155288740419207</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.06189022864862159</v>
+        <v>-0.06229048881773158</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,40 +4498,40 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1330977920625</v>
+        <v>1330410023714</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>8.113760780990328</v>
+        <v>8.16182290731822</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.003878990629858609</v>
+        <v>0.004325440585223388</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>6.968315520817014</v>
+        <v>7.009592564828316</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>5.049665129599325</v>
+        <v>5.079576985509715</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.01815758347958247</v>
+        <v>0.01826514051688748</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>8.197577490578496</v>
+        <v>8.246347839925653</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>6.938063216567753</v>
+        <v>6.979340260579054</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.06917298904518683</v>
+        <v>0.06876565345659098</v>
       </c>
       <c r="T32" s="4" t="n">
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2090.719613482562</v>
+        <v>1885.934462861591</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2709.926668716981</v>
+        <v>2499.96749011031</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.6</v>
+        <v>1.600682958062107</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.8651532945538819</v>
+        <v>0.8588674710572904</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3534679079.809164</v>
+        <v>3456528975.402265</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>573</v>
+        <v>592.87</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5349585286292171</v>
+        <v>0.5881864971525375</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1471056666120895</v>
+        <v>-0.1175297322239257</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>313.6</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>72221348604</v>
+        <v>74725778267</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.826773971888191</v>
+        <v>1.814977300506886</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.3952270456297697</v>
+        <v>0.4040323760577721</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3790890765.425822</v>
+        <v>3780078705.484049</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>152.71</v>
+        <v>154.25</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.05119600561963333</v>
+        <v>-0.04162781655967818</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3232139691544051</v>
+        <v>-0.3163889381315369</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,38 +4706,38 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2012989615401</v>
+        <v>2033289556516</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-99.16233766233766</v>
+        <v>-100.1623376623377</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>134.8342969109074</v>
+        <v>135.6101115205819</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>121.447337279095</v>
+        <v>122.672069774721</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.038698987612401</v>
+        <v>7.109680563415708</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.9916233766233766</v>
+        <v>-1.001623376623377</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>470.081981137749</v>
+        <v>474.9535772776578</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>118.1798862987029</v>
+        <v>119.4046187943288</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.0141197946489843</v>
+        <v>-0.01397882554843897</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
       </c>
       <c r="U34" s="4" t="inlineStr"/>
       <c r="V34" s="4" t="n">
-        <v>4.295094526746421</v>
+        <v>4.305288125787722</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>-0.027727343466307</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.346077245157795</v>
+        <v>3.218096694234215</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7751488656668594</v>
+        <v>0.7523639494381489</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>14747168834.83454</v>
+        <v>13939309755.23863</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>761.6900000000001</v>
+        <v>772.62</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1149348171817584</v>
+        <v>0.1309337636715331</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.02268498915790951</v>
+        <v>-0.008660841448862588</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>811381304362</v>
+        <v>823024352971</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.9948420724730013</v>
+        <v>0.995118982523625</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1144605303882855</v>
+        <v>0.1192715547493287</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>30651027451.90654</v>
+        <v>30155278187.22266</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>434.67</v>
+        <v>442.2113</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3600013138571829</v>
+        <v>0.3835966342340003</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.09254697286012525</v>
+        <v>-0.07680313152400842</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,40 +4914,40 @@
         <v>265.45</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2254407261600</v>
+        <v>2293520082471</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>28.51512692708937</v>
+        <v>28.74695722730961</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6605140703029319</v>
+        <v>0.6777653749865373</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>14.36635940341746</v>
+        <v>14.48315907336394</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>9.916369735770658</v>
+        <v>9.996990627931394</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.535669551549927</v>
+        <v>0.5400245885543979</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>18.9112426634564</v>
+        <v>19.07035964288201</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>13.88177999194684</v>
+        <v>13.99857966189332</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>0.01753258319974648</v>
+        <v>0.01739119139974853</v>
       </c>
       <c r="T36" s="4" t="n">
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42.17111203098439</v>
+        <v>41.41431959825422</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42.15420560240253</v>
+        <v>41.40052630287702</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2760715025191525</v>
+        <v>0.2713634861886162</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.182055485317523</v>
+        <v>2.16778013413212</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3384223806071351</v>
+        <v>0.3401245430090488</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4129131543.744608</v>
+        <v>4080379986.731384</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -5027,53 +5027,53 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>27.8</v>
+        <v>30.9</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.02490355044482162</v>
+        <v>0.08383022630413706</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.07333333333333336</v>
+        <v>-0.0005724876041879323</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>30</v>
+        <v>30.9177</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>69698400316</v>
+        <v>77470524092</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-21.88976377952756</v>
+        <v>-24.3267716535433</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-87.36095804432952</v>
+        <v>-98.07278392725289</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.929901711643361</v>
+        <v>2.144759474124325</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.125762835739083</v>
+        <v>2.36242600036543</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1629005676616005</v>
+        <v>0.1810364402124154</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>16.25659509355372</v>
+        <v>17.53917163768595</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.723311652111311</v>
+        <v>2.938169414592275</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.03127761885662041</v>
+        <v>0.02814428885652349</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02094875164040277</v>
+        <v>0.02085721239547977</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2271828399419369</v>
+        <v>0.2833535847437162</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.1624865549921377</v>
+        <v>0.3020347553594716</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>528269668.4239769</v>
+        <v>690960971.7207906</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>311.56</v>
+        <v>313.46</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1641134579543472</v>
+        <v>-0.1590159344279423</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1959534439598442</v>
+        <v>-0.1910500916152675</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,40 +5170,40 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>210399583600</v>
+        <v>211682672600</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>18.89387507580352</v>
+        <v>19.00909642207398</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.00561869427619</v>
+        <v>16.09751262125699</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.50258208461694</v>
+        <v>2.517843690602215</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.162126021003501</v>
+        <v>6.199704784130688</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.171585266709216</v>
+        <v>1.178729996477953</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.06833779323734</v>
+        <v>9.12023429056787</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.666796517312336</v>
+        <v>2.68205812329761</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07154006553841868</v>
+        <v>0.07110643405585952</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>0.1804526545768712</v>
+        <v>0.1808716582071328</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.007056827402637245</v>
+        <v>0.007289919654722699</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0.03713461582139044</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01136217742970856</v>
+        <v>0.01129330696101576</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.9623591680626296</v>
+        <v>0.953805729113185</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2346867436799534</v>
+        <v>0.2355795532036712</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>838049893.4372965</v>
+        <v>825938388.2113851</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>147.6</v>
+        <v>148.49</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2458229271035957</v>
+        <v>-0.2412753824228517</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5520485584218513</v>
+        <v>-0.5493474962063732</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,40 +5296,40 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>425157372000</v>
+        <v>427720990300</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.77777777777778</v>
+        <v>22.91512345679012</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.36102450346003</v>
+        <v>16.44530522845881</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.92330930520919</v>
+        <v>5.95902573665659</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.556364943389444</v>
+        <v>6.595898580243216</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4957516339869283</v>
+        <v>0.4987409222948441</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.44112863202545</v>
+        <v>14.50909306203605</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.589051813254943</v>
+        <v>7.624768244702342</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.06755145715784507</v>
+        <v>-0.0671465760421438</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.3921975224082528</v>
+        <v>0.3934142990021985</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.43520912853463</v>
+        <v>0.4367736814882319</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>0.06238891508578476</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01355013550135501</v>
+        <v>0.01346892046602465</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.080442925700819</v>
+        <v>2.069945695208964</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5583366535191318</v>
+        <v>0.5573848342617406</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4260749803.749593</v>
+        <v>4215373940.411263</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>109.51</v>
+        <v>109.8502</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4401630547276612</v>
+        <v>0.4446370157469137</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1600061363810693</v>
+        <v>-0.1573966403313646</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,40 +5422,40 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>431626510164</v>
+        <v>432967386237</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>32.59226190476191</v>
+        <v>32.69351190476191</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.08743235214967</v>
+        <v>21.14767862253797</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.816052272625346</v>
+        <v>6.837226786213976</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.608790494183157</v>
+        <v>8.635534266679924</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.042952380952381</v>
+        <v>1.046192380952381</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.67553375113642</v>
+        <v>22.74251392362256</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.168440744792736</v>
+        <v>7.189615258381367</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.0314971385674028</v>
+        <v>0.03139959366952941</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.5455775440313109</v>
+        <v>0.5459622064579257</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.1669616053539418</v>
+        <v>0.1671879793890401</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>0.1023396098336123</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01515843301981554</v>
+        <v>0.01511148819028094</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.7094121578490867</v>
+        <v>0.6981848286848316</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3338654993278114</v>
+        <v>0.3339784224757248</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>2099847167.455622</v>
+        <v>2055917983.750985</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>86.12</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.0953781222616924</v>
+        <v>-0.08802518084951394</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1190671031096563</v>
+        <v>-0.1119067103109658</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,40 +5548,40 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>260426880000</v>
+        <v>262543680000</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.28530670470756</v>
+        <v>12.38516405135521</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.06339943310153</v>
+        <v>11.15065860608368</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.017171139769955</v>
+        <v>2.03356709654932</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.457480274155059</v>
+        <v>1.469326955435929</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.6530027888087817</v>
+        <v>0.6583105216486115</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.58029881379976</v>
+        <v>15.64419063716761</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>3.998225320475582</v>
+        <v>4.014621277254947</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.07360991307809701</v>
+        <v>0.07301642149603449</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.1104459148379029</v>
+        <v>0.1107114376722098</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>-0.2900527598102426</v>
+        <v>-0.2899692959204386</v>
       </c>
       <c r="W41" s="4" t="n">
         <v>0.009923315255755299</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02148165350673479</v>
+        <v>0.02130845427320894</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.728303923042646</v>
+        <v>0.7244587304160582</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.2243370392460025</v>
+        <v>0.2221829194790843</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1132677059.453532</v>
+        <v>1121901762.751183</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:09 ET</t>
+          <t>2026-09-21 13:30 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -470,7 +470,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>338.73001</v>
+        <v>338.721</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2498800700864909</v>
+        <v>0.2498468240820066</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.01694863162782601</v>
+        <v>-0.01697478016078002</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,31 +714,31 @@
         <v>243.42</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4975048259240</v>
+        <v>4974915911676</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.66780936073059</v>
+        <v>38.66678082191781</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>35.30365975903797</v>
+        <v>35.30272070443684</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.65724752045208</v>
+        <v>10.65696401350405</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>46.28716288016323</v>
+        <v>46.28593167145648</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.181516397133433</v>
+        <v>1.181484969558598</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.79364017924338</v>
+        <v>29.79285466849471</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.7531361120596</v>
+        <v>10.75285260511157</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.02747370334471489</v>
+        <v>0.0274744342269602</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003129335956976472</v>
+        <v>0.003129419197510636</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3109023404336923</v>
+        <v>0.3100570591227713</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2918276013444279</v>
+        <v>0.2918136906615251</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13426178369.28659</v>
+        <v>13462680898.54019</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>497.21</v>
+        <v>498.545</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.05131728640695932</v>
+        <v>0.05414005460822913</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.1020551903489129</v>
+        <v>-0.09964422451780686</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,37 +842,37 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3692057715500</v>
+        <v>3701970824750</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.62277777777777</v>
+        <v>27.69694444444444</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.15071427882669</v>
+        <v>24.21555851679905</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.12605123418284</v>
+        <v>11.15592448371047</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.349642032880713</v>
+        <v>8.372060673121045</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8773917117813853</v>
+        <v>0.8797474929105423</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.31213842708379</v>
+        <v>18.35919242334437</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.45168787951386</v>
+        <v>11.48111358972273</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01814262863331959</v>
+        <v>0.01809477474373416</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1437664931506848</v>
+        <v>0.143766493150685</v>
       </c>
       <c r="V3" s="4" t="n">
         <v>0.2292678194734146</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.00732085034492468</v>
+        <v>0.007301246627686568</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5552190936757947</v>
+        <v>0.5553302034500899</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4296743117557364</v>
+        <v>0.4297687079231736</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10717377452.03641</v>
+        <v>10759864313.60875</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>355.99</v>
+        <v>355.335</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1295891064396788</v>
+        <v>0.127510731022622</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1287780524216245</v>
+        <v>-0.1303810479430264</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4308230596703</v>
+        <v>4300303713811</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.48108738828202</v>
+        <v>17.45978152929493</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>21.39083141810268</v>
+        <v>21.3514735862005</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.582870759293151</v>
+        <v>9.571191205925096</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.679352413970772</v>
+        <v>6.671211653759681</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1554603268676488</v>
+        <v>0.1552708526244991</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.35184064207868</v>
+        <v>13.33578114814164</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.710364221454428</v>
+        <v>9.698684668086374</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01246829781465144</v>
+        <v>0.01248351265537523</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1827766276775904</v>
+        <v>-0.1822680781817689</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2920481943604654</v>
+        <v>0.2928522223410996</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002415798196578555</v>
+        <v>0.002420251312142063</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7624166777559729</v>
+        <v>0.7592980624839859</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3629042708997856</v>
+        <v>0.3623772568261484</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8089666871.93655</v>
+        <v>8128369753.914919</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>257.575</v>
+        <v>258.625</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1371964679911699</v>
+        <v>0.1418322295805738</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1031511142061281</v>
+        <v>-0.09949512534818938</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,40 +1094,40 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2770760032500</v>
+        <v>2782054987500</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.44319841269841</v>
+        <v>20.52579365079365</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.96315303847702</v>
+        <v>23.05676193177179</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.57216903043781</v>
+        <v>3.586601417465966</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>5.022618343787389</v>
+        <v>5.042910880678727</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.231412855128515</v>
+        <v>0.2323478164531464</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.47997446241491</v>
+        <v>11.52404944743442</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.759126280850351</v>
+        <v>3.773558667878507</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004195448233223147</v>
+        <v>-0.004178565863087564</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.1097390511466859</v>
+        <v>-0.1097711937377691</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1813247578209447</v>
+        <v>0.1812821064627379</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8364343821079248</v>
+        <v>0.8371125768166782</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4630905271732186</v>
+        <v>0.4639730853230861</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8437203402.756631</v>
+        <v>8469833184.420419</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>227.27</v>
+        <v>228.325</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2034418461994911</v>
+        <v>0.2090282902868781</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.03918998900820148</v>
+        <v>-0.0347298554155745</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5504706670000</v>
+        <v>5530259825000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>28.58742138364779</v>
+        <v>28.72199999999999</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.85156152217641</v>
+        <v>16.929787409473</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>18.16920764170592</v>
+        <v>18.25474168578634</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>24.00893206512245</v>
+        <v>24.12195690965308</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2294772600864245</v>
+        <v>0.2305575510204081</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>23.62817030218216</v>
+        <v>23.73907241416631</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>18.22339470374857</v>
+        <v>18.30892874782899</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02307225572838743</v>
+        <v>0.02296414883909394</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6964256603773582</v>
+        <v>0.6965363654790317</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9516327173898933</v>
+        <v>0.9517601176585231</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.002288027456329476</v>
+        <v>0.00227745538158327</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.316562868039854</v>
+        <v>1.316147750937678</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4119391543254972</v>
+        <v>0.4135223273920259</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26685025267.72803</v>
+        <v>26783144167.61311</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>737.5309999999999</v>
+        <v>745.2835</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1339478643512575</v>
+        <v>0.1458672695266103</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.06134295495908271</v>
+        <v>-0.05147633410968144</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>785.73</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1878850317459</v>
+        <v>1898599707093</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>27.40732069862505</v>
+        <v>27.69899219620959</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>22.29374016167409</v>
+        <v>22.52807908519511</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>8.231617878180751</v>
+        <v>8.319219625201535</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>7.179902584401713</v>
+        <v>7.256311838787846</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.61850074321813</v>
+        <v>-5.678293400222961</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>18.45212863735617</v>
+        <v>18.63887142308914</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>8.655963326990818</v>
+        <v>8.743565074011602</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02180908165979761</v>
+        <v>0.02157943107471994</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2293729315882977</v>
+        <v>0.2295319139931766</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2754641026512139</v>
+        <v>0.2756290503754621</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.002847337942405133</v>
+        <v>0.002817719699953105</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.8244058033176008</v>
+        <v>0.8378172630163945</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4774682281582845</v>
+        <v>0.4913606372031905</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>11033935205.32499</v>
+        <v>11259648772.54138</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>373.1022</v>
+        <v>375.96</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1483046230922074</v>
+        <v>-0.1417810082538947</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2520453862037167</v>
+        <v>-0.2463163803299722</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,31 +1472,31 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1473584821706</v>
+        <v>1484871838248</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>316.1883050847458</v>
+        <v>318.6101694915254</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>174.4401124928839</v>
+        <v>175.7762476147947</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>14.22118358318455</v>
+        <v>14.33011164215057</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.90466993713878</v>
+        <v>14.01117363973382</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.416843614227735</v>
+        <v>-8.481312962520883</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>122.024262970735</v>
+        <v>122.9626569876954</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>14.16446631420878</v>
+        <v>14.27339424476206</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.0039101922489268</v>
+        <v>0.003880469580996689</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.534176558605315</v>
+        <v>1.535136630064105</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5692931213186111</v>
+        <v>0.5715255642673231</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>13184996020.47722</v>
+        <v>13234436152.7239</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>359.223</v>
+        <v>362.85001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.03337841621826443</v>
+        <v>0.04381225216253237</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2742969696969697</v>
+        <v>-0.2669696767676768</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,40 +1598,40 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1709032160340</v>
+        <v>1726287932038</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>44.5854094292804</v>
+        <v>45.01861166253101</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.54608832275813</v>
+        <v>19.74344165984269</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>19.18742521853115</v>
+        <v>19.3738545075193</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>17.18028021265924</v>
+        <v>17.34720782084462</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4436468958062057</v>
+        <v>0.4479574724836005</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>33.39112444122993</v>
+        <v>33.7089706300442</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.58520758520381</v>
+        <v>19.77163687419196</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02304705233079414</v>
+        <v>0.0228252768664623</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.28104000621793</v>
+        <v>1.280180549984704</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.8623942193149883</v>
+        <v>0.8616925015388202</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>0.2033771286434084</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007237843901977323</v>
+        <v>0.007165495186289233</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.586250399704904</v>
+        <v>1.586814593676824</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3872302666399897</v>
+        <v>0.3890610351438917</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8946248609.782087</v>
+        <v>8985365344.157597</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>897.3899</v>
+        <v>898.38</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.05019297834991221</v>
+        <v>0.05135166764189592</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1815869585043319</v>
+        <v>-0.1806839945280437</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,40 +1724,40 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>397973575462</v>
+        <v>398412664020</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.07081868407835</v>
+        <v>45.1225514816675</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.60596170439074</v>
+        <v>39.64965939107466</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.355510684873649</v>
+        <v>1.357066555433313</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.88811194843176</v>
+        <v>11.9017572583485</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.555363241730649</v>
+        <v>3.559444128040471</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.7620121243953</v>
+        <v>26.79357973807879</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.319017243406554</v>
+        <v>1.320573113966218</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02212783450597016</v>
+        <v>0.02210246504555636</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1379806661551608</v>
+        <v>0.1380312510786617</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1143953782763263</v>
+        <v>0.1144449147986222</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006173459273388301</v>
+        <v>0.006166655535519491</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1773280087527101</v>
+        <v>-0.1754405861414696</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1764326601584382</v>
+        <v>0.1766073689180791</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1770592802.520325</v>
+        <v>1775516737.825877</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>73.62</v>
+        <v>73.545</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1909000799162116</v>
+        <v>-0.1917243463384649</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4103796251802018</v>
+        <v>-0.4109802979336857</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,40 +1850,40 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>306549262726</v>
+        <v>306236967226</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>22.79256965944273</v>
+        <v>22.76934984520124</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>19.62186658715291</v>
+        <v>19.60187691051563</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.33749061160167</v>
+        <v>6.331034325320974</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.22870638655041</v>
+        <v>10.21828594402132</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6698791814543534</v>
+        <v>0.6691967454504268</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.18919990640924</v>
+        <v>10.17942866999087</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.44520183154436</v>
+        <v>6.439021013478307</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03586571340028701</v>
+        <v>0.03590072660554237</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1615902879681073</v>
+        <v>0.1615902879681075</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1453958417687611</v>
+        <v>0.1453958417687613</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.1067428780225328</v>
+        <v>0.1076767456070794</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.3578414218266984</v>
+        <v>0.357385417634816</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2342091763.981251</v>
+        <v>2357777559.722336</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>507.64499</v>
+        <v>505.06</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.02172684666171731</v>
+        <v>0.01652408935419003</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.0559657269312307</v>
+        <v>-0.06077286420946926</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1094915919538</v>
+        <v>1089340476691</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.77318609861637</v>
+        <v>12.70498055357849</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.8842790595741</v>
+        <v>22.76774952871788</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.848827425933291</v>
+        <v>2.833615416510046</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.458631762903955</v>
+        <v>1.450843042561955</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3518687487737715</v>
+        <v>0.3499898597004718</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.48302109417884</v>
+        <v>15.40654015906893</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.079563062957677</v>
+        <v>3.064351053534432</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02209585552413306</v>
+        <v>0.02221447513655095</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4418357657077925</v>
+        <v>-0.4419746871532831</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06188401707386548</v>
+        <v>0.06161972279484895</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.03626418744575198</v>
+        <v>0.03096258283992644</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1494815903370572</v>
+        <v>0.1510562423419694</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2251531071.274144</v>
+        <v>2261272038.932377</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>352.255</v>
+        <v>352.24</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.08226308255469661</v>
+        <v>0.08221699677525196</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.03886766712141887</v>
+        <v>-0.03890859481582531</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,31 +2102,31 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>943870808134</v>
+        <v>943830602400</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.14423903697335</v>
+        <v>15.14359415305245</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>14.06294831787748</v>
+        <v>14.06234947833009</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.17125724679051</v>
+        <v>3.171122161857052</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.622367227000678</v>
+        <v>2.622255559292896</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7929409876463529</v>
+        <v>0.7929072220083502</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.0937184213611</v>
+        <v>20.09328684413912</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.289392668601936</v>
+        <v>6.289257583668477</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1721994139445038</v>
+        <v>-0.1722067493750508</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01703311521483017</v>
+        <v>0.01703384056325233</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.763789019754343</v>
+        <v>0.7618293761887743</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1642307875462587</v>
+        <v>0.1641860223756799</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2246023087.747815</v>
+        <v>2254397061.946411</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>368.25</v>
+        <v>368.93</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06283187578902183</v>
+        <v>0.06479447097038382</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04492050730087915</v>
+        <v>-0.04315688461239198</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,40 +2228,40 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>687540135451</v>
+        <v>688809727554</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.28632115548004</v>
+        <v>31.34494477485132</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.56520812966425</v>
+        <v>24.61056954589825</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.45408795583079</v>
+        <v>15.48304548538932</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.02982535220877</v>
+        <v>20.06735679771448</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.109768367392569</v>
+        <v>2.113721604883067</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.02297288401265</v>
+        <v>24.06724611842738</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.7125621511194</v>
+        <v>15.74151968067794</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03056340939208615</v>
+        <v>0.03050624745765174</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2736029342938711</v>
+        <v>0.2736375205130295</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1396355759563579</v>
+        <v>0.1396665241306259</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>0.238841315149593</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007277664630006789</v>
+        <v>0.007264250670858971</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3079912209734742</v>
+        <v>0.3084719681080962</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1731368413704722</v>
+        <v>0.1731220608576809</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2393201495.369767</v>
+        <v>2400638727.220361</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>565.23</v>
+        <v>566.6900000000001</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.003729147974675051</v>
+        <v>0.006321799737750489</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05987725163415003</v>
+        <v>-0.05744889642898721</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.23</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>495727058280</v>
+        <v>497007532981</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.03953871499176</v>
+        <v>31.11971444261395</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.43751910952335</v>
+        <v>25.50322471237511</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.13012166234359</v>
+        <v>14.166620100362</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>88.84919978613438</v>
+        <v>89.07869898413831</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.371836755707224</v>
+        <v>1.375380236526241</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.01858646590703</v>
+        <v>23.0764845804395</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.51070485078243</v>
+        <v>14.54720328880084</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03317954855453891</v>
+        <v>0.03309406580086742</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005962174689949224</v>
+        <v>0.005946813954719511</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2950387562166457</v>
+        <v>0.2967674941275374</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1864926849625038</v>
+        <v>0.1864675334534982</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1512409281.778219</v>
+        <v>1518424954.993953</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>377.315</v>
+        <v>377.70001</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.121626060778425</v>
+        <v>0.1227705613937209</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1826285689528183</v>
+        <v>-0.1817945279667258</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,37 +2480,37 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>342656508012</v>
+        <v>343006152477</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.26306989904187</v>
+        <v>24.28782779242493</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.32993387047288</v>
+        <v>17.34761723275498</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7612406843638156</v>
+        <v>0.7620174493911744</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.472388778276636</v>
+        <v>3.475931983300355</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.735177352946164</v>
+        <v>-0.7359275235798728</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.03704956767457</v>
+        <v>15.05062114183131</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8606410784730599</v>
+        <v>0.8614178435004187</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06892324951602238</v>
+        <v>0.06885299237186021</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.4000670793315502</v>
+        <v>0.4000670793315499</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>0.01079669339117584</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.0240117673561878</v>
+        <v>0.02398729086610297</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4297623421872889</v>
+        <v>0.4291603666741114</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2072665871450886</v>
+        <v>0.2073923706713177</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1787935432.073832</v>
+        <v>1792704122.263428</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>158.325</v>
+        <v>159.37</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2908683084410213</v>
+        <v>0.2993884877072199</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.102516864123349</v>
+        <v>-0.09659316365285409</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,31 +2606,31 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>656171616852</v>
+        <v>660502590200</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>20.37644787644788</v>
+        <v>20.51093951093951</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>14.34530170298521</v>
+        <v>14.439985677592</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1.817347855902066</v>
+        <v>1.829343018334903</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>2.547709767811705</v>
+        <v>2.564525537319763</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>1.995193854568856</v>
+        <v>2.008362827112828</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>9.578163826689872</v>
+        <v>9.638462794291682</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>1.90536646776713</v>
+        <v>1.917361630199967</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.04656251385358421</v>
+        <v>0.04625719937108583</v>
       </c>
       <c r="T17" s="4" t="n">
         <v>-0.04522368657644726</v>
@@ -2675,16 +2675,16 @@
         <v>69.43781094527363</v>
       </c>
       <c r="AH17" s="4" t="n">
-        <v>0.02602242223274909</v>
+        <v>0.02585179142875071</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>-0.551854144028243</v>
+        <v>-0.5480358390216704</v>
       </c>
       <c r="AJ17" s="4" t="n">
-        <v>0.2603882970005258</v>
+        <v>0.2557210168408703</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>2318966523.51605</v>
+        <v>2328179559.520315</v>
       </c>
       <c r="AL17" s="7" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -2717,13 +2717,13 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>270.88</v>
+        <v>270.96</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3063901231079211</v>
+        <v>0.3067759441720403</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.03625431387198919</v>
+        <v>-0.03596968726651728</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>281.07</v>
@@ -2732,40 +2732,40 @@
         <v>174.12</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>652793282926</v>
+        <v>652986074799</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>31.31560693641618</v>
+        <v>31.32658959537573</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>21.85550363721279</v>
+        <v>21.86195830455987</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6.665985386616835</v>
+        <v>6.668323206363794</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>7.778822045168351</v>
+        <v>7.781550146520578</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-3.877366595679957</v>
+        <v>-3.878726422269553</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>20.20061908354085</v>
+        <v>20.21062024866595</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>6.958176668055428</v>
+        <v>6.961621605734767</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.02865838311960805</v>
+        <v>0.02864358030451933</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0.06048119251078021</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.43284764589437</v>
+        <v>0.4329269665125</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.09061244409666647</v>
+        <v>0.09067281901180313</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>0.1046304585695812</v>
@@ -2801,16 +2801,16 @@
         <v>34.55406797116375</v>
       </c>
       <c r="AH18" s="4" t="n">
-        <v>0.01949202598936799</v>
+        <v>0.01948627103631533</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>-0.1582184663195926</v>
+        <v>-0.1571749726932908</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>0.1988117512032154</v>
+        <v>0.1988348894733133</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>1690795642.735026</v>
+        <v>1694582039.352351</v>
       </c>
       <c r="AL18" s="7" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -2843,13 +2843,13 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="3" t="n">
-        <v>107.7035</v>
+        <v>107.47</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04484304753844781</v>
+        <v>-0.04691381727573385</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2031407221071322</v>
+        <v>-0.2048683042320213</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>135.16</v>
@@ -2858,37 +2858,37 @@
         <v>98.88</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>857113069280</v>
+        <v>855254857600</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>38.88212996389892</v>
+        <v>38.79783393501805</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>34.6726751551757</v>
+        <v>34.59750517788866</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1.164809020004349</v>
+        <v>1.162283726897152</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>8.720389655734033</v>
+        <v>8.701483947148761</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>9.402405973088291</v>
+        <v>9.382021660649828</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>21.460329822825</v>
+        <v>21.41695318751605</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1.249373599260709</v>
+        <v>1.246848306153512</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.01576104773591652</v>
+        <v>0.01579529175421313</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0.04725214211766771</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1214055387963009</v>
+        <v>0.1214055387963011</v>
       </c>
       <c r="V19" s="4" t="n">
         <v>0.05165093466825343</v>
@@ -2927,16 +2927,16 @@
         <v>11.52840300107181</v>
       </c>
       <c r="AH19" s="4" t="n">
-        <v>0.009075842474942782</v>
+        <v>0.009095561552061041</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>-0.04943727187952437</v>
+        <v>-0.05024574151990511</v>
       </c>
       <c r="AJ19" s="4" t="n">
-        <v>0.3023135323099588</v>
+        <v>0.301940976179534</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>2729666069.604243</v>
+        <v>2734966063.067333</v>
       </c>
       <c r="AL19" s="7" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -2969,13 +2969,13 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>146.67</v>
+        <v>146.52</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03441714468537493</v>
+        <v>0.03335924210336927</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1230493273542602</v>
+        <v>-0.1239461883408071</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>167.25</v>
@@ -2984,31 +2984,31 @@
         <v>137.62</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>348665230437</v>
+        <v>348308653449</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>21.72888888888889</v>
+        <v>21.70666666666667</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>20.74397698593049</v>
+        <v>20.72276203708008</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4.006172792042007</v>
+        <v>4.002075712944664</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>6.542101507981807</v>
+        <v>6.535410874408499</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>20.73556825396847</v>
+        <v>20.71436190476213</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>17.58488898263856</v>
+        <v>17.56811204709702</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>4.29438862070273</v>
+        <v>4.290291541605387</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.04563976734948713</v>
+        <v>0.04568649053770928</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0.03260405296378899</v>
@@ -3053,16 +3053,16 @@
         <v>24.23489167616876</v>
       </c>
       <c r="AH20" s="4" t="n">
-        <v>0.02925342605849868</v>
+        <v>0.02928337428337428</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>-0.03592844684359042</v>
+        <v>-0.03656023747027416</v>
       </c>
       <c r="AJ20" s="4" t="n">
-        <v>0.1475051370718759</v>
+        <v>0.1474244245426157</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>1273994170.671572</v>
+        <v>1277048926.526657</v>
       </c>
       <c r="AL20" s="7" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -3095,13 +3095,13 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="3" t="n">
-        <v>299.0801</v>
+        <v>299.02</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1351567472508853</v>
+        <v>-0.1353305370800657</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2791166120323949</v>
+        <v>-0.2792614731970691</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>414.88</v>
@@ -3110,37 +3110,37 @@
         <v>289.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>298217852072</v>
+        <v>298157925340</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>20.88548184357542</v>
+        <v>20.88128491620111</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>19.93039557570422</v>
+        <v>19.92639057244891</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1.76276689407481</v>
+        <v>1.762412666926751</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>17.89045070710718</v>
+        <v>17.88685562977673</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-7.164205981226483</v>
+        <v>-7.162766337534134</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>14.99894844541083</v>
+        <v>14.99644262345808</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>2.120276233461011</v>
+        <v>2.119922006312952</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.0506374782565133</v>
+        <v>0.05064765587827255</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0.03240467921310985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.0479210893854749</v>
+        <v>0.04792108938547468</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>0.01423568777486173</v>
@@ -3179,16 +3179,16 @@
         <v>8.712271973466004</v>
       </c>
       <c r="AH21" s="4" t="n">
-        <v>0.03106191284542167</v>
+        <v>0.03106815597618888</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0.6973263151319282</v>
+        <v>0.6945437931976368</v>
       </c>
       <c r="AJ21" s="4" t="n">
-        <v>0.2382353227908371</v>
+        <v>0.2382387236666814</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>1262761881.639897</v>
+        <v>1267043216.321684</v>
       </c>
       <c r="AL21" s="7" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="3" t="n">
-        <v>606.64001</v>
+        <v>609.235</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.714637341416001</v>
+        <v>1.726249593556444</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.01517880160392227</v>
+        <v>-0.0109660871118038</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>615.99</v>
@@ -3236,31 +3236,31 @@
         <v>154.78</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>989187207886</v>
+        <v>993418591000</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>153.9695456852792</v>
+        <v>154.6281725888325</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>44.32768658139424</v>
+        <v>44.51730464401074</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>23.94836479569059</v>
+        <v>24.05080719041278</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>14.71840200389742</v>
+        <v>14.78136208794478</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1.243056882596749</v>
+        <v>1.248374237414427</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>92.21230893823474</v>
+        <v>92.61136322075014</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>23.92764864302143</v>
+        <v>24.03119697373199</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.008495245391007581</v>
+        <v>0.008458669966646517</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0.3433779329067288</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>2.564944611511842</v>
+        <v>2.56388606770836</v>
       </c>
       <c r="AJ22" s="4" t="n">
-        <v>0.6845070365174124</v>
+        <v>0.6876534221498499</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>9816473311.898008</v>
+        <v>9878642795.098608</v>
       </c>
       <c r="AL22" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -3347,13 +3347,13 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="3" t="n">
-        <v>1710.1299</v>
+        <v>1714.64</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4694614591669999</v>
+        <v>0.4733368478886342</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1449179483589672</v>
+        <v>-0.1426628532570651</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1999.96</v>
@@ -3362,13 +3362,13 @@
         <v>935.41</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>659114830407</v>
+        <v>660853104088</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>53.75181422351234</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>34.9922796659698</v>
+        <v>35.08456428161303</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>16.16186290756493</v>
@@ -3392,10 +3392,10 @@
         <v>0.1558368037250246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5361049561965605</v>
+        <v>0.5320644655029207</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2850763763526722</v>
+        <v>0.2816961781977867</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>0.2118578586392856</v>
@@ -3429,16 +3429,16 @@
       </c>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="4" t="n">
-        <v>0.004549362010453125</v>
+        <v>0.004537395604908319</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>1.658503110145121</v>
+        <v>1.654807192014109</v>
       </c>
       <c r="AJ23" s="4" t="n">
-        <v>0.4382365466804631</v>
+        <v>0.4390115061248543</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>2126492654.149658</v>
+        <v>2132813076.387695</v>
       </c>
       <c r="AL23" s="7" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3475,13 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="3" t="n">
-        <v>200.71</v>
+        <v>201.24</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1188040732531728</v>
+        <v>-0.116477164573108</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2108905052093571</v>
+        <v>-0.2088067623353645</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>254.35</v>
@@ -3490,31 +3490,31 @@
         <v>176.77</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>158635162700</v>
+        <v>159054058800</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>75.17228464419473</v>
+        <v>75.37078651685391</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>76.88619795501751</v>
+        <v>77.08922563134733</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1.687697884993883</v>
+        <v>1.692154463535294</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>26.02796671982951</v>
+        <v>26.09669683971148</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.4023276062355203</v>
+        <v>0.4033900028839426</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>28.38649823021583</v>
+        <v>28.44677105035971</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>2.098900608543008</v>
+        <v>2.103357187084419</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.001323792256557505</v>
+        <v>-0.001320305822965896</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0.3449644451794278</v>
@@ -3562,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>1.223270381950688</v>
+        <v>1.222635278977037</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>0.3425999429553007</v>
+        <v>0.3431722710142726</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>1131035388.394091</v>
+        <v>1135398496.273049</v>
       </c>
       <c r="AL24" s="7" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -3601,13 +3601,13 @@
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>953.635</v>
+        <v>958.6900000000001</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.04297632389524897</v>
+        <v>0.0485049017235486</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1736193554536868</v>
+        <v>-0.1692389015502733</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1153.99</v>
@@ -3616,40 +3616,40 @@
         <v>740.01</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>281329000445</v>
+        <v>282820260830</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14.52780316879951</v>
+        <v>14.60527117611213</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>13.17505273292933</v>
+        <v>13.24489065998209</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2.385342600159407</v>
+        <v>2.398062192780891</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2.331531672125271</v>
+        <v>2.343964323540434</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.3405115760552547</v>
+        <v>0.3423273188043394</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>26.62785175787596</v>
+        <v>26.6755426611028</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>7.087921095457744</v>
+        <v>7.100615674131103</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1475720810092009</v>
+        <v>-0.1467908731910325</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>-0.01384279441558334</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1026751439475575</v>
+        <v>0.1027098336296779</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3821630148620359</v>
+        <v>-0.3821435779782589</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>0.009857071754575692</v>
@@ -3685,16 +3685,16 @@
         <v>0.327057203580088</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>0.01887514615130527</v>
+        <v>0.01877562089935224</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>1.568739059563203</v>
+        <v>1.569721885410625</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.3100899717742037</v>
+        <v>0.312015573613821</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>1969286600.109009</v>
+        <v>1975606308.956641</v>
       </c>
       <c r="AL25" s="7" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>228.765</v>
+        <v>230.42</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2152144082332762</v>
+        <v>-0.2095368782161235</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3119021837213499</v>
+        <v>-0.3069241412500752</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>332.46</v>
@@ -3742,31 +3742,31 @@
         <v>199.19</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>215527284510</v>
+        <v>217086514555</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>19.97947598253275</v>
+        <v>20.12401746724891</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>17.71390952978631</v>
+        <v>17.84206077788719</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3.119198872744113</v>
+        <v>3.141764686672359</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>6.24103748693835</v>
+        <v>6.286188261929642</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.2435482634304865</v>
+        <v>0.2453102129244102</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>16.86870627643179</v>
+        <v>16.96483043924542</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>3.960045798080959</v>
+        <v>3.982611612009205</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.0632448927800023</v>
+        <v>0.06279063454467373</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.07621946361130139</v>
@@ -3811,16 +3811,16 @@
         <v>6.337467700258398</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>0.02946254890389701</v>
+        <v>0.02925093307872581</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.8823698743961197</v>
+        <v>0.8856075782955786</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.3343853572537092</v>
+        <v>0.334063737299512</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>1256225166.119612</v>
+        <v>1265350963.607128</v>
       </c>
       <c r="AL26" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3853,13 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>1167.33</v>
+        <v>1167.15002</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.08050095878008312</v>
+        <v>0.08033436616054868</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.09694812981085377</v>
+        <v>-0.09708736316868449</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1292.65</v>
@@ -3868,37 +3868,37 @@
         <v>712.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1099322521530</v>
+        <v>1099153031142</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>39.0541987286718</v>
+        <v>39.04817731682837</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>26.60614431054024</v>
+        <v>26.60204215103692</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>13.79917758347999</v>
+        <v>13.7970500659254</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>30.74840733197556</v>
+        <v>30.74366651459606</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.4128509927545759</v>
+        <v>0.4127873390134094</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>26.44835033368125</v>
+        <v>26.44443643988657</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>14.3768156665721</v>
+        <v>14.37468814901752</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01824205327121804</v>
+        <v>0.01824486621227288</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.4470394955930999</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.4678638991370185</v>
+        <v>0.4678638991370183</v>
       </c>
       <c r="V27" s="4" t="n">
         <v>0.2321044287935796</v>
@@ -3937,16 +3937,16 @@
         <v>37.33936879165095</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>0.005731027215954358</v>
+        <v>0.005731910967195117</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>0.3548820357182461</v>
+        <v>0.3547737125820647</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.3129111703445646</v>
+        <v>0.3128740793912009</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2811762385.221431</v>
+        <v>2817936279.322974</v>
       </c>
       <c r="AL27" s="7" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="3" t="n">
-        <v>205.62</v>
+        <v>206.32</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1304013573360217</v>
+        <v>0.1342496257444217</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1146609257265877</v>
+        <v>-0.1116469321851453</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>232.25</v>
@@ -3994,31 +3994,31 @@
         <v>151.84</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>324320313600</v>
+        <v>325424409600</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>16.52893890675241</v>
+        <v>16.58520900321543</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>15.26334534500181</v>
+        <v>15.3153069330842</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.563209332247943</v>
+        <v>2.571935363434469</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.925537009699593</v>
+        <v>2.935496526802938</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.4205225767444417</v>
+        <v>0.4219541777741134</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>23.46959871877875</v>
+        <v>23.50722082666031</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>5.443513452252053</v>
+        <v>5.452239483438579</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.04835959803413313</v>
+        <v>-0.04819552417496343</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0.1147704687575744</v>
@@ -4027,7 +4027,7 @@
         <v>0.08291718054882602</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3267741682980033</v>
+        <v>-0.3267741682980034</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>0.01207481297651363</v>
@@ -4063,16 +4063,16 @@
         <v>0.4478854275047432</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>0.02018286158933956</v>
+        <v>0.0201143854207057</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>1.370230159780131</v>
+        <v>1.370489597433928</v>
       </c>
       <c r="AJ28" s="4" t="n">
-        <v>0.2533154516306673</v>
+        <v>0.2548606604520665</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>904113498.0990347</v>
+        <v>907501703.6040944</v>
       </c>
       <c r="AL28" s="7" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -4105,13 +4105,13 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>1040.34</v>
+        <v>1046.79504</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.298268834289906</v>
+        <v>2.318733737356302</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1710438247011953</v>
+        <v>-0.1659003665338645</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1255</v>
@@ -4120,40 +4120,40 @@
         <v>154.65</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>1174949592600</v>
+        <v>1182239854681</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>23.21669270252175</v>
+        <v>23.36197277393439</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>6.63106438928352</v>
+        <v>6.672208424767498</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>13.01537089970534</v>
+        <v>13.09681548950971</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>11.65068424605854</v>
+        <v>11.72358921408999</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.03309059464739843</v>
+        <v>0.03329766134785651</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>16.91877494805841</v>
+        <v>17.02635006437831</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>12.80912103817267</v>
+        <v>12.89056562797705</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02227499814871632</v>
+        <v>0.02213647759854376</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0.4885110111106685</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.501201517518411</v>
+        <v>2.501385341503096</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.784318972372997</v>
+        <v>1.784465147297665</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>0.3763197924123121</v>
@@ -4189,16 +4189,16 @@
         <v>21.25786163522013</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>0.000509448834035027</v>
+        <v>0.0005063073283190185</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>2.849763739789576</v>
+        <v>2.843605602223764</v>
       </c>
       <c r="AJ29" s="4" t="n">
-        <v>0.7784115439297378</v>
+        <v>0.779608037659956</v>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>25346216338.7304</v>
+        <v>25429986536.17271</v>
       </c>
       <c r="AL29" s="7" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="3" t="n">
-        <v>137.405</v>
+        <v>137.21</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0681247687768225</v>
+        <v>-0.0694472510015488</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2943674701888808</v>
+        <v>-0.2953688772942493</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>194.726</v>
@@ -4246,31 +4246,31 @@
         <v>81.23999999999999</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>142057806848</v>
+        <v>141856205020</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>85.34472049689442</v>
+        <v>85.22360248447207</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>28.89566710342278</v>
+        <v>28.85465946115964</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>9.642805243551452</v>
+        <v>9.629120623133316</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>11.34063318951742</v>
+        <v>11.32453899009268</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>136.551552795034</v>
+        <v>136.3577639751582</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>42.42126880137575</v>
+        <v>42.36348667813127</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>10.04668794786859</v>
+        <v>10.03300332745045</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.03224039636836391</v>
+        <v>0.03228621546272351</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0.2088492352512745</v>
@@ -4279,7 +4279,7 @@
         <v>1.953547332595934</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2494717167744058</v>
+        <v>0.2494717167744063</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0.0527379523779448</v>
@@ -4318,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0.703082710186232</v>
+        <v>0.7010512475555388</v>
       </c>
       <c r="AJ30" s="4" t="n">
-        <v>0.6016878335038168</v>
+        <v>0.6016148982532028</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>2132357723.640202</v>
+        <v>2136565421.382077</v>
       </c>
       <c r="AL30" s="7" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -4357,13 +4357,13 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="3" t="n">
-        <v>27.7137</v>
+        <v>27.8977</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1006234973834934</v>
+        <v>0.1079308841098621</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05122560766860673</v>
+        <v>-0.04492639507018148</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>29.21</v>
@@ -4372,40 +4372,40 @@
         <v>23.58</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>157952566571</v>
+        <v>159001263618</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>36.61958245243129</v>
+        <v>36.86271141649049</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9.49648477055605</v>
+        <v>9.559534929783519</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.479787844935318</v>
+        <v>2.496251940749811</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1.853977888249795</v>
+        <v>1.866287032515553</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.6124868215495144</v>
+        <v>-0.616553314842186</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>17.44063423407795</v>
+        <v>17.52370592664765</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>3.456583876083271</v>
+        <v>3.473047971897764</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.06955252604307491</v>
+        <v>0.06909379051473344</v>
       </c>
       <c r="T31" s="4" t="n">
         <v>-0.01647099501783833</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.856119747169046</v>
+        <v>2.856119747169047</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05096012505918535</v>
+        <v>-0.05096012505918546</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>0.02155311712267129</v>
@@ -4441,16 +4441,16 @@
         <v>3.815424934481467</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>0.06206316731436077</v>
+        <v>0.06165382809335537</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0.3470077692005</v>
+        <v>0.3518378758600464</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>0.2042335836475987</v>
+        <v>0.2046934116178563</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>949503793.4137268</v>
+        <v>952843405.2452723</v>
       </c>
       <c r="AL31" s="7" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -4483,13 +4483,13 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="3" t="n">
-        <v>187.42</v>
+        <v>188.36</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1155288740419207</v>
+        <v>0.1211237792900237</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.06229048881773158</v>
+        <v>-0.05758743183068993</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>199.87</v>
@@ -4498,13 +4498,13 @@
         <v>124.8</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1330410023714</v>
+        <v>1337082672688</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>8.16182290731822</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.004325440585223388</v>
+        <v>0.004347134716853471</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>7.009592564828316</v>
@@ -4528,10 +4528,10 @@
         <v>0.4676285061130367</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1885.934462861591</v>
+        <v>1876.517822411974</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2499.96749011031</v>
+        <v>2487.486528014419</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>0.4645609082788198</v>
@@ -4567,14 +4567,14 @@
         <v>55.63395918385022</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>1.600682958062107</v>
+        <v>1.592694839668719</v>
       </c>
       <c r="AI32" s="6" t="inlineStr"/>
       <c r="AJ32" s="4" t="n">
-        <v>0.8588674710572904</v>
+        <v>0.8588310163431628</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>3456528975.402265</v>
+        <v>3468965670.801849</v>
       </c>
       <c r="AL32" s="7" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -4611,13 +4611,13 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="3" t="n">
-        <v>592.87</v>
+        <v>595.885</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5881864971525375</v>
+        <v>0.5962631114000367</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1175297322239257</v>
+        <v>-0.1130419897890836</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>671.83</v>
@@ -4626,7 +4626,7 @@
         <v>313.6</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>74725778267</v>
+        <v>75105791122</v>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
@@ -4652,13 +4652,13 @@
       <c r="AG33" s="6" t="inlineStr"/>
       <c r="AH33" s="4" t="inlineStr"/>
       <c r="AI33" s="6" t="n">
-        <v>1.814977300506886</v>
+        <v>1.813712121380484</v>
       </c>
       <c r="AJ33" s="4" t="n">
-        <v>0.4040323760577721</v>
+        <v>0.4068257721631223</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>3780078705.484049</v>
+        <v>3801623160.893311</v>
       </c>
       <c r="AL33" s="7" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -4691,13 +4691,13 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="3" t="n">
-        <v>154.25</v>
+        <v>152.9101</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.04162781655967818</v>
+        <v>-0.0499527623528172</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3163889381315369</v>
+        <v>-0.322327158305265</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>225.64</v>
@@ -4706,31 +4706,31 @@
         <v>104.83</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2033289556516</v>
+        <v>2015627226491</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>-100.1623376623377</v>
+        <v>-99.29227272727273</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>135.6101115205819</v>
+        <v>134.4321278030687</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>122.672069774721</v>
+        <v>121.6064691698944</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>7.109680563415708</v>
+        <v>7.047921983273596</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-1.001623376623377</v>
+        <v>-0.9929227272727273</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>474.9535772776578</v>
+        <v>470.7149571612671</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>119.4046187943288</v>
+        <v>118.3390181895023</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.01397882554843897</v>
+        <v>-0.01410131775679649</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0.3324295397788084</v>
@@ -4776,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>3.218096694234215</v>
+        <v>3.139577505383215</v>
       </c>
       <c r="AJ34" s="4" t="n">
-        <v>0.7523639494381489</v>
+        <v>0.7524392309670248</v>
       </c>
       <c r="AK34" s="5" t="n">
-        <v>13939309755.23863</v>
+        <v>13999848630.61996</v>
       </c>
       <c r="AL34" s="7" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -4819,13 +4819,13 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="3" t="n">
-        <v>772.62</v>
+        <v>774.5415</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1309337636715331</v>
+        <v>0.133746387247023</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.008660841448862588</v>
+        <v>-0.006195388583086325</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>779.37</v>
@@ -4834,7 +4834,7 @@
         <v>629.28</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>823024352971</v>
+        <v>825071213423</v>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="AG35" s="6" t="inlineStr"/>
       <c r="AH35" s="4" t="inlineStr"/>
       <c r="AI35" s="6" t="n">
-        <v>0.995118982523625</v>
+        <v>0.9956680796999005</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>0.1192715547493287</v>
+        <v>0.1211436481531878</v>
       </c>
       <c r="AK35" s="5" t="n">
-        <v>30155278187.22266</v>
+        <v>30321001849.08377</v>
       </c>
       <c r="AL35" s="7" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4899,13 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="3" t="n">
-        <v>442.2113</v>
+        <v>443.6676</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.3835966342340003</v>
+        <v>0.3881531251659032</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.07680313152400842</v>
+        <v>-0.0737628392484343</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>479</v>
@@ -4914,13 +4914,13 @@
         <v>265.45</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2293520082471</v>
+        <v>2301073147217</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>28.74695722730961</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.6777653749865373</v>
+        <v>0.6799974068581627</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>14.48315907336394</v>
@@ -4944,10 +4944,10 @@
         <v>0.3296825869948878</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>41.41431959825422</v>
+        <v>41.27509831269959</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>41.40052630287702</v>
+        <v>41.26135040539743</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>0.2386060493906826</v>
@@ -4981,16 +4981,16 @@
       </c>
       <c r="AG36" s="6" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
-        <v>0.2713634861886162</v>
+        <v>0.2704727593360435</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>2.16778013413212</v>
+        <v>2.165239174429794</v>
       </c>
       <c r="AJ36" s="4" t="n">
-        <v>0.3401245430090488</v>
+        <v>0.34117521774022</v>
       </c>
       <c r="AK36" s="5" t="n">
-        <v>4080379986.731384</v>
+        <v>4093967179.137105</v>
       </c>
       <c r="AL36" s="7" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -5027,53 +5027,53 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="3" t="n">
-        <v>30.9</v>
+        <v>30.79</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.08383022630413706</v>
+        <v>0.07997193100014166</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-0.0005724876041879323</v>
+        <v>-0.004204398447606783</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>30.9177</v>
+        <v>30.92</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>17.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>77470524092</v>
+        <v>77194739055</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>-24.3267716535433</v>
+        <v>-24.24409448818897</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>-98.07278392725289</v>
+        <v>-97.72365751197788</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>2.144759474124325</v>
+        <v>2.137470277031704</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>2.36242600036543</v>
+        <v>2.354397040014617</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.1810364402124154</v>
+        <v>0.1804211682841971</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>17.53917163768595</v>
+        <v>17.49565934793388</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>2.938169414592275</v>
+        <v>2.930880217499654</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0.02814428885652349</v>
+        <v>0.02824026645710643</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>-0.05149919890135046</v>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
       <c r="V37" s="4" t="n">
-        <v>0.02085721239547977</v>
+        <v>0.02102242638678953</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>-0.03256622244159263</v>
@@ -5112,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0.2833535847437162</v>
+        <v>0.288245070500637</v>
       </c>
       <c r="AJ37" s="4" t="n">
-        <v>0.3020347553594716</v>
+        <v>0.2947083321418568</v>
       </c>
       <c r="AK37" s="5" t="n">
-        <v>690960971.7207906</v>
+        <v>730234988.8003621</v>
       </c>
       <c r="AL37" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -5155,13 +5155,13 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="3" t="n">
-        <v>313.46</v>
+        <v>313.69</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1590159344279423</v>
+        <v>-0.1583988657905353</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1910500916152675</v>
+        <v>-0.1904565279103977</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>387.49</v>
@@ -5170,31 +5170,31 @@
         <v>290.97</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>211682672600</v>
+        <v>211837993900</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>19.00909642207398</v>
+        <v>19.0230442692541</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>16.09751262125699</v>
+        <v>16.10932410566613</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2.517843690602215</v>
+        <v>2.519691148168853</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>6.199704784130688</v>
+        <v>6.204253792298717</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.178729996477953</v>
+        <v>1.179594884818379</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>9.12023429056787</v>
+        <v>9.126516498139461</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>2.68205812329761</v>
+        <v>2.683905580864249</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.07110643405585952</v>
+        <v>0.07105429825352967</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0.08440587054082838</v>
@@ -5239,16 +5239,16 @@
         <v>1.675370415350984</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>0.01129330696101576</v>
+        <v>0.01128502661863623</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0.953805729113185</v>
+        <v>0.9518911245654249</v>
       </c>
       <c r="AJ38" s="4" t="n">
-        <v>0.2355795532036712</v>
+        <v>0.2357296706848069</v>
       </c>
       <c r="AK38" s="5" t="n">
-        <v>825938388.2113851</v>
+        <v>828723533.3733947</v>
       </c>
       <c r="AL38" s="7" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -5281,13 +5281,13 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="3" t="n">
-        <v>148.49</v>
+        <v>148.75</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.2412753824228517</v>
+        <v>-0.2399468862239827</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-0.5493474962063732</v>
+        <v>-0.5485584218512898</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>329.5</v>
@@ -5296,31 +5296,31 @@
         <v>114.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>427720990300</v>
+        <v>428469912500</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>22.91512345679012</v>
+        <v>22.95524691358025</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>16.44530522845881</v>
+        <v>16.47410029451982</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>5.95902573665659</v>
+        <v>5.969459750337852</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>6.595898580243216</v>
+        <v>6.60744773258252</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.4987409222948441</v>
+        <v>0.4996141975308644</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>14.50909306203605</v>
+        <v>14.52894783934252</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>7.624768244702342</v>
+        <v>7.635202258383605</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>-0.0671465760421438</v>
+        <v>-0.06702921059830542</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0.1735047648913743</v>
@@ -5365,16 +5365,16 @@
         <v>5.261852979556329</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>0.01346892046602465</v>
+        <v>0.01344537815126051</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>2.069945695208964</v>
+        <v>2.065565792341079</v>
       </c>
       <c r="AJ39" s="4" t="n">
-        <v>0.5573848342617406</v>
+        <v>0.5574455493119089</v>
       </c>
       <c r="AK39" s="5" t="n">
-        <v>4215373940.411263</v>
+        <v>4227818743.567207</v>
       </c>
       <c r="AL39" s="7" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -5407,13 +5407,13 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>109.8502</v>
+        <v>111.0326</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.4446370157469137</v>
+        <v>0.4601867262382842</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1573966403313646</v>
+        <v>-0.1483270691109918</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>130.37</v>
@@ -5422,31 +5422,31 @@
         <v>66.81</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>432967386237</v>
+        <v>437627738585</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>32.69351190476191</v>
+        <v>33.04541666666667</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>21.14767862253797</v>
+        <v>21.37530693093694</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>6.837226786213976</v>
+        <v>6.910820980418476</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>8.635534266679924</v>
+        <v>8.728484991548177</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.046192380952381</v>
+        <v>1.057453333333333</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>22.74251392362256</v>
+        <v>22.97531038438483</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>7.189615258381367</v>
+        <v>7.263209452585867</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.03139959366952941</v>
+        <v>0.03106521548190085</v>
       </c>
       <c r="T40" s="4" t="n">
         <v>0.1177498499664631</v>
@@ -5491,16 +5491,16 @@
         <v>11.89047619047619</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>0.01511148819028094</v>
+        <v>0.01495056406857085</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>0.6981848286848316</v>
+        <v>0.7035408725770994</v>
       </c>
       <c r="AJ40" s="4" t="n">
-        <v>0.3339784224757248</v>
+        <v>0.3359622655888229</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>2055917983.750985</v>
+        <v>2063583854.185614</v>
       </c>
       <c r="AL40" s="7" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>
@@ -5533,13 +5533,13 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="3" t="n">
-        <v>86.81999999999999</v>
+        <v>86.58</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.08802518084951394</v>
+        <v>-0.09054618933368941</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-0.1119067103109658</v>
+        <v>-0.1143617021276596</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>97.76000000000001</v>
@@ -5548,37 +5548,37 @@
         <v>72.78</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>262543680000</v>
+        <v>261817920000</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>12.38516405135521</v>
+        <v>12.3509272467903</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>11.15065860608368</v>
+        <v>11.11983439431842</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.03356709654932</v>
+        <v>2.027945625653538</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.469326955435929</v>
+        <v>1.465265236139631</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.6583105216486115</v>
+        <v>0.6564907275320985</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>15.64419063716761</v>
+        <v>15.62228486915577</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>4.014621277254947</v>
+        <v>4.008999806359165</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.07301642149603449</v>
+        <v>0.07321882321882323</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>-0.01489668811853551</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.1107114376722098</v>
+        <v>0.11071143767221</v>
       </c>
       <c r="V41" s="4" t="n">
         <v>-0.2899692959204386</v>
@@ -5617,16 +5617,16 @@
         <v>0.6326638212402712</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>0.02130845427320894</v>
+        <v>0.02136752136752137</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0.7244587304160582</v>
+        <v>0.7203459105261545</v>
       </c>
       <c r="AJ41" s="4" t="n">
-        <v>0.2221829194790843</v>
+        <v>0.2216743119884411</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1121901762.751183</v>
+        <v>1124974971.312578</v>
       </c>
       <c r="AL41" s="7" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:30 ET</t>
+          <t>2026-09-21 14:53 ET</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -442,7 +442,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -454,7 +454,7 @@
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
     <col width="24" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
@@ -699,13 +699,13 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>338.721</v>
+        <v>338.98</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.2498468240820066</v>
+        <v>0.2508025083396619</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.01697478016078002</v>
+        <v>-0.01622311866964621</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>344.57</v>
@@ -714,31 +714,31 @@
         <v>243.42</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4974915911676</v>
+        <v>4978719936880</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>38.66678082191781</v>
+        <v>38.69634703196348</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>35.30272070443684</v>
+        <v>35.32971461583428</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>10.65696401350405</v>
+        <v>10.66511276625188</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>46.28593167145648</v>
+        <v>46.32132379743305</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>1.181484969558598</v>
+        <v>1.182388381532216</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>29.79285466849471</v>
+        <v>29.81543236162055</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>10.75285260511157</v>
+        <v>10.7610013578594</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.0274744342269602</v>
+        <v>0.02745344219656082</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.06425511782832749</v>
@@ -747,7 +747,7 @@
         <v>0.09529180896978762</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.1204046456526846</v>
+        <v>0.1204046456526848</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.3363982195133406</v>
@@ -781,16 +781,16 @@
       </c>
       <c r="AG2" s="6" t="inlineStr"/>
       <c r="AH2" s="4" t="n">
-        <v>0.003129419197510636</v>
+        <v>0.003127028143253289</v>
       </c>
       <c r="AI2" s="6" t="n">
-        <v>0.3100570591227713</v>
+        <v>0.3105715180243301</v>
       </c>
       <c r="AJ2" s="4" t="n">
-        <v>0.2918136906615251</v>
+        <v>0.2919331128025581</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>13462680898.54019</v>
+        <v>13631088621.46381</v>
       </c>
       <c r="AL2" s="7" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -827,13 +827,13 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>498.545</v>
+        <v>501.61</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.05414005460822913</v>
+        <v>0.06062079208904669</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.09964422451780686</v>
+        <v>-0.09410893592429392</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>553.72</v>
@@ -842,31 +842,31 @@
         <v>349.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3701970824750</v>
+        <v>3724730135500</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>27.69694444444444</v>
+        <v>27.86722222222222</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>24.21555851679905</v>
+        <v>24.3644331155895</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>11.15592448371047</v>
+        <v>11.22450988431137</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>8.372060673121045</v>
+        <v>8.423531184234617</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0.8797474929105423</v>
+        <v>0.8851560840422773</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>18.35919242334437</v>
+        <v>18.46868689373022</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>11.48111358972273</v>
+        <v>11.54958710549393</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01809477474373416</v>
+        <v>0.01798439016066</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>0.1778868679984666</v>
@@ -911,16 +911,16 @@
         <v>55.38675843985578</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>0.007301246627686568</v>
+        <v>0.00725663363968023</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0.5553302034500899</v>
+        <v>0.5595574674859327</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.4297687079231736</v>
+        <v>0.4303611555697466</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>10759864313.60875</v>
+        <v>10978589959.94085</v>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -953,13 +953,13 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>355.335</v>
+        <v>354.97</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.127510731022622</v>
+        <v>0.1263525523551021</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.1303810479430264</v>
+        <v>-0.1312743202564792</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>408.61</v>
@@ -968,40 +968,40 @@
         <v>235.84</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4300303713811</v>
+        <v>4295886443191</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>17.45978152929493</v>
+        <v>17.42154915590864</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>21.3514735862005</v>
+        <v>21.32954135926265</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>9.571191205925096</v>
+        <v>9.550232790419093</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>6.671211653759681</v>
+        <v>6.656603438046465</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1552708526244991</v>
+        <v>0.1549308499043283</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>13.33578114814164</v>
+        <v>13.30696313291947</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>9.698684668086374</v>
+        <v>9.677726252580371</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.01248351265537523</v>
+        <v>0.01251090828550775</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.1509008108154437</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1822680781817689</v>
+        <v>-0.1832197016114886</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2928522223410996</v>
+        <v>0.2913476846888949</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0.2648693088701202</v>
@@ -1037,16 +1037,16 @@
         <v>216.7961956521739</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>0.002420251312142063</v>
+        <v>0.002422739949854917</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>0.7592980624839859</v>
+        <v>0.7585210482680368</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.3623772568261484</v>
+        <v>0.3621372614873961</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>8128369753.914919</v>
+        <v>8253448509.16108</v>
       </c>
       <c r="AL4" s="7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1079,13 +1079,13 @@
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>258.625</v>
+        <v>258.45</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1418322295805738</v>
+        <v>0.1410596026490065</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.09949512534818938</v>
+        <v>-0.1001044568245125</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>287.2</v>
@@ -1094,31 +1094,31 @@
         <v>196</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2782054987500</v>
+        <v>2780172495000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>20.52579365079365</v>
+        <v>20.51190476190476</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>23.05676193177179</v>
+        <v>23.041160449556</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3.586601417465966</v>
+        <v>3.584174524288366</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>5.042910880678727</v>
+        <v>5.039498567854682</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2323478164531464</v>
+        <v>0.2321905970510031</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>11.52404944743442</v>
+        <v>11.51663797210203</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>3.773558667878507</v>
+        <v>3.771131774700908</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.004178565863087564</v>
+        <v>-0.004181395226701572</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0.1237775468329469</v>
@@ -1127,7 +1127,7 @@
         <v>-0.1097711937377691</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1812821064627379</v>
+        <v>0.1812821064627377</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>0.1234666041185044</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>0.8371125768166782</v>
+        <v>0.836520583502414</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>0.4639730853230861</v>
+        <v>0.4638156688227242</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>8469833184.420419</v>
+        <v>8606352112.473917</v>
       </c>
       <c r="AL5" s="7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>228.325</v>
+        <v>227.38</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2090282902868781</v>
+        <v>0.2040243190427258</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0347298554155745</v>
+        <v>-0.03872495138243004</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>236.54</v>
@@ -1220,40 +1220,40 @@
         <v>164.27</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5530259825000</v>
+        <v>5507370980000</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>28.72199999999999</v>
+        <v>28.60125786163521</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>16.929787409473</v>
+        <v>16.85971777582818</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>18.25474168578634</v>
+        <v>18.17800164373253</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>24.12195690965308</v>
+        <v>24.02055252768752</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2305575510204081</v>
+        <v>0.2295883284131262</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>23.73907241416631</v>
+        <v>23.63957246851288</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>18.30892874782899</v>
+        <v>18.23218870577518</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02296414883909394</v>
+        <v>0.02306109402493892</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>0.6547353579009478</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6965363654790317</v>
+        <v>0.6964256603773582</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.9517601176585231</v>
+        <v>0.9516327173898933</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>0.6022349752710197</v>
@@ -1289,16 +1289,16 @@
         <v>547.1389961389962</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>0.00227745538158327</v>
+        <v>0.002286920573489313</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1.316147750937678</v>
+        <v>1.312998078869084</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.4135223273920259</v>
+        <v>0.4120962992058929</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>26783144167.61311</v>
+        <v>27063682401.42276</v>
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>745.2835</v>
+        <v>741.245</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1458672695266103</v>
+        <v>0.1396581088944708</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05147633410968144</v>
+        <v>-0.05661614040446461</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>785.73</v>
@@ -1346,40 +1346,40 @@
         <v>520.26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1898599707093</v>
+        <v>1888311682580</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>27.69899219620959</v>
+        <v>27.54533630620587</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>22.52807908519511</v>
+        <v>22.40600520675078</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>8.319219625201535</v>
+        <v>8.273070005345064</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>7.256311838787846</v>
+        <v>7.216058567266797</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-5.678293400222961</v>
+        <v>-5.646793942772199</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>18.63887142308914</v>
+        <v>18.54049315021668</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>8.743565074011602</v>
+        <v>8.697415454155131</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.02157943107471994</v>
+        <v>0.02169980749365195</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.2216703849824622</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.2295319139931766</v>
+        <v>0.2293729315882977</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2756290503754621</v>
+        <v>0.2754641026512139</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>0.1513436869382784</v>
@@ -1415,16 +1415,16 @@
         <v>73.76137339055794</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>0.002817719699953105</v>
+        <v>0.002833071386653536</v>
       </c>
       <c r="AI7" s="6" t="n">
-        <v>0.8378172630163945</v>
+        <v>0.8337369446796072</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>0.4913606372031905</v>
+        <v>0.4838029410403111</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>11259648772.54138</v>
+        <v>11563975508.17238</v>
       </c>
       <c r="AL7" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1457,13 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>375.96</v>
+        <v>375.3</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1417810082538947</v>
+        <v>-0.1432876167615881</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2463163803299722</v>
+        <v>-0.2476394763747168</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>498.83</v>
@@ -1472,31 +1472,31 @@
         <v>297.38</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1484871838248</v>
+        <v>1482265136968</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>318.6101694915254</v>
+        <v>318.0508474576271</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>175.7762476147947</v>
+        <v>175.4676713741686</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>14.33011164215057</v>
+        <v>14.30495504654552</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>14.01117363973382</v>
+        <v>13.98657694167492</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-8.481312962520883</v>
+        <v>-8.466423967534014</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>122.9626569876954</v>
+        <v>122.745937559694</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>14.27339424476206</v>
+        <v>14.24823764915701</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.003880469580996689</v>
+        <v>0.003887293748125436</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-0.02930699150373628</v>
@@ -1505,7 +1505,7 @@
         <v>0.8125894358021826</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.1243484142571567</v>
+        <v>0.1243484142571569</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>0.02570628315962403</v>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1.535136630064105</v>
+        <v>1.533736783990318</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.5715255642673231</v>
+        <v>0.5709828204719943</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>13234436152.7239</v>
+        <v>13342347926.85518</v>
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1583,13 +1583,13 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>362.85001</v>
+        <v>362.66</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.04381225216253237</v>
+        <v>0.04326564954280698</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2669696767676768</v>
+        <v>-0.2673535353535353</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>495</v>
@@ -1598,31 +1598,31 @@
         <v>289.96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1726287932038</v>
+        <v>1725383962800</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>45.01861166253101</v>
+        <v>44.99503722084367</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19.74344165984269</v>
+        <v>19.73310281115481</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>19.3738545075193</v>
+        <v>19.36370940474053</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>17.34720782084462</v>
+        <v>17.33812378372956</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.4479574724836005</v>
+        <v>0.4477228951182957</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>33.7089706300442</v>
+        <v>33.69167408683007</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>19.77163687419196</v>
+        <v>19.76149177141318</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.0228252768664623</v>
+        <v>0.02283723556584805</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>0.2387443285376352</v>
@@ -1667,16 +1667,16 @@
         <v>8.080685358255451</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>0.007165495186289233</v>
+        <v>0.007169249434732256</v>
       </c>
       <c r="AI9" s="6" t="n">
-        <v>1.586814593676824</v>
+        <v>1.586133867910815</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>0.3890610351438917</v>
+        <v>0.3889214972981607</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>8985365344.157597</v>
+        <v>9109853972.231266</v>
       </c>
       <c r="AL9" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>898.38</v>
+        <v>898.48</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.05135166764189592</v>
+        <v>0.05146869514335872</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1806839945280437</v>
+        <v>-0.1805927952576379</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1096.5</v>
@@ -1724,40 +1724,40 @@
         <v>844.0599999999999</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>398412664020</v>
+        <v>398457011920</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>45.1225514816675</v>
+        <v>45.12707182320442</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>39.64965939107466</v>
+        <v>39.65407285301627</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1.357066555433313</v>
+        <v>1.357202505288041</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>11.9017572583485</v>
+        <v>11.902949566982</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>3.559444128040471</v>
+        <v>3.559800710339388</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>26.79357973807879</v>
+        <v>26.79633807325501</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1.320573113966218</v>
+        <v>1.320709063820946</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.02210246504555636</v>
+        <v>0.02210025105987599</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0.08167323631476142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.1380312510786617</v>
+        <v>0.1380185836263184</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1144449147986222</v>
+        <v>0.114432509886337</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0.1022561610551892</v>
@@ -1793,16 +1793,16 @@
         <v>71.24675324675324</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>0.006166655535519491</v>
+        <v>0.006165969192413854</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>-0.1754405861414696</v>
+        <v>-0.1753623077384928</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>0.1766073689180791</v>
+        <v>0.1766123257139956</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>1775516737.825877</v>
+        <v>1804523230.726188</v>
       </c>
       <c r="AL10" s="7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>73.545</v>
+        <v>73.36</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1917243463384649</v>
+        <v>-0.1937575368466896</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4109802979336857</v>
+        <v>-0.4124619573922793</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>124.86</v>
@@ -1850,31 +1850,31 @@
         <v>65.08</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>306236967226</v>
+        <v>305466638327</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>22.76934984520124</v>
+        <v>22.71207430340558</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>19.60187691051563</v>
+        <v>19.55256904147701</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6.331034325320974</v>
+        <v>6.315108819182596</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>10.21828594402132</v>
+        <v>10.19258218578291</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6691967454504268</v>
+        <v>0.6675134033074079</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>10.17942866999087</v>
+        <v>10.15381659907733</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>6.439021013478307</v>
+        <v>6.422820039125287</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.03590072660554237</v>
+        <v>0.03599282743351614</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.1585106891967754</v>
@@ -1883,7 +1883,7 @@
         <v>0.1615902879681075</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1453958417687613</v>
+        <v>0.1453958417687611</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>0.2335250473131588</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0.1076767456070794</v>
+        <v>0.1060156206289896</v>
       </c>
       <c r="AJ11" s="4" t="n">
-        <v>0.357385417634816</v>
+        <v>0.356490446342517</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>2357777559.722336</v>
+        <v>2388117769.965398</v>
       </c>
       <c r="AL11" s="7" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -1961,13 +1961,13 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="3" t="n">
-        <v>505.06</v>
+        <v>502.01</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.01652408935419003</v>
+        <v>0.01038541578564312</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.06077286420946926</v>
+        <v>-0.06644475025105068</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>537.74</v>
@@ -1976,40 +1976,40 @@
         <v>464.01</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1089340476691</v>
+        <v>1082762073226</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.70498055357849</v>
+        <v>12.60857627251609</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>22.76774952871788</v>
+        <v>22.63025767416082</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2.833615416510046</v>
+        <v>2.81211419060171</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1.450843042561955</v>
+        <v>1.439834172468631</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3499898597004718</v>
+        <v>0.3473341672607027</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>15.40654015906893</v>
+        <v>15.29843913061662</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>3.064351053534432</v>
+        <v>3.042849827626096</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.02221447513655095</v>
+        <v>0.02238432543990719</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>2.961503151310829e-05</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4419746871532831</v>
+        <v>-0.4428443346046148</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.06161972279484895</v>
+        <v>0.05996525504052541</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>0.06790433791924602</v>
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0.03096258283992644</v>
+        <v>0.02658849397143491</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>0.1510562423419694</v>
+        <v>0.1542243684565831</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>2261272038.932377</v>
+        <v>2299833880.106328</v>
       </c>
       <c r="AL12" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2087,13 +2087,13 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>352.24</v>
+        <v>352.04</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.08221699677525196</v>
+        <v>0.0816025197159882</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.03890859481582531</v>
+        <v>-0.03945429740791262</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>366.5</v>
@@ -2102,31 +2102,31 @@
         <v>279.1</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>943830602400</v>
+        <v>943294700400</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>15.14359415305245</v>
+        <v>15.13499570077386</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>14.06234947833009</v>
+        <v>14.05436495103147</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>3.171122161857052</v>
+        <v>3.169321615546663</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>2.622255559292896</v>
+        <v>2.620766656522459</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7929072220083502</v>
+        <v>0.7924570135016454</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>20.09328684413912</v>
+        <v>20.08753435379991</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>6.289257583668477</v>
+        <v>6.287457037358088</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1722067493750508</v>
+        <v>-0.1723045830015563</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.03307372160612143</v>
@@ -2171,16 +2171,16 @@
         <v>0.7415371100533208</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>0.01703384056325233</v>
+        <v>0.01704351778207022</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0.7618293761887743</v>
+        <v>0.7625563978645357</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>0.1641860223756799</v>
+        <v>0.1640717347099889</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>2254397061.946411</v>
+        <v>2292921037.383805</v>
       </c>
       <c r="AL13" s="7" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2213,13 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>368.93</v>
+        <v>369.95</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06479447097038382</v>
+        <v>0.0677383637424267</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.04315688461239198</v>
+        <v>-0.04051145057966132</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>385.57</v>
@@ -2228,31 +2228,31 @@
         <v>293.89</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>688809727554</v>
+        <v>690714115709</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>31.34494477485132</v>
+        <v>31.43160577740017</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>24.61056954589825</v>
+        <v>24.67861167024925</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15.48304548538932</v>
+        <v>15.52585226822963</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>20.06735679771448</v>
+        <v>20.1228380649838</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>2.113721604883067</v>
+        <v>2.119565521173368</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>24.06724611842738</v>
+        <v>24.13269350845419</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>15.74151968067794</v>
+        <v>15.78432646351825</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03050624745765174</v>
+        <v>0.03042213778768761</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0.1133997661860491</v>
@@ -2297,16 +2297,16 @@
         <v>42.07640067911715</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>0.007264250670858971</v>
+        <v>0.007244222192188134</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0.3084719681080962</v>
+        <v>0.3114815638989182</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>0.1731220608576809</v>
+        <v>0.1733265299386152</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>2400638727.220361</v>
+        <v>2453149791.321373</v>
       </c>
       <c r="AL14" s="7" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2339,13 +2339,13 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>566.6900000000001</v>
+        <v>567.65</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.006321799737750489</v>
+        <v>0.008026557061416195</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05744889642898721</v>
+        <v>-0.05585216971874329</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>601.23</v>
@@ -2354,31 +2354,31 @@
         <v>464.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>497007532981</v>
+        <v>497849485400</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31.11971444261395</v>
+        <v>31.17243272926963</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.50322471237511</v>
+        <v>25.54642839644202</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>14.166620100362</v>
+        <v>14.19061897215175</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>89.07869898413831</v>
+        <v>89.22960256638746</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1.375380236526241</v>
+        <v>1.377710196516827</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>23.0764845804395</v>
+        <v>23.11455441309459</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>14.54720328880084</v>
+        <v>14.5712021605906</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03309406580086742</v>
+        <v>0.03303809782345112</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>0.164163737707246</v>
@@ -2423,16 +2423,16 @@
         <v>26.73130193905817</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0.005946813954719511</v>
+        <v>0.00593675680436889</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>0.2967674941275374</v>
+        <v>0.2985024035678206</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>0.1864675334534982</v>
+        <v>0.1865666401680327</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>1518424954.993953</v>
+        <v>1543984005.893982</v>
       </c>
       <c r="AL15" s="7" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>377.70001</v>
+        <v>377.56</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1227705613937209</v>
+        <v>0.1223543604349209</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1817945279667258</v>
+        <v>-0.1820978293834756</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>461.62</v>
@@ -2480,37 +2480,37 @@
         <v>255.97</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>343006152477</v>
+        <v>342879001174</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.28782779242493</v>
+        <v>24.27882451289307</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>17.34761723275498</v>
+        <v>17.34118662691846</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.7620174493911744</v>
+        <v>0.7617349719169393</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>3.475931983300355</v>
+        <v>3.47464348654606</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-0.7359275235798728</v>
+        <v>-0.7356547218593317</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>15.05062114183131</v>
+        <v>15.04568571882157</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.8614178435004187</v>
+        <v>0.8611353660261836</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06885299237186021</v>
+        <v>0.06887852542481929</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0.118140392427263</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.4000670793315499</v>
+        <v>0.4000670793315502</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>0.01079669339117584</v>
@@ -2549,16 +2549,16 @@
         <v>4.672413793103448</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>0.02398729086610297</v>
+        <v>0.02399618603665643</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>0.4291603666741114</v>
+        <v>0.429638174493114</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>0.2073923706713177</v>
+        <v>0.2073363274630195</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>1792704122.263428</v>
+        <v>1826761950.108105</v>
       </c>
       <c r="AL16" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:53 ET</t>
+          <t>2026-09-21 18:46 ET</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>159.37</v>
+        <v>158.4</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2993884877072199</v>
+        <v>0.2914798045606051</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.09659316365285409</v>
+        <v>-0.102091718156567</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>176.41</v>
@@ -2606,31 +2606,31 @@
         <v>110.39</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>660502590200</v>
+        <v>656482464000</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>20.51093951093951</v>
+        <v>20.38610038610039</v>
       </c